--- a/SPC_Statistical_Calculator.xlsx
+++ b/SPC_Statistical_Calculator.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,6 +109,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="003B82F6"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F97316"/>
       <sz val="10"/>
     </font>
     <font>
@@ -248,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -337,10 +343,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,10 +359,14 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -556,7 +569,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>1. Current Process Distribution</a:t>
+              <a:t>1. Process Distribution — Current vs Centered</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -713,7 +726,356 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>2. Capability Index vs Target</a:t>
+              <a:t>2. I-Chart — Individual Values with Control Limits</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!I4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="3B82F6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts'!$H$5:$H$54</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$I$5:$I$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!K4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="059669"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts'!$H$5:$H$54</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$K$5:$K$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!L4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="15000">
+              <a:solidFill>
+                <a:srgbClr val="DC2626"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts'!$H$5:$H$54</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$L$5:$L$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!M4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="15000">
+              <a:solidFill>
+                <a:srgbClr val="DC2626"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts'!$H$5:$H$54</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$M$5:$M$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Part Number</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Value</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>3. Moving Range (MR) Chart</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!J4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="F97316"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts'!$H$5:$H$54</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$J$5:$J$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Part Number</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Moving Range</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>4. Capability Index vs Target</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -732,6 +1094,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3B82F6"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -756,6 +1121,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="059669"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -768,6 +1136,33 @@
           <val>
             <numRef>
               <f>'Charts'!$D$42:$D$43</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!E41</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="DC2626"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$B$42:$B$43</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$E$42:$E$43</f>
             </numRef>
           </val>
         </ser>
@@ -850,10 +1245,10 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="4320000"/>
+    <ext cx="8640000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -863,6 +1258,50 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5040000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1854,7 +2293,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Enter DMC and measured Value below. Statistics auto-link to Analysis sheet when Mode = "Use Data Worksheet".</t>
+          <t>Enter DMC and measured Value below (max 100 parts). Statistics auto-link to Analysis sheet.</t>
         </is>
       </c>
     </row>
@@ -1863,19 +2302,23 @@
         <f>Analysis!C5&amp;" | Tₘ="&amp;TEXT(Analysis!C6,"0.000")&amp;" | LSL="&amp;TEXT(Analysis!C7,"0.000")&amp;" | USL="&amp;TEXT(Analysis!C8,"0.000")</f>
         <v/>
       </c>
+      <c r="F3" s="34">
+        <f>G5&amp;" of 100 rows used ("&amp;TEXT(G5/100,"0%")&amp;" capacity)"</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>DMC / Serial Number</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1888,11 +2331,17 @@
       <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="36" t="n"/>
-      <c r="D5" s="37" t="n"/>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>DMC-2024-001</t>
+        </is>
+      </c>
+      <c r="D5" s="38" t="n">
+        <v>10.005</v>
+      </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Count (n)</t>
@@ -1904,11 +2353,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="39" t="n"/>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>DMC-2024-002</t>
+        </is>
+      </c>
+      <c r="D6" s="40" t="n">
+        <v>9.997999999999999</v>
+      </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Mean (x̄)</t>
@@ -1920,11 +2375,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="37" t="n"/>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>DMC-2024-003</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="n">
+        <v>10.012</v>
+      </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Std Dev (σ)</t>
@@ -1936,180 +2397,222 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="39" t="n"/>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>DMC-2024-004</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>9.984999999999999</v>
+      </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="41">
         <f>IF(G5&gt;=1,MIN(D5:D104),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="36" t="n"/>
-      <c r="D9" s="37" t="n"/>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>DMC-2024-005</t>
+        </is>
+      </c>
+      <c r="D9" s="38" t="n">
+        <v>10.008</v>
+      </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="41">
         <f>IF(G5&gt;=1,MAX(D5:D104),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="39" t="n"/>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>DMC-2024-006</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>9.992000000000001</v>
+      </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="41">
         <f>IF(G5&gt;=2,G9-G8,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="37" t="n"/>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>DMC-2024-007</t>
+        </is>
+      </c>
+      <c r="D11" s="38" t="n">
+        <v>10.015</v>
+      </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Median</t>
         </is>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <f>IF(G5&gt;=1,MEDIAN(D5:D104),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="39" t="n"/>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>DMC-2024-008</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>10.001</v>
+      </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Q1 (25th %ile)</t>
         </is>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="41">
         <f>IF(G5&gt;=4,PERCENTILE(D5:D104,0.25),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="37" t="n"/>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>DMC-2024-009</t>
+        </is>
+      </c>
+      <c r="D13" s="38" t="n">
+        <v>9.99</v>
+      </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Q3 (75th %ile)</t>
         </is>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="41">
         <f>IF(G5&gt;=4,PERCENTILE(D5:D104,0.75),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="39" t="n"/>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>DMC-2024-010</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>10.01</v>
+      </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>IQR</t>
         </is>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="41">
         <f>IF(G5&gt;=4,G13-G12,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="36" t="n"/>
-      <c r="D15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="38" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Skewness</t>
         </is>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="41">
         <f>IF(G5&gt;=3,SKEW(D5:D104),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="39" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="40" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Kurtosis</t>
         </is>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="41">
         <f>IF(G5&gt;=4,KURT(D5:D104),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="38" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="38" t="n"/>
-      <c r="D18" s="39" t="n"/>
-      <c r="F18" s="41">
-        <f>IF(G5&gt;=2,"✅ "&amp;G5&amp;" data points ready. Analysis sheet auto-linked.","⚠ Need ≥2 data points.")</f>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="F18" s="42">
+        <f>IF(G5&gt;=2,"✅ "&amp;G5&amp;" of 100 data points ready. Analysis auto-linked.","⚠ Need ≥2 data points (100 max allowed).")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="36" t="n"/>
-      <c r="D19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="39" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="40" t="n"/>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>QUICK PREVIEW (from worksheet data)</t>
@@ -2118,11 +2621,11 @@
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="36" t="n"/>
-      <c r="D21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="38" t="n"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Cp (preview)</t>
@@ -2134,11 +2637,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="35" t="n">
+      <c r="B22" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="38" t="n"/>
-      <c r="D22" s="39" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="40" t="n"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Cpk (preview)</t>
@@ -2150,587 +2653,594 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="36" t="n"/>
-      <c r="D23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="38" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="38" t="n"/>
-      <c r="D24" s="39" t="n"/>
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>💡 10 sample data points pre-filled as template. Replace with your actual measurements.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="37" t="n"/>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="38" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="39" t="n"/>
+      <c r="C26" s="39" t="n"/>
+      <c r="D26" s="40" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="35" t="n">
+      <c r="B27" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="36" t="n"/>
-      <c r="D27" s="37" t="n"/>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="38" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="38" t="n"/>
-      <c r="D28" s="39" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="40" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="35" t="n">
+      <c r="B29" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="37" t="n"/>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="38" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="39" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="40" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="35" t="n">
+      <c r="B31" s="36" t="n">
         <v>27</v>
       </c>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="37" t="n"/>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="38" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="36" t="n">
         <v>28</v>
       </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="39" t="n"/>
+      <c r="C32" s="39" t="n"/>
+      <c r="D32" s="40" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="35" t="n">
+      <c r="B33" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="C33" s="36" t="n"/>
-      <c r="D33" s="37" t="n"/>
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="38" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="35" t="n">
+      <c r="B34" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="39" t="n"/>
+      <c r="C34" s="39" t="n"/>
+      <c r="D34" s="40" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="35" t="n">
+      <c r="B35" s="36" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="37" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="38" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="35" t="n">
+      <c r="B36" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="39" t="n"/>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="40" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="35" t="n">
+      <c r="B37" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="37" t="n"/>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="38" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="35" t="n">
+      <c r="B38" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="39" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="40" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="35" t="n">
+      <c r="B39" s="36" t="n">
         <v>35</v>
       </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="37" t="n"/>
+      <c r="C39" s="37" t="n"/>
+      <c r="D39" s="38" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="35" t="n">
+      <c r="B40" s="36" t="n">
         <v>36</v>
       </c>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="39" t="n"/>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="40" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="35" t="n">
+      <c r="B41" s="36" t="n">
         <v>37</v>
       </c>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="37" t="n"/>
+      <c r="C41" s="37" t="n"/>
+      <c r="D41" s="38" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="35" t="n">
+      <c r="B42" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39" t="n"/>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="40" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="35" t="n">
+      <c r="B43" s="36" t="n">
         <v>39</v>
       </c>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="37" t="n"/>
+      <c r="C43" s="37" t="n"/>
+      <c r="D43" s="38" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="35" t="n">
+      <c r="B44" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="39" t="n"/>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="40" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="35" t="n">
+      <c r="B45" s="36" t="n">
         <v>41</v>
       </c>
-      <c r="C45" s="36" t="n"/>
-      <c r="D45" s="37" t="n"/>
+      <c r="C45" s="37" t="n"/>
+      <c r="D45" s="38" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="35" t="n">
+      <c r="B46" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="39" t="n"/>
+      <c r="C46" s="39" t="n"/>
+      <c r="D46" s="40" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="35" t="n">
+      <c r="B47" s="36" t="n">
         <v>43</v>
       </c>
-      <c r="C47" s="36" t="n"/>
-      <c r="D47" s="37" t="n"/>
+      <c r="C47" s="37" t="n"/>
+      <c r="D47" s="38" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="35" t="n">
+      <c r="B48" s="36" t="n">
         <v>44</v>
       </c>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39" t="n"/>
+      <c r="C48" s="39" t="n"/>
+      <c r="D48" s="40" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="35" t="n">
+      <c r="B49" s="36" t="n">
         <v>45</v>
       </c>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="37" t="n"/>
+      <c r="C49" s="37" t="n"/>
+      <c r="D49" s="38" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="35" t="n">
+      <c r="B50" s="36" t="n">
         <v>46</v>
       </c>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="39" t="n"/>
+      <c r="C50" s="39" t="n"/>
+      <c r="D50" s="40" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="35" t="n">
+      <c r="B51" s="36" t="n">
         <v>47</v>
       </c>
-      <c r="C51" s="36" t="n"/>
-      <c r="D51" s="37" t="n"/>
+      <c r="C51" s="37" t="n"/>
+      <c r="D51" s="38" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="35" t="n">
+      <c r="B52" s="36" t="n">
         <v>48</v>
       </c>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="39" t="n"/>
+      <c r="C52" s="39" t="n"/>
+      <c r="D52" s="40" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="35" t="n">
+      <c r="B53" s="36" t="n">
         <v>49</v>
       </c>
-      <c r="C53" s="36" t="n"/>
-      <c r="D53" s="37" t="n"/>
+      <c r="C53" s="37" t="n"/>
+      <c r="D53" s="38" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="35" t="n">
+      <c r="B54" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39" t="n"/>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="40" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="35" t="n">
+      <c r="B55" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="C55" s="36" t="n"/>
-      <c r="D55" s="37" t="n"/>
+      <c r="C55" s="37" t="n"/>
+      <c r="D55" s="38" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="35" t="n">
+      <c r="B56" s="36" t="n">
         <v>52</v>
       </c>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="39" t="n"/>
+      <c r="C56" s="39" t="n"/>
+      <c r="D56" s="40" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="35" t="n">
+      <c r="B57" s="36" t="n">
         <v>53</v>
       </c>
-      <c r="C57" s="36" t="n"/>
-      <c r="D57" s="37" t="n"/>
+      <c r="C57" s="37" t="n"/>
+      <c r="D57" s="38" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="35" t="n">
+      <c r="B58" s="36" t="n">
         <v>54</v>
       </c>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="39" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="40" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="35" t="n">
+      <c r="B59" s="36" t="n">
         <v>55</v>
       </c>
-      <c r="C59" s="36" t="n"/>
-      <c r="D59" s="37" t="n"/>
+      <c r="C59" s="37" t="n"/>
+      <c r="D59" s="38" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="35" t="n">
+      <c r="B60" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39" t="n"/>
+      <c r="C60" s="39" t="n"/>
+      <c r="D60" s="40" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="35" t="n">
+      <c r="B61" s="36" t="n">
         <v>57</v>
       </c>
-      <c r="C61" s="36" t="n"/>
-      <c r="D61" s="37" t="n"/>
+      <c r="C61" s="37" t="n"/>
+      <c r="D61" s="38" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="35" t="n">
+      <c r="B62" s="36" t="n">
         <v>58</v>
       </c>
-      <c r="C62" s="38" t="n"/>
-      <c r="D62" s="39" t="n"/>
+      <c r="C62" s="39" t="n"/>
+      <c r="D62" s="40" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="35" t="n">
+      <c r="B63" s="36" t="n">
         <v>59</v>
       </c>
-      <c r="C63" s="36" t="n"/>
-      <c r="D63" s="37" t="n"/>
+      <c r="C63" s="37" t="n"/>
+      <c r="D63" s="38" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="35" t="n">
+      <c r="B64" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="C64" s="38" t="n"/>
-      <c r="D64" s="39" t="n"/>
+      <c r="C64" s="39" t="n"/>
+      <c r="D64" s="40" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="35" t="n">
+      <c r="B65" s="36" t="n">
         <v>61</v>
       </c>
-      <c r="C65" s="36" t="n"/>
-      <c r="D65" s="37" t="n"/>
+      <c r="C65" s="37" t="n"/>
+      <c r="D65" s="38" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="35" t="n">
+      <c r="B66" s="36" t="n">
         <v>62</v>
       </c>
-      <c r="C66" s="38" t="n"/>
-      <c r="D66" s="39" t="n"/>
+      <c r="C66" s="39" t="n"/>
+      <c r="D66" s="40" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="35" t="n">
+      <c r="B67" s="36" t="n">
         <v>63</v>
       </c>
-      <c r="C67" s="36" t="n"/>
-      <c r="D67" s="37" t="n"/>
+      <c r="C67" s="37" t="n"/>
+      <c r="D67" s="38" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="35" t="n">
+      <c r="B68" s="36" t="n">
         <v>64</v>
       </c>
-      <c r="C68" s="38" t="n"/>
-      <c r="D68" s="39" t="n"/>
+      <c r="C68" s="39" t="n"/>
+      <c r="D68" s="40" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="35" t="n">
+      <c r="B69" s="36" t="n">
         <v>65</v>
       </c>
-      <c r="C69" s="36" t="n"/>
-      <c r="D69" s="37" t="n"/>
+      <c r="C69" s="37" t="n"/>
+      <c r="D69" s="38" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="35" t="n">
+      <c r="B70" s="36" t="n">
         <v>66</v>
       </c>
-      <c r="C70" s="38" t="n"/>
-      <c r="D70" s="39" t="n"/>
+      <c r="C70" s="39" t="n"/>
+      <c r="D70" s="40" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="35" t="n">
+      <c r="B71" s="36" t="n">
         <v>67</v>
       </c>
-      <c r="C71" s="36" t="n"/>
-      <c r="D71" s="37" t="n"/>
+      <c r="C71" s="37" t="n"/>
+      <c r="D71" s="38" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="35" t="n">
+      <c r="B72" s="36" t="n">
         <v>68</v>
       </c>
-      <c r="C72" s="38" t="n"/>
-      <c r="D72" s="39" t="n"/>
+      <c r="C72" s="39" t="n"/>
+      <c r="D72" s="40" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="35" t="n">
+      <c r="B73" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="C73" s="36" t="n"/>
-      <c r="D73" s="37" t="n"/>
+      <c r="C73" s="37" t="n"/>
+      <c r="D73" s="38" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="35" t="n">
+      <c r="B74" s="36" t="n">
         <v>70</v>
       </c>
-      <c r="C74" s="38" t="n"/>
-      <c r="D74" s="39" t="n"/>
+      <c r="C74" s="39" t="n"/>
+      <c r="D74" s="40" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="35" t="n">
+      <c r="B75" s="36" t="n">
         <v>71</v>
       </c>
-      <c r="C75" s="36" t="n"/>
-      <c r="D75" s="37" t="n"/>
+      <c r="C75" s="37" t="n"/>
+      <c r="D75" s="38" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="35" t="n">
+      <c r="B76" s="36" t="n">
         <v>72</v>
       </c>
-      <c r="C76" s="38" t="n"/>
-      <c r="D76" s="39" t="n"/>
+      <c r="C76" s="39" t="n"/>
+      <c r="D76" s="40" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="35" t="n">
+      <c r="B77" s="36" t="n">
         <v>73</v>
       </c>
-      <c r="C77" s="36" t="n"/>
-      <c r="D77" s="37" t="n"/>
+      <c r="C77" s="37" t="n"/>
+      <c r="D77" s="38" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="35" t="n">
+      <c r="B78" s="36" t="n">
         <v>74</v>
       </c>
-      <c r="C78" s="38" t="n"/>
-      <c r="D78" s="39" t="n"/>
+      <c r="C78" s="39" t="n"/>
+      <c r="D78" s="40" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="35" t="n">
+      <c r="B79" s="36" t="n">
         <v>75</v>
       </c>
-      <c r="C79" s="36" t="n"/>
-      <c r="D79" s="37" t="n"/>
+      <c r="C79" s="37" t="n"/>
+      <c r="D79" s="38" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="35" t="n">
+      <c r="B80" s="36" t="n">
         <v>76</v>
       </c>
-      <c r="C80" s="38" t="n"/>
-      <c r="D80" s="39" t="n"/>
+      <c r="C80" s="39" t="n"/>
+      <c r="D80" s="40" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="35" t="n">
+      <c r="B81" s="36" t="n">
         <v>77</v>
       </c>
-      <c r="C81" s="36" t="n"/>
-      <c r="D81" s="37" t="n"/>
+      <c r="C81" s="37" t="n"/>
+      <c r="D81" s="38" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="35" t="n">
+      <c r="B82" s="36" t="n">
         <v>78</v>
       </c>
-      <c r="C82" s="38" t="n"/>
-      <c r="D82" s="39" t="n"/>
+      <c r="C82" s="39" t="n"/>
+      <c r="D82" s="40" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="35" t="n">
+      <c r="B83" s="36" t="n">
         <v>79</v>
       </c>
-      <c r="C83" s="36" t="n"/>
-      <c r="D83" s="37" t="n"/>
+      <c r="C83" s="37" t="n"/>
+      <c r="D83" s="38" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="35" t="n">
+      <c r="B84" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="C84" s="38" t="n"/>
-      <c r="D84" s="39" t="n"/>
+      <c r="C84" s="39" t="n"/>
+      <c r="D84" s="40" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="35" t="n">
+      <c r="B85" s="36" t="n">
         <v>81</v>
       </c>
-      <c r="C85" s="36" t="n"/>
-      <c r="D85" s="37" t="n"/>
+      <c r="C85" s="37" t="n"/>
+      <c r="D85" s="38" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="35" t="n">
+      <c r="B86" s="36" t="n">
         <v>82</v>
       </c>
-      <c r="C86" s="38" t="n"/>
-      <c r="D86" s="39" t="n"/>
+      <c r="C86" s="39" t="n"/>
+      <c r="D86" s="40" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="35" t="n">
+      <c r="B87" s="36" t="n">
         <v>83</v>
       </c>
-      <c r="C87" s="36" t="n"/>
-      <c r="D87" s="37" t="n"/>
+      <c r="C87" s="37" t="n"/>
+      <c r="D87" s="38" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="35" t="n">
+      <c r="B88" s="36" t="n">
         <v>84</v>
       </c>
-      <c r="C88" s="38" t="n"/>
-      <c r="D88" s="39" t="n"/>
+      <c r="C88" s="39" t="n"/>
+      <c r="D88" s="40" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="35" t="n">
+      <c r="B89" s="36" t="n">
         <v>85</v>
       </c>
-      <c r="C89" s="36" t="n"/>
-      <c r="D89" s="37" t="n"/>
+      <c r="C89" s="37" t="n"/>
+      <c r="D89" s="38" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="35" t="n">
+      <c r="B90" s="36" t="n">
         <v>86</v>
       </c>
-      <c r="C90" s="38" t="n"/>
-      <c r="D90" s="39" t="n"/>
+      <c r="C90" s="39" t="n"/>
+      <c r="D90" s="40" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="35" t="n">
+      <c r="B91" s="36" t="n">
         <v>87</v>
       </c>
-      <c r="C91" s="36" t="n"/>
-      <c r="D91" s="37" t="n"/>
+      <c r="C91" s="37" t="n"/>
+      <c r="D91" s="38" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="35" t="n">
+      <c r="B92" s="36" t="n">
         <v>88</v>
       </c>
-      <c r="C92" s="38" t="n"/>
-      <c r="D92" s="39" t="n"/>
+      <c r="C92" s="39" t="n"/>
+      <c r="D92" s="40" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="35" t="n">
+      <c r="B93" s="36" t="n">
         <v>89</v>
       </c>
-      <c r="C93" s="36" t="n"/>
-      <c r="D93" s="37" t="n"/>
+      <c r="C93" s="37" t="n"/>
+      <c r="D93" s="38" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="35" t="n">
+      <c r="B94" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="C94" s="38" t="n"/>
-      <c r="D94" s="39" t="n"/>
+      <c r="C94" s="39" t="n"/>
+      <c r="D94" s="40" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="35" t="n">
+      <c r="B95" s="36" t="n">
         <v>91</v>
       </c>
-      <c r="C95" s="36" t="n"/>
-      <c r="D95" s="37" t="n"/>
+      <c r="C95" s="37" t="n"/>
+      <c r="D95" s="38" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="35" t="n">
+      <c r="B96" s="36" t="n">
         <v>92</v>
       </c>
-      <c r="C96" s="38" t="n"/>
-      <c r="D96" s="39" t="n"/>
+      <c r="C96" s="39" t="n"/>
+      <c r="D96" s="40" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="35" t="n">
+      <c r="B97" s="36" t="n">
         <v>93</v>
       </c>
-      <c r="C97" s="36" t="n"/>
-      <c r="D97" s="37" t="n"/>
+      <c r="C97" s="37" t="n"/>
+      <c r="D97" s="38" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="35" t="n">
+      <c r="B98" s="36" t="n">
         <v>94</v>
       </c>
-      <c r="C98" s="38" t="n"/>
-      <c r="D98" s="39" t="n"/>
+      <c r="C98" s="39" t="n"/>
+      <c r="D98" s="40" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="35" t="n">
+      <c r="B99" s="36" t="n">
         <v>95</v>
       </c>
-      <c r="C99" s="36" t="n"/>
-      <c r="D99" s="37" t="n"/>
+      <c r="C99" s="37" t="n"/>
+      <c r="D99" s="38" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="35" t="n">
+      <c r="B100" s="36" t="n">
         <v>96</v>
       </c>
-      <c r="C100" s="38" t="n"/>
-      <c r="D100" s="39" t="n"/>
+      <c r="C100" s="39" t="n"/>
+      <c r="D100" s="40" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="35" t="n">
+      <c r="B101" s="36" t="n">
         <v>97</v>
       </c>
-      <c r="C101" s="36" t="n"/>
-      <c r="D101" s="37" t="n"/>
+      <c r="C101" s="37" t="n"/>
+      <c r="D101" s="38" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="35" t="n">
+      <c r="B102" s="36" t="n">
         <v>98</v>
       </c>
-      <c r="C102" s="38" t="n"/>
-      <c r="D102" s="39" t="n"/>
+      <c r="C102" s="39" t="n"/>
+      <c r="D102" s="40" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="35" t="n">
+      <c r="B103" s="36" t="n">
         <v>99</v>
       </c>
-      <c r="C103" s="36" t="n"/>
-      <c r="D103" s="37" t="n"/>
+      <c r="C103" s="37" t="n"/>
+      <c r="D103" s="38" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="35" t="n">
+      <c r="B104" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="C104" s="38" t="n"/>
-      <c r="D104" s="39" t="n"/>
+      <c r="C104" s="39" t="n"/>
+      <c r="D104" s="40" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B1:G1"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="G21">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
@@ -2767,7 +3277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F50"/>
+  <dimension ref="B1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2776,605 +3286,1461 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Visualization — Capability Charts</t>
+          <t>Visualization — Process Capability &amp; Control Charts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Normal Distribution Curve Data (auto-calculated)</t>
+          <t>Normal Distribution Curve Data</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>I-MR Control Chart Data (from Data Worksheet)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>x Value</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Current PDF</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>Centered PDF</t>
         </is>
       </c>
+      <c r="H4" s="35" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="I4" s="35" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="J4" s="35" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="K4" s="35" t="inlineStr">
+        <is>
+          <t>x̄ (CL)</t>
+        </is>
+      </c>
+      <c r="L4" s="35" t="inlineStr">
+        <is>
+          <t>UCL</t>
+        </is>
+      </c>
+      <c r="M4" s="35" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="42" t="n">
+      <c r="B5" s="43" t="n">
         <v>-4</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="44">
         <f>Analysis!G9+B5*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B5^2),0)</f>
         <v/>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C5-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="45">
+        <f>IF(Data!D5="""",NA(),Data!D5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="45">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="K5" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L5" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M5" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="42" t="n">
+      <c r="B6" s="43" t="n">
         <v>-3.75</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="44">
         <f>Analysis!G9+B6*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B6^2),0)</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C6-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H6" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="45">
+        <f>IF(Data!D6="""",NA(),Data!D6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="45">
+        <f>IF(OR(Data!D6="""",Data!D5=""""),NA(),ABS(Data!D6-Data!D5))</f>
+        <v/>
+      </c>
+      <c r="K6" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L6" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M6" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="43" t="n">
         <v>-3.5</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="44">
         <f>Analysis!G9+B7*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B7^2),0)</f>
         <v/>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C7-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H7" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="45">
+        <f>IF(Data!D7="""",NA(),Data!D7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="45">
+        <f>IF(OR(Data!D7="""",Data!D6=""""),NA(),ABS(Data!D7-Data!D6))</f>
+        <v/>
+      </c>
+      <c r="K7" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L7" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M7" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="42" t="n">
+      <c r="B8" s="43" t="n">
         <v>-3.25</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="44">
         <f>Analysis!G9+B8*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B8^2),0)</f>
         <v/>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C8-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H8" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="45">
+        <f>IF(Data!D8="""",NA(),Data!D8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="45">
+        <f>IF(OR(Data!D8="""",Data!D7=""""),NA(),ABS(Data!D8-Data!D7))</f>
+        <v/>
+      </c>
+      <c r="K8" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L8" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M8" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="43" t="n">
         <v>-3</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="44">
         <f>Analysis!G9+B9*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B9^2),0)</f>
         <v/>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C9-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H9" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="45">
+        <f>IF(Data!D9="""",NA(),Data!D9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="45">
+        <f>IF(OR(Data!D9="""",Data!D8=""""),NA(),ABS(Data!D9-Data!D8))</f>
+        <v/>
+      </c>
+      <c r="K9" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L9" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M9" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="42" t="n">
+      <c r="B10" s="43" t="n">
         <v>-2.75</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="44">
         <f>Analysis!G9+B10*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B10^2),0)</f>
         <v/>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C10-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H10" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="45">
+        <f>IF(Data!D10="""",NA(),Data!D10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="45">
+        <f>IF(OR(Data!D10="""",Data!D9=""""),NA(),ABS(Data!D10-Data!D9))</f>
+        <v/>
+      </c>
+      <c r="K10" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L10" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M10" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="42" t="n">
+      <c r="B11" s="43" t="n">
         <v>-2.5</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="44">
         <f>Analysis!G9+B11*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B11^2),0)</f>
         <v/>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C11-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H11" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="45">
+        <f>IF(Data!D11="""",NA(),Data!D11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="45">
+        <f>IF(OR(Data!D11="""",Data!D10=""""),NA(),ABS(Data!D11-Data!D10))</f>
+        <v/>
+      </c>
+      <c r="K11" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L11" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M11" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="42" t="n">
+      <c r="B12" s="43" t="n">
         <v>-2.25</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="44">
         <f>Analysis!G9+B12*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B12^2),0)</f>
         <v/>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C12-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H12" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="45">
+        <f>IF(Data!D12="""",NA(),Data!D12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="45">
+        <f>IF(OR(Data!D12="""",Data!D11=""""),NA(),ABS(Data!D12-Data!D11))</f>
+        <v/>
+      </c>
+      <c r="K12" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L12" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M12" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="42" t="n">
+      <c r="B13" s="43" t="n">
         <v>-2</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="44">
         <f>Analysis!G9+B13*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B13^2),0)</f>
         <v/>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C13-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H13" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" s="45">
+        <f>IF(Data!D13="""",NA(),Data!D13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="45">
+        <f>IF(OR(Data!D13="""",Data!D12=""""),NA(),ABS(Data!D13-Data!D12))</f>
+        <v/>
+      </c>
+      <c r="K13" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L13" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M13" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="42" t="n">
+      <c r="B14" s="43" t="n">
         <v>-1.75</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="44">
         <f>Analysis!G9+B14*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B14^2),0)</f>
         <v/>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C14-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H14" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="45">
+        <f>IF(Data!D14="""",NA(),Data!D14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="45">
+        <f>IF(OR(Data!D14="""",Data!D13=""""),NA(),ABS(Data!D14-Data!D13))</f>
+        <v/>
+      </c>
+      <c r="K14" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L14" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M14" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="42" t="n">
+      <c r="B15" s="43" t="n">
         <v>-1.5</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="44">
         <f>Analysis!G9+B15*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B15^2),0)</f>
         <v/>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C15-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H15" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" s="45">
+        <f>IF(Data!D15="""",NA(),Data!D15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="45">
+        <f>IF(OR(Data!D15="""",Data!D14=""""),NA(),ABS(Data!D15-Data!D14))</f>
+        <v/>
+      </c>
+      <c r="K15" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L15" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M15" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="42" t="n">
+      <c r="B16" s="43" t="n">
         <v>-1.25</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="44">
         <f>Analysis!G9+B16*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B16^2),0)</f>
         <v/>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C16-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H16" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" s="45">
+        <f>IF(Data!D16="""",NA(),Data!D16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="45">
+        <f>IF(OR(Data!D16="""",Data!D15=""""),NA(),ABS(Data!D16-Data!D15))</f>
+        <v/>
+      </c>
+      <c r="K16" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L16" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M16" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="42" t="n">
+      <c r="B17" s="43" t="n">
         <v>-1</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="44">
         <f>Analysis!G9+B17*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B17^2),0)</f>
         <v/>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C17-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H17" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" s="45">
+        <f>IF(Data!D17="""",NA(),Data!D17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="45">
+        <f>IF(OR(Data!D17="""",Data!D16=""""),NA(),ABS(Data!D17-Data!D16))</f>
+        <v/>
+      </c>
+      <c r="K17" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L17" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M17" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="42" t="n">
+      <c r="B18" s="43" t="n">
         <v>-0.75</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="44">
         <f>Analysis!G9+B18*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B18^2),0)</f>
         <v/>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C18-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H18" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" s="45">
+        <f>IF(Data!D18="""",NA(),Data!D18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="45">
+        <f>IF(OR(Data!D18="""",Data!D17=""""),NA(),ABS(Data!D18-Data!D17))</f>
+        <v/>
+      </c>
+      <c r="K18" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L18" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M18" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="42" t="n">
+      <c r="B19" s="43" t="n">
         <v>-0.5</v>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="44">
         <f>Analysis!G9+B19*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D19" s="43">
+      <c r="D19" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B19^2),0)</f>
         <v/>
       </c>
-      <c r="E19" s="43">
+      <c r="E19" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C19-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H19" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" s="45">
+        <f>IF(Data!D19="""",NA(),Data!D19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="45">
+        <f>IF(OR(Data!D19="""",Data!D18=""""),NA(),ABS(Data!D19-Data!D18))</f>
+        <v/>
+      </c>
+      <c r="K19" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L19" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M19" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="42" t="n">
+      <c r="B20" s="43" t="n">
         <v>-0.25</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="44">
         <f>Analysis!G9+B20*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B20^2),0)</f>
         <v/>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C20-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H20" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="I20" s="45">
+        <f>IF(Data!D20="""",NA(),Data!D20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="45">
+        <f>IF(OR(Data!D20="""",Data!D19=""""),NA(),ABS(Data!D20-Data!D19))</f>
+        <v/>
+      </c>
+      <c r="K20" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L20" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M20" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="42" t="n">
+      <c r="B21" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="44">
         <f>Analysis!G9+B21*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B21^2),0)</f>
         <v/>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C21-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H21" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="I21" s="45">
+        <f>IF(Data!D21="""",NA(),Data!D21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="45">
+        <f>IF(OR(Data!D21="""",Data!D20=""""),NA(),ABS(Data!D21-Data!D20))</f>
+        <v/>
+      </c>
+      <c r="K21" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L21" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M21" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="42" t="n">
+      <c r="B22" s="43" t="n">
         <v>0.25</v>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="44">
         <f>Analysis!G9+B22*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B22^2),0)</f>
         <v/>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C22-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H22" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="I22" s="45">
+        <f>IF(Data!D22="""",NA(),Data!D22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="45">
+        <f>IF(OR(Data!D22="""",Data!D21=""""),NA(),ABS(Data!D22-Data!D21))</f>
+        <v/>
+      </c>
+      <c r="K22" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L22" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M22" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="42" t="n">
+      <c r="B23" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="44">
         <f>Analysis!G9+B23*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B23^2),0)</f>
         <v/>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C23-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H23" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="I23" s="45">
+        <f>IF(Data!D23="""",NA(),Data!D23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="45">
+        <f>IF(OR(Data!D23="""",Data!D22=""""),NA(),ABS(Data!D23-Data!D22))</f>
+        <v/>
+      </c>
+      <c r="K23" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L23" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M23" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="42" t="n">
+      <c r="B24" s="43" t="n">
         <v>0.75</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="44">
         <f>Analysis!G9+B24*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B24^2),0)</f>
         <v/>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C24-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H24" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" s="45">
+        <f>IF(Data!D24="""",NA(),Data!D24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="45">
+        <f>IF(OR(Data!D24="""",Data!D23=""""),NA(),ABS(Data!D24-Data!D23))</f>
+        <v/>
+      </c>
+      <c r="K24" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L24" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M24" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="42" t="n">
+      <c r="B25" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="44">
         <f>Analysis!G9+B25*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B25^2),0)</f>
         <v/>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C25-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H25" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" s="45">
+        <f>IF(Data!D25="""",NA(),Data!D25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="45">
+        <f>IF(OR(Data!D25="""",Data!D24=""""),NA(),ABS(Data!D25-Data!D24))</f>
+        <v/>
+      </c>
+      <c r="K25" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L25" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M25" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="B26" s="42" t="n">
+      <c r="B26" s="43" t="n">
         <v>1.25</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="44">
         <f>Analysis!G9+B26*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B26^2),0)</f>
         <v/>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C26-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H26" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" s="45">
+        <f>IF(Data!D26="""",NA(),Data!D26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="45">
+        <f>IF(OR(Data!D26="""",Data!D25=""""),NA(),ABS(Data!D26-Data!D25))</f>
+        <v/>
+      </c>
+      <c r="K26" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L26" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M26" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="42" t="n">
+      <c r="B27" s="43" t="n">
         <v>1.5</v>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="44">
         <f>Analysis!G9+B27*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B27^2),0)</f>
         <v/>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C27-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H27" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="I27" s="45">
+        <f>IF(Data!D27="""",NA(),Data!D27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="45">
+        <f>IF(OR(Data!D27="""",Data!D26=""""),NA(),ABS(Data!D27-Data!D26))</f>
+        <v/>
+      </c>
+      <c r="K27" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L27" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M27" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="42" t="n">
+      <c r="B28" s="43" t="n">
         <v>1.75</v>
       </c>
-      <c r="C28" s="43">
+      <c r="C28" s="44">
         <f>Analysis!G9+B28*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D28" s="43">
+      <c r="D28" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B28^2),0)</f>
         <v/>
       </c>
-      <c r="E28" s="43">
+      <c r="E28" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C28-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H28" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" s="45">
+        <f>IF(Data!D28="""",NA(),Data!D28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="45">
+        <f>IF(OR(Data!D28="""",Data!D27=""""),NA(),ABS(Data!D28-Data!D27))</f>
+        <v/>
+      </c>
+      <c r="K28" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L28" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M28" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="42" t="n">
+      <c r="B29" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C29" s="44">
         <f>Analysis!G9+B29*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B29^2),0)</f>
         <v/>
       </c>
-      <c r="E29" s="43">
+      <c r="E29" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C29-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H29" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" s="45">
+        <f>IF(Data!D29="""",NA(),Data!D29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="45">
+        <f>IF(OR(Data!D29="""",Data!D28=""""),NA(),ABS(Data!D29-Data!D28))</f>
+        <v/>
+      </c>
+      <c r="K29" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L29" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M29" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="B30" s="42" t="n">
+      <c r="B30" s="43" t="n">
         <v>2.25</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="44">
         <f>Analysis!G9+B30*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B30^2),0)</f>
         <v/>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C30-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H30" s="36" t="n">
+        <v>26</v>
+      </c>
+      <c r="I30" s="45">
+        <f>IF(Data!D30="""",NA(),Data!D30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="45">
+        <f>IF(OR(Data!D30="""",Data!D29=""""),NA(),ABS(Data!D30-Data!D29))</f>
+        <v/>
+      </c>
+      <c r="K30" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L30" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M30" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="42" t="n">
+      <c r="B31" s="43" t="n">
         <v>2.5</v>
       </c>
-      <c r="C31" s="43">
+      <c r="C31" s="44">
         <f>Analysis!G9+B31*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D31" s="43">
+      <c r="D31" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B31^2),0)</f>
         <v/>
       </c>
-      <c r="E31" s="43">
+      <c r="E31" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C31-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H31" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="I31" s="45">
+        <f>IF(Data!D31="""",NA(),Data!D31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="45">
+        <f>IF(OR(Data!D31="""",Data!D30=""""),NA(),ABS(Data!D31-Data!D30))</f>
+        <v/>
+      </c>
+      <c r="K31" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L31" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M31" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="42" t="n">
+      <c r="B32" s="43" t="n">
         <v>2.75</v>
       </c>
-      <c r="C32" s="43">
+      <c r="C32" s="44">
         <f>Analysis!G9+B32*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D32" s="43">
+      <c r="D32" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B32^2),0)</f>
         <v/>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C32-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H32" s="36" t="n">
+        <v>28</v>
+      </c>
+      <c r="I32" s="45">
+        <f>IF(Data!D32="""",NA(),Data!D32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="45">
+        <f>IF(OR(Data!D32="""",Data!D31=""""),NA(),ABS(Data!D32-Data!D31))</f>
+        <v/>
+      </c>
+      <c r="K32" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L32" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M32" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="42" t="n">
+      <c r="B33" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="43">
+      <c r="C33" s="44">
         <f>Analysis!G9+B33*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B33^2),0)</f>
         <v/>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C33-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H33" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="I33" s="45">
+        <f>IF(Data!D33="""",NA(),Data!D33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="45">
+        <f>IF(OR(Data!D33="""",Data!D32=""""),NA(),ABS(Data!D33-Data!D32))</f>
+        <v/>
+      </c>
+      <c r="K33" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L33" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M33" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="B34" s="42" t="n">
+      <c r="B34" s="43" t="n">
         <v>3.25</v>
       </c>
-      <c r="C34" s="43">
+      <c r="C34" s="44">
         <f>Analysis!G9+B34*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B34^2),0)</f>
         <v/>
       </c>
-      <c r="E34" s="43">
+      <c r="E34" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C34-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H34" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="45">
+        <f>IF(Data!D34="""",NA(),Data!D34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="45">
+        <f>IF(OR(Data!D34="""",Data!D33=""""),NA(),ABS(Data!D34-Data!D33))</f>
+        <v/>
+      </c>
+      <c r="K34" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L34" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M34" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="42" t="n">
+      <c r="B35" s="43" t="n">
         <v>3.5</v>
       </c>
-      <c r="C35" s="43">
+      <c r="C35" s="44">
         <f>Analysis!G9+B35*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D35" s="43">
+      <c r="D35" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B35^2),0)</f>
         <v/>
       </c>
-      <c r="E35" s="43">
+      <c r="E35" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C35-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H35" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="I35" s="45">
+        <f>IF(Data!D35="""",NA(),Data!D35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="45">
+        <f>IF(OR(Data!D35="""",Data!D34=""""),NA(),ABS(Data!D35-Data!D34))</f>
+        <v/>
+      </c>
+      <c r="K35" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L35" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M35" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="B36" s="42" t="n">
+      <c r="B36" s="43" t="n">
         <v>3.75</v>
       </c>
-      <c r="C36" s="43">
+      <c r="C36" s="44">
         <f>Analysis!G9+B36*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D36" s="43">
+      <c r="D36" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B36^2),0)</f>
         <v/>
       </c>
-      <c r="E36" s="43">
+      <c r="E36" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C36-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
+      <c r="H36" s="36" t="n">
+        <v>32</v>
+      </c>
+      <c r="I36" s="45">
+        <f>IF(Data!D36="""",NA(),Data!D36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="45">
+        <f>IF(OR(Data!D36="""",Data!D35=""""),NA(),ABS(Data!D36-Data!D35))</f>
+        <v/>
+      </c>
+      <c r="K36" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L36" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M36" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="B37" s="42" t="n">
+      <c r="B37" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="C37" s="43">
+      <c r="C37" s="44">
         <f>Analysis!G9+B37*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D37" s="43">
+      <c r="D37" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B37^2),0)</f>
         <v/>
       </c>
-      <c r="E37" s="43">
+      <c r="E37" s="44">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C37-Analysis!C6)/Analysis!G10)^2),0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="36" t="n">
+        <v>33</v>
+      </c>
+      <c r="I37" s="45">
+        <f>IF(Data!D37="""",NA(),Data!D37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="45">
+        <f>IF(OR(Data!D37="""",Data!D36=""""),NA(),ABS(Data!D37-Data!D36))</f>
+        <v/>
+      </c>
+      <c r="K37" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L37" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M37" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" s="36" t="n">
+        <v>34</v>
+      </c>
+      <c r="I38" s="45">
+        <f>IF(Data!D38="""",NA(),Data!D38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="45">
+        <f>IF(OR(Data!D38="""",Data!D37=""""),NA(),ABS(Data!D38-Data!D37))</f>
+        <v/>
+      </c>
+      <c r="K38" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L38" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M38" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" s="36" t="n">
+        <v>35</v>
+      </c>
+      <c r="I39" s="45">
+        <f>IF(Data!D39="""",NA(),Data!D39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="45">
+        <f>IF(OR(Data!D39="""",Data!D38=""""),NA(),ABS(Data!D39-Data!D38))</f>
+        <v/>
+      </c>
+      <c r="K39" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L39" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M39" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
         <v/>
       </c>
     </row>
@@ -3387,63 +4753,239 @@
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
+      <c r="H40" s="36" t="n">
+        <v>36</v>
+      </c>
+      <c r="I40" s="45">
+        <f>IF(Data!D40="""",NA(),Data!D40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="45">
+        <f>IF(OR(Data!D40="""",Data!D39=""""),NA(),ABS(Data!D40-Data!D39))</f>
+        <v/>
+      </c>
+      <c r="K40" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L40" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M40" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="B41" s="34" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="E41" s="34" t="inlineStr"/>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>Min (1.0)</t>
+        </is>
+      </c>
+      <c r="H41" s="36" t="n">
+        <v>37</v>
+      </c>
+      <c r="I41" s="45">
+        <f>IF(Data!D41="""",NA(),Data!D41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="45">
+        <f>IF(OR(Data!D41="""",Data!D40=""""),NA(),ABS(Data!D41-Data!D40))</f>
+        <v/>
+      </c>
+      <c r="K41" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L41" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M41" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="B42" s="44" t="inlineStr">
+      <c r="B42" s="46" t="inlineStr">
         <is>
           <t>Cp</t>
         </is>
       </c>
-      <c r="C42" s="42">
+      <c r="C42" s="43">
         <f>Analysis!G17</f>
         <v/>
       </c>
-      <c r="D42" s="42">
+      <c r="D42" s="43">
         <f>Analysis!C16</f>
         <v/>
       </c>
+      <c r="E42" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="36" t="n">
+        <v>38</v>
+      </c>
+      <c r="I42" s="45">
+        <f>IF(Data!D42="""",NA(),Data!D42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="45">
+        <f>IF(OR(Data!D42="""",Data!D41=""""),NA(),ABS(Data!D42-Data!D41))</f>
+        <v/>
+      </c>
+      <c r="K42" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L42" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M42" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="B43" s="44" t="inlineStr">
+      <c r="B43" s="46" t="inlineStr">
         <is>
           <t>Cpk</t>
         </is>
       </c>
-      <c r="C43" s="42">
+      <c r="C43" s="43">
         <f>Analysis!G18</f>
         <v/>
       </c>
-      <c r="D43" s="42">
+      <c r="D43" s="43">
         <f>Analysis!C16</f>
+        <v/>
+      </c>
+      <c r="E43" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="36" t="n">
+        <v>39</v>
+      </c>
+      <c r="I43" s="45">
+        <f>IF(Data!D43="""",NA(),Data!D43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="45">
+        <f>IF(OR(Data!D43="""",Data!D42=""""),NA(),ABS(Data!D43-Data!D42))</f>
+        <v/>
+      </c>
+      <c r="K43" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L43" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M43" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" s="36" t="n">
+        <v>40</v>
+      </c>
+      <c r="I44" s="45">
+        <f>IF(Data!D44="""",NA(),Data!D44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="45">
+        <f>IF(OR(Data!D44="""",Data!D43=""""),NA(),ABS(Data!D44-Data!D43))</f>
+        <v/>
+      </c>
+      <c r="K44" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L44" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M44" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="36" t="n">
+        <v>41</v>
+      </c>
+      <c r="I45" s="45">
+        <f>IF(Data!D45="""",NA(),Data!D45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="45">
+        <f>IF(OR(Data!D45="""",Data!D44=""""),NA(),ABS(Data!D45-Data!D44))</f>
+        <v/>
+      </c>
+      <c r="K45" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L45" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M45" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Specification Lines</t>
+          <t>Specification Summary</t>
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="H46" s="36" t="n">
+        <v>42</v>
+      </c>
+      <c r="I46" s="45">
+        <f>IF(Data!D46="""",NA(),Data!D46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="45">
+        <f>IF(OR(Data!D46="""",Data!D45=""""),NA(),ABS(Data!D46-Data!D45))</f>
+        <v/>
+      </c>
+      <c r="K46" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L46" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M46" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="inlineStr">
@@ -3455,6 +4997,38 @@
         <f>Analysis!C7</f>
         <v/>
       </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Tₘ</t>
+        </is>
+      </c>
+      <c r="E47" s="21">
+        <f>Analysis!C6</f>
+        <v/>
+      </c>
+      <c r="H47" s="36" t="n">
+        <v>43</v>
+      </c>
+      <c r="I47" s="45">
+        <f>IF(Data!D47="""",NA(),Data!D47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="45">
+        <f>IF(OR(Data!D47="""",Data!D46=""""),NA(),ABS(Data!D47-Data!D46))</f>
+        <v/>
+      </c>
+      <c r="K47" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L47" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M47" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="5" t="inlineStr">
@@ -3466,35 +5040,232 @@
         <f>Analysis!C8</f>
         <v/>
       </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Mean (x̄)</t>
+        </is>
+      </c>
+      <c r="E48" s="21">
+        <f>Analysis!G9</f>
+        <v/>
+      </c>
+      <c r="H48" s="36" t="n">
+        <v>44</v>
+      </c>
+      <c r="I48" s="45">
+        <f>IF(Data!D48="""",NA(),Data!D48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="45">
+        <f>IF(OR(Data!D48="""",Data!D47=""""),NA(),ABS(Data!D48-Data!D47))</f>
+        <v/>
+      </c>
+      <c r="K48" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L48" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M48" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Target (Tₘ)</t>
-        </is>
-      </c>
-      <c r="C49" s="21">
-        <f>Analysis!C6</f>
+          <t>σ (ACTIVE)</t>
+        </is>
+      </c>
+      <c r="C49" s="19">
+        <f>Analysis!G10</f>
+        <v/>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>n (ACTIVE)</t>
+        </is>
+      </c>
+      <c r="E49" s="47">
+        <f>Analysis!G11</f>
+        <v/>
+      </c>
+      <c r="H49" s="36" t="n">
+        <v>45</v>
+      </c>
+      <c r="I49" s="45">
+        <f>IF(Data!D49="""",NA(),Data!D49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="45">
+        <f>IF(OR(Data!D49="""",Data!D48=""""),NA(),ABS(Data!D49-Data!D48))</f>
+        <v/>
+      </c>
+      <c r="K49" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L49" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M49" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Mean (x̄)</t>
+          <t>6σ Spread</t>
         </is>
       </c>
       <c r="C50" s="21">
-        <f>Analysis!G9</f>
+        <f>Analysis!G15</f>
+        <v/>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>8σ Spread</t>
+        </is>
+      </c>
+      <c r="E50" s="21">
+        <f>Analysis!G16</f>
+        <v/>
+      </c>
+      <c r="H50" s="36" t="n">
+        <v>46</v>
+      </c>
+      <c r="I50" s="45">
+        <f>IF(Data!D50="""",NA(),Data!D50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="45">
+        <f>IF(OR(Data!D50="""",Data!D49=""""),NA(),ABS(Data!D50-Data!D49))</f>
+        <v/>
+      </c>
+      <c r="K50" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L50" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M50" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51" s="36" t="n">
+        <v>47</v>
+      </c>
+      <c r="I51" s="45">
+        <f>IF(Data!D51="""",NA(),Data!D51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="45">
+        <f>IF(OR(Data!D51="""",Data!D50=""""),NA(),ABS(Data!D51-Data!D50))</f>
+        <v/>
+      </c>
+      <c r="K51" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L51" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M51" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="I52" s="45">
+        <f>IF(Data!D52="""",NA(),Data!D52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="45">
+        <f>IF(OR(Data!D52="""",Data!D51=""""),NA(),ABS(Data!D52-Data!D51))</f>
+        <v/>
+      </c>
+      <c r="K52" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L52" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M52" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="H53" s="36" t="n">
+        <v>49</v>
+      </c>
+      <c r="I53" s="45">
+        <f>IF(Data!D53="""",NA(),Data!D53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="45">
+        <f>IF(OR(Data!D53="""",Data!D52=""""),NA(),ABS(Data!D53-Data!D52))</f>
+        <v/>
+      </c>
+      <c r="K53" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L53" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M53" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54" s="36" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" s="45">
+        <f>IF(Data!D54="""",NA(),Data!D54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="45">
+        <f>IF(OR(Data!D54="""",Data!D53=""""),NA(),ABS(Data!D54-Data!D53))</f>
+        <v/>
+      </c>
+      <c r="K54" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
+        <v/>
+      </c>
+      <c r="L54" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
+        <v/>
+      </c>
+      <c r="M54" s="45">
+        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B46:D46"/>
+  <mergeCells count="5">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="H3:M3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3543,934 +5314,934 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>Tₘ</t>
         </is>
       </c>
-      <c r="F3" s="34" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>LSL</t>
         </is>
       </c>
-      <c r="G3" s="34" t="inlineStr">
+      <c r="G3" s="35" t="inlineStr">
         <is>
           <t>USL</t>
         </is>
       </c>
-      <c r="H3" s="34" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>x̄</t>
         </is>
       </c>
-      <c r="I3" s="34" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>σ</t>
         </is>
       </c>
-      <c r="J3" s="34" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="K3" s="34" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>Cp</t>
         </is>
       </c>
-      <c r="L3" s="34" t="inlineStr">
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>Cpk</t>
         </is>
       </c>
-      <c r="M3" s="34" t="inlineStr">
+      <c r="M3" s="35" t="inlineStr">
         <is>
           <t>PPM Total</t>
         </is>
       </c>
-      <c r="N3" s="34" t="inlineStr">
+      <c r="N3" s="35" t="inlineStr">
         <is>
           <t>Shift (Δ)</t>
         </is>
       </c>
-      <c r="O3" s="34" t="inlineStr">
+      <c r="O3" s="35" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="45">
+      <c r="B4" s="48">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="49">
         <f>Analysis!C5</f>
         <v/>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="49">
         <f>Analysis!C10</f>
         <v/>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="50">
         <f>Analysis!C6</f>
         <v/>
       </c>
-      <c r="F4" s="47">
+      <c r="F4" s="50">
         <f>Analysis!C7</f>
         <v/>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="50">
         <f>Analysis!C8</f>
         <v/>
       </c>
-      <c r="H4" s="48">
+      <c r="H4" s="51">
         <f>Analysis!G9</f>
         <v/>
       </c>
-      <c r="I4" s="48">
+      <c r="I4" s="51">
         <f>Analysis!G10</f>
         <v/>
       </c>
-      <c r="J4" s="49">
+      <c r="J4" s="52">
         <f>Analysis!G11</f>
         <v/>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="50">
         <f>Analysis!G17</f>
         <v/>
       </c>
-      <c r="L4" s="47">
+      <c r="L4" s="50">
         <f>Analysis!G18</f>
         <v/>
       </c>
-      <c r="M4" s="50">
+      <c r="M4" s="53">
         <f>Analysis!J10</f>
         <v/>
       </c>
-      <c r="N4" s="47">
+      <c r="N4" s="50">
         <f>Analysis!G19</f>
         <v/>
       </c>
-      <c r="O4" s="46">
+      <c r="O4" s="49">
         <f>Analysis!B28</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="38" t="n"/>
-      <c r="C5" s="38" t="n"/>
-      <c r="D5" s="38" t="n"/>
-      <c r="E5" s="38" t="n"/>
-      <c r="F5" s="38" t="n"/>
-      <c r="G5" s="38" t="n"/>
-      <c r="H5" s="38" t="n"/>
-      <c r="I5" s="38" t="n"/>
-      <c r="J5" s="38" t="n"/>
-      <c r="K5" s="38" t="n"/>
-      <c r="L5" s="38" t="n"/>
-      <c r="M5" s="38" t="n"/>
-      <c r="N5" s="38" t="n"/>
-      <c r="O5" s="38" t="n"/>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="39" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="39" t="n"/>
+      <c r="H5" s="39" t="n"/>
+      <c r="I5" s="39" t="n"/>
+      <c r="J5" s="39" t="n"/>
+      <c r="K5" s="39" t="n"/>
+      <c r="L5" s="39" t="n"/>
+      <c r="M5" s="39" t="n"/>
+      <c r="N5" s="39" t="n"/>
+      <c r="O5" s="39" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="36" t="n"/>
-      <c r="C6" s="36" t="n"/>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
-      <c r="F6" s="36" t="n"/>
-      <c r="G6" s="36" t="n"/>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n"/>
-      <c r="J6" s="36" t="n"/>
-      <c r="K6" s="36" t="n"/>
-      <c r="L6" s="36" t="n"/>
-      <c r="M6" s="36" t="n"/>
-      <c r="N6" s="36" t="n"/>
-      <c r="O6" s="36" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="37" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="37" t="n"/>
+      <c r="H6" s="37" t="n"/>
+      <c r="I6" s="37" t="n"/>
+      <c r="J6" s="37" t="n"/>
+      <c r="K6" s="37" t="n"/>
+      <c r="L6" s="37" t="n"/>
+      <c r="M6" s="37" t="n"/>
+      <c r="N6" s="37" t="n"/>
+      <c r="O6" s="37" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="38" t="n"/>
-      <c r="C7" s="38" t="n"/>
-      <c r="D7" s="38" t="n"/>
-      <c r="E7" s="38" t="n"/>
-      <c r="F7" s="38" t="n"/>
-      <c r="G7" s="38" t="n"/>
-      <c r="H7" s="38" t="n"/>
-      <c r="I7" s="38" t="n"/>
-      <c r="J7" s="38" t="n"/>
-      <c r="K7" s="38" t="n"/>
-      <c r="L7" s="38" t="n"/>
-      <c r="M7" s="38" t="n"/>
-      <c r="N7" s="38" t="n"/>
-      <c r="O7" s="38" t="n"/>
+      <c r="B7" s="39" t="n"/>
+      <c r="C7" s="39" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="39" t="n"/>
+      <c r="H7" s="39" t="n"/>
+      <c r="I7" s="39" t="n"/>
+      <c r="J7" s="39" t="n"/>
+      <c r="K7" s="39" t="n"/>
+      <c r="L7" s="39" t="n"/>
+      <c r="M7" s="39" t="n"/>
+      <c r="N7" s="39" t="n"/>
+      <c r="O7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="36" t="n"/>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="36" t="n"/>
-      <c r="K8" s="36" t="n"/>
-      <c r="L8" s="36" t="n"/>
-      <c r="M8" s="36" t="n"/>
-      <c r="N8" s="36" t="n"/>
-      <c r="O8" s="36" t="n"/>
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="37" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="37" t="n"/>
+      <c r="H8" s="37" t="n"/>
+      <c r="I8" s="37" t="n"/>
+      <c r="J8" s="37" t="n"/>
+      <c r="K8" s="37" t="n"/>
+      <c r="L8" s="37" t="n"/>
+      <c r="M8" s="37" t="n"/>
+      <c r="N8" s="37" t="n"/>
+      <c r="O8" s="37" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="38" t="n"/>
-      <c r="C9" s="38" t="n"/>
-      <c r="D9" s="38" t="n"/>
-      <c r="E9" s="38" t="n"/>
-      <c r="F9" s="38" t="n"/>
-      <c r="G9" s="38" t="n"/>
-      <c r="H9" s="38" t="n"/>
-      <c r="I9" s="38" t="n"/>
-      <c r="J9" s="38" t="n"/>
-      <c r="K9" s="38" t="n"/>
-      <c r="L9" s="38" t="n"/>
-      <c r="M9" s="38" t="n"/>
-      <c r="N9" s="38" t="n"/>
-      <c r="O9" s="38" t="n"/>
+      <c r="B9" s="39" t="n"/>
+      <c r="C9" s="39" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
+      <c r="H9" s="39" t="n"/>
+      <c r="I9" s="39" t="n"/>
+      <c r="J9" s="39" t="n"/>
+      <c r="K9" s="39" t="n"/>
+      <c r="L9" s="39" t="n"/>
+      <c r="M9" s="39" t="n"/>
+      <c r="N9" s="39" t="n"/>
+      <c r="O9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="36" t="n"/>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
-      <c r="G10" s="36" t="n"/>
-      <c r="H10" s="36" t="n"/>
-      <c r="I10" s="36" t="n"/>
-      <c r="J10" s="36" t="n"/>
-      <c r="K10" s="36" t="n"/>
-      <c r="L10" s="36" t="n"/>
-      <c r="M10" s="36" t="n"/>
-      <c r="N10" s="36" t="n"/>
-      <c r="O10" s="36" t="n"/>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="37" t="n"/>
+      <c r="H10" s="37" t="n"/>
+      <c r="I10" s="37" t="n"/>
+      <c r="J10" s="37" t="n"/>
+      <c r="K10" s="37" t="n"/>
+      <c r="L10" s="37" t="n"/>
+      <c r="M10" s="37" t="n"/>
+      <c r="N10" s="37" t="n"/>
+      <c r="O10" s="37" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="38" t="n"/>
-      <c r="F11" s="38" t="n"/>
-      <c r="G11" s="38" t="n"/>
-      <c r="H11" s="38" t="n"/>
-      <c r="I11" s="38" t="n"/>
-      <c r="J11" s="38" t="n"/>
-      <c r="K11" s="38" t="n"/>
-      <c r="L11" s="38" t="n"/>
-      <c r="M11" s="38" t="n"/>
-      <c r="N11" s="38" t="n"/>
-      <c r="O11" s="38" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
+      <c r="H11" s="39" t="n"/>
+      <c r="I11" s="39" t="n"/>
+      <c r="J11" s="39" t="n"/>
+      <c r="K11" s="39" t="n"/>
+      <c r="L11" s="39" t="n"/>
+      <c r="M11" s="39" t="n"/>
+      <c r="N11" s="39" t="n"/>
+      <c r="O11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
-      <c r="F12" s="36" t="n"/>
-      <c r="G12" s="36" t="n"/>
-      <c r="H12" s="36" t="n"/>
-      <c r="I12" s="36" t="n"/>
-      <c r="J12" s="36" t="n"/>
-      <c r="K12" s="36" t="n"/>
-      <c r="L12" s="36" t="n"/>
-      <c r="M12" s="36" t="n"/>
-      <c r="N12" s="36" t="n"/>
-      <c r="O12" s="36" t="n"/>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="37" t="n"/>
+      <c r="H12" s="37" t="n"/>
+      <c r="I12" s="37" t="n"/>
+      <c r="J12" s="37" t="n"/>
+      <c r="K12" s="37" t="n"/>
+      <c r="L12" s="37" t="n"/>
+      <c r="M12" s="37" t="n"/>
+      <c r="N12" s="37" t="n"/>
+      <c r="O12" s="37" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="38" t="n"/>
-      <c r="C13" s="38" t="n"/>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="38" t="n"/>
-      <c r="F13" s="38" t="n"/>
-      <c r="G13" s="38" t="n"/>
-      <c r="H13" s="38" t="n"/>
-      <c r="I13" s="38" t="n"/>
-      <c r="J13" s="38" t="n"/>
-      <c r="K13" s="38" t="n"/>
-      <c r="L13" s="38" t="n"/>
-      <c r="M13" s="38" t="n"/>
-      <c r="N13" s="38" t="n"/>
-      <c r="O13" s="38" t="n"/>
+      <c r="B13" s="39" t="n"/>
+      <c r="C13" s="39" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="39" t="n"/>
+      <c r="H13" s="39" t="n"/>
+      <c r="I13" s="39" t="n"/>
+      <c r="J13" s="39" t="n"/>
+      <c r="K13" s="39" t="n"/>
+      <c r="L13" s="39" t="n"/>
+      <c r="M13" s="39" t="n"/>
+      <c r="N13" s="39" t="n"/>
+      <c r="O13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="36" t="n"/>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
-      <c r="F14" s="36" t="n"/>
-      <c r="G14" s="36" t="n"/>
-      <c r="H14" s="36" t="n"/>
-      <c r="I14" s="36" t="n"/>
-      <c r="J14" s="36" t="n"/>
-      <c r="K14" s="36" t="n"/>
-      <c r="L14" s="36" t="n"/>
-      <c r="M14" s="36" t="n"/>
-      <c r="N14" s="36" t="n"/>
-      <c r="O14" s="36" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="37" t="n"/>
+      <c r="H14" s="37" t="n"/>
+      <c r="I14" s="37" t="n"/>
+      <c r="J14" s="37" t="n"/>
+      <c r="K14" s="37" t="n"/>
+      <c r="L14" s="37" t="n"/>
+      <c r="M14" s="37" t="n"/>
+      <c r="N14" s="37" t="n"/>
+      <c r="O14" s="37" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="38" t="n"/>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="38" t="n"/>
-      <c r="F15" s="38" t="n"/>
-      <c r="G15" s="38" t="n"/>
-      <c r="H15" s="38" t="n"/>
-      <c r="I15" s="38" t="n"/>
-      <c r="J15" s="38" t="n"/>
-      <c r="K15" s="38" t="n"/>
-      <c r="L15" s="38" t="n"/>
-      <c r="M15" s="38" t="n"/>
-      <c r="N15" s="38" t="n"/>
-      <c r="O15" s="38" t="n"/>
+      <c r="B15" s="39" t="n"/>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="39" t="n"/>
+      <c r="H15" s="39" t="n"/>
+      <c r="I15" s="39" t="n"/>
+      <c r="J15" s="39" t="n"/>
+      <c r="K15" s="39" t="n"/>
+      <c r="L15" s="39" t="n"/>
+      <c r="M15" s="39" t="n"/>
+      <c r="N15" s="39" t="n"/>
+      <c r="O15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="36" t="n"/>
-      <c r="C16" s="36" t="n"/>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
-      <c r="J16" s="36" t="n"/>
-      <c r="K16" s="36" t="n"/>
-      <c r="L16" s="36" t="n"/>
-      <c r="M16" s="36" t="n"/>
-      <c r="N16" s="36" t="n"/>
-      <c r="O16" s="36" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="37" t="n"/>
+      <c r="H16" s="37" t="n"/>
+      <c r="I16" s="37" t="n"/>
+      <c r="J16" s="37" t="n"/>
+      <c r="K16" s="37" t="n"/>
+      <c r="L16" s="37" t="n"/>
+      <c r="M16" s="37" t="n"/>
+      <c r="N16" s="37" t="n"/>
+      <c r="O16" s="37" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="38" t="n"/>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="38" t="n"/>
-      <c r="F17" s="38" t="n"/>
-      <c r="G17" s="38" t="n"/>
-      <c r="H17" s="38" t="n"/>
-      <c r="I17" s="38" t="n"/>
-      <c r="J17" s="38" t="n"/>
-      <c r="K17" s="38" t="n"/>
-      <c r="L17" s="38" t="n"/>
-      <c r="M17" s="38" t="n"/>
-      <c r="N17" s="38" t="n"/>
-      <c r="O17" s="38" t="n"/>
+      <c r="B17" s="39" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
+      <c r="H17" s="39" t="n"/>
+      <c r="I17" s="39" t="n"/>
+      <c r="J17" s="39" t="n"/>
+      <c r="K17" s="39" t="n"/>
+      <c r="L17" s="39" t="n"/>
+      <c r="M17" s="39" t="n"/>
+      <c r="N17" s="39" t="n"/>
+      <c r="O17" s="39" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="36" t="n"/>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
-      <c r="I18" s="36" t="n"/>
-      <c r="J18" s="36" t="n"/>
-      <c r="K18" s="36" t="n"/>
-      <c r="L18" s="36" t="n"/>
-      <c r="M18" s="36" t="n"/>
-      <c r="N18" s="36" t="n"/>
-      <c r="O18" s="36" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="37" t="n"/>
+      <c r="H18" s="37" t="n"/>
+      <c r="I18" s="37" t="n"/>
+      <c r="J18" s="37" t="n"/>
+      <c r="K18" s="37" t="n"/>
+      <c r="L18" s="37" t="n"/>
+      <c r="M18" s="37" t="n"/>
+      <c r="N18" s="37" t="n"/>
+      <c r="O18" s="37" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="38" t="n"/>
-      <c r="F19" s="38" t="n"/>
-      <c r="G19" s="38" t="n"/>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="38" t="n"/>
-      <c r="J19" s="38" t="n"/>
-      <c r="K19" s="38" t="n"/>
-      <c r="L19" s="38" t="n"/>
-      <c r="M19" s="38" t="n"/>
-      <c r="N19" s="38" t="n"/>
-      <c r="O19" s="38" t="n"/>
+      <c r="B19" s="39" t="n"/>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
+      <c r="H19" s="39" t="n"/>
+      <c r="I19" s="39" t="n"/>
+      <c r="J19" s="39" t="n"/>
+      <c r="K19" s="39" t="n"/>
+      <c r="L19" s="39" t="n"/>
+      <c r="M19" s="39" t="n"/>
+      <c r="N19" s="39" t="n"/>
+      <c r="O19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="36" t="n"/>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="36" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="37" t="n"/>
+      <c r="H20" s="37" t="n"/>
+      <c r="I20" s="37" t="n"/>
+      <c r="J20" s="37" t="n"/>
+      <c r="K20" s="37" t="n"/>
+      <c r="L20" s="37" t="n"/>
+      <c r="M20" s="37" t="n"/>
+      <c r="N20" s="37" t="n"/>
+      <c r="O20" s="37" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="38" t="n"/>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="38" t="n"/>
-      <c r="H21" s="38" t="n"/>
-      <c r="I21" s="38" t="n"/>
-      <c r="J21" s="38" t="n"/>
-      <c r="K21" s="38" t="n"/>
-      <c r="L21" s="38" t="n"/>
-      <c r="M21" s="38" t="n"/>
-      <c r="N21" s="38" t="n"/>
-      <c r="O21" s="38" t="n"/>
+      <c r="B21" s="39" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="39" t="n"/>
+      <c r="K21" s="39" t="n"/>
+      <c r="L21" s="39" t="n"/>
+      <c r="M21" s="39" t="n"/>
+      <c r="N21" s="39" t="n"/>
+      <c r="O21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="36" t="n"/>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="36" t="n"/>
-      <c r="G22" s="36" t="n"/>
-      <c r="H22" s="36" t="n"/>
-      <c r="I22" s="36" t="n"/>
-      <c r="J22" s="36" t="n"/>
-      <c r="K22" s="36" t="n"/>
-      <c r="L22" s="36" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="36" t="n"/>
-      <c r="O22" s="36" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="37" t="n"/>
+      <c r="H22" s="37" t="n"/>
+      <c r="I22" s="37" t="n"/>
+      <c r="J22" s="37" t="n"/>
+      <c r="K22" s="37" t="n"/>
+      <c r="L22" s="37" t="n"/>
+      <c r="M22" s="37" t="n"/>
+      <c r="N22" s="37" t="n"/>
+      <c r="O22" s="37" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="38" t="n"/>
-      <c r="D23" s="38" t="n"/>
-      <c r="E23" s="38" t="n"/>
-      <c r="F23" s="38" t="n"/>
-      <c r="G23" s="38" t="n"/>
-      <c r="H23" s="38" t="n"/>
-      <c r="I23" s="38" t="n"/>
-      <c r="J23" s="38" t="n"/>
-      <c r="K23" s="38" t="n"/>
-      <c r="L23" s="38" t="n"/>
-      <c r="M23" s="38" t="n"/>
-      <c r="N23" s="38" t="n"/>
-      <c r="O23" s="38" t="n"/>
+      <c r="B23" s="39" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+      <c r="H23" s="39" t="n"/>
+      <c r="I23" s="39" t="n"/>
+      <c r="J23" s="39" t="n"/>
+      <c r="K23" s="39" t="n"/>
+      <c r="L23" s="39" t="n"/>
+      <c r="M23" s="39" t="n"/>
+      <c r="N23" s="39" t="n"/>
+      <c r="O23" s="39" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="36" t="n"/>
-      <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
-      <c r="M24" s="36" t="n"/>
-      <c r="N24" s="36" t="n"/>
-      <c r="O24" s="36" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="37" t="n"/>
+      <c r="H24" s="37" t="n"/>
+      <c r="I24" s="37" t="n"/>
+      <c r="J24" s="37" t="n"/>
+      <c r="K24" s="37" t="n"/>
+      <c r="L24" s="37" t="n"/>
+      <c r="M24" s="37" t="n"/>
+      <c r="N24" s="37" t="n"/>
+      <c r="O24" s="37" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="38" t="n"/>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="38" t="n"/>
-      <c r="E25" s="38" t="n"/>
-      <c r="F25" s="38" t="n"/>
-      <c r="G25" s="38" t="n"/>
-      <c r="H25" s="38" t="n"/>
-      <c r="I25" s="38" t="n"/>
-      <c r="J25" s="38" t="n"/>
-      <c r="K25" s="38" t="n"/>
-      <c r="L25" s="38" t="n"/>
-      <c r="M25" s="38" t="n"/>
-      <c r="N25" s="38" t="n"/>
-      <c r="O25" s="38" t="n"/>
+      <c r="B25" s="39" t="n"/>
+      <c r="C25" s="39" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+      <c r="H25" s="39" t="n"/>
+      <c r="I25" s="39" t="n"/>
+      <c r="J25" s="39" t="n"/>
+      <c r="K25" s="39" t="n"/>
+      <c r="L25" s="39" t="n"/>
+      <c r="M25" s="39" t="n"/>
+      <c r="N25" s="39" t="n"/>
+      <c r="O25" s="39" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="36" t="n"/>
-      <c r="C26" s="36" t="n"/>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="36" t="n"/>
-      <c r="G26" s="36" t="n"/>
-      <c r="H26" s="36" t="n"/>
-      <c r="I26" s="36" t="n"/>
-      <c r="J26" s="36" t="n"/>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="36" t="n"/>
-      <c r="M26" s="36" t="n"/>
-      <c r="N26" s="36" t="n"/>
-      <c r="O26" s="36" t="n"/>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="37" t="n"/>
+      <c r="H26" s="37" t="n"/>
+      <c r="I26" s="37" t="n"/>
+      <c r="J26" s="37" t="n"/>
+      <c r="K26" s="37" t="n"/>
+      <c r="L26" s="37" t="n"/>
+      <c r="M26" s="37" t="n"/>
+      <c r="N26" s="37" t="n"/>
+      <c r="O26" s="37" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="38" t="n"/>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="38" t="n"/>
-      <c r="E27" s="38" t="n"/>
-      <c r="F27" s="38" t="n"/>
-      <c r="G27" s="38" t="n"/>
-      <c r="H27" s="38" t="n"/>
-      <c r="I27" s="38" t="n"/>
-      <c r="J27" s="38" t="n"/>
-      <c r="K27" s="38" t="n"/>
-      <c r="L27" s="38" t="n"/>
-      <c r="M27" s="38" t="n"/>
-      <c r="N27" s="38" t="n"/>
-      <c r="O27" s="38" t="n"/>
+      <c r="B27" s="39" t="n"/>
+      <c r="C27" s="39" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+      <c r="H27" s="39" t="n"/>
+      <c r="I27" s="39" t="n"/>
+      <c r="J27" s="39" t="n"/>
+      <c r="K27" s="39" t="n"/>
+      <c r="L27" s="39" t="n"/>
+      <c r="M27" s="39" t="n"/>
+      <c r="N27" s="39" t="n"/>
+      <c r="O27" s="39" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="n"/>
-      <c r="C28" s="36" t="n"/>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="36" t="n"/>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="36" t="n"/>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="36" t="n"/>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="36" t="n"/>
-      <c r="M28" s="36" t="n"/>
-      <c r="N28" s="36" t="n"/>
-      <c r="O28" s="36" t="n"/>
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="37" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="37" t="n"/>
+      <c r="H28" s="37" t="n"/>
+      <c r="I28" s="37" t="n"/>
+      <c r="J28" s="37" t="n"/>
+      <c r="K28" s="37" t="n"/>
+      <c r="L28" s="37" t="n"/>
+      <c r="M28" s="37" t="n"/>
+      <c r="N28" s="37" t="n"/>
+      <c r="O28" s="37" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="38" t="n"/>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="38" t="n"/>
-      <c r="E29" s="38" t="n"/>
-      <c r="F29" s="38" t="n"/>
-      <c r="G29" s="38" t="n"/>
-      <c r="H29" s="38" t="n"/>
-      <c r="I29" s="38" t="n"/>
-      <c r="J29" s="38" t="n"/>
-      <c r="K29" s="38" t="n"/>
-      <c r="L29" s="38" t="n"/>
-      <c r="M29" s="38" t="n"/>
-      <c r="N29" s="38" t="n"/>
-      <c r="O29" s="38" t="n"/>
+      <c r="B29" s="39" t="n"/>
+      <c r="C29" s="39" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="39" t="n"/>
+      <c r="H29" s="39" t="n"/>
+      <c r="I29" s="39" t="n"/>
+      <c r="J29" s="39" t="n"/>
+      <c r="K29" s="39" t="n"/>
+      <c r="L29" s="39" t="n"/>
+      <c r="M29" s="39" t="n"/>
+      <c r="N29" s="39" t="n"/>
+      <c r="O29" s="39" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="36" t="n"/>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="36" t="n"/>
-      <c r="K30" s="36" t="n"/>
-      <c r="L30" s="36" t="n"/>
-      <c r="M30" s="36" t="n"/>
-      <c r="N30" s="36" t="n"/>
-      <c r="O30" s="36" t="n"/>
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="37" t="n"/>
+      <c r="G30" s="37" t="n"/>
+      <c r="H30" s="37" t="n"/>
+      <c r="I30" s="37" t="n"/>
+      <c r="J30" s="37" t="n"/>
+      <c r="K30" s="37" t="n"/>
+      <c r="L30" s="37" t="n"/>
+      <c r="M30" s="37" t="n"/>
+      <c r="N30" s="37" t="n"/>
+      <c r="O30" s="37" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="38" t="n"/>
-      <c r="E31" s="38" t="n"/>
-      <c r="F31" s="38" t="n"/>
-      <c r="G31" s="38" t="n"/>
-      <c r="H31" s="38" t="n"/>
-      <c r="I31" s="38" t="n"/>
-      <c r="J31" s="38" t="n"/>
-      <c r="K31" s="38" t="n"/>
-      <c r="L31" s="38" t="n"/>
-      <c r="M31" s="38" t="n"/>
-      <c r="N31" s="38" t="n"/>
-      <c r="O31" s="38" t="n"/>
+      <c r="B31" s="39" t="n"/>
+      <c r="C31" s="39" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="39" t="n"/>
+      <c r="H31" s="39" t="n"/>
+      <c r="I31" s="39" t="n"/>
+      <c r="J31" s="39" t="n"/>
+      <c r="K31" s="39" t="n"/>
+      <c r="L31" s="39" t="n"/>
+      <c r="M31" s="39" t="n"/>
+      <c r="N31" s="39" t="n"/>
+      <c r="O31" s="39" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="36" t="n"/>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="36" t="n"/>
-      <c r="I32" s="36" t="n"/>
-      <c r="J32" s="36" t="n"/>
-      <c r="K32" s="36" t="n"/>
-      <c r="L32" s="36" t="n"/>
-      <c r="M32" s="36" t="n"/>
-      <c r="N32" s="36" t="n"/>
-      <c r="O32" s="36" t="n"/>
+      <c r="B32" s="37" t="n"/>
+      <c r="C32" s="37" t="n"/>
+      <c r="D32" s="37" t="n"/>
+      <c r="E32" s="37" t="n"/>
+      <c r="F32" s="37" t="n"/>
+      <c r="G32" s="37" t="n"/>
+      <c r="H32" s="37" t="n"/>
+      <c r="I32" s="37" t="n"/>
+      <c r="J32" s="37" t="n"/>
+      <c r="K32" s="37" t="n"/>
+      <c r="L32" s="37" t="n"/>
+      <c r="M32" s="37" t="n"/>
+      <c r="N32" s="37" t="n"/>
+      <c r="O32" s="37" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="38" t="n"/>
-      <c r="C33" s="38" t="n"/>
-      <c r="D33" s="38" t="n"/>
-      <c r="E33" s="38" t="n"/>
-      <c r="F33" s="38" t="n"/>
-      <c r="G33" s="38" t="n"/>
-      <c r="H33" s="38" t="n"/>
-      <c r="I33" s="38" t="n"/>
-      <c r="J33" s="38" t="n"/>
-      <c r="K33" s="38" t="n"/>
-      <c r="L33" s="38" t="n"/>
-      <c r="M33" s="38" t="n"/>
-      <c r="N33" s="38" t="n"/>
-      <c r="O33" s="38" t="n"/>
+      <c r="B33" s="39" t="n"/>
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="39" t="n"/>
+      <c r="H33" s="39" t="n"/>
+      <c r="I33" s="39" t="n"/>
+      <c r="J33" s="39" t="n"/>
+      <c r="K33" s="39" t="n"/>
+      <c r="L33" s="39" t="n"/>
+      <c r="M33" s="39" t="n"/>
+      <c r="N33" s="39" t="n"/>
+      <c r="O33" s="39" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="36" t="n"/>
-      <c r="C34" s="36" t="n"/>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="36" t="n"/>
-      <c r="I34" s="36" t="n"/>
-      <c r="J34" s="36" t="n"/>
-      <c r="K34" s="36" t="n"/>
-      <c r="L34" s="36" t="n"/>
-      <c r="M34" s="36" t="n"/>
-      <c r="N34" s="36" t="n"/>
-      <c r="O34" s="36" t="n"/>
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="37" t="n"/>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="37" t="n"/>
+      <c r="G34" s="37" t="n"/>
+      <c r="H34" s="37" t="n"/>
+      <c r="I34" s="37" t="n"/>
+      <c r="J34" s="37" t="n"/>
+      <c r="K34" s="37" t="n"/>
+      <c r="L34" s="37" t="n"/>
+      <c r="M34" s="37" t="n"/>
+      <c r="N34" s="37" t="n"/>
+      <c r="O34" s="37" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="38" t="n"/>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="38" t="n"/>
-      <c r="E35" s="38" t="n"/>
-      <c r="F35" s="38" t="n"/>
-      <c r="G35" s="38" t="n"/>
-      <c r="H35" s="38" t="n"/>
-      <c r="I35" s="38" t="n"/>
-      <c r="J35" s="38" t="n"/>
-      <c r="K35" s="38" t="n"/>
-      <c r="L35" s="38" t="n"/>
-      <c r="M35" s="38" t="n"/>
-      <c r="N35" s="38" t="n"/>
-      <c r="O35" s="38" t="n"/>
+      <c r="B35" s="39" t="n"/>
+      <c r="C35" s="39" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="39" t="n"/>
+      <c r="H35" s="39" t="n"/>
+      <c r="I35" s="39" t="n"/>
+      <c r="J35" s="39" t="n"/>
+      <c r="K35" s="39" t="n"/>
+      <c r="L35" s="39" t="n"/>
+      <c r="M35" s="39" t="n"/>
+      <c r="N35" s="39" t="n"/>
+      <c r="O35" s="39" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="36" t="n"/>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="36" t="n"/>
-      <c r="K36" s="36" t="n"/>
-      <c r="L36" s="36" t="n"/>
-      <c r="M36" s="36" t="n"/>
-      <c r="N36" s="36" t="n"/>
-      <c r="O36" s="36" t="n"/>
+      <c r="B36" s="37" t="n"/>
+      <c r="C36" s="37" t="n"/>
+      <c r="D36" s="37" t="n"/>
+      <c r="E36" s="37" t="n"/>
+      <c r="F36" s="37" t="n"/>
+      <c r="G36" s="37" t="n"/>
+      <c r="H36" s="37" t="n"/>
+      <c r="I36" s="37" t="n"/>
+      <c r="J36" s="37" t="n"/>
+      <c r="K36" s="37" t="n"/>
+      <c r="L36" s="37" t="n"/>
+      <c r="M36" s="37" t="n"/>
+      <c r="N36" s="37" t="n"/>
+      <c r="O36" s="37" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="38" t="n"/>
-      <c r="C37" s="38" t="n"/>
-      <c r="D37" s="38" t="n"/>
-      <c r="E37" s="38" t="n"/>
-      <c r="F37" s="38" t="n"/>
-      <c r="G37" s="38" t="n"/>
-      <c r="H37" s="38" t="n"/>
-      <c r="I37" s="38" t="n"/>
-      <c r="J37" s="38" t="n"/>
-      <c r="K37" s="38" t="n"/>
-      <c r="L37" s="38" t="n"/>
-      <c r="M37" s="38" t="n"/>
-      <c r="N37" s="38" t="n"/>
-      <c r="O37" s="38" t="n"/>
+      <c r="B37" s="39" t="n"/>
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="39" t="n"/>
+      <c r="H37" s="39" t="n"/>
+      <c r="I37" s="39" t="n"/>
+      <c r="J37" s="39" t="n"/>
+      <c r="K37" s="39" t="n"/>
+      <c r="L37" s="39" t="n"/>
+      <c r="M37" s="39" t="n"/>
+      <c r="N37" s="39" t="n"/>
+      <c r="O37" s="39" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="36" t="n"/>
-      <c r="C38" s="36" t="n"/>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="36" t="n"/>
-      <c r="J38" s="36" t="n"/>
-      <c r="K38" s="36" t="n"/>
-      <c r="L38" s="36" t="n"/>
-      <c r="M38" s="36" t="n"/>
-      <c r="N38" s="36" t="n"/>
-      <c r="O38" s="36" t="n"/>
+      <c r="B38" s="37" t="n"/>
+      <c r="C38" s="37" t="n"/>
+      <c r="D38" s="37" t="n"/>
+      <c r="E38" s="37" t="n"/>
+      <c r="F38" s="37" t="n"/>
+      <c r="G38" s="37" t="n"/>
+      <c r="H38" s="37" t="n"/>
+      <c r="I38" s="37" t="n"/>
+      <c r="J38" s="37" t="n"/>
+      <c r="K38" s="37" t="n"/>
+      <c r="L38" s="37" t="n"/>
+      <c r="M38" s="37" t="n"/>
+      <c r="N38" s="37" t="n"/>
+      <c r="O38" s="37" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="38" t="n"/>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="38" t="n"/>
-      <c r="G39" s="38" t="n"/>
-      <c r="H39" s="38" t="n"/>
-      <c r="I39" s="38" t="n"/>
-      <c r="J39" s="38" t="n"/>
-      <c r="K39" s="38" t="n"/>
-      <c r="L39" s="38" t="n"/>
-      <c r="M39" s="38" t="n"/>
-      <c r="N39" s="38" t="n"/>
-      <c r="O39" s="38" t="n"/>
+      <c r="B39" s="39" t="n"/>
+      <c r="C39" s="39" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="39" t="n"/>
+      <c r="H39" s="39" t="n"/>
+      <c r="I39" s="39" t="n"/>
+      <c r="J39" s="39" t="n"/>
+      <c r="K39" s="39" t="n"/>
+      <c r="L39" s="39" t="n"/>
+      <c r="M39" s="39" t="n"/>
+      <c r="N39" s="39" t="n"/>
+      <c r="O39" s="39" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="36" t="n"/>
-      <c r="C40" s="36" t="n"/>
-      <c r="D40" s="36" t="n"/>
-      <c r="E40" s="36" t="n"/>
-      <c r="F40" s="36" t="n"/>
-      <c r="G40" s="36" t="n"/>
-      <c r="H40" s="36" t="n"/>
-      <c r="I40" s="36" t="n"/>
-      <c r="J40" s="36" t="n"/>
-      <c r="K40" s="36" t="n"/>
-      <c r="L40" s="36" t="n"/>
-      <c r="M40" s="36" t="n"/>
-      <c r="N40" s="36" t="n"/>
-      <c r="O40" s="36" t="n"/>
+      <c r="B40" s="37" t="n"/>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="37" t="n"/>
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="37" t="n"/>
+      <c r="G40" s="37" t="n"/>
+      <c r="H40" s="37" t="n"/>
+      <c r="I40" s="37" t="n"/>
+      <c r="J40" s="37" t="n"/>
+      <c r="K40" s="37" t="n"/>
+      <c r="L40" s="37" t="n"/>
+      <c r="M40" s="37" t="n"/>
+      <c r="N40" s="37" t="n"/>
+      <c r="O40" s="37" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="38" t="n"/>
-      <c r="C41" s="38" t="n"/>
-      <c r="D41" s="38" t="n"/>
-      <c r="E41" s="38" t="n"/>
-      <c r="F41" s="38" t="n"/>
-      <c r="G41" s="38" t="n"/>
-      <c r="H41" s="38" t="n"/>
-      <c r="I41" s="38" t="n"/>
-      <c r="J41" s="38" t="n"/>
-      <c r="K41" s="38" t="n"/>
-      <c r="L41" s="38" t="n"/>
-      <c r="M41" s="38" t="n"/>
-      <c r="N41" s="38" t="n"/>
-      <c r="O41" s="38" t="n"/>
+      <c r="B41" s="39" t="n"/>
+      <c r="C41" s="39" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="39" t="n"/>
+      <c r="H41" s="39" t="n"/>
+      <c r="I41" s="39" t="n"/>
+      <c r="J41" s="39" t="n"/>
+      <c r="K41" s="39" t="n"/>
+      <c r="L41" s="39" t="n"/>
+      <c r="M41" s="39" t="n"/>
+      <c r="N41" s="39" t="n"/>
+      <c r="O41" s="39" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="36" t="n"/>
-      <c r="C42" s="36" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="36" t="n"/>
-      <c r="F42" s="36" t="n"/>
-      <c r="G42" s="36" t="n"/>
-      <c r="H42" s="36" t="n"/>
-      <c r="I42" s="36" t="n"/>
-      <c r="J42" s="36" t="n"/>
-      <c r="K42" s="36" t="n"/>
-      <c r="L42" s="36" t="n"/>
-      <c r="M42" s="36" t="n"/>
-      <c r="N42" s="36" t="n"/>
-      <c r="O42" s="36" t="n"/>
+      <c r="B42" s="37" t="n"/>
+      <c r="C42" s="37" t="n"/>
+      <c r="D42" s="37" t="n"/>
+      <c r="E42" s="37" t="n"/>
+      <c r="F42" s="37" t="n"/>
+      <c r="G42" s="37" t="n"/>
+      <c r="H42" s="37" t="n"/>
+      <c r="I42" s="37" t="n"/>
+      <c r="J42" s="37" t="n"/>
+      <c r="K42" s="37" t="n"/>
+      <c r="L42" s="37" t="n"/>
+      <c r="M42" s="37" t="n"/>
+      <c r="N42" s="37" t="n"/>
+      <c r="O42" s="37" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="38" t="n"/>
-      <c r="C43" s="38" t="n"/>
-      <c r="D43" s="38" t="n"/>
-      <c r="E43" s="38" t="n"/>
-      <c r="F43" s="38" t="n"/>
-      <c r="G43" s="38" t="n"/>
-      <c r="H43" s="38" t="n"/>
-      <c r="I43" s="38" t="n"/>
-      <c r="J43" s="38" t="n"/>
-      <c r="K43" s="38" t="n"/>
-      <c r="L43" s="38" t="n"/>
-      <c r="M43" s="38" t="n"/>
-      <c r="N43" s="38" t="n"/>
-      <c r="O43" s="38" t="n"/>
+      <c r="B43" s="39" t="n"/>
+      <c r="C43" s="39" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="39" t="n"/>
+      <c r="H43" s="39" t="n"/>
+      <c r="I43" s="39" t="n"/>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="39" t="n"/>
+      <c r="L43" s="39" t="n"/>
+      <c r="M43" s="39" t="n"/>
+      <c r="N43" s="39" t="n"/>
+      <c r="O43" s="39" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="36" t="n"/>
-      <c r="C44" s="36" t="n"/>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="36" t="n"/>
-      <c r="F44" s="36" t="n"/>
-      <c r="G44" s="36" t="n"/>
-      <c r="H44" s="36" t="n"/>
-      <c r="I44" s="36" t="n"/>
-      <c r="J44" s="36" t="n"/>
-      <c r="K44" s="36" t="n"/>
-      <c r="L44" s="36" t="n"/>
-      <c r="M44" s="36" t="n"/>
-      <c r="N44" s="36" t="n"/>
-      <c r="O44" s="36" t="n"/>
+      <c r="B44" s="37" t="n"/>
+      <c r="C44" s="37" t="n"/>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="37" t="n"/>
+      <c r="G44" s="37" t="n"/>
+      <c r="H44" s="37" t="n"/>
+      <c r="I44" s="37" t="n"/>
+      <c r="J44" s="37" t="n"/>
+      <c r="K44" s="37" t="n"/>
+      <c r="L44" s="37" t="n"/>
+      <c r="M44" s="37" t="n"/>
+      <c r="N44" s="37" t="n"/>
+      <c r="O44" s="37" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="38" t="n"/>
-      <c r="C45" s="38" t="n"/>
-      <c r="D45" s="38" t="n"/>
-      <c r="E45" s="38" t="n"/>
-      <c r="F45" s="38" t="n"/>
-      <c r="G45" s="38" t="n"/>
-      <c r="H45" s="38" t="n"/>
-      <c r="I45" s="38" t="n"/>
-      <c r="J45" s="38" t="n"/>
-      <c r="K45" s="38" t="n"/>
-      <c r="L45" s="38" t="n"/>
-      <c r="M45" s="38" t="n"/>
-      <c r="N45" s="38" t="n"/>
-      <c r="O45" s="38" t="n"/>
+      <c r="B45" s="39" t="n"/>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="39" t="n"/>
+      <c r="H45" s="39" t="n"/>
+      <c r="I45" s="39" t="n"/>
+      <c r="J45" s="39" t="n"/>
+      <c r="K45" s="39" t="n"/>
+      <c r="L45" s="39" t="n"/>
+      <c r="M45" s="39" t="n"/>
+      <c r="N45" s="39" t="n"/>
+      <c r="O45" s="39" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="36" t="n"/>
-      <c r="C46" s="36" t="n"/>
-      <c r="D46" s="36" t="n"/>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="36" t="n"/>
-      <c r="G46" s="36" t="n"/>
-      <c r="H46" s="36" t="n"/>
-      <c r="I46" s="36" t="n"/>
-      <c r="J46" s="36" t="n"/>
-      <c r="K46" s="36" t="n"/>
-      <c r="L46" s="36" t="n"/>
-      <c r="M46" s="36" t="n"/>
-      <c r="N46" s="36" t="n"/>
-      <c r="O46" s="36" t="n"/>
+      <c r="B46" s="37" t="n"/>
+      <c r="C46" s="37" t="n"/>
+      <c r="D46" s="37" t="n"/>
+      <c r="E46" s="37" t="n"/>
+      <c r="F46" s="37" t="n"/>
+      <c r="G46" s="37" t="n"/>
+      <c r="H46" s="37" t="n"/>
+      <c r="I46" s="37" t="n"/>
+      <c r="J46" s="37" t="n"/>
+      <c r="K46" s="37" t="n"/>
+      <c r="L46" s="37" t="n"/>
+      <c r="M46" s="37" t="n"/>
+      <c r="N46" s="37" t="n"/>
+      <c r="O46" s="37" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="38" t="n"/>
-      <c r="C47" s="38" t="n"/>
-      <c r="D47" s="38" t="n"/>
-      <c r="E47" s="38" t="n"/>
-      <c r="F47" s="38" t="n"/>
-      <c r="G47" s="38" t="n"/>
-      <c r="H47" s="38" t="n"/>
-      <c r="I47" s="38" t="n"/>
-      <c r="J47" s="38" t="n"/>
-      <c r="K47" s="38" t="n"/>
-      <c r="L47" s="38" t="n"/>
-      <c r="M47" s="38" t="n"/>
-      <c r="N47" s="38" t="n"/>
-      <c r="O47" s="38" t="n"/>
+      <c r="B47" s="39" t="n"/>
+      <c r="C47" s="39" t="n"/>
+      <c r="D47" s="39" t="n"/>
+      <c r="E47" s="39" t="n"/>
+      <c r="F47" s="39" t="n"/>
+      <c r="G47" s="39" t="n"/>
+      <c r="H47" s="39" t="n"/>
+      <c r="I47" s="39" t="n"/>
+      <c r="J47" s="39" t="n"/>
+      <c r="K47" s="39" t="n"/>
+      <c r="L47" s="39" t="n"/>
+      <c r="M47" s="39" t="n"/>
+      <c r="N47" s="39" t="n"/>
+      <c r="O47" s="39" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-      <c r="G48" s="36" t="n"/>
-      <c r="H48" s="36" t="n"/>
-      <c r="I48" s="36" t="n"/>
-      <c r="J48" s="36" t="n"/>
-      <c r="K48" s="36" t="n"/>
-      <c r="L48" s="36" t="n"/>
-      <c r="M48" s="36" t="n"/>
-      <c r="N48" s="36" t="n"/>
-      <c r="O48" s="36" t="n"/>
+      <c r="B48" s="37" t="n"/>
+      <c r="C48" s="37" t="n"/>
+      <c r="D48" s="37" t="n"/>
+      <c r="E48" s="37" t="n"/>
+      <c r="F48" s="37" t="n"/>
+      <c r="G48" s="37" t="n"/>
+      <c r="H48" s="37" t="n"/>
+      <c r="I48" s="37" t="n"/>
+      <c r="J48" s="37" t="n"/>
+      <c r="K48" s="37" t="n"/>
+      <c r="L48" s="37" t="n"/>
+      <c r="M48" s="37" t="n"/>
+      <c r="N48" s="37" t="n"/>
+      <c r="O48" s="37" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="38" t="n"/>
-      <c r="C49" s="38" t="n"/>
-      <c r="D49" s="38" t="n"/>
-      <c r="E49" s="38" t="n"/>
-      <c r="F49" s="38" t="n"/>
-      <c r="G49" s="38" t="n"/>
-      <c r="H49" s="38" t="n"/>
-      <c r="I49" s="38" t="n"/>
-      <c r="J49" s="38" t="n"/>
-      <c r="K49" s="38" t="n"/>
-      <c r="L49" s="38" t="n"/>
-      <c r="M49" s="38" t="n"/>
-      <c r="N49" s="38" t="n"/>
-      <c r="O49" s="38" t="n"/>
+      <c r="B49" s="39" t="n"/>
+      <c r="C49" s="39" t="n"/>
+      <c r="D49" s="39" t="n"/>
+      <c r="E49" s="39" t="n"/>
+      <c r="F49" s="39" t="n"/>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="39" t="n"/>
+      <c r="I49" s="39" t="n"/>
+      <c r="J49" s="39" t="n"/>
+      <c r="K49" s="39" t="n"/>
+      <c r="L49" s="39" t="n"/>
+      <c r="M49" s="39" t="n"/>
+      <c r="N49" s="39" t="n"/>
+      <c r="O49" s="39" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="36" t="n"/>
-      <c r="C50" s="36" t="n"/>
-      <c r="D50" s="36" t="n"/>
-      <c r="E50" s="36" t="n"/>
-      <c r="F50" s="36" t="n"/>
-      <c r="G50" s="36" t="n"/>
-      <c r="H50" s="36" t="n"/>
-      <c r="I50" s="36" t="n"/>
-      <c r="J50" s="36" t="n"/>
-      <c r="K50" s="36" t="n"/>
-      <c r="L50" s="36" t="n"/>
-      <c r="M50" s="36" t="n"/>
-      <c r="N50" s="36" t="n"/>
-      <c r="O50" s="36" t="n"/>
+      <c r="B50" s="37" t="n"/>
+      <c r="C50" s="37" t="n"/>
+      <c r="D50" s="37" t="n"/>
+      <c r="E50" s="37" t="n"/>
+      <c r="F50" s="37" t="n"/>
+      <c r="G50" s="37" t="n"/>
+      <c r="H50" s="37" t="n"/>
+      <c r="I50" s="37" t="n"/>
+      <c r="J50" s="37" t="n"/>
+      <c r="K50" s="37" t="n"/>
+      <c r="L50" s="37" t="n"/>
+      <c r="M50" s="37" t="n"/>
+      <c r="N50" s="37" t="n"/>
+      <c r="O50" s="37" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="38" t="n"/>
-      <c r="C51" s="38" t="n"/>
-      <c r="D51" s="38" t="n"/>
-      <c r="E51" s="38" t="n"/>
-      <c r="F51" s="38" t="n"/>
-      <c r="G51" s="38" t="n"/>
-      <c r="H51" s="38" t="n"/>
-      <c r="I51" s="38" t="n"/>
-      <c r="J51" s="38" t="n"/>
-      <c r="K51" s="38" t="n"/>
-      <c r="L51" s="38" t="n"/>
-      <c r="M51" s="38" t="n"/>
-      <c r="N51" s="38" t="n"/>
-      <c r="O51" s="38" t="n"/>
+      <c r="B51" s="39" t="n"/>
+      <c r="C51" s="39" t="n"/>
+      <c r="D51" s="39" t="n"/>
+      <c r="E51" s="39" t="n"/>
+      <c r="F51" s="39" t="n"/>
+      <c r="G51" s="39" t="n"/>
+      <c r="H51" s="39" t="n"/>
+      <c r="I51" s="39" t="n"/>
+      <c r="J51" s="39" t="n"/>
+      <c r="K51" s="39" t="n"/>
+      <c r="L51" s="39" t="n"/>
+      <c r="M51" s="39" t="n"/>
+      <c r="N51" s="39" t="n"/>
+      <c r="O51" s="39" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="36" t="n"/>
-      <c r="C52" s="36" t="n"/>
-      <c r="D52" s="36" t="n"/>
-      <c r="E52" s="36" t="n"/>
-      <c r="F52" s="36" t="n"/>
-      <c r="G52" s="36" t="n"/>
-      <c r="H52" s="36" t="n"/>
-      <c r="I52" s="36" t="n"/>
-      <c r="J52" s="36" t="n"/>
-      <c r="K52" s="36" t="n"/>
-      <c r="L52" s="36" t="n"/>
-      <c r="M52" s="36" t="n"/>
-      <c r="N52" s="36" t="n"/>
-      <c r="O52" s="36" t="n"/>
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="37" t="n"/>
+      <c r="D52" s="37" t="n"/>
+      <c r="E52" s="37" t="n"/>
+      <c r="F52" s="37" t="n"/>
+      <c r="G52" s="37" t="n"/>
+      <c r="H52" s="37" t="n"/>
+      <c r="I52" s="37" t="n"/>
+      <c r="J52" s="37" t="n"/>
+      <c r="K52" s="37" t="n"/>
+      <c r="L52" s="37" t="n"/>
+      <c r="M52" s="37" t="n"/>
+      <c r="N52" s="37" t="n"/>
+      <c r="O52" s="37" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="38" t="n"/>
-      <c r="C53" s="38" t="n"/>
-      <c r="D53" s="38" t="n"/>
-      <c r="E53" s="38" t="n"/>
-      <c r="F53" s="38" t="n"/>
-      <c r="G53" s="38" t="n"/>
-      <c r="H53" s="38" t="n"/>
-      <c r="I53" s="38" t="n"/>
-      <c r="J53" s="38" t="n"/>
-      <c r="K53" s="38" t="n"/>
-      <c r="L53" s="38" t="n"/>
-      <c r="M53" s="38" t="n"/>
-      <c r="N53" s="38" t="n"/>
-      <c r="O53" s="38" t="n"/>
+      <c r="B53" s="39" t="n"/>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="39" t="n"/>
+      <c r="G53" s="39" t="n"/>
+      <c r="H53" s="39" t="n"/>
+      <c r="I53" s="39" t="n"/>
+      <c r="J53" s="39" t="n"/>
+      <c r="K53" s="39" t="n"/>
+      <c r="L53" s="39" t="n"/>
+      <c r="M53" s="39" t="n"/>
+      <c r="N53" s="39" t="n"/>
+      <c r="O53" s="39" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="36" t="n"/>
-      <c r="C54" s="36" t="n"/>
-      <c r="D54" s="36" t="n"/>
-      <c r="E54" s="36" t="n"/>
-      <c r="F54" s="36" t="n"/>
-      <c r="G54" s="36" t="n"/>
-      <c r="H54" s="36" t="n"/>
-      <c r="I54" s="36" t="n"/>
-      <c r="J54" s="36" t="n"/>
-      <c r="K54" s="36" t="n"/>
-      <c r="L54" s="36" t="n"/>
-      <c r="M54" s="36" t="n"/>
-      <c r="N54" s="36" t="n"/>
-      <c r="O54" s="36" t="n"/>
+      <c r="B54" s="37" t="n"/>
+      <c r="C54" s="37" t="n"/>
+      <c r="D54" s="37" t="n"/>
+      <c r="E54" s="37" t="n"/>
+      <c r="F54" s="37" t="n"/>
+      <c r="G54" s="37" t="n"/>
+      <c r="H54" s="37" t="n"/>
+      <c r="I54" s="37" t="n"/>
+      <c r="J54" s="37" t="n"/>
+      <c r="K54" s="37" t="n"/>
+      <c r="L54" s="37" t="n"/>
+      <c r="M54" s="37" t="n"/>
+      <c r="N54" s="37" t="n"/>
+      <c r="O54" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4520,325 +6291,325 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Reference Guide — Formulas, Definitions &amp; How to Use</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="52" t="inlineStr"/>
+      <c r="B3" s="55" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="B4" s="53" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>How to Use This Workbook</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>1. Enter specifications (Tₘ, LSL, USL) in the Analysis sheet (blue cells)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>2. Choose Mode: 'Enter Manually' or 'Use Data Worksheet' (dropdown in C10)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>3. If Manual: enter x̄, σ, n directly in the Analysis sheet</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>4. If Worksheet: enter part data in the Data sheet — mean &amp; σ auto-link</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>5. All results, probability, hypothesis test, and verdict update INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>6. View charts in the Charts sheet (bell curve + capability bars)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>7. To save a run: go to History sheet, copy Row 4, paste as VALUES into Row 5+</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="52" t="inlineStr"/>
+      <c r="B12" s="55" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="53" t="inlineStr">
+      <c r="B13" s="56" t="inlineStr">
         <is>
           <t>Core Capability Formulas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cp = (USL − LSL) / 6σ  — Potential capability if process is perfectly centered</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="52" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cpk = min[(USL − x̄) / 3σ,  (x̄ − LSL) / 3σ]  — Actual capability with centering error</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="52" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Required Shift (Δ) = Tₘ − x̄  — How far to adjust the process mean</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="52" t="inlineStr">
+      <c r="B17" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Required Tolerance = Target Index × 6σ  — Minimum tolerance band needed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="52" t="inlineStr"/>
+      <c r="B18" s="55" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="53" t="inlineStr">
+      <c r="B19" s="56" t="inlineStr">
         <is>
           <t>Capability Index Interpretation (Automotive Standards)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="52" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cpk ≥ 1.67  →  ✅ GOOD — Capable (standard automotive target)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="52" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.33 ≤ Cpk &lt; 1.67  →  ⚠ ACCEPTABLE — Meets minimum but below target</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="52" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.00 ≤ Cpk &lt; 1.33  →  ⚠ MARGINAL — High risk, improvement needed</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="52" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cpk &lt; 1.00  →  ❌ NOT CAPABLE — Produces significant defects</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="52" t="inlineStr"/>
+      <c r="B24" s="55" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="56" t="inlineStr">
         <is>
           <t>Probability &amp; PPM</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="52" t="inlineStr">
+      <c r="B26" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  P(x &gt; USL) — Probability a part exceeds upper spec limit</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="52" t="inlineStr">
+      <c r="B27" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  P(x &lt; LSL) — Probability a part falls below lower spec limit</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="52" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  PPM = Probability × 1,000,000 — Parts Per Million defective</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="52" t="inlineStr"/>
+      <c r="B29" s="55" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="53" t="inlineStr">
+      <c r="B30" s="56" t="inlineStr">
         <is>
           <t>Hypothesis Testing</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="52" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  H₀: μ = Tₘ (process is on target)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="52" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Z = (x̄ − Tₘ) / (σ / √n)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="52" t="inlineStr">
+      <c r="B33" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  p-value &lt; α → Reject H₀ → Significant shift detected</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="52" t="inlineStr">
+      <c r="B34" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  p-value ≥ α → Fail to Reject H₀ → No significant shift</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="52" t="inlineStr">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Two-Sided: tests if mean differs in either direction</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="52" t="inlineStr">
+      <c r="B36" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upper-Sided: tests if mean is significantly above target</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="52" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  Lower-Sided: tests if mean is significantly below target</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="52" t="inlineStr"/>
+      <c r="B38" s="55" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="B39" s="53" t="inlineStr">
+      <c r="B39" s="56" t="inlineStr">
         <is>
           <t>Robustness Assessment</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="52" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  ROBUST: ±4σ spread contained within specification limits</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="52" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARGINAL: ±3σ contained but ±4σ is NOT — low tolerance for future shifts</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="52" t="inlineStr">
+      <c r="B42" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOT ROBUST: ±3σ breaches specification limits</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="52" t="inlineStr"/>
+      <c r="B43" s="55" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="B44" s="53" t="inlineStr">
+      <c r="B44" s="56" t="inlineStr">
         <is>
           <t>Spread Metrics</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="52" t="inlineStr">
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  6σ Spread — Contains ~99.73% of process output (±3σ)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="52" t="inlineStr">
+      <c r="B46" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  8σ Spread — Contains ~99.9937% of process output (±4σ)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="52" t="inlineStr"/>
+      <c r="B47" s="55" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="B48" s="53" t="inlineStr">
+      <c r="B48" s="56" t="inlineStr">
         <is>
           <t>Color Coding</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="52" t="inlineStr">
+      <c r="B49" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  🟢 Green cells = Good / Capable / Within target</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="52" t="inlineStr">
+      <c r="B50" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  🟡 Yellow cells = Warning / Marginal</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="52" t="inlineStr">
+      <c r="B51" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  🔴 Red cells = Bad / Action Required / Not capable</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="52" t="inlineStr">
+      <c r="B52" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  🔵 Blue cells = Input cells (enter your data here)</t>
         </is>

--- a/SPC_Statistical_Calculator.xlsx
+++ b/SPC_Statistical_Calculator.xlsx
@@ -2271,7 +2271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G104"/>
+  <dimension ref="B1:G1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2293,7 +2293,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Enter DMC and measured Value below (max 100 parts). Statistics auto-link to Analysis sheet.</t>
+          <t>Enter DMC and measured Value below (max 1000 parts). Statistics auto-link to Analysis sheet.</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <v/>
       </c>
       <c r="F3" s="34">
-        <f>G5&amp;" of 100 rows used ("&amp;TEXT(G5/100,"0%")&amp;" capacity)"</f>
+        <f>G5&amp;" of 1000 rows used ("&amp;TEXT(G5/1000,"0%")&amp;" capacity)"</f>
         <v/>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="G5" s="10">
-        <f>COUNTA(D5:D104)</f>
+        <f>COUNTA(D5:D1004)</f>
         <v/>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="G6" s="7">
-        <f>IF(G5&gt;=2,AVERAGE(D5:D104),"")</f>
+        <f>IF(G5&gt;=2,AVERAGE(D5:D1004),"")</f>
         <v/>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="G7" s="7">
-        <f>IF(G5&gt;=2,STDEV.S(D5:D104),"")</f>
+        <f>IF(G5&gt;=2,STDEV.S(D5:D1004),"")</f>
         <v/>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="G8" s="41">
-        <f>IF(G5&gt;=1,MIN(D5:D104),"")</f>
+        <f>IF(G5&gt;=1,MIN(D5:D1004),"")</f>
         <v/>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G9" s="41">
-        <f>IF(G5&gt;=1,MAX(D5:D104),"")</f>
+        <f>IF(G5&gt;=1,MAX(D5:D1004),"")</f>
         <v/>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="G11" s="41">
-        <f>IF(G5&gt;=1,MEDIAN(D5:D104),"")</f>
+        <f>IF(G5&gt;=1,MEDIAN(D5:D1004),"")</f>
         <v/>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="G12" s="41">
-        <f>IF(G5&gt;=4,PERCENTILE(D5:D104,0.25),"")</f>
+        <f>IF(G5&gt;=4,PERCENTILE(D5:D1004,0.25),"")</f>
         <v/>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="G13" s="41">
-        <f>IF(G5&gt;=4,PERCENTILE(D5:D104,0.75),"")</f>
+        <f>IF(G5&gt;=4,PERCENTILE(D5:D1004,0.75),"")</f>
         <v/>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="G15" s="41">
-        <f>IF(G5&gt;=3,SKEW(D5:D104),"")</f>
+        <f>IF(G5&gt;=3,SKEW(D5:D1004),"")</f>
         <v/>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="G16" s="41">
-        <f>IF(G5&gt;=4,KURT(D5:D104),"")</f>
+        <f>IF(G5&gt;=4,KURT(D5:D1004),"")</f>
         <v/>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       <c r="C18" s="39" t="n"/>
       <c r="D18" s="40" t="n"/>
       <c r="F18" s="42">
-        <f>IF(G5&gt;=2,"✅ "&amp;G5&amp;" of 100 data points ready. Analysis auto-linked.","⚠ Need ≥2 data points (100 max allowed).")</f>
+        <f>IF(G5&gt;=2,"✅ "&amp;G5&amp;" of 1000 data points ready. Analysis auto-linked.","⚠ Need ≥2 data points (1000 max allowed).")</f>
         <v/>
       </c>
     </row>
@@ -3230,6 +3230,6306 @@
       </c>
       <c r="C104" s="39" t="n"/>
       <c r="D104" s="40" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="36" t="n">
+        <v>101</v>
+      </c>
+      <c r="C105" s="37" t="n"/>
+      <c r="D105" s="38" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="36" t="n">
+        <v>102</v>
+      </c>
+      <c r="C106" s="39" t="n"/>
+      <c r="D106" s="40" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="36" t="n">
+        <v>103</v>
+      </c>
+      <c r="C107" s="37" t="n"/>
+      <c r="D107" s="38" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="36" t="n">
+        <v>104</v>
+      </c>
+      <c r="C108" s="39" t="n"/>
+      <c r="D108" s="40" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="36" t="n">
+        <v>105</v>
+      </c>
+      <c r="C109" s="37" t="n"/>
+      <c r="D109" s="38" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="36" t="n">
+        <v>106</v>
+      </c>
+      <c r="C110" s="39" t="n"/>
+      <c r="D110" s="40" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="36" t="n">
+        <v>107</v>
+      </c>
+      <c r="C111" s="37" t="n"/>
+      <c r="D111" s="38" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="36" t="n">
+        <v>108</v>
+      </c>
+      <c r="C112" s="39" t="n"/>
+      <c r="D112" s="40" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="36" t="n">
+        <v>109</v>
+      </c>
+      <c r="C113" s="37" t="n"/>
+      <c r="D113" s="38" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="36" t="n">
+        <v>110</v>
+      </c>
+      <c r="C114" s="39" t="n"/>
+      <c r="D114" s="40" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="36" t="n">
+        <v>111</v>
+      </c>
+      <c r="C115" s="37" t="n"/>
+      <c r="D115" s="38" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="36" t="n">
+        <v>112</v>
+      </c>
+      <c r="C116" s="39" t="n"/>
+      <c r="D116" s="40" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="36" t="n">
+        <v>113</v>
+      </c>
+      <c r="C117" s="37" t="n"/>
+      <c r="D117" s="38" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="36" t="n">
+        <v>114</v>
+      </c>
+      <c r="C118" s="39" t="n"/>
+      <c r="D118" s="40" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="36" t="n">
+        <v>115</v>
+      </c>
+      <c r="C119" s="37" t="n"/>
+      <c r="D119" s="38" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="36" t="n">
+        <v>116</v>
+      </c>
+      <c r="C120" s="39" t="n"/>
+      <c r="D120" s="40" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="36" t="n">
+        <v>117</v>
+      </c>
+      <c r="C121" s="37" t="n"/>
+      <c r="D121" s="38" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="36" t="n">
+        <v>118</v>
+      </c>
+      <c r="C122" s="39" t="n"/>
+      <c r="D122" s="40" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="36" t="n">
+        <v>119</v>
+      </c>
+      <c r="C123" s="37" t="n"/>
+      <c r="D123" s="38" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="36" t="n">
+        <v>120</v>
+      </c>
+      <c r="C124" s="39" t="n"/>
+      <c r="D124" s="40" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="36" t="n">
+        <v>121</v>
+      </c>
+      <c r="C125" s="37" t="n"/>
+      <c r="D125" s="38" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="36" t="n">
+        <v>122</v>
+      </c>
+      <c r="C126" s="39" t="n"/>
+      <c r="D126" s="40" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="36" t="n">
+        <v>123</v>
+      </c>
+      <c r="C127" s="37" t="n"/>
+      <c r="D127" s="38" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="36" t="n">
+        <v>124</v>
+      </c>
+      <c r="C128" s="39" t="n"/>
+      <c r="D128" s="40" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="36" t="n">
+        <v>125</v>
+      </c>
+      <c r="C129" s="37" t="n"/>
+      <c r="D129" s="38" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="36" t="n">
+        <v>126</v>
+      </c>
+      <c r="C130" s="39" t="n"/>
+      <c r="D130" s="40" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="36" t="n">
+        <v>127</v>
+      </c>
+      <c r="C131" s="37" t="n"/>
+      <c r="D131" s="38" t="n"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="36" t="n">
+        <v>128</v>
+      </c>
+      <c r="C132" s="39" t="n"/>
+      <c r="D132" s="40" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="36" t="n">
+        <v>129</v>
+      </c>
+      <c r="C133" s="37" t="n"/>
+      <c r="D133" s="38" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="36" t="n">
+        <v>130</v>
+      </c>
+      <c r="C134" s="39" t="n"/>
+      <c r="D134" s="40" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="36" t="n">
+        <v>131</v>
+      </c>
+      <c r="C135" s="37" t="n"/>
+      <c r="D135" s="38" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="36" t="n">
+        <v>132</v>
+      </c>
+      <c r="C136" s="39" t="n"/>
+      <c r="D136" s="40" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="36" t="n">
+        <v>133</v>
+      </c>
+      <c r="C137" s="37" t="n"/>
+      <c r="D137" s="38" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="36" t="n">
+        <v>134</v>
+      </c>
+      <c r="C138" s="39" t="n"/>
+      <c r="D138" s="40" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="36" t="n">
+        <v>135</v>
+      </c>
+      <c r="C139" s="37" t="n"/>
+      <c r="D139" s="38" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="36" t="n">
+        <v>136</v>
+      </c>
+      <c r="C140" s="39" t="n"/>
+      <c r="D140" s="40" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="36" t="n">
+        <v>137</v>
+      </c>
+      <c r="C141" s="37" t="n"/>
+      <c r="D141" s="38" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="36" t="n">
+        <v>138</v>
+      </c>
+      <c r="C142" s="39" t="n"/>
+      <c r="D142" s="40" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="36" t="n">
+        <v>139</v>
+      </c>
+      <c r="C143" s="37" t="n"/>
+      <c r="D143" s="38" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="36" t="n">
+        <v>140</v>
+      </c>
+      <c r="C144" s="39" t="n"/>
+      <c r="D144" s="40" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="36" t="n">
+        <v>141</v>
+      </c>
+      <c r="C145" s="37" t="n"/>
+      <c r="D145" s="38" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="36" t="n">
+        <v>142</v>
+      </c>
+      <c r="C146" s="39" t="n"/>
+      <c r="D146" s="40" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="36" t="n">
+        <v>143</v>
+      </c>
+      <c r="C147" s="37" t="n"/>
+      <c r="D147" s="38" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="36" t="n">
+        <v>144</v>
+      </c>
+      <c r="C148" s="39" t="n"/>
+      <c r="D148" s="40" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="36" t="n">
+        <v>145</v>
+      </c>
+      <c r="C149" s="37" t="n"/>
+      <c r="D149" s="38" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="36" t="n">
+        <v>146</v>
+      </c>
+      <c r="C150" s="39" t="n"/>
+      <c r="D150" s="40" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="36" t="n">
+        <v>147</v>
+      </c>
+      <c r="C151" s="37" t="n"/>
+      <c r="D151" s="38" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="36" t="n">
+        <v>148</v>
+      </c>
+      <c r="C152" s="39" t="n"/>
+      <c r="D152" s="40" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="36" t="n">
+        <v>149</v>
+      </c>
+      <c r="C153" s="37" t="n"/>
+      <c r="D153" s="38" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="C154" s="39" t="n"/>
+      <c r="D154" s="40" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="36" t="n">
+        <v>151</v>
+      </c>
+      <c r="C155" s="37" t="n"/>
+      <c r="D155" s="38" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="36" t="n">
+        <v>152</v>
+      </c>
+      <c r="C156" s="39" t="n"/>
+      <c r="D156" s="40" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="36" t="n">
+        <v>153</v>
+      </c>
+      <c r="C157" s="37" t="n"/>
+      <c r="D157" s="38" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="36" t="n">
+        <v>154</v>
+      </c>
+      <c r="C158" s="39" t="n"/>
+      <c r="D158" s="40" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="36" t="n">
+        <v>155</v>
+      </c>
+      <c r="C159" s="37" t="n"/>
+      <c r="D159" s="38" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="36" t="n">
+        <v>156</v>
+      </c>
+      <c r="C160" s="39" t="n"/>
+      <c r="D160" s="40" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="36" t="n">
+        <v>157</v>
+      </c>
+      <c r="C161" s="37" t="n"/>
+      <c r="D161" s="38" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="36" t="n">
+        <v>158</v>
+      </c>
+      <c r="C162" s="39" t="n"/>
+      <c r="D162" s="40" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="36" t="n">
+        <v>159</v>
+      </c>
+      <c r="C163" s="37" t="n"/>
+      <c r="D163" s="38" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="36" t="n">
+        <v>160</v>
+      </c>
+      <c r="C164" s="39" t="n"/>
+      <c r="D164" s="40" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="36" t="n">
+        <v>161</v>
+      </c>
+      <c r="C165" s="37" t="n"/>
+      <c r="D165" s="38" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="36" t="n">
+        <v>162</v>
+      </c>
+      <c r="C166" s="39" t="n"/>
+      <c r="D166" s="40" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="36" t="n">
+        <v>163</v>
+      </c>
+      <c r="C167" s="37" t="n"/>
+      <c r="D167" s="38" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="36" t="n">
+        <v>164</v>
+      </c>
+      <c r="C168" s="39" t="n"/>
+      <c r="D168" s="40" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="36" t="n">
+        <v>165</v>
+      </c>
+      <c r="C169" s="37" t="n"/>
+      <c r="D169" s="38" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="36" t="n">
+        <v>166</v>
+      </c>
+      <c r="C170" s="39" t="n"/>
+      <c r="D170" s="40" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="36" t="n">
+        <v>167</v>
+      </c>
+      <c r="C171" s="37" t="n"/>
+      <c r="D171" s="38" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="36" t="n">
+        <v>168</v>
+      </c>
+      <c r="C172" s="39" t="n"/>
+      <c r="D172" s="40" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="36" t="n">
+        <v>169</v>
+      </c>
+      <c r="C173" s="37" t="n"/>
+      <c r="D173" s="38" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="36" t="n">
+        <v>170</v>
+      </c>
+      <c r="C174" s="39" t="n"/>
+      <c r="D174" s="40" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="36" t="n">
+        <v>171</v>
+      </c>
+      <c r="C175" s="37" t="n"/>
+      <c r="D175" s="38" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="36" t="n">
+        <v>172</v>
+      </c>
+      <c r="C176" s="39" t="n"/>
+      <c r="D176" s="40" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="36" t="n">
+        <v>173</v>
+      </c>
+      <c r="C177" s="37" t="n"/>
+      <c r="D177" s="38" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="36" t="n">
+        <v>174</v>
+      </c>
+      <c r="C178" s="39" t="n"/>
+      <c r="D178" s="40" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="36" t="n">
+        <v>175</v>
+      </c>
+      <c r="C179" s="37" t="n"/>
+      <c r="D179" s="38" t="n"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="36" t="n">
+        <v>176</v>
+      </c>
+      <c r="C180" s="39" t="n"/>
+      <c r="D180" s="40" t="n"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="36" t="n">
+        <v>177</v>
+      </c>
+      <c r="C181" s="37" t="n"/>
+      <c r="D181" s="38" t="n"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="36" t="n">
+        <v>178</v>
+      </c>
+      <c r="C182" s="39" t="n"/>
+      <c r="D182" s="40" t="n"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="36" t="n">
+        <v>179</v>
+      </c>
+      <c r="C183" s="37" t="n"/>
+      <c r="D183" s="38" t="n"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="36" t="n">
+        <v>180</v>
+      </c>
+      <c r="C184" s="39" t="n"/>
+      <c r="D184" s="40" t="n"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="36" t="n">
+        <v>181</v>
+      </c>
+      <c r="C185" s="37" t="n"/>
+      <c r="D185" s="38" t="n"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="36" t="n">
+        <v>182</v>
+      </c>
+      <c r="C186" s="39" t="n"/>
+      <c r="D186" s="40" t="n"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="36" t="n">
+        <v>183</v>
+      </c>
+      <c r="C187" s="37" t="n"/>
+      <c r="D187" s="38" t="n"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="36" t="n">
+        <v>184</v>
+      </c>
+      <c r="C188" s="39" t="n"/>
+      <c r="D188" s="40" t="n"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="36" t="n">
+        <v>185</v>
+      </c>
+      <c r="C189" s="37" t="n"/>
+      <c r="D189" s="38" t="n"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="36" t="n">
+        <v>186</v>
+      </c>
+      <c r="C190" s="39" t="n"/>
+      <c r="D190" s="40" t="n"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="36" t="n">
+        <v>187</v>
+      </c>
+      <c r="C191" s="37" t="n"/>
+      <c r="D191" s="38" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="36" t="n">
+        <v>188</v>
+      </c>
+      <c r="C192" s="39" t="n"/>
+      <c r="D192" s="40" t="n"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="36" t="n">
+        <v>189</v>
+      </c>
+      <c r="C193" s="37" t="n"/>
+      <c r="D193" s="38" t="n"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="36" t="n">
+        <v>190</v>
+      </c>
+      <c r="C194" s="39" t="n"/>
+      <c r="D194" s="40" t="n"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="36" t="n">
+        <v>191</v>
+      </c>
+      <c r="C195" s="37" t="n"/>
+      <c r="D195" s="38" t="n"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="36" t="n">
+        <v>192</v>
+      </c>
+      <c r="C196" s="39" t="n"/>
+      <c r="D196" s="40" t="n"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="36" t="n">
+        <v>193</v>
+      </c>
+      <c r="C197" s="37" t="n"/>
+      <c r="D197" s="38" t="n"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="36" t="n">
+        <v>194</v>
+      </c>
+      <c r="C198" s="39" t="n"/>
+      <c r="D198" s="40" t="n"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="36" t="n">
+        <v>195</v>
+      </c>
+      <c r="C199" s="37" t="n"/>
+      <c r="D199" s="38" t="n"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="36" t="n">
+        <v>196</v>
+      </c>
+      <c r="C200" s="39" t="n"/>
+      <c r="D200" s="40" t="n"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="36" t="n">
+        <v>197</v>
+      </c>
+      <c r="C201" s="37" t="n"/>
+      <c r="D201" s="38" t="n"/>
+    </row>
+    <row r="202">
+      <c r="B202" s="36" t="n">
+        <v>198</v>
+      </c>
+      <c r="C202" s="39" t="n"/>
+      <c r="D202" s="40" t="n"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="36" t="n">
+        <v>199</v>
+      </c>
+      <c r="C203" s="37" t="n"/>
+      <c r="D203" s="38" t="n"/>
+    </row>
+    <row r="204">
+      <c r="B204" s="36" t="n">
+        <v>200</v>
+      </c>
+      <c r="C204" s="39" t="n"/>
+      <c r="D204" s="40" t="n"/>
+    </row>
+    <row r="205">
+      <c r="B205" s="36" t="n">
+        <v>201</v>
+      </c>
+      <c r="C205" s="37" t="n"/>
+      <c r="D205" s="38" t="n"/>
+    </row>
+    <row r="206">
+      <c r="B206" s="36" t="n">
+        <v>202</v>
+      </c>
+      <c r="C206" s="39" t="n"/>
+      <c r="D206" s="40" t="n"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="36" t="n">
+        <v>203</v>
+      </c>
+      <c r="C207" s="37" t="n"/>
+      <c r="D207" s="38" t="n"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="36" t="n">
+        <v>204</v>
+      </c>
+      <c r="C208" s="39" t="n"/>
+      <c r="D208" s="40" t="n"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="36" t="n">
+        <v>205</v>
+      </c>
+      <c r="C209" s="37" t="n"/>
+      <c r="D209" s="38" t="n"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="36" t="n">
+        <v>206</v>
+      </c>
+      <c r="C210" s="39" t="n"/>
+      <c r="D210" s="40" t="n"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="36" t="n">
+        <v>207</v>
+      </c>
+      <c r="C211" s="37" t="n"/>
+      <c r="D211" s="38" t="n"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="36" t="n">
+        <v>208</v>
+      </c>
+      <c r="C212" s="39" t="n"/>
+      <c r="D212" s="40" t="n"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="36" t="n">
+        <v>209</v>
+      </c>
+      <c r="C213" s="37" t="n"/>
+      <c r="D213" s="38" t="n"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="36" t="n">
+        <v>210</v>
+      </c>
+      <c r="C214" s="39" t="n"/>
+      <c r="D214" s="40" t="n"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="36" t="n">
+        <v>211</v>
+      </c>
+      <c r="C215" s="37" t="n"/>
+      <c r="D215" s="38" t="n"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="36" t="n">
+        <v>212</v>
+      </c>
+      <c r="C216" s="39" t="n"/>
+      <c r="D216" s="40" t="n"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="36" t="n">
+        <v>213</v>
+      </c>
+      <c r="C217" s="37" t="n"/>
+      <c r="D217" s="38" t="n"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="36" t="n">
+        <v>214</v>
+      </c>
+      <c r="C218" s="39" t="n"/>
+      <c r="D218" s="40" t="n"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="36" t="n">
+        <v>215</v>
+      </c>
+      <c r="C219" s="37" t="n"/>
+      <c r="D219" s="38" t="n"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="36" t="n">
+        <v>216</v>
+      </c>
+      <c r="C220" s="39" t="n"/>
+      <c r="D220" s="40" t="n"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="36" t="n">
+        <v>217</v>
+      </c>
+      <c r="C221" s="37" t="n"/>
+      <c r="D221" s="38" t="n"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="36" t="n">
+        <v>218</v>
+      </c>
+      <c r="C222" s="39" t="n"/>
+      <c r="D222" s="40" t="n"/>
+    </row>
+    <row r="223">
+      <c r="B223" s="36" t="n">
+        <v>219</v>
+      </c>
+      <c r="C223" s="37" t="n"/>
+      <c r="D223" s="38" t="n"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="36" t="n">
+        <v>220</v>
+      </c>
+      <c r="C224" s="39" t="n"/>
+      <c r="D224" s="40" t="n"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="36" t="n">
+        <v>221</v>
+      </c>
+      <c r="C225" s="37" t="n"/>
+      <c r="D225" s="38" t="n"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="36" t="n">
+        <v>222</v>
+      </c>
+      <c r="C226" s="39" t="n"/>
+      <c r="D226" s="40" t="n"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="36" t="n">
+        <v>223</v>
+      </c>
+      <c r="C227" s="37" t="n"/>
+      <c r="D227" s="38" t="n"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="36" t="n">
+        <v>224</v>
+      </c>
+      <c r="C228" s="39" t="n"/>
+      <c r="D228" s="40" t="n"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="36" t="n">
+        <v>225</v>
+      </c>
+      <c r="C229" s="37" t="n"/>
+      <c r="D229" s="38" t="n"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="36" t="n">
+        <v>226</v>
+      </c>
+      <c r="C230" s="39" t="n"/>
+      <c r="D230" s="40" t="n"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="36" t="n">
+        <v>227</v>
+      </c>
+      <c r="C231" s="37" t="n"/>
+      <c r="D231" s="38" t="n"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="36" t="n">
+        <v>228</v>
+      </c>
+      <c r="C232" s="39" t="n"/>
+      <c r="D232" s="40" t="n"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="36" t="n">
+        <v>229</v>
+      </c>
+      <c r="C233" s="37" t="n"/>
+      <c r="D233" s="38" t="n"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="36" t="n">
+        <v>230</v>
+      </c>
+      <c r="C234" s="39" t="n"/>
+      <c r="D234" s="40" t="n"/>
+    </row>
+    <row r="235">
+      <c r="B235" s="36" t="n">
+        <v>231</v>
+      </c>
+      <c r="C235" s="37" t="n"/>
+      <c r="D235" s="38" t="n"/>
+    </row>
+    <row r="236">
+      <c r="B236" s="36" t="n">
+        <v>232</v>
+      </c>
+      <c r="C236" s="39" t="n"/>
+      <c r="D236" s="40" t="n"/>
+    </row>
+    <row r="237">
+      <c r="B237" s="36" t="n">
+        <v>233</v>
+      </c>
+      <c r="C237" s="37" t="n"/>
+      <c r="D237" s="38" t="n"/>
+    </row>
+    <row r="238">
+      <c r="B238" s="36" t="n">
+        <v>234</v>
+      </c>
+      <c r="C238" s="39" t="n"/>
+      <c r="D238" s="40" t="n"/>
+    </row>
+    <row r="239">
+      <c r="B239" s="36" t="n">
+        <v>235</v>
+      </c>
+      <c r="C239" s="37" t="n"/>
+      <c r="D239" s="38" t="n"/>
+    </row>
+    <row r="240">
+      <c r="B240" s="36" t="n">
+        <v>236</v>
+      </c>
+      <c r="C240" s="39" t="n"/>
+      <c r="D240" s="40" t="n"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="36" t="n">
+        <v>237</v>
+      </c>
+      <c r="C241" s="37" t="n"/>
+      <c r="D241" s="38" t="n"/>
+    </row>
+    <row r="242">
+      <c r="B242" s="36" t="n">
+        <v>238</v>
+      </c>
+      <c r="C242" s="39" t="n"/>
+      <c r="D242" s="40" t="n"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="36" t="n">
+        <v>239</v>
+      </c>
+      <c r="C243" s="37" t="n"/>
+      <c r="D243" s="38" t="n"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="36" t="n">
+        <v>240</v>
+      </c>
+      <c r="C244" s="39" t="n"/>
+      <c r="D244" s="40" t="n"/>
+    </row>
+    <row r="245">
+      <c r="B245" s="36" t="n">
+        <v>241</v>
+      </c>
+      <c r="C245" s="37" t="n"/>
+      <c r="D245" s="38" t="n"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="36" t="n">
+        <v>242</v>
+      </c>
+      <c r="C246" s="39" t="n"/>
+      <c r="D246" s="40" t="n"/>
+    </row>
+    <row r="247">
+      <c r="B247" s="36" t="n">
+        <v>243</v>
+      </c>
+      <c r="C247" s="37" t="n"/>
+      <c r="D247" s="38" t="n"/>
+    </row>
+    <row r="248">
+      <c r="B248" s="36" t="n">
+        <v>244</v>
+      </c>
+      <c r="C248" s="39" t="n"/>
+      <c r="D248" s="40" t="n"/>
+    </row>
+    <row r="249">
+      <c r="B249" s="36" t="n">
+        <v>245</v>
+      </c>
+      <c r="C249" s="37" t="n"/>
+      <c r="D249" s="38" t="n"/>
+    </row>
+    <row r="250">
+      <c r="B250" s="36" t="n">
+        <v>246</v>
+      </c>
+      <c r="C250" s="39" t="n"/>
+      <c r="D250" s="40" t="n"/>
+    </row>
+    <row r="251">
+      <c r="B251" s="36" t="n">
+        <v>247</v>
+      </c>
+      <c r="C251" s="37" t="n"/>
+      <c r="D251" s="38" t="n"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="36" t="n">
+        <v>248</v>
+      </c>
+      <c r="C252" s="39" t="n"/>
+      <c r="D252" s="40" t="n"/>
+    </row>
+    <row r="253">
+      <c r="B253" s="36" t="n">
+        <v>249</v>
+      </c>
+      <c r="C253" s="37" t="n"/>
+      <c r="D253" s="38" t="n"/>
+    </row>
+    <row r="254">
+      <c r="B254" s="36" t="n">
+        <v>250</v>
+      </c>
+      <c r="C254" s="39" t="n"/>
+      <c r="D254" s="40" t="n"/>
+    </row>
+    <row r="255">
+      <c r="B255" s="36" t="n">
+        <v>251</v>
+      </c>
+      <c r="C255" s="37" t="n"/>
+      <c r="D255" s="38" t="n"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="36" t="n">
+        <v>252</v>
+      </c>
+      <c r="C256" s="39" t="n"/>
+      <c r="D256" s="40" t="n"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="36" t="n">
+        <v>253</v>
+      </c>
+      <c r="C257" s="37" t="n"/>
+      <c r="D257" s="38" t="n"/>
+    </row>
+    <row r="258">
+      <c r="B258" s="36" t="n">
+        <v>254</v>
+      </c>
+      <c r="C258" s="39" t="n"/>
+      <c r="D258" s="40" t="n"/>
+    </row>
+    <row r="259">
+      <c r="B259" s="36" t="n">
+        <v>255</v>
+      </c>
+      <c r="C259" s="37" t="n"/>
+      <c r="D259" s="38" t="n"/>
+    </row>
+    <row r="260">
+      <c r="B260" s="36" t="n">
+        <v>256</v>
+      </c>
+      <c r="C260" s="39" t="n"/>
+      <c r="D260" s="40" t="n"/>
+    </row>
+    <row r="261">
+      <c r="B261" s="36" t="n">
+        <v>257</v>
+      </c>
+      <c r="C261" s="37" t="n"/>
+      <c r="D261" s="38" t="n"/>
+    </row>
+    <row r="262">
+      <c r="B262" s="36" t="n">
+        <v>258</v>
+      </c>
+      <c r="C262" s="39" t="n"/>
+      <c r="D262" s="40" t="n"/>
+    </row>
+    <row r="263">
+      <c r="B263" s="36" t="n">
+        <v>259</v>
+      </c>
+      <c r="C263" s="37" t="n"/>
+      <c r="D263" s="38" t="n"/>
+    </row>
+    <row r="264">
+      <c r="B264" s="36" t="n">
+        <v>260</v>
+      </c>
+      <c r="C264" s="39" t="n"/>
+      <c r="D264" s="40" t="n"/>
+    </row>
+    <row r="265">
+      <c r="B265" s="36" t="n">
+        <v>261</v>
+      </c>
+      <c r="C265" s="37" t="n"/>
+      <c r="D265" s="38" t="n"/>
+    </row>
+    <row r="266">
+      <c r="B266" s="36" t="n">
+        <v>262</v>
+      </c>
+      <c r="C266" s="39" t="n"/>
+      <c r="D266" s="40" t="n"/>
+    </row>
+    <row r="267">
+      <c r="B267" s="36" t="n">
+        <v>263</v>
+      </c>
+      <c r="C267" s="37" t="n"/>
+      <c r="D267" s="38" t="n"/>
+    </row>
+    <row r="268">
+      <c r="B268" s="36" t="n">
+        <v>264</v>
+      </c>
+      <c r="C268" s="39" t="n"/>
+      <c r="D268" s="40" t="n"/>
+    </row>
+    <row r="269">
+      <c r="B269" s="36" t="n">
+        <v>265</v>
+      </c>
+      <c r="C269" s="37" t="n"/>
+      <c r="D269" s="38" t="n"/>
+    </row>
+    <row r="270">
+      <c r="B270" s="36" t="n">
+        <v>266</v>
+      </c>
+      <c r="C270" s="39" t="n"/>
+      <c r="D270" s="40" t="n"/>
+    </row>
+    <row r="271">
+      <c r="B271" s="36" t="n">
+        <v>267</v>
+      </c>
+      <c r="C271" s="37" t="n"/>
+      <c r="D271" s="38" t="n"/>
+    </row>
+    <row r="272">
+      <c r="B272" s="36" t="n">
+        <v>268</v>
+      </c>
+      <c r="C272" s="39" t="n"/>
+      <c r="D272" s="40" t="n"/>
+    </row>
+    <row r="273">
+      <c r="B273" s="36" t="n">
+        <v>269</v>
+      </c>
+      <c r="C273" s="37" t="n"/>
+      <c r="D273" s="38" t="n"/>
+    </row>
+    <row r="274">
+      <c r="B274" s="36" t="n">
+        <v>270</v>
+      </c>
+      <c r="C274" s="39" t="n"/>
+      <c r="D274" s="40" t="n"/>
+    </row>
+    <row r="275">
+      <c r="B275" s="36" t="n">
+        <v>271</v>
+      </c>
+      <c r="C275" s="37" t="n"/>
+      <c r="D275" s="38" t="n"/>
+    </row>
+    <row r="276">
+      <c r="B276" s="36" t="n">
+        <v>272</v>
+      </c>
+      <c r="C276" s="39" t="n"/>
+      <c r="D276" s="40" t="n"/>
+    </row>
+    <row r="277">
+      <c r="B277" s="36" t="n">
+        <v>273</v>
+      </c>
+      <c r="C277" s="37" t="n"/>
+      <c r="D277" s="38" t="n"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="36" t="n">
+        <v>274</v>
+      </c>
+      <c r="C278" s="39" t="n"/>
+      <c r="D278" s="40" t="n"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="36" t="n">
+        <v>275</v>
+      </c>
+      <c r="C279" s="37" t="n"/>
+      <c r="D279" s="38" t="n"/>
+    </row>
+    <row r="280">
+      <c r="B280" s="36" t="n">
+        <v>276</v>
+      </c>
+      <c r="C280" s="39" t="n"/>
+      <c r="D280" s="40" t="n"/>
+    </row>
+    <row r="281">
+      <c r="B281" s="36" t="n">
+        <v>277</v>
+      </c>
+      <c r="C281" s="37" t="n"/>
+      <c r="D281" s="38" t="n"/>
+    </row>
+    <row r="282">
+      <c r="B282" s="36" t="n">
+        <v>278</v>
+      </c>
+      <c r="C282" s="39" t="n"/>
+      <c r="D282" s="40" t="n"/>
+    </row>
+    <row r="283">
+      <c r="B283" s="36" t="n">
+        <v>279</v>
+      </c>
+      <c r="C283" s="37" t="n"/>
+      <c r="D283" s="38" t="n"/>
+    </row>
+    <row r="284">
+      <c r="B284" s="36" t="n">
+        <v>280</v>
+      </c>
+      <c r="C284" s="39" t="n"/>
+      <c r="D284" s="40" t="n"/>
+    </row>
+    <row r="285">
+      <c r="B285" s="36" t="n">
+        <v>281</v>
+      </c>
+      <c r="C285" s="37" t="n"/>
+      <c r="D285" s="38" t="n"/>
+    </row>
+    <row r="286">
+      <c r="B286" s="36" t="n">
+        <v>282</v>
+      </c>
+      <c r="C286" s="39" t="n"/>
+      <c r="D286" s="40" t="n"/>
+    </row>
+    <row r="287">
+      <c r="B287" s="36" t="n">
+        <v>283</v>
+      </c>
+      <c r="C287" s="37" t="n"/>
+      <c r="D287" s="38" t="n"/>
+    </row>
+    <row r="288">
+      <c r="B288" s="36" t="n">
+        <v>284</v>
+      </c>
+      <c r="C288" s="39" t="n"/>
+      <c r="D288" s="40" t="n"/>
+    </row>
+    <row r="289">
+      <c r="B289" s="36" t="n">
+        <v>285</v>
+      </c>
+      <c r="C289" s="37" t="n"/>
+      <c r="D289" s="38" t="n"/>
+    </row>
+    <row r="290">
+      <c r="B290" s="36" t="n">
+        <v>286</v>
+      </c>
+      <c r="C290" s="39" t="n"/>
+      <c r="D290" s="40" t="n"/>
+    </row>
+    <row r="291">
+      <c r="B291" s="36" t="n">
+        <v>287</v>
+      </c>
+      <c r="C291" s="37" t="n"/>
+      <c r="D291" s="38" t="n"/>
+    </row>
+    <row r="292">
+      <c r="B292" s="36" t="n">
+        <v>288</v>
+      </c>
+      <c r="C292" s="39" t="n"/>
+      <c r="D292" s="40" t="n"/>
+    </row>
+    <row r="293">
+      <c r="B293" s="36" t="n">
+        <v>289</v>
+      </c>
+      <c r="C293" s="37" t="n"/>
+      <c r="D293" s="38" t="n"/>
+    </row>
+    <row r="294">
+      <c r="B294" s="36" t="n">
+        <v>290</v>
+      </c>
+      <c r="C294" s="39" t="n"/>
+      <c r="D294" s="40" t="n"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="36" t="n">
+        <v>291</v>
+      </c>
+      <c r="C295" s="37" t="n"/>
+      <c r="D295" s="38" t="n"/>
+    </row>
+    <row r="296">
+      <c r="B296" s="36" t="n">
+        <v>292</v>
+      </c>
+      <c r="C296" s="39" t="n"/>
+      <c r="D296" s="40" t="n"/>
+    </row>
+    <row r="297">
+      <c r="B297" s="36" t="n">
+        <v>293</v>
+      </c>
+      <c r="C297" s="37" t="n"/>
+      <c r="D297" s="38" t="n"/>
+    </row>
+    <row r="298">
+      <c r="B298" s="36" t="n">
+        <v>294</v>
+      </c>
+      <c r="C298" s="39" t="n"/>
+      <c r="D298" s="40" t="n"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="36" t="n">
+        <v>295</v>
+      </c>
+      <c r="C299" s="37" t="n"/>
+      <c r="D299" s="38" t="n"/>
+    </row>
+    <row r="300">
+      <c r="B300" s="36" t="n">
+        <v>296</v>
+      </c>
+      <c r="C300" s="39" t="n"/>
+      <c r="D300" s="40" t="n"/>
+    </row>
+    <row r="301">
+      <c r="B301" s="36" t="n">
+        <v>297</v>
+      </c>
+      <c r="C301" s="37" t="n"/>
+      <c r="D301" s="38" t="n"/>
+    </row>
+    <row r="302">
+      <c r="B302" s="36" t="n">
+        <v>298</v>
+      </c>
+      <c r="C302" s="39" t="n"/>
+      <c r="D302" s="40" t="n"/>
+    </row>
+    <row r="303">
+      <c r="B303" s="36" t="n">
+        <v>299</v>
+      </c>
+      <c r="C303" s="37" t="n"/>
+      <c r="D303" s="38" t="n"/>
+    </row>
+    <row r="304">
+      <c r="B304" s="36" t="n">
+        <v>300</v>
+      </c>
+      <c r="C304" s="39" t="n"/>
+      <c r="D304" s="40" t="n"/>
+    </row>
+    <row r="305">
+      <c r="B305" s="36" t="n">
+        <v>301</v>
+      </c>
+      <c r="C305" s="37" t="n"/>
+      <c r="D305" s="38" t="n"/>
+    </row>
+    <row r="306">
+      <c r="B306" s="36" t="n">
+        <v>302</v>
+      </c>
+      <c r="C306" s="39" t="n"/>
+      <c r="D306" s="40" t="n"/>
+    </row>
+    <row r="307">
+      <c r="B307" s="36" t="n">
+        <v>303</v>
+      </c>
+      <c r="C307" s="37" t="n"/>
+      <c r="D307" s="38" t="n"/>
+    </row>
+    <row r="308">
+      <c r="B308" s="36" t="n">
+        <v>304</v>
+      </c>
+      <c r="C308" s="39" t="n"/>
+      <c r="D308" s="40" t="n"/>
+    </row>
+    <row r="309">
+      <c r="B309" s="36" t="n">
+        <v>305</v>
+      </c>
+      <c r="C309" s="37" t="n"/>
+      <c r="D309" s="38" t="n"/>
+    </row>
+    <row r="310">
+      <c r="B310" s="36" t="n">
+        <v>306</v>
+      </c>
+      <c r="C310" s="39" t="n"/>
+      <c r="D310" s="40" t="n"/>
+    </row>
+    <row r="311">
+      <c r="B311" s="36" t="n">
+        <v>307</v>
+      </c>
+      <c r="C311" s="37" t="n"/>
+      <c r="D311" s="38" t="n"/>
+    </row>
+    <row r="312">
+      <c r="B312" s="36" t="n">
+        <v>308</v>
+      </c>
+      <c r="C312" s="39" t="n"/>
+      <c r="D312" s="40" t="n"/>
+    </row>
+    <row r="313">
+      <c r="B313" s="36" t="n">
+        <v>309</v>
+      </c>
+      <c r="C313" s="37" t="n"/>
+      <c r="D313" s="38" t="n"/>
+    </row>
+    <row r="314">
+      <c r="B314" s="36" t="n">
+        <v>310</v>
+      </c>
+      <c r="C314" s="39" t="n"/>
+      <c r="D314" s="40" t="n"/>
+    </row>
+    <row r="315">
+      <c r="B315" s="36" t="n">
+        <v>311</v>
+      </c>
+      <c r="C315" s="37" t="n"/>
+      <c r="D315" s="38" t="n"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="36" t="n">
+        <v>312</v>
+      </c>
+      <c r="C316" s="39" t="n"/>
+      <c r="D316" s="40" t="n"/>
+    </row>
+    <row r="317">
+      <c r="B317" s="36" t="n">
+        <v>313</v>
+      </c>
+      <c r="C317" s="37" t="n"/>
+      <c r="D317" s="38" t="n"/>
+    </row>
+    <row r="318">
+      <c r="B318" s="36" t="n">
+        <v>314</v>
+      </c>
+      <c r="C318" s="39" t="n"/>
+      <c r="D318" s="40" t="n"/>
+    </row>
+    <row r="319">
+      <c r="B319" s="36" t="n">
+        <v>315</v>
+      </c>
+      <c r="C319" s="37" t="n"/>
+      <c r="D319" s="38" t="n"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="36" t="n">
+        <v>316</v>
+      </c>
+      <c r="C320" s="39" t="n"/>
+      <c r="D320" s="40" t="n"/>
+    </row>
+    <row r="321">
+      <c r="B321" s="36" t="n">
+        <v>317</v>
+      </c>
+      <c r="C321" s="37" t="n"/>
+      <c r="D321" s="38" t="n"/>
+    </row>
+    <row r="322">
+      <c r="B322" s="36" t="n">
+        <v>318</v>
+      </c>
+      <c r="C322" s="39" t="n"/>
+      <c r="D322" s="40" t="n"/>
+    </row>
+    <row r="323">
+      <c r="B323" s="36" t="n">
+        <v>319</v>
+      </c>
+      <c r="C323" s="37" t="n"/>
+      <c r="D323" s="38" t="n"/>
+    </row>
+    <row r="324">
+      <c r="B324" s="36" t="n">
+        <v>320</v>
+      </c>
+      <c r="C324" s="39" t="n"/>
+      <c r="D324" s="40" t="n"/>
+    </row>
+    <row r="325">
+      <c r="B325" s="36" t="n">
+        <v>321</v>
+      </c>
+      <c r="C325" s="37" t="n"/>
+      <c r="D325" s="38" t="n"/>
+    </row>
+    <row r="326">
+      <c r="B326" s="36" t="n">
+        <v>322</v>
+      </c>
+      <c r="C326" s="39" t="n"/>
+      <c r="D326" s="40" t="n"/>
+    </row>
+    <row r="327">
+      <c r="B327" s="36" t="n">
+        <v>323</v>
+      </c>
+      <c r="C327" s="37" t="n"/>
+      <c r="D327" s="38" t="n"/>
+    </row>
+    <row r="328">
+      <c r="B328" s="36" t="n">
+        <v>324</v>
+      </c>
+      <c r="C328" s="39" t="n"/>
+      <c r="D328" s="40" t="n"/>
+    </row>
+    <row r="329">
+      <c r="B329" s="36" t="n">
+        <v>325</v>
+      </c>
+      <c r="C329" s="37" t="n"/>
+      <c r="D329" s="38" t="n"/>
+    </row>
+    <row r="330">
+      <c r="B330" s="36" t="n">
+        <v>326</v>
+      </c>
+      <c r="C330" s="39" t="n"/>
+      <c r="D330" s="40" t="n"/>
+    </row>
+    <row r="331">
+      <c r="B331" s="36" t="n">
+        <v>327</v>
+      </c>
+      <c r="C331" s="37" t="n"/>
+      <c r="D331" s="38" t="n"/>
+    </row>
+    <row r="332">
+      <c r="B332" s="36" t="n">
+        <v>328</v>
+      </c>
+      <c r="C332" s="39" t="n"/>
+      <c r="D332" s="40" t="n"/>
+    </row>
+    <row r="333">
+      <c r="B333" s="36" t="n">
+        <v>329</v>
+      </c>
+      <c r="C333" s="37" t="n"/>
+      <c r="D333" s="38" t="n"/>
+    </row>
+    <row r="334">
+      <c r="B334" s="36" t="n">
+        <v>330</v>
+      </c>
+      <c r="C334" s="39" t="n"/>
+      <c r="D334" s="40" t="n"/>
+    </row>
+    <row r="335">
+      <c r="B335" s="36" t="n">
+        <v>331</v>
+      </c>
+      <c r="C335" s="37" t="n"/>
+      <c r="D335" s="38" t="n"/>
+    </row>
+    <row r="336">
+      <c r="B336" s="36" t="n">
+        <v>332</v>
+      </c>
+      <c r="C336" s="39" t="n"/>
+      <c r="D336" s="40" t="n"/>
+    </row>
+    <row r="337">
+      <c r="B337" s="36" t="n">
+        <v>333</v>
+      </c>
+      <c r="C337" s="37" t="n"/>
+      <c r="D337" s="38" t="n"/>
+    </row>
+    <row r="338">
+      <c r="B338" s="36" t="n">
+        <v>334</v>
+      </c>
+      <c r="C338" s="39" t="n"/>
+      <c r="D338" s="40" t="n"/>
+    </row>
+    <row r="339">
+      <c r="B339" s="36" t="n">
+        <v>335</v>
+      </c>
+      <c r="C339" s="37" t="n"/>
+      <c r="D339" s="38" t="n"/>
+    </row>
+    <row r="340">
+      <c r="B340" s="36" t="n">
+        <v>336</v>
+      </c>
+      <c r="C340" s="39" t="n"/>
+      <c r="D340" s="40" t="n"/>
+    </row>
+    <row r="341">
+      <c r="B341" s="36" t="n">
+        <v>337</v>
+      </c>
+      <c r="C341" s="37" t="n"/>
+      <c r="D341" s="38" t="n"/>
+    </row>
+    <row r="342">
+      <c r="B342" s="36" t="n">
+        <v>338</v>
+      </c>
+      <c r="C342" s="39" t="n"/>
+      <c r="D342" s="40" t="n"/>
+    </row>
+    <row r="343">
+      <c r="B343" s="36" t="n">
+        <v>339</v>
+      </c>
+      <c r="C343" s="37" t="n"/>
+      <c r="D343" s="38" t="n"/>
+    </row>
+    <row r="344">
+      <c r="B344" s="36" t="n">
+        <v>340</v>
+      </c>
+      <c r="C344" s="39" t="n"/>
+      <c r="D344" s="40" t="n"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="36" t="n">
+        <v>341</v>
+      </c>
+      <c r="C345" s="37" t="n"/>
+      <c r="D345" s="38" t="n"/>
+    </row>
+    <row r="346">
+      <c r="B346" s="36" t="n">
+        <v>342</v>
+      </c>
+      <c r="C346" s="39" t="n"/>
+      <c r="D346" s="40" t="n"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="36" t="n">
+        <v>343</v>
+      </c>
+      <c r="C347" s="37" t="n"/>
+      <c r="D347" s="38" t="n"/>
+    </row>
+    <row r="348">
+      <c r="B348" s="36" t="n">
+        <v>344</v>
+      </c>
+      <c r="C348" s="39" t="n"/>
+      <c r="D348" s="40" t="n"/>
+    </row>
+    <row r="349">
+      <c r="B349" s="36" t="n">
+        <v>345</v>
+      </c>
+      <c r="C349" s="37" t="n"/>
+      <c r="D349" s="38" t="n"/>
+    </row>
+    <row r="350">
+      <c r="B350" s="36" t="n">
+        <v>346</v>
+      </c>
+      <c r="C350" s="39" t="n"/>
+      <c r="D350" s="40" t="n"/>
+    </row>
+    <row r="351">
+      <c r="B351" s="36" t="n">
+        <v>347</v>
+      </c>
+      <c r="C351" s="37" t="n"/>
+      <c r="D351" s="38" t="n"/>
+    </row>
+    <row r="352">
+      <c r="B352" s="36" t="n">
+        <v>348</v>
+      </c>
+      <c r="C352" s="39" t="n"/>
+      <c r="D352" s="40" t="n"/>
+    </row>
+    <row r="353">
+      <c r="B353" s="36" t="n">
+        <v>349</v>
+      </c>
+      <c r="C353" s="37" t="n"/>
+      <c r="D353" s="38" t="n"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="36" t="n">
+        <v>350</v>
+      </c>
+      <c r="C354" s="39" t="n"/>
+      <c r="D354" s="40" t="n"/>
+    </row>
+    <row r="355">
+      <c r="B355" s="36" t="n">
+        <v>351</v>
+      </c>
+      <c r="C355" s="37" t="n"/>
+      <c r="D355" s="38" t="n"/>
+    </row>
+    <row r="356">
+      <c r="B356" s="36" t="n">
+        <v>352</v>
+      </c>
+      <c r="C356" s="39" t="n"/>
+      <c r="D356" s="40" t="n"/>
+    </row>
+    <row r="357">
+      <c r="B357" s="36" t="n">
+        <v>353</v>
+      </c>
+      <c r="C357" s="37" t="n"/>
+      <c r="D357" s="38" t="n"/>
+    </row>
+    <row r="358">
+      <c r="B358" s="36" t="n">
+        <v>354</v>
+      </c>
+      <c r="C358" s="39" t="n"/>
+      <c r="D358" s="40" t="n"/>
+    </row>
+    <row r="359">
+      <c r="B359" s="36" t="n">
+        <v>355</v>
+      </c>
+      <c r="C359" s="37" t="n"/>
+      <c r="D359" s="38" t="n"/>
+    </row>
+    <row r="360">
+      <c r="B360" s="36" t="n">
+        <v>356</v>
+      </c>
+      <c r="C360" s="39" t="n"/>
+      <c r="D360" s="40" t="n"/>
+    </row>
+    <row r="361">
+      <c r="B361" s="36" t="n">
+        <v>357</v>
+      </c>
+      <c r="C361" s="37" t="n"/>
+      <c r="D361" s="38" t="n"/>
+    </row>
+    <row r="362">
+      <c r="B362" s="36" t="n">
+        <v>358</v>
+      </c>
+      <c r="C362" s="39" t="n"/>
+      <c r="D362" s="40" t="n"/>
+    </row>
+    <row r="363">
+      <c r="B363" s="36" t="n">
+        <v>359</v>
+      </c>
+      <c r="C363" s="37" t="n"/>
+      <c r="D363" s="38" t="n"/>
+    </row>
+    <row r="364">
+      <c r="B364" s="36" t="n">
+        <v>360</v>
+      </c>
+      <c r="C364" s="39" t="n"/>
+      <c r="D364" s="40" t="n"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="36" t="n">
+        <v>361</v>
+      </c>
+      <c r="C365" s="37" t="n"/>
+      <c r="D365" s="38" t="n"/>
+    </row>
+    <row r="366">
+      <c r="B366" s="36" t="n">
+        <v>362</v>
+      </c>
+      <c r="C366" s="39" t="n"/>
+      <c r="D366" s="40" t="n"/>
+    </row>
+    <row r="367">
+      <c r="B367" s="36" t="n">
+        <v>363</v>
+      </c>
+      <c r="C367" s="37" t="n"/>
+      <c r="D367" s="38" t="n"/>
+    </row>
+    <row r="368">
+      <c r="B368" s="36" t="n">
+        <v>364</v>
+      </c>
+      <c r="C368" s="39" t="n"/>
+      <c r="D368" s="40" t="n"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="36" t="n">
+        <v>365</v>
+      </c>
+      <c r="C369" s="37" t="n"/>
+      <c r="D369" s="38" t="n"/>
+    </row>
+    <row r="370">
+      <c r="B370" s="36" t="n">
+        <v>366</v>
+      </c>
+      <c r="C370" s="39" t="n"/>
+      <c r="D370" s="40" t="n"/>
+    </row>
+    <row r="371">
+      <c r="B371" s="36" t="n">
+        <v>367</v>
+      </c>
+      <c r="C371" s="37" t="n"/>
+      <c r="D371" s="38" t="n"/>
+    </row>
+    <row r="372">
+      <c r="B372" s="36" t="n">
+        <v>368</v>
+      </c>
+      <c r="C372" s="39" t="n"/>
+      <c r="D372" s="40" t="n"/>
+    </row>
+    <row r="373">
+      <c r="B373" s="36" t="n">
+        <v>369</v>
+      </c>
+      <c r="C373" s="37" t="n"/>
+      <c r="D373" s="38" t="n"/>
+    </row>
+    <row r="374">
+      <c r="B374" s="36" t="n">
+        <v>370</v>
+      </c>
+      <c r="C374" s="39" t="n"/>
+      <c r="D374" s="40" t="n"/>
+    </row>
+    <row r="375">
+      <c r="B375" s="36" t="n">
+        <v>371</v>
+      </c>
+      <c r="C375" s="37" t="n"/>
+      <c r="D375" s="38" t="n"/>
+    </row>
+    <row r="376">
+      <c r="B376" s="36" t="n">
+        <v>372</v>
+      </c>
+      <c r="C376" s="39" t="n"/>
+      <c r="D376" s="40" t="n"/>
+    </row>
+    <row r="377">
+      <c r="B377" s="36" t="n">
+        <v>373</v>
+      </c>
+      <c r="C377" s="37" t="n"/>
+      <c r="D377" s="38" t="n"/>
+    </row>
+    <row r="378">
+      <c r="B378" s="36" t="n">
+        <v>374</v>
+      </c>
+      <c r="C378" s="39" t="n"/>
+      <c r="D378" s="40" t="n"/>
+    </row>
+    <row r="379">
+      <c r="B379" s="36" t="n">
+        <v>375</v>
+      </c>
+      <c r="C379" s="37" t="n"/>
+      <c r="D379" s="38" t="n"/>
+    </row>
+    <row r="380">
+      <c r="B380" s="36" t="n">
+        <v>376</v>
+      </c>
+      <c r="C380" s="39" t="n"/>
+      <c r="D380" s="40" t="n"/>
+    </row>
+    <row r="381">
+      <c r="B381" s="36" t="n">
+        <v>377</v>
+      </c>
+      <c r="C381" s="37" t="n"/>
+      <c r="D381" s="38" t="n"/>
+    </row>
+    <row r="382">
+      <c r="B382" s="36" t="n">
+        <v>378</v>
+      </c>
+      <c r="C382" s="39" t="n"/>
+      <c r="D382" s="40" t="n"/>
+    </row>
+    <row r="383">
+      <c r="B383" s="36" t="n">
+        <v>379</v>
+      </c>
+      <c r="C383" s="37" t="n"/>
+      <c r="D383" s="38" t="n"/>
+    </row>
+    <row r="384">
+      <c r="B384" s="36" t="n">
+        <v>380</v>
+      </c>
+      <c r="C384" s="39" t="n"/>
+      <c r="D384" s="40" t="n"/>
+    </row>
+    <row r="385">
+      <c r="B385" s="36" t="n">
+        <v>381</v>
+      </c>
+      <c r="C385" s="37" t="n"/>
+      <c r="D385" s="38" t="n"/>
+    </row>
+    <row r="386">
+      <c r="B386" s="36" t="n">
+        <v>382</v>
+      </c>
+      <c r="C386" s="39" t="n"/>
+      <c r="D386" s="40" t="n"/>
+    </row>
+    <row r="387">
+      <c r="B387" s="36" t="n">
+        <v>383</v>
+      </c>
+      <c r="C387" s="37" t="n"/>
+      <c r="D387" s="38" t="n"/>
+    </row>
+    <row r="388">
+      <c r="B388" s="36" t="n">
+        <v>384</v>
+      </c>
+      <c r="C388" s="39" t="n"/>
+      <c r="D388" s="40" t="n"/>
+    </row>
+    <row r="389">
+      <c r="B389" s="36" t="n">
+        <v>385</v>
+      </c>
+      <c r="C389" s="37" t="n"/>
+      <c r="D389" s="38" t="n"/>
+    </row>
+    <row r="390">
+      <c r="B390" s="36" t="n">
+        <v>386</v>
+      </c>
+      <c r="C390" s="39" t="n"/>
+      <c r="D390" s="40" t="n"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="36" t="n">
+        <v>387</v>
+      </c>
+      <c r="C391" s="37" t="n"/>
+      <c r="D391" s="38" t="n"/>
+    </row>
+    <row r="392">
+      <c r="B392" s="36" t="n">
+        <v>388</v>
+      </c>
+      <c r="C392" s="39" t="n"/>
+      <c r="D392" s="40" t="n"/>
+    </row>
+    <row r="393">
+      <c r="B393" s="36" t="n">
+        <v>389</v>
+      </c>
+      <c r="C393" s="37" t="n"/>
+      <c r="D393" s="38" t="n"/>
+    </row>
+    <row r="394">
+      <c r="B394" s="36" t="n">
+        <v>390</v>
+      </c>
+      <c r="C394" s="39" t="n"/>
+      <c r="D394" s="40" t="n"/>
+    </row>
+    <row r="395">
+      <c r="B395" s="36" t="n">
+        <v>391</v>
+      </c>
+      <c r="C395" s="37" t="n"/>
+      <c r="D395" s="38" t="n"/>
+    </row>
+    <row r="396">
+      <c r="B396" s="36" t="n">
+        <v>392</v>
+      </c>
+      <c r="C396" s="39" t="n"/>
+      <c r="D396" s="40" t="n"/>
+    </row>
+    <row r="397">
+      <c r="B397" s="36" t="n">
+        <v>393</v>
+      </c>
+      <c r="C397" s="37" t="n"/>
+      <c r="D397" s="38" t="n"/>
+    </row>
+    <row r="398">
+      <c r="B398" s="36" t="n">
+        <v>394</v>
+      </c>
+      <c r="C398" s="39" t="n"/>
+      <c r="D398" s="40" t="n"/>
+    </row>
+    <row r="399">
+      <c r="B399" s="36" t="n">
+        <v>395</v>
+      </c>
+      <c r="C399" s="37" t="n"/>
+      <c r="D399" s="38" t="n"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="36" t="n">
+        <v>396</v>
+      </c>
+      <c r="C400" s="39" t="n"/>
+      <c r="D400" s="40" t="n"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="36" t="n">
+        <v>397</v>
+      </c>
+      <c r="C401" s="37" t="n"/>
+      <c r="D401" s="38" t="n"/>
+    </row>
+    <row r="402">
+      <c r="B402" s="36" t="n">
+        <v>398</v>
+      </c>
+      <c r="C402" s="39" t="n"/>
+      <c r="D402" s="40" t="n"/>
+    </row>
+    <row r="403">
+      <c r="B403" s="36" t="n">
+        <v>399</v>
+      </c>
+      <c r="C403" s="37" t="n"/>
+      <c r="D403" s="38" t="n"/>
+    </row>
+    <row r="404">
+      <c r="B404" s="36" t="n">
+        <v>400</v>
+      </c>
+      <c r="C404" s="39" t="n"/>
+      <c r="D404" s="40" t="n"/>
+    </row>
+    <row r="405">
+      <c r="B405" s="36" t="n">
+        <v>401</v>
+      </c>
+      <c r="C405" s="37" t="n"/>
+      <c r="D405" s="38" t="n"/>
+    </row>
+    <row r="406">
+      <c r="B406" s="36" t="n">
+        <v>402</v>
+      </c>
+      <c r="C406" s="39" t="n"/>
+      <c r="D406" s="40" t="n"/>
+    </row>
+    <row r="407">
+      <c r="B407" s="36" t="n">
+        <v>403</v>
+      </c>
+      <c r="C407" s="37" t="n"/>
+      <c r="D407" s="38" t="n"/>
+    </row>
+    <row r="408">
+      <c r="B408" s="36" t="n">
+        <v>404</v>
+      </c>
+      <c r="C408" s="39" t="n"/>
+      <c r="D408" s="40" t="n"/>
+    </row>
+    <row r="409">
+      <c r="B409" s="36" t="n">
+        <v>405</v>
+      </c>
+      <c r="C409" s="37" t="n"/>
+      <c r="D409" s="38" t="n"/>
+    </row>
+    <row r="410">
+      <c r="B410" s="36" t="n">
+        <v>406</v>
+      </c>
+      <c r="C410" s="39" t="n"/>
+      <c r="D410" s="40" t="n"/>
+    </row>
+    <row r="411">
+      <c r="B411" s="36" t="n">
+        <v>407</v>
+      </c>
+      <c r="C411" s="37" t="n"/>
+      <c r="D411" s="38" t="n"/>
+    </row>
+    <row r="412">
+      <c r="B412" s="36" t="n">
+        <v>408</v>
+      </c>
+      <c r="C412" s="39" t="n"/>
+      <c r="D412" s="40" t="n"/>
+    </row>
+    <row r="413">
+      <c r="B413" s="36" t="n">
+        <v>409</v>
+      </c>
+      <c r="C413" s="37" t="n"/>
+      <c r="D413" s="38" t="n"/>
+    </row>
+    <row r="414">
+      <c r="B414" s="36" t="n">
+        <v>410</v>
+      </c>
+      <c r="C414" s="39" t="n"/>
+      <c r="D414" s="40" t="n"/>
+    </row>
+    <row r="415">
+      <c r="B415" s="36" t="n">
+        <v>411</v>
+      </c>
+      <c r="C415" s="37" t="n"/>
+      <c r="D415" s="38" t="n"/>
+    </row>
+    <row r="416">
+      <c r="B416" s="36" t="n">
+        <v>412</v>
+      </c>
+      <c r="C416" s="39" t="n"/>
+      <c r="D416" s="40" t="n"/>
+    </row>
+    <row r="417">
+      <c r="B417" s="36" t="n">
+        <v>413</v>
+      </c>
+      <c r="C417" s="37" t="n"/>
+      <c r="D417" s="38" t="n"/>
+    </row>
+    <row r="418">
+      <c r="B418" s="36" t="n">
+        <v>414</v>
+      </c>
+      <c r="C418" s="39" t="n"/>
+      <c r="D418" s="40" t="n"/>
+    </row>
+    <row r="419">
+      <c r="B419" s="36" t="n">
+        <v>415</v>
+      </c>
+      <c r="C419" s="37" t="n"/>
+      <c r="D419" s="38" t="n"/>
+    </row>
+    <row r="420">
+      <c r="B420" s="36" t="n">
+        <v>416</v>
+      </c>
+      <c r="C420" s="39" t="n"/>
+      <c r="D420" s="40" t="n"/>
+    </row>
+    <row r="421">
+      <c r="B421" s="36" t="n">
+        <v>417</v>
+      </c>
+      <c r="C421" s="37" t="n"/>
+      <c r="D421" s="38" t="n"/>
+    </row>
+    <row r="422">
+      <c r="B422" s="36" t="n">
+        <v>418</v>
+      </c>
+      <c r="C422" s="39" t="n"/>
+      <c r="D422" s="40" t="n"/>
+    </row>
+    <row r="423">
+      <c r="B423" s="36" t="n">
+        <v>419</v>
+      </c>
+      <c r="C423" s="37" t="n"/>
+      <c r="D423" s="38" t="n"/>
+    </row>
+    <row r="424">
+      <c r="B424" s="36" t="n">
+        <v>420</v>
+      </c>
+      <c r="C424" s="39" t="n"/>
+      <c r="D424" s="40" t="n"/>
+    </row>
+    <row r="425">
+      <c r="B425" s="36" t="n">
+        <v>421</v>
+      </c>
+      <c r="C425" s="37" t="n"/>
+      <c r="D425" s="38" t="n"/>
+    </row>
+    <row r="426">
+      <c r="B426" s="36" t="n">
+        <v>422</v>
+      </c>
+      <c r="C426" s="39" t="n"/>
+      <c r="D426" s="40" t="n"/>
+    </row>
+    <row r="427">
+      <c r="B427" s="36" t="n">
+        <v>423</v>
+      </c>
+      <c r="C427" s="37" t="n"/>
+      <c r="D427" s="38" t="n"/>
+    </row>
+    <row r="428">
+      <c r="B428" s="36" t="n">
+        <v>424</v>
+      </c>
+      <c r="C428" s="39" t="n"/>
+      <c r="D428" s="40" t="n"/>
+    </row>
+    <row r="429">
+      <c r="B429" s="36" t="n">
+        <v>425</v>
+      </c>
+      <c r="C429" s="37" t="n"/>
+      <c r="D429" s="38" t="n"/>
+    </row>
+    <row r="430">
+      <c r="B430" s="36" t="n">
+        <v>426</v>
+      </c>
+      <c r="C430" s="39" t="n"/>
+      <c r="D430" s="40" t="n"/>
+    </row>
+    <row r="431">
+      <c r="B431" s="36" t="n">
+        <v>427</v>
+      </c>
+      <c r="C431" s="37" t="n"/>
+      <c r="D431" s="38" t="n"/>
+    </row>
+    <row r="432">
+      <c r="B432" s="36" t="n">
+        <v>428</v>
+      </c>
+      <c r="C432" s="39" t="n"/>
+      <c r="D432" s="40" t="n"/>
+    </row>
+    <row r="433">
+      <c r="B433" s="36" t="n">
+        <v>429</v>
+      </c>
+      <c r="C433" s="37" t="n"/>
+      <c r="D433" s="38" t="n"/>
+    </row>
+    <row r="434">
+      <c r="B434" s="36" t="n">
+        <v>430</v>
+      </c>
+      <c r="C434" s="39" t="n"/>
+      <c r="D434" s="40" t="n"/>
+    </row>
+    <row r="435">
+      <c r="B435" s="36" t="n">
+        <v>431</v>
+      </c>
+      <c r="C435" s="37" t="n"/>
+      <c r="D435" s="38" t="n"/>
+    </row>
+    <row r="436">
+      <c r="B436" s="36" t="n">
+        <v>432</v>
+      </c>
+      <c r="C436" s="39" t="n"/>
+      <c r="D436" s="40" t="n"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="36" t="n">
+        <v>433</v>
+      </c>
+      <c r="C437" s="37" t="n"/>
+      <c r="D437" s="38" t="n"/>
+    </row>
+    <row r="438">
+      <c r="B438" s="36" t="n">
+        <v>434</v>
+      </c>
+      <c r="C438" s="39" t="n"/>
+      <c r="D438" s="40" t="n"/>
+    </row>
+    <row r="439">
+      <c r="B439" s="36" t="n">
+        <v>435</v>
+      </c>
+      <c r="C439" s="37" t="n"/>
+      <c r="D439" s="38" t="n"/>
+    </row>
+    <row r="440">
+      <c r="B440" s="36" t="n">
+        <v>436</v>
+      </c>
+      <c r="C440" s="39" t="n"/>
+      <c r="D440" s="40" t="n"/>
+    </row>
+    <row r="441">
+      <c r="B441" s="36" t="n">
+        <v>437</v>
+      </c>
+      <c r="C441" s="37" t="n"/>
+      <c r="D441" s="38" t="n"/>
+    </row>
+    <row r="442">
+      <c r="B442" s="36" t="n">
+        <v>438</v>
+      </c>
+      <c r="C442" s="39" t="n"/>
+      <c r="D442" s="40" t="n"/>
+    </row>
+    <row r="443">
+      <c r="B443" s="36" t="n">
+        <v>439</v>
+      </c>
+      <c r="C443" s="37" t="n"/>
+      <c r="D443" s="38" t="n"/>
+    </row>
+    <row r="444">
+      <c r="B444" s="36" t="n">
+        <v>440</v>
+      </c>
+      <c r="C444" s="39" t="n"/>
+      <c r="D444" s="40" t="n"/>
+    </row>
+    <row r="445">
+      <c r="B445" s="36" t="n">
+        <v>441</v>
+      </c>
+      <c r="C445" s="37" t="n"/>
+      <c r="D445" s="38" t="n"/>
+    </row>
+    <row r="446">
+      <c r="B446" s="36" t="n">
+        <v>442</v>
+      </c>
+      <c r="C446" s="39" t="n"/>
+      <c r="D446" s="40" t="n"/>
+    </row>
+    <row r="447">
+      <c r="B447" s="36" t="n">
+        <v>443</v>
+      </c>
+      <c r="C447" s="37" t="n"/>
+      <c r="D447" s="38" t="n"/>
+    </row>
+    <row r="448">
+      <c r="B448" s="36" t="n">
+        <v>444</v>
+      </c>
+      <c r="C448" s="39" t="n"/>
+      <c r="D448" s="40" t="n"/>
+    </row>
+    <row r="449">
+      <c r="B449" s="36" t="n">
+        <v>445</v>
+      </c>
+      <c r="C449" s="37" t="n"/>
+      <c r="D449" s="38" t="n"/>
+    </row>
+    <row r="450">
+      <c r="B450" s="36" t="n">
+        <v>446</v>
+      </c>
+      <c r="C450" s="39" t="n"/>
+      <c r="D450" s="40" t="n"/>
+    </row>
+    <row r="451">
+      <c r="B451" s="36" t="n">
+        <v>447</v>
+      </c>
+      <c r="C451" s="37" t="n"/>
+      <c r="D451" s="38" t="n"/>
+    </row>
+    <row r="452">
+      <c r="B452" s="36" t="n">
+        <v>448</v>
+      </c>
+      <c r="C452" s="39" t="n"/>
+      <c r="D452" s="40" t="n"/>
+    </row>
+    <row r="453">
+      <c r="B453" s="36" t="n">
+        <v>449</v>
+      </c>
+      <c r="C453" s="37" t="n"/>
+      <c r="D453" s="38" t="n"/>
+    </row>
+    <row r="454">
+      <c r="B454" s="36" t="n">
+        <v>450</v>
+      </c>
+      <c r="C454" s="39" t="n"/>
+      <c r="D454" s="40" t="n"/>
+    </row>
+    <row r="455">
+      <c r="B455" s="36" t="n">
+        <v>451</v>
+      </c>
+      <c r="C455" s="37" t="n"/>
+      <c r="D455" s="38" t="n"/>
+    </row>
+    <row r="456">
+      <c r="B456" s="36" t="n">
+        <v>452</v>
+      </c>
+      <c r="C456" s="39" t="n"/>
+      <c r="D456" s="40" t="n"/>
+    </row>
+    <row r="457">
+      <c r="B457" s="36" t="n">
+        <v>453</v>
+      </c>
+      <c r="C457" s="37" t="n"/>
+      <c r="D457" s="38" t="n"/>
+    </row>
+    <row r="458">
+      <c r="B458" s="36" t="n">
+        <v>454</v>
+      </c>
+      <c r="C458" s="39" t="n"/>
+      <c r="D458" s="40" t="n"/>
+    </row>
+    <row r="459">
+      <c r="B459" s="36" t="n">
+        <v>455</v>
+      </c>
+      <c r="C459" s="37" t="n"/>
+      <c r="D459" s="38" t="n"/>
+    </row>
+    <row r="460">
+      <c r="B460" s="36" t="n">
+        <v>456</v>
+      </c>
+      <c r="C460" s="39" t="n"/>
+      <c r="D460" s="40" t="n"/>
+    </row>
+    <row r="461">
+      <c r="B461" s="36" t="n">
+        <v>457</v>
+      </c>
+      <c r="C461" s="37" t="n"/>
+      <c r="D461" s="38" t="n"/>
+    </row>
+    <row r="462">
+      <c r="B462" s="36" t="n">
+        <v>458</v>
+      </c>
+      <c r="C462" s="39" t="n"/>
+      <c r="D462" s="40" t="n"/>
+    </row>
+    <row r="463">
+      <c r="B463" s="36" t="n">
+        <v>459</v>
+      </c>
+      <c r="C463" s="37" t="n"/>
+      <c r="D463" s="38" t="n"/>
+    </row>
+    <row r="464">
+      <c r="B464" s="36" t="n">
+        <v>460</v>
+      </c>
+      <c r="C464" s="39" t="n"/>
+      <c r="D464" s="40" t="n"/>
+    </row>
+    <row r="465">
+      <c r="B465" s="36" t="n">
+        <v>461</v>
+      </c>
+      <c r="C465" s="37" t="n"/>
+      <c r="D465" s="38" t="n"/>
+    </row>
+    <row r="466">
+      <c r="B466" s="36" t="n">
+        <v>462</v>
+      </c>
+      <c r="C466" s="39" t="n"/>
+      <c r="D466" s="40" t="n"/>
+    </row>
+    <row r="467">
+      <c r="B467" s="36" t="n">
+        <v>463</v>
+      </c>
+      <c r="C467" s="37" t="n"/>
+      <c r="D467" s="38" t="n"/>
+    </row>
+    <row r="468">
+      <c r="B468" s="36" t="n">
+        <v>464</v>
+      </c>
+      <c r="C468" s="39" t="n"/>
+      <c r="D468" s="40" t="n"/>
+    </row>
+    <row r="469">
+      <c r="B469" s="36" t="n">
+        <v>465</v>
+      </c>
+      <c r="C469" s="37" t="n"/>
+      <c r="D469" s="38" t="n"/>
+    </row>
+    <row r="470">
+      <c r="B470" s="36" t="n">
+        <v>466</v>
+      </c>
+      <c r="C470" s="39" t="n"/>
+      <c r="D470" s="40" t="n"/>
+    </row>
+    <row r="471">
+      <c r="B471" s="36" t="n">
+        <v>467</v>
+      </c>
+      <c r="C471" s="37" t="n"/>
+      <c r="D471" s="38" t="n"/>
+    </row>
+    <row r="472">
+      <c r="B472" s="36" t="n">
+        <v>468</v>
+      </c>
+      <c r="C472" s="39" t="n"/>
+      <c r="D472" s="40" t="n"/>
+    </row>
+    <row r="473">
+      <c r="B473" s="36" t="n">
+        <v>469</v>
+      </c>
+      <c r="C473" s="37" t="n"/>
+      <c r="D473" s="38" t="n"/>
+    </row>
+    <row r="474">
+      <c r="B474" s="36" t="n">
+        <v>470</v>
+      </c>
+      <c r="C474" s="39" t="n"/>
+      <c r="D474" s="40" t="n"/>
+    </row>
+    <row r="475">
+      <c r="B475" s="36" t="n">
+        <v>471</v>
+      </c>
+      <c r="C475" s="37" t="n"/>
+      <c r="D475" s="38" t="n"/>
+    </row>
+    <row r="476">
+      <c r="B476" s="36" t="n">
+        <v>472</v>
+      </c>
+      <c r="C476" s="39" t="n"/>
+      <c r="D476" s="40" t="n"/>
+    </row>
+    <row r="477">
+      <c r="B477" s="36" t="n">
+        <v>473</v>
+      </c>
+      <c r="C477" s="37" t="n"/>
+      <c r="D477" s="38" t="n"/>
+    </row>
+    <row r="478">
+      <c r="B478" s="36" t="n">
+        <v>474</v>
+      </c>
+      <c r="C478" s="39" t="n"/>
+      <c r="D478" s="40" t="n"/>
+    </row>
+    <row r="479">
+      <c r="B479" s="36" t="n">
+        <v>475</v>
+      </c>
+      <c r="C479" s="37" t="n"/>
+      <c r="D479" s="38" t="n"/>
+    </row>
+    <row r="480">
+      <c r="B480" s="36" t="n">
+        <v>476</v>
+      </c>
+      <c r="C480" s="39" t="n"/>
+      <c r="D480" s="40" t="n"/>
+    </row>
+    <row r="481">
+      <c r="B481" s="36" t="n">
+        <v>477</v>
+      </c>
+      <c r="C481" s="37" t="n"/>
+      <c r="D481" s="38" t="n"/>
+    </row>
+    <row r="482">
+      <c r="B482" s="36" t="n">
+        <v>478</v>
+      </c>
+      <c r="C482" s="39" t="n"/>
+      <c r="D482" s="40" t="n"/>
+    </row>
+    <row r="483">
+      <c r="B483" s="36" t="n">
+        <v>479</v>
+      </c>
+      <c r="C483" s="37" t="n"/>
+      <c r="D483" s="38" t="n"/>
+    </row>
+    <row r="484">
+      <c r="B484" s="36" t="n">
+        <v>480</v>
+      </c>
+      <c r="C484" s="39" t="n"/>
+      <c r="D484" s="40" t="n"/>
+    </row>
+    <row r="485">
+      <c r="B485" s="36" t="n">
+        <v>481</v>
+      </c>
+      <c r="C485" s="37" t="n"/>
+      <c r="D485" s="38" t="n"/>
+    </row>
+    <row r="486">
+      <c r="B486" s="36" t="n">
+        <v>482</v>
+      </c>
+      <c r="C486" s="39" t="n"/>
+      <c r="D486" s="40" t="n"/>
+    </row>
+    <row r="487">
+      <c r="B487" s="36" t="n">
+        <v>483</v>
+      </c>
+      <c r="C487" s="37" t="n"/>
+      <c r="D487" s="38" t="n"/>
+    </row>
+    <row r="488">
+      <c r="B488" s="36" t="n">
+        <v>484</v>
+      </c>
+      <c r="C488" s="39" t="n"/>
+      <c r="D488" s="40" t="n"/>
+    </row>
+    <row r="489">
+      <c r="B489" s="36" t="n">
+        <v>485</v>
+      </c>
+      <c r="C489" s="37" t="n"/>
+      <c r="D489" s="38" t="n"/>
+    </row>
+    <row r="490">
+      <c r="B490" s="36" t="n">
+        <v>486</v>
+      </c>
+      <c r="C490" s="39" t="n"/>
+      <c r="D490" s="40" t="n"/>
+    </row>
+    <row r="491">
+      <c r="B491" s="36" t="n">
+        <v>487</v>
+      </c>
+      <c r="C491" s="37" t="n"/>
+      <c r="D491" s="38" t="n"/>
+    </row>
+    <row r="492">
+      <c r="B492" s="36" t="n">
+        <v>488</v>
+      </c>
+      <c r="C492" s="39" t="n"/>
+      <c r="D492" s="40" t="n"/>
+    </row>
+    <row r="493">
+      <c r="B493" s="36" t="n">
+        <v>489</v>
+      </c>
+      <c r="C493" s="37" t="n"/>
+      <c r="D493" s="38" t="n"/>
+    </row>
+    <row r="494">
+      <c r="B494" s="36" t="n">
+        <v>490</v>
+      </c>
+      <c r="C494" s="39" t="n"/>
+      <c r="D494" s="40" t="n"/>
+    </row>
+    <row r="495">
+      <c r="B495" s="36" t="n">
+        <v>491</v>
+      </c>
+      <c r="C495" s="37" t="n"/>
+      <c r="D495" s="38" t="n"/>
+    </row>
+    <row r="496">
+      <c r="B496" s="36" t="n">
+        <v>492</v>
+      </c>
+      <c r="C496" s="39" t="n"/>
+      <c r="D496" s="40" t="n"/>
+    </row>
+    <row r="497">
+      <c r="B497" s="36" t="n">
+        <v>493</v>
+      </c>
+      <c r="C497" s="37" t="n"/>
+      <c r="D497" s="38" t="n"/>
+    </row>
+    <row r="498">
+      <c r="B498" s="36" t="n">
+        <v>494</v>
+      </c>
+      <c r="C498" s="39" t="n"/>
+      <c r="D498" s="40" t="n"/>
+    </row>
+    <row r="499">
+      <c r="B499" s="36" t="n">
+        <v>495</v>
+      </c>
+      <c r="C499" s="37" t="n"/>
+      <c r="D499" s="38" t="n"/>
+    </row>
+    <row r="500">
+      <c r="B500" s="36" t="n">
+        <v>496</v>
+      </c>
+      <c r="C500" s="39" t="n"/>
+      <c r="D500" s="40" t="n"/>
+    </row>
+    <row r="501">
+      <c r="B501" s="36" t="n">
+        <v>497</v>
+      </c>
+      <c r="C501" s="37" t="n"/>
+      <c r="D501" s="38" t="n"/>
+    </row>
+    <row r="502">
+      <c r="B502" s="36" t="n">
+        <v>498</v>
+      </c>
+      <c r="C502" s="39" t="n"/>
+      <c r="D502" s="40" t="n"/>
+    </row>
+    <row r="503">
+      <c r="B503" s="36" t="n">
+        <v>499</v>
+      </c>
+      <c r="C503" s="37" t="n"/>
+      <c r="D503" s="38" t="n"/>
+    </row>
+    <row r="504">
+      <c r="B504" s="36" t="n">
+        <v>500</v>
+      </c>
+      <c r="C504" s="39" t="n"/>
+      <c r="D504" s="40" t="n"/>
+    </row>
+    <row r="505">
+      <c r="B505" s="36" t="n">
+        <v>501</v>
+      </c>
+      <c r="C505" s="37" t="n"/>
+      <c r="D505" s="38" t="n"/>
+    </row>
+    <row r="506">
+      <c r="B506" s="36" t="n">
+        <v>502</v>
+      </c>
+      <c r="C506" s="39" t="n"/>
+      <c r="D506" s="40" t="n"/>
+    </row>
+    <row r="507">
+      <c r="B507" s="36" t="n">
+        <v>503</v>
+      </c>
+      <c r="C507" s="37" t="n"/>
+      <c r="D507" s="38" t="n"/>
+    </row>
+    <row r="508">
+      <c r="B508" s="36" t="n">
+        <v>504</v>
+      </c>
+      <c r="C508" s="39" t="n"/>
+      <c r="D508" s="40" t="n"/>
+    </row>
+    <row r="509">
+      <c r="B509" s="36" t="n">
+        <v>505</v>
+      </c>
+      <c r="C509" s="37" t="n"/>
+      <c r="D509" s="38" t="n"/>
+    </row>
+    <row r="510">
+      <c r="B510" s="36" t="n">
+        <v>506</v>
+      </c>
+      <c r="C510" s="39" t="n"/>
+      <c r="D510" s="40" t="n"/>
+    </row>
+    <row r="511">
+      <c r="B511" s="36" t="n">
+        <v>507</v>
+      </c>
+      <c r="C511" s="37" t="n"/>
+      <c r="D511" s="38" t="n"/>
+    </row>
+    <row r="512">
+      <c r="B512" s="36" t="n">
+        <v>508</v>
+      </c>
+      <c r="C512" s="39" t="n"/>
+      <c r="D512" s="40" t="n"/>
+    </row>
+    <row r="513">
+      <c r="B513" s="36" t="n">
+        <v>509</v>
+      </c>
+      <c r="C513" s="37" t="n"/>
+      <c r="D513" s="38" t="n"/>
+    </row>
+    <row r="514">
+      <c r="B514" s="36" t="n">
+        <v>510</v>
+      </c>
+      <c r="C514" s="39" t="n"/>
+      <c r="D514" s="40" t="n"/>
+    </row>
+    <row r="515">
+      <c r="B515" s="36" t="n">
+        <v>511</v>
+      </c>
+      <c r="C515" s="37" t="n"/>
+      <c r="D515" s="38" t="n"/>
+    </row>
+    <row r="516">
+      <c r="B516" s="36" t="n">
+        <v>512</v>
+      </c>
+      <c r="C516" s="39" t="n"/>
+      <c r="D516" s="40" t="n"/>
+    </row>
+    <row r="517">
+      <c r="B517" s="36" t="n">
+        <v>513</v>
+      </c>
+      <c r="C517" s="37" t="n"/>
+      <c r="D517" s="38" t="n"/>
+    </row>
+    <row r="518">
+      <c r="B518" s="36" t="n">
+        <v>514</v>
+      </c>
+      <c r="C518" s="39" t="n"/>
+      <c r="D518" s="40" t="n"/>
+    </row>
+    <row r="519">
+      <c r="B519" s="36" t="n">
+        <v>515</v>
+      </c>
+      <c r="C519" s="37" t="n"/>
+      <c r="D519" s="38" t="n"/>
+    </row>
+    <row r="520">
+      <c r="B520" s="36" t="n">
+        <v>516</v>
+      </c>
+      <c r="C520" s="39" t="n"/>
+      <c r="D520" s="40" t="n"/>
+    </row>
+    <row r="521">
+      <c r="B521" s="36" t="n">
+        <v>517</v>
+      </c>
+      <c r="C521" s="37" t="n"/>
+      <c r="D521" s="38" t="n"/>
+    </row>
+    <row r="522">
+      <c r="B522" s="36" t="n">
+        <v>518</v>
+      </c>
+      <c r="C522" s="39" t="n"/>
+      <c r="D522" s="40" t="n"/>
+    </row>
+    <row r="523">
+      <c r="B523" s="36" t="n">
+        <v>519</v>
+      </c>
+      <c r="C523" s="37" t="n"/>
+      <c r="D523" s="38" t="n"/>
+    </row>
+    <row r="524">
+      <c r="B524" s="36" t="n">
+        <v>520</v>
+      </c>
+      <c r="C524" s="39" t="n"/>
+      <c r="D524" s="40" t="n"/>
+    </row>
+    <row r="525">
+      <c r="B525" s="36" t="n">
+        <v>521</v>
+      </c>
+      <c r="C525" s="37" t="n"/>
+      <c r="D525" s="38" t="n"/>
+    </row>
+    <row r="526">
+      <c r="B526" s="36" t="n">
+        <v>522</v>
+      </c>
+      <c r="C526" s="39" t="n"/>
+      <c r="D526" s="40" t="n"/>
+    </row>
+    <row r="527">
+      <c r="B527" s="36" t="n">
+        <v>523</v>
+      </c>
+      <c r="C527" s="37" t="n"/>
+      <c r="D527" s="38" t="n"/>
+    </row>
+    <row r="528">
+      <c r="B528" s="36" t="n">
+        <v>524</v>
+      </c>
+      <c r="C528" s="39" t="n"/>
+      <c r="D528" s="40" t="n"/>
+    </row>
+    <row r="529">
+      <c r="B529" s="36" t="n">
+        <v>525</v>
+      </c>
+      <c r="C529" s="37" t="n"/>
+      <c r="D529" s="38" t="n"/>
+    </row>
+    <row r="530">
+      <c r="B530" s="36" t="n">
+        <v>526</v>
+      </c>
+      <c r="C530" s="39" t="n"/>
+      <c r="D530" s="40" t="n"/>
+    </row>
+    <row r="531">
+      <c r="B531" s="36" t="n">
+        <v>527</v>
+      </c>
+      <c r="C531" s="37" t="n"/>
+      <c r="D531" s="38" t="n"/>
+    </row>
+    <row r="532">
+      <c r="B532" s="36" t="n">
+        <v>528</v>
+      </c>
+      <c r="C532" s="39" t="n"/>
+      <c r="D532" s="40" t="n"/>
+    </row>
+    <row r="533">
+      <c r="B533" s="36" t="n">
+        <v>529</v>
+      </c>
+      <c r="C533" s="37" t="n"/>
+      <c r="D533" s="38" t="n"/>
+    </row>
+    <row r="534">
+      <c r="B534" s="36" t="n">
+        <v>530</v>
+      </c>
+      <c r="C534" s="39" t="n"/>
+      <c r="D534" s="40" t="n"/>
+    </row>
+    <row r="535">
+      <c r="B535" s="36" t="n">
+        <v>531</v>
+      </c>
+      <c r="C535" s="37" t="n"/>
+      <c r="D535" s="38" t="n"/>
+    </row>
+    <row r="536">
+      <c r="B536" s="36" t="n">
+        <v>532</v>
+      </c>
+      <c r="C536" s="39" t="n"/>
+      <c r="D536" s="40" t="n"/>
+    </row>
+    <row r="537">
+      <c r="B537" s="36" t="n">
+        <v>533</v>
+      </c>
+      <c r="C537" s="37" t="n"/>
+      <c r="D537" s="38" t="n"/>
+    </row>
+    <row r="538">
+      <c r="B538" s="36" t="n">
+        <v>534</v>
+      </c>
+      <c r="C538" s="39" t="n"/>
+      <c r="D538" s="40" t="n"/>
+    </row>
+    <row r="539">
+      <c r="B539" s="36" t="n">
+        <v>535</v>
+      </c>
+      <c r="C539" s="37" t="n"/>
+      <c r="D539" s="38" t="n"/>
+    </row>
+    <row r="540">
+      <c r="B540" s="36" t="n">
+        <v>536</v>
+      </c>
+      <c r="C540" s="39" t="n"/>
+      <c r="D540" s="40" t="n"/>
+    </row>
+    <row r="541">
+      <c r="B541" s="36" t="n">
+        <v>537</v>
+      </c>
+      <c r="C541" s="37" t="n"/>
+      <c r="D541" s="38" t="n"/>
+    </row>
+    <row r="542">
+      <c r="B542" s="36" t="n">
+        <v>538</v>
+      </c>
+      <c r="C542" s="39" t="n"/>
+      <c r="D542" s="40" t="n"/>
+    </row>
+    <row r="543">
+      <c r="B543" s="36" t="n">
+        <v>539</v>
+      </c>
+      <c r="C543" s="37" t="n"/>
+      <c r="D543" s="38" t="n"/>
+    </row>
+    <row r="544">
+      <c r="B544" s="36" t="n">
+        <v>540</v>
+      </c>
+      <c r="C544" s="39" t="n"/>
+      <c r="D544" s="40" t="n"/>
+    </row>
+    <row r="545">
+      <c r="B545" s="36" t="n">
+        <v>541</v>
+      </c>
+      <c r="C545" s="37" t="n"/>
+      <c r="D545" s="38" t="n"/>
+    </row>
+    <row r="546">
+      <c r="B546" s="36" t="n">
+        <v>542</v>
+      </c>
+      <c r="C546" s="39" t="n"/>
+      <c r="D546" s="40" t="n"/>
+    </row>
+    <row r="547">
+      <c r="B547" s="36" t="n">
+        <v>543</v>
+      </c>
+      <c r="C547" s="37" t="n"/>
+      <c r="D547" s="38" t="n"/>
+    </row>
+    <row r="548">
+      <c r="B548" s="36" t="n">
+        <v>544</v>
+      </c>
+      <c r="C548" s="39" t="n"/>
+      <c r="D548" s="40" t="n"/>
+    </row>
+    <row r="549">
+      <c r="B549" s="36" t="n">
+        <v>545</v>
+      </c>
+      <c r="C549" s="37" t="n"/>
+      <c r="D549" s="38" t="n"/>
+    </row>
+    <row r="550">
+      <c r="B550" s="36" t="n">
+        <v>546</v>
+      </c>
+      <c r="C550" s="39" t="n"/>
+      <c r="D550" s="40" t="n"/>
+    </row>
+    <row r="551">
+      <c r="B551" s="36" t="n">
+        <v>547</v>
+      </c>
+      <c r="C551" s="37" t="n"/>
+      <c r="D551" s="38" t="n"/>
+    </row>
+    <row r="552">
+      <c r="B552" s="36" t="n">
+        <v>548</v>
+      </c>
+      <c r="C552" s="39" t="n"/>
+      <c r="D552" s="40" t="n"/>
+    </row>
+    <row r="553">
+      <c r="B553" s="36" t="n">
+        <v>549</v>
+      </c>
+      <c r="C553" s="37" t="n"/>
+      <c r="D553" s="38" t="n"/>
+    </row>
+    <row r="554">
+      <c r="B554" s="36" t="n">
+        <v>550</v>
+      </c>
+      <c r="C554" s="39" t="n"/>
+      <c r="D554" s="40" t="n"/>
+    </row>
+    <row r="555">
+      <c r="B555" s="36" t="n">
+        <v>551</v>
+      </c>
+      <c r="C555" s="37" t="n"/>
+      <c r="D555" s="38" t="n"/>
+    </row>
+    <row r="556">
+      <c r="B556" s="36" t="n">
+        <v>552</v>
+      </c>
+      <c r="C556" s="39" t="n"/>
+      <c r="D556" s="40" t="n"/>
+    </row>
+    <row r="557">
+      <c r="B557" s="36" t="n">
+        <v>553</v>
+      </c>
+      <c r="C557" s="37" t="n"/>
+      <c r="D557" s="38" t="n"/>
+    </row>
+    <row r="558">
+      <c r="B558" s="36" t="n">
+        <v>554</v>
+      </c>
+      <c r="C558" s="39" t="n"/>
+      <c r="D558" s="40" t="n"/>
+    </row>
+    <row r="559">
+      <c r="B559" s="36" t="n">
+        <v>555</v>
+      </c>
+      <c r="C559" s="37" t="n"/>
+      <c r="D559" s="38" t="n"/>
+    </row>
+    <row r="560">
+      <c r="B560" s="36" t="n">
+        <v>556</v>
+      </c>
+      <c r="C560" s="39" t="n"/>
+      <c r="D560" s="40" t="n"/>
+    </row>
+    <row r="561">
+      <c r="B561" s="36" t="n">
+        <v>557</v>
+      </c>
+      <c r="C561" s="37" t="n"/>
+      <c r="D561" s="38" t="n"/>
+    </row>
+    <row r="562">
+      <c r="B562" s="36" t="n">
+        <v>558</v>
+      </c>
+      <c r="C562" s="39" t="n"/>
+      <c r="D562" s="40" t="n"/>
+    </row>
+    <row r="563">
+      <c r="B563" s="36" t="n">
+        <v>559</v>
+      </c>
+      <c r="C563" s="37" t="n"/>
+      <c r="D563" s="38" t="n"/>
+    </row>
+    <row r="564">
+      <c r="B564" s="36" t="n">
+        <v>560</v>
+      </c>
+      <c r="C564" s="39" t="n"/>
+      <c r="D564" s="40" t="n"/>
+    </row>
+    <row r="565">
+      <c r="B565" s="36" t="n">
+        <v>561</v>
+      </c>
+      <c r="C565" s="37" t="n"/>
+      <c r="D565" s="38" t="n"/>
+    </row>
+    <row r="566">
+      <c r="B566" s="36" t="n">
+        <v>562</v>
+      </c>
+      <c r="C566" s="39" t="n"/>
+      <c r="D566" s="40" t="n"/>
+    </row>
+    <row r="567">
+      <c r="B567" s="36" t="n">
+        <v>563</v>
+      </c>
+      <c r="C567" s="37" t="n"/>
+      <c r="D567" s="38" t="n"/>
+    </row>
+    <row r="568">
+      <c r="B568" s="36" t="n">
+        <v>564</v>
+      </c>
+      <c r="C568" s="39" t="n"/>
+      <c r="D568" s="40" t="n"/>
+    </row>
+    <row r="569">
+      <c r="B569" s="36" t="n">
+        <v>565</v>
+      </c>
+      <c r="C569" s="37" t="n"/>
+      <c r="D569" s="38" t="n"/>
+    </row>
+    <row r="570">
+      <c r="B570" s="36" t="n">
+        <v>566</v>
+      </c>
+      <c r="C570" s="39" t="n"/>
+      <c r="D570" s="40" t="n"/>
+    </row>
+    <row r="571">
+      <c r="B571" s="36" t="n">
+        <v>567</v>
+      </c>
+      <c r="C571" s="37" t="n"/>
+      <c r="D571" s="38" t="n"/>
+    </row>
+    <row r="572">
+      <c r="B572" s="36" t="n">
+        <v>568</v>
+      </c>
+      <c r="C572" s="39" t="n"/>
+      <c r="D572" s="40" t="n"/>
+    </row>
+    <row r="573">
+      <c r="B573" s="36" t="n">
+        <v>569</v>
+      </c>
+      <c r="C573" s="37" t="n"/>
+      <c r="D573" s="38" t="n"/>
+    </row>
+    <row r="574">
+      <c r="B574" s="36" t="n">
+        <v>570</v>
+      </c>
+      <c r="C574" s="39" t="n"/>
+      <c r="D574" s="40" t="n"/>
+    </row>
+    <row r="575">
+      <c r="B575" s="36" t="n">
+        <v>571</v>
+      </c>
+      <c r="C575" s="37" t="n"/>
+      <c r="D575" s="38" t="n"/>
+    </row>
+    <row r="576">
+      <c r="B576" s="36" t="n">
+        <v>572</v>
+      </c>
+      <c r="C576" s="39" t="n"/>
+      <c r="D576" s="40" t="n"/>
+    </row>
+    <row r="577">
+      <c r="B577" s="36" t="n">
+        <v>573</v>
+      </c>
+      <c r="C577" s="37" t="n"/>
+      <c r="D577" s="38" t="n"/>
+    </row>
+    <row r="578">
+      <c r="B578" s="36" t="n">
+        <v>574</v>
+      </c>
+      <c r="C578" s="39" t="n"/>
+      <c r="D578" s="40" t="n"/>
+    </row>
+    <row r="579">
+      <c r="B579" s="36" t="n">
+        <v>575</v>
+      </c>
+      <c r="C579" s="37" t="n"/>
+      <c r="D579" s="38" t="n"/>
+    </row>
+    <row r="580">
+      <c r="B580" s="36" t="n">
+        <v>576</v>
+      </c>
+      <c r="C580" s="39" t="n"/>
+      <c r="D580" s="40" t="n"/>
+    </row>
+    <row r="581">
+      <c r="B581" s="36" t="n">
+        <v>577</v>
+      </c>
+      <c r="C581" s="37" t="n"/>
+      <c r="D581" s="38" t="n"/>
+    </row>
+    <row r="582">
+      <c r="B582" s="36" t="n">
+        <v>578</v>
+      </c>
+      <c r="C582" s="39" t="n"/>
+      <c r="D582" s="40" t="n"/>
+    </row>
+    <row r="583">
+      <c r="B583" s="36" t="n">
+        <v>579</v>
+      </c>
+      <c r="C583" s="37" t="n"/>
+      <c r="D583" s="38" t="n"/>
+    </row>
+    <row r="584">
+      <c r="B584" s="36" t="n">
+        <v>580</v>
+      </c>
+      <c r="C584" s="39" t="n"/>
+      <c r="D584" s="40" t="n"/>
+    </row>
+    <row r="585">
+      <c r="B585" s="36" t="n">
+        <v>581</v>
+      </c>
+      <c r="C585" s="37" t="n"/>
+      <c r="D585" s="38" t="n"/>
+    </row>
+    <row r="586">
+      <c r="B586" s="36" t="n">
+        <v>582</v>
+      </c>
+      <c r="C586" s="39" t="n"/>
+      <c r="D586" s="40" t="n"/>
+    </row>
+    <row r="587">
+      <c r="B587" s="36" t="n">
+        <v>583</v>
+      </c>
+      <c r="C587" s="37" t="n"/>
+      <c r="D587" s="38" t="n"/>
+    </row>
+    <row r="588">
+      <c r="B588" s="36" t="n">
+        <v>584</v>
+      </c>
+      <c r="C588" s="39" t="n"/>
+      <c r="D588" s="40" t="n"/>
+    </row>
+    <row r="589">
+      <c r="B589" s="36" t="n">
+        <v>585</v>
+      </c>
+      <c r="C589" s="37" t="n"/>
+      <c r="D589" s="38" t="n"/>
+    </row>
+    <row r="590">
+      <c r="B590" s="36" t="n">
+        <v>586</v>
+      </c>
+      <c r="C590" s="39" t="n"/>
+      <c r="D590" s="40" t="n"/>
+    </row>
+    <row r="591">
+      <c r="B591" s="36" t="n">
+        <v>587</v>
+      </c>
+      <c r="C591" s="37" t="n"/>
+      <c r="D591" s="38" t="n"/>
+    </row>
+    <row r="592">
+      <c r="B592" s="36" t="n">
+        <v>588</v>
+      </c>
+      <c r="C592" s="39" t="n"/>
+      <c r="D592" s="40" t="n"/>
+    </row>
+    <row r="593">
+      <c r="B593" s="36" t="n">
+        <v>589</v>
+      </c>
+      <c r="C593" s="37" t="n"/>
+      <c r="D593" s="38" t="n"/>
+    </row>
+    <row r="594">
+      <c r="B594" s="36" t="n">
+        <v>590</v>
+      </c>
+      <c r="C594" s="39" t="n"/>
+      <c r="D594" s="40" t="n"/>
+    </row>
+    <row r="595">
+      <c r="B595" s="36" t="n">
+        <v>591</v>
+      </c>
+      <c r="C595" s="37" t="n"/>
+      <c r="D595" s="38" t="n"/>
+    </row>
+    <row r="596">
+      <c r="B596" s="36" t="n">
+        <v>592</v>
+      </c>
+      <c r="C596" s="39" t="n"/>
+      <c r="D596" s="40" t="n"/>
+    </row>
+    <row r="597">
+      <c r="B597" s="36" t="n">
+        <v>593</v>
+      </c>
+      <c r="C597" s="37" t="n"/>
+      <c r="D597" s="38" t="n"/>
+    </row>
+    <row r="598">
+      <c r="B598" s="36" t="n">
+        <v>594</v>
+      </c>
+      <c r="C598" s="39" t="n"/>
+      <c r="D598" s="40" t="n"/>
+    </row>
+    <row r="599">
+      <c r="B599" s="36" t="n">
+        <v>595</v>
+      </c>
+      <c r="C599" s="37" t="n"/>
+      <c r="D599" s="38" t="n"/>
+    </row>
+    <row r="600">
+      <c r="B600" s="36" t="n">
+        <v>596</v>
+      </c>
+      <c r="C600" s="39" t="n"/>
+      <c r="D600" s="40" t="n"/>
+    </row>
+    <row r="601">
+      <c r="B601" s="36" t="n">
+        <v>597</v>
+      </c>
+      <c r="C601" s="37" t="n"/>
+      <c r="D601" s="38" t="n"/>
+    </row>
+    <row r="602">
+      <c r="B602" s="36" t="n">
+        <v>598</v>
+      </c>
+      <c r="C602" s="39" t="n"/>
+      <c r="D602" s="40" t="n"/>
+    </row>
+    <row r="603">
+      <c r="B603" s="36" t="n">
+        <v>599</v>
+      </c>
+      <c r="C603" s="37" t="n"/>
+      <c r="D603" s="38" t="n"/>
+    </row>
+    <row r="604">
+      <c r="B604" s="36" t="n">
+        <v>600</v>
+      </c>
+      <c r="C604" s="39" t="n"/>
+      <c r="D604" s="40" t="n"/>
+    </row>
+    <row r="605">
+      <c r="B605" s="36" t="n">
+        <v>601</v>
+      </c>
+      <c r="C605" s="37" t="n"/>
+      <c r="D605" s="38" t="n"/>
+    </row>
+    <row r="606">
+      <c r="B606" s="36" t="n">
+        <v>602</v>
+      </c>
+      <c r="C606" s="39" t="n"/>
+      <c r="D606" s="40" t="n"/>
+    </row>
+    <row r="607">
+      <c r="B607" s="36" t="n">
+        <v>603</v>
+      </c>
+      <c r="C607" s="37" t="n"/>
+      <c r="D607" s="38" t="n"/>
+    </row>
+    <row r="608">
+      <c r="B608" s="36" t="n">
+        <v>604</v>
+      </c>
+      <c r="C608" s="39" t="n"/>
+      <c r="D608" s="40" t="n"/>
+    </row>
+    <row r="609">
+      <c r="B609" s="36" t="n">
+        <v>605</v>
+      </c>
+      <c r="C609" s="37" t="n"/>
+      <c r="D609" s="38" t="n"/>
+    </row>
+    <row r="610">
+      <c r="B610" s="36" t="n">
+        <v>606</v>
+      </c>
+      <c r="C610" s="39" t="n"/>
+      <c r="D610" s="40" t="n"/>
+    </row>
+    <row r="611">
+      <c r="B611" s="36" t="n">
+        <v>607</v>
+      </c>
+      <c r="C611" s="37" t="n"/>
+      <c r="D611" s="38" t="n"/>
+    </row>
+    <row r="612">
+      <c r="B612" s="36" t="n">
+        <v>608</v>
+      </c>
+      <c r="C612" s="39" t="n"/>
+      <c r="D612" s="40" t="n"/>
+    </row>
+    <row r="613">
+      <c r="B613" s="36" t="n">
+        <v>609</v>
+      </c>
+      <c r="C613" s="37" t="n"/>
+      <c r="D613" s="38" t="n"/>
+    </row>
+    <row r="614">
+      <c r="B614" s="36" t="n">
+        <v>610</v>
+      </c>
+      <c r="C614" s="39" t="n"/>
+      <c r="D614" s="40" t="n"/>
+    </row>
+    <row r="615">
+      <c r="B615" s="36" t="n">
+        <v>611</v>
+      </c>
+      <c r="C615" s="37" t="n"/>
+      <c r="D615" s="38" t="n"/>
+    </row>
+    <row r="616">
+      <c r="B616" s="36" t="n">
+        <v>612</v>
+      </c>
+      <c r="C616" s="39" t="n"/>
+      <c r="D616" s="40" t="n"/>
+    </row>
+    <row r="617">
+      <c r="B617" s="36" t="n">
+        <v>613</v>
+      </c>
+      <c r="C617" s="37" t="n"/>
+      <c r="D617" s="38" t="n"/>
+    </row>
+    <row r="618">
+      <c r="B618" s="36" t="n">
+        <v>614</v>
+      </c>
+      <c r="C618" s="39" t="n"/>
+      <c r="D618" s="40" t="n"/>
+    </row>
+    <row r="619">
+      <c r="B619" s="36" t="n">
+        <v>615</v>
+      </c>
+      <c r="C619" s="37" t="n"/>
+      <c r="D619" s="38" t="n"/>
+    </row>
+    <row r="620">
+      <c r="B620" s="36" t="n">
+        <v>616</v>
+      </c>
+      <c r="C620" s="39" t="n"/>
+      <c r="D620" s="40" t="n"/>
+    </row>
+    <row r="621">
+      <c r="B621" s="36" t="n">
+        <v>617</v>
+      </c>
+      <c r="C621" s="37" t="n"/>
+      <c r="D621" s="38" t="n"/>
+    </row>
+    <row r="622">
+      <c r="B622" s="36" t="n">
+        <v>618</v>
+      </c>
+      <c r="C622" s="39" t="n"/>
+      <c r="D622" s="40" t="n"/>
+    </row>
+    <row r="623">
+      <c r="B623" s="36" t="n">
+        <v>619</v>
+      </c>
+      <c r="C623" s="37" t="n"/>
+      <c r="D623" s="38" t="n"/>
+    </row>
+    <row r="624">
+      <c r="B624" s="36" t="n">
+        <v>620</v>
+      </c>
+      <c r="C624" s="39" t="n"/>
+      <c r="D624" s="40" t="n"/>
+    </row>
+    <row r="625">
+      <c r="B625" s="36" t="n">
+        <v>621</v>
+      </c>
+      <c r="C625" s="37" t="n"/>
+      <c r="D625" s="38" t="n"/>
+    </row>
+    <row r="626">
+      <c r="B626" s="36" t="n">
+        <v>622</v>
+      </c>
+      <c r="C626" s="39" t="n"/>
+      <c r="D626" s="40" t="n"/>
+    </row>
+    <row r="627">
+      <c r="B627" s="36" t="n">
+        <v>623</v>
+      </c>
+      <c r="C627" s="37" t="n"/>
+      <c r="D627" s="38" t="n"/>
+    </row>
+    <row r="628">
+      <c r="B628" s="36" t="n">
+        <v>624</v>
+      </c>
+      <c r="C628" s="39" t="n"/>
+      <c r="D628" s="40" t="n"/>
+    </row>
+    <row r="629">
+      <c r="B629" s="36" t="n">
+        <v>625</v>
+      </c>
+      <c r="C629" s="37" t="n"/>
+      <c r="D629" s="38" t="n"/>
+    </row>
+    <row r="630">
+      <c r="B630" s="36" t="n">
+        <v>626</v>
+      </c>
+      <c r="C630" s="39" t="n"/>
+      <c r="D630" s="40" t="n"/>
+    </row>
+    <row r="631">
+      <c r="B631" s="36" t="n">
+        <v>627</v>
+      </c>
+      <c r="C631" s="37" t="n"/>
+      <c r="D631" s="38" t="n"/>
+    </row>
+    <row r="632">
+      <c r="B632" s="36" t="n">
+        <v>628</v>
+      </c>
+      <c r="C632" s="39" t="n"/>
+      <c r="D632" s="40" t="n"/>
+    </row>
+    <row r="633">
+      <c r="B633" s="36" t="n">
+        <v>629</v>
+      </c>
+      <c r="C633" s="37" t="n"/>
+      <c r="D633" s="38" t="n"/>
+    </row>
+    <row r="634">
+      <c r="B634" s="36" t="n">
+        <v>630</v>
+      </c>
+      <c r="C634" s="39" t="n"/>
+      <c r="D634" s="40" t="n"/>
+    </row>
+    <row r="635">
+      <c r="B635" s="36" t="n">
+        <v>631</v>
+      </c>
+      <c r="C635" s="37" t="n"/>
+      <c r="D635" s="38" t="n"/>
+    </row>
+    <row r="636">
+      <c r="B636" s="36" t="n">
+        <v>632</v>
+      </c>
+      <c r="C636" s="39" t="n"/>
+      <c r="D636" s="40" t="n"/>
+    </row>
+    <row r="637">
+      <c r="B637" s="36" t="n">
+        <v>633</v>
+      </c>
+      <c r="C637" s="37" t="n"/>
+      <c r="D637" s="38" t="n"/>
+    </row>
+    <row r="638">
+      <c r="B638" s="36" t="n">
+        <v>634</v>
+      </c>
+      <c r="C638" s="39" t="n"/>
+      <c r="D638" s="40" t="n"/>
+    </row>
+    <row r="639">
+      <c r="B639" s="36" t="n">
+        <v>635</v>
+      </c>
+      <c r="C639" s="37" t="n"/>
+      <c r="D639" s="38" t="n"/>
+    </row>
+    <row r="640">
+      <c r="B640" s="36" t="n">
+        <v>636</v>
+      </c>
+      <c r="C640" s="39" t="n"/>
+      <c r="D640" s="40" t="n"/>
+    </row>
+    <row r="641">
+      <c r="B641" s="36" t="n">
+        <v>637</v>
+      </c>
+      <c r="C641" s="37" t="n"/>
+      <c r="D641" s="38" t="n"/>
+    </row>
+    <row r="642">
+      <c r="B642" s="36" t="n">
+        <v>638</v>
+      </c>
+      <c r="C642" s="39" t="n"/>
+      <c r="D642" s="40" t="n"/>
+    </row>
+    <row r="643">
+      <c r="B643" s="36" t="n">
+        <v>639</v>
+      </c>
+      <c r="C643" s="37" t="n"/>
+      <c r="D643" s="38" t="n"/>
+    </row>
+    <row r="644">
+      <c r="B644" s="36" t="n">
+        <v>640</v>
+      </c>
+      <c r="C644" s="39" t="n"/>
+      <c r="D644" s="40" t="n"/>
+    </row>
+    <row r="645">
+      <c r="B645" s="36" t="n">
+        <v>641</v>
+      </c>
+      <c r="C645" s="37" t="n"/>
+      <c r="D645" s="38" t="n"/>
+    </row>
+    <row r="646">
+      <c r="B646" s="36" t="n">
+        <v>642</v>
+      </c>
+      <c r="C646" s="39" t="n"/>
+      <c r="D646" s="40" t="n"/>
+    </row>
+    <row r="647">
+      <c r="B647" s="36" t="n">
+        <v>643</v>
+      </c>
+      <c r="C647" s="37" t="n"/>
+      <c r="D647" s="38" t="n"/>
+    </row>
+    <row r="648">
+      <c r="B648" s="36" t="n">
+        <v>644</v>
+      </c>
+      <c r="C648" s="39" t="n"/>
+      <c r="D648" s="40" t="n"/>
+    </row>
+    <row r="649">
+      <c r="B649" s="36" t="n">
+        <v>645</v>
+      </c>
+      <c r="C649" s="37" t="n"/>
+      <c r="D649" s="38" t="n"/>
+    </row>
+    <row r="650">
+      <c r="B650" s="36" t="n">
+        <v>646</v>
+      </c>
+      <c r="C650" s="39" t="n"/>
+      <c r="D650" s="40" t="n"/>
+    </row>
+    <row r="651">
+      <c r="B651" s="36" t="n">
+        <v>647</v>
+      </c>
+      <c r="C651" s="37" t="n"/>
+      <c r="D651" s="38" t="n"/>
+    </row>
+    <row r="652">
+      <c r="B652" s="36" t="n">
+        <v>648</v>
+      </c>
+      <c r="C652" s="39" t="n"/>
+      <c r="D652" s="40" t="n"/>
+    </row>
+    <row r="653">
+      <c r="B653" s="36" t="n">
+        <v>649</v>
+      </c>
+      <c r="C653" s="37" t="n"/>
+      <c r="D653" s="38" t="n"/>
+    </row>
+    <row r="654">
+      <c r="B654" s="36" t="n">
+        <v>650</v>
+      </c>
+      <c r="C654" s="39" t="n"/>
+      <c r="D654" s="40" t="n"/>
+    </row>
+    <row r="655">
+      <c r="B655" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="C655" s="37" t="n"/>
+      <c r="D655" s="38" t="n"/>
+    </row>
+    <row r="656">
+      <c r="B656" s="36" t="n">
+        <v>652</v>
+      </c>
+      <c r="C656" s="39" t="n"/>
+      <c r="D656" s="40" t="n"/>
+    </row>
+    <row r="657">
+      <c r="B657" s="36" t="n">
+        <v>653</v>
+      </c>
+      <c r="C657" s="37" t="n"/>
+      <c r="D657" s="38" t="n"/>
+    </row>
+    <row r="658">
+      <c r="B658" s="36" t="n">
+        <v>654</v>
+      </c>
+      <c r="C658" s="39" t="n"/>
+      <c r="D658" s="40" t="n"/>
+    </row>
+    <row r="659">
+      <c r="B659" s="36" t="n">
+        <v>655</v>
+      </c>
+      <c r="C659" s="37" t="n"/>
+      <c r="D659" s="38" t="n"/>
+    </row>
+    <row r="660">
+      <c r="B660" s="36" t="n">
+        <v>656</v>
+      </c>
+      <c r="C660" s="39" t="n"/>
+      <c r="D660" s="40" t="n"/>
+    </row>
+    <row r="661">
+      <c r="B661" s="36" t="n">
+        <v>657</v>
+      </c>
+      <c r="C661" s="37" t="n"/>
+      <c r="D661" s="38" t="n"/>
+    </row>
+    <row r="662">
+      <c r="B662" s="36" t="n">
+        <v>658</v>
+      </c>
+      <c r="C662" s="39" t="n"/>
+      <c r="D662" s="40" t="n"/>
+    </row>
+    <row r="663">
+      <c r="B663" s="36" t="n">
+        <v>659</v>
+      </c>
+      <c r="C663" s="37" t="n"/>
+      <c r="D663" s="38" t="n"/>
+    </row>
+    <row r="664">
+      <c r="B664" s="36" t="n">
+        <v>660</v>
+      </c>
+      <c r="C664" s="39" t="n"/>
+      <c r="D664" s="40" t="n"/>
+    </row>
+    <row r="665">
+      <c r="B665" s="36" t="n">
+        <v>661</v>
+      </c>
+      <c r="C665" s="37" t="n"/>
+      <c r="D665" s="38" t="n"/>
+    </row>
+    <row r="666">
+      <c r="B666" s="36" t="n">
+        <v>662</v>
+      </c>
+      <c r="C666" s="39" t="n"/>
+      <c r="D666" s="40" t="n"/>
+    </row>
+    <row r="667">
+      <c r="B667" s="36" t="n">
+        <v>663</v>
+      </c>
+      <c r="C667" s="37" t="n"/>
+      <c r="D667" s="38" t="n"/>
+    </row>
+    <row r="668">
+      <c r="B668" s="36" t="n">
+        <v>664</v>
+      </c>
+      <c r="C668" s="39" t="n"/>
+      <c r="D668" s="40" t="n"/>
+    </row>
+    <row r="669">
+      <c r="B669" s="36" t="n">
+        <v>665</v>
+      </c>
+      <c r="C669" s="37" t="n"/>
+      <c r="D669" s="38" t="n"/>
+    </row>
+    <row r="670">
+      <c r="B670" s="36" t="n">
+        <v>666</v>
+      </c>
+      <c r="C670" s="39" t="n"/>
+      <c r="D670" s="40" t="n"/>
+    </row>
+    <row r="671">
+      <c r="B671" s="36" t="n">
+        <v>667</v>
+      </c>
+      <c r="C671" s="37" t="n"/>
+      <c r="D671" s="38" t="n"/>
+    </row>
+    <row r="672">
+      <c r="B672" s="36" t="n">
+        <v>668</v>
+      </c>
+      <c r="C672" s="39" t="n"/>
+      <c r="D672" s="40" t="n"/>
+    </row>
+    <row r="673">
+      <c r="B673" s="36" t="n">
+        <v>669</v>
+      </c>
+      <c r="C673" s="37" t="n"/>
+      <c r="D673" s="38" t="n"/>
+    </row>
+    <row r="674">
+      <c r="B674" s="36" t="n">
+        <v>670</v>
+      </c>
+      <c r="C674" s="39" t="n"/>
+      <c r="D674" s="40" t="n"/>
+    </row>
+    <row r="675">
+      <c r="B675" s="36" t="n">
+        <v>671</v>
+      </c>
+      <c r="C675" s="37" t="n"/>
+      <c r="D675" s="38" t="n"/>
+    </row>
+    <row r="676">
+      <c r="B676" s="36" t="n">
+        <v>672</v>
+      </c>
+      <c r="C676" s="39" t="n"/>
+      <c r="D676" s="40" t="n"/>
+    </row>
+    <row r="677">
+      <c r="B677" s="36" t="n">
+        <v>673</v>
+      </c>
+      <c r="C677" s="37" t="n"/>
+      <c r="D677" s="38" t="n"/>
+    </row>
+    <row r="678">
+      <c r="B678" s="36" t="n">
+        <v>674</v>
+      </c>
+      <c r="C678" s="39" t="n"/>
+      <c r="D678" s="40" t="n"/>
+    </row>
+    <row r="679">
+      <c r="B679" s="36" t="n">
+        <v>675</v>
+      </c>
+      <c r="C679" s="37" t="n"/>
+      <c r="D679" s="38" t="n"/>
+    </row>
+    <row r="680">
+      <c r="B680" s="36" t="n">
+        <v>676</v>
+      </c>
+      <c r="C680" s="39" t="n"/>
+      <c r="D680" s="40" t="n"/>
+    </row>
+    <row r="681">
+      <c r="B681" s="36" t="n">
+        <v>677</v>
+      </c>
+      <c r="C681" s="37" t="n"/>
+      <c r="D681" s="38" t="n"/>
+    </row>
+    <row r="682">
+      <c r="B682" s="36" t="n">
+        <v>678</v>
+      </c>
+      <c r="C682" s="39" t="n"/>
+      <c r="D682" s="40" t="n"/>
+    </row>
+    <row r="683">
+      <c r="B683" s="36" t="n">
+        <v>679</v>
+      </c>
+      <c r="C683" s="37" t="n"/>
+      <c r="D683" s="38" t="n"/>
+    </row>
+    <row r="684">
+      <c r="B684" s="36" t="n">
+        <v>680</v>
+      </c>
+      <c r="C684" s="39" t="n"/>
+      <c r="D684" s="40" t="n"/>
+    </row>
+    <row r="685">
+      <c r="B685" s="36" t="n">
+        <v>681</v>
+      </c>
+      <c r="C685" s="37" t="n"/>
+      <c r="D685" s="38" t="n"/>
+    </row>
+    <row r="686">
+      <c r="B686" s="36" t="n">
+        <v>682</v>
+      </c>
+      <c r="C686" s="39" t="n"/>
+      <c r="D686" s="40" t="n"/>
+    </row>
+    <row r="687">
+      <c r="B687" s="36" t="n">
+        <v>683</v>
+      </c>
+      <c r="C687" s="37" t="n"/>
+      <c r="D687" s="38" t="n"/>
+    </row>
+    <row r="688">
+      <c r="B688" s="36" t="n">
+        <v>684</v>
+      </c>
+      <c r="C688" s="39" t="n"/>
+      <c r="D688" s="40" t="n"/>
+    </row>
+    <row r="689">
+      <c r="B689" s="36" t="n">
+        <v>685</v>
+      </c>
+      <c r="C689" s="37" t="n"/>
+      <c r="D689" s="38" t="n"/>
+    </row>
+    <row r="690">
+      <c r="B690" s="36" t="n">
+        <v>686</v>
+      </c>
+      <c r="C690" s="39" t="n"/>
+      <c r="D690" s="40" t="n"/>
+    </row>
+    <row r="691">
+      <c r="B691" s="36" t="n">
+        <v>687</v>
+      </c>
+      <c r="C691" s="37" t="n"/>
+      <c r="D691" s="38" t="n"/>
+    </row>
+    <row r="692">
+      <c r="B692" s="36" t="n">
+        <v>688</v>
+      </c>
+      <c r="C692" s="39" t="n"/>
+      <c r="D692" s="40" t="n"/>
+    </row>
+    <row r="693">
+      <c r="B693" s="36" t="n">
+        <v>689</v>
+      </c>
+      <c r="C693" s="37" t="n"/>
+      <c r="D693" s="38" t="n"/>
+    </row>
+    <row r="694">
+      <c r="B694" s="36" t="n">
+        <v>690</v>
+      </c>
+      <c r="C694" s="39" t="n"/>
+      <c r="D694" s="40" t="n"/>
+    </row>
+    <row r="695">
+      <c r="B695" s="36" t="n">
+        <v>691</v>
+      </c>
+      <c r="C695" s="37" t="n"/>
+      <c r="D695" s="38" t="n"/>
+    </row>
+    <row r="696">
+      <c r="B696" s="36" t="n">
+        <v>692</v>
+      </c>
+      <c r="C696" s="39" t="n"/>
+      <c r="D696" s="40" t="n"/>
+    </row>
+    <row r="697">
+      <c r="B697" s="36" t="n">
+        <v>693</v>
+      </c>
+      <c r="C697" s="37" t="n"/>
+      <c r="D697" s="38" t="n"/>
+    </row>
+    <row r="698">
+      <c r="B698" s="36" t="n">
+        <v>694</v>
+      </c>
+      <c r="C698" s="39" t="n"/>
+      <c r="D698" s="40" t="n"/>
+    </row>
+    <row r="699">
+      <c r="B699" s="36" t="n">
+        <v>695</v>
+      </c>
+      <c r="C699" s="37" t="n"/>
+      <c r="D699" s="38" t="n"/>
+    </row>
+    <row r="700">
+      <c r="B700" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="C700" s="39" t="n"/>
+      <c r="D700" s="40" t="n"/>
+    </row>
+    <row r="701">
+      <c r="B701" s="36" t="n">
+        <v>697</v>
+      </c>
+      <c r="C701" s="37" t="n"/>
+      <c r="D701" s="38" t="n"/>
+    </row>
+    <row r="702">
+      <c r="B702" s="36" t="n">
+        <v>698</v>
+      </c>
+      <c r="C702" s="39" t="n"/>
+      <c r="D702" s="40" t="n"/>
+    </row>
+    <row r="703">
+      <c r="B703" s="36" t="n">
+        <v>699</v>
+      </c>
+      <c r="C703" s="37" t="n"/>
+      <c r="D703" s="38" t="n"/>
+    </row>
+    <row r="704">
+      <c r="B704" s="36" t="n">
+        <v>700</v>
+      </c>
+      <c r="C704" s="39" t="n"/>
+      <c r="D704" s="40" t="n"/>
+    </row>
+    <row r="705">
+      <c r="B705" s="36" t="n">
+        <v>701</v>
+      </c>
+      <c r="C705" s="37" t="n"/>
+      <c r="D705" s="38" t="n"/>
+    </row>
+    <row r="706">
+      <c r="B706" s="36" t="n">
+        <v>702</v>
+      </c>
+      <c r="C706" s="39" t="n"/>
+      <c r="D706" s="40" t="n"/>
+    </row>
+    <row r="707">
+      <c r="B707" s="36" t="n">
+        <v>703</v>
+      </c>
+      <c r="C707" s="37" t="n"/>
+      <c r="D707" s="38" t="n"/>
+    </row>
+    <row r="708">
+      <c r="B708" s="36" t="n">
+        <v>704</v>
+      </c>
+      <c r="C708" s="39" t="n"/>
+      <c r="D708" s="40" t="n"/>
+    </row>
+    <row r="709">
+      <c r="B709" s="36" t="n">
+        <v>705</v>
+      </c>
+      <c r="C709" s="37" t="n"/>
+      <c r="D709" s="38" t="n"/>
+    </row>
+    <row r="710">
+      <c r="B710" s="36" t="n">
+        <v>706</v>
+      </c>
+      <c r="C710" s="39" t="n"/>
+      <c r="D710" s="40" t="n"/>
+    </row>
+    <row r="711">
+      <c r="B711" s="36" t="n">
+        <v>707</v>
+      </c>
+      <c r="C711" s="37" t="n"/>
+      <c r="D711" s="38" t="n"/>
+    </row>
+    <row r="712">
+      <c r="B712" s="36" t="n">
+        <v>708</v>
+      </c>
+      <c r="C712" s="39" t="n"/>
+      <c r="D712" s="40" t="n"/>
+    </row>
+    <row r="713">
+      <c r="B713" s="36" t="n">
+        <v>709</v>
+      </c>
+      <c r="C713" s="37" t="n"/>
+      <c r="D713" s="38" t="n"/>
+    </row>
+    <row r="714">
+      <c r="B714" s="36" t="n">
+        <v>710</v>
+      </c>
+      <c r="C714" s="39" t="n"/>
+      <c r="D714" s="40" t="n"/>
+    </row>
+    <row r="715">
+      <c r="B715" s="36" t="n">
+        <v>711</v>
+      </c>
+      <c r="C715" s="37" t="n"/>
+      <c r="D715" s="38" t="n"/>
+    </row>
+    <row r="716">
+      <c r="B716" s="36" t="n">
+        <v>712</v>
+      </c>
+      <c r="C716" s="39" t="n"/>
+      <c r="D716" s="40" t="n"/>
+    </row>
+    <row r="717">
+      <c r="B717" s="36" t="n">
+        <v>713</v>
+      </c>
+      <c r="C717" s="37" t="n"/>
+      <c r="D717" s="38" t="n"/>
+    </row>
+    <row r="718">
+      <c r="B718" s="36" t="n">
+        <v>714</v>
+      </c>
+      <c r="C718" s="39" t="n"/>
+      <c r="D718" s="40" t="n"/>
+    </row>
+    <row r="719">
+      <c r="B719" s="36" t="n">
+        <v>715</v>
+      </c>
+      <c r="C719" s="37" t="n"/>
+      <c r="D719" s="38" t="n"/>
+    </row>
+    <row r="720">
+      <c r="B720" s="36" t="n">
+        <v>716</v>
+      </c>
+      <c r="C720" s="39" t="n"/>
+      <c r="D720" s="40" t="n"/>
+    </row>
+    <row r="721">
+      <c r="B721" s="36" t="n">
+        <v>717</v>
+      </c>
+      <c r="C721" s="37" t="n"/>
+      <c r="D721" s="38" t="n"/>
+    </row>
+    <row r="722">
+      <c r="B722" s="36" t="n">
+        <v>718</v>
+      </c>
+      <c r="C722" s="39" t="n"/>
+      <c r="D722" s="40" t="n"/>
+    </row>
+    <row r="723">
+      <c r="B723" s="36" t="n">
+        <v>719</v>
+      </c>
+      <c r="C723" s="37" t="n"/>
+      <c r="D723" s="38" t="n"/>
+    </row>
+    <row r="724">
+      <c r="B724" s="36" t="n">
+        <v>720</v>
+      </c>
+      <c r="C724" s="39" t="n"/>
+      <c r="D724" s="40" t="n"/>
+    </row>
+    <row r="725">
+      <c r="B725" s="36" t="n">
+        <v>721</v>
+      </c>
+      <c r="C725" s="37" t="n"/>
+      <c r="D725" s="38" t="n"/>
+    </row>
+    <row r="726">
+      <c r="B726" s="36" t="n">
+        <v>722</v>
+      </c>
+      <c r="C726" s="39" t="n"/>
+      <c r="D726" s="40" t="n"/>
+    </row>
+    <row r="727">
+      <c r="B727" s="36" t="n">
+        <v>723</v>
+      </c>
+      <c r="C727" s="37" t="n"/>
+      <c r="D727" s="38" t="n"/>
+    </row>
+    <row r="728">
+      <c r="B728" s="36" t="n">
+        <v>724</v>
+      </c>
+      <c r="C728" s="39" t="n"/>
+      <c r="D728" s="40" t="n"/>
+    </row>
+    <row r="729">
+      <c r="B729" s="36" t="n">
+        <v>725</v>
+      </c>
+      <c r="C729" s="37" t="n"/>
+      <c r="D729" s="38" t="n"/>
+    </row>
+    <row r="730">
+      <c r="B730" s="36" t="n">
+        <v>726</v>
+      </c>
+      <c r="C730" s="39" t="n"/>
+      <c r="D730" s="40" t="n"/>
+    </row>
+    <row r="731">
+      <c r="B731" s="36" t="n">
+        <v>727</v>
+      </c>
+      <c r="C731" s="37" t="n"/>
+      <c r="D731" s="38" t="n"/>
+    </row>
+    <row r="732">
+      <c r="B732" s="36" t="n">
+        <v>728</v>
+      </c>
+      <c r="C732" s="39" t="n"/>
+      <c r="D732" s="40" t="n"/>
+    </row>
+    <row r="733">
+      <c r="B733" s="36" t="n">
+        <v>729</v>
+      </c>
+      <c r="C733" s="37" t="n"/>
+      <c r="D733" s="38" t="n"/>
+    </row>
+    <row r="734">
+      <c r="B734" s="36" t="n">
+        <v>730</v>
+      </c>
+      <c r="C734" s="39" t="n"/>
+      <c r="D734" s="40" t="n"/>
+    </row>
+    <row r="735">
+      <c r="B735" s="36" t="n">
+        <v>731</v>
+      </c>
+      <c r="C735" s="37" t="n"/>
+      <c r="D735" s="38" t="n"/>
+    </row>
+    <row r="736">
+      <c r="B736" s="36" t="n">
+        <v>732</v>
+      </c>
+      <c r="C736" s="39" t="n"/>
+      <c r="D736" s="40" t="n"/>
+    </row>
+    <row r="737">
+      <c r="B737" s="36" t="n">
+        <v>733</v>
+      </c>
+      <c r="C737" s="37" t="n"/>
+      <c r="D737" s="38" t="n"/>
+    </row>
+    <row r="738">
+      <c r="B738" s="36" t="n">
+        <v>734</v>
+      </c>
+      <c r="C738" s="39" t="n"/>
+      <c r="D738" s="40" t="n"/>
+    </row>
+    <row r="739">
+      <c r="B739" s="36" t="n">
+        <v>735</v>
+      </c>
+      <c r="C739" s="37" t="n"/>
+      <c r="D739" s="38" t="n"/>
+    </row>
+    <row r="740">
+      <c r="B740" s="36" t="n">
+        <v>736</v>
+      </c>
+      <c r="C740" s="39" t="n"/>
+      <c r="D740" s="40" t="n"/>
+    </row>
+    <row r="741">
+      <c r="B741" s="36" t="n">
+        <v>737</v>
+      </c>
+      <c r="C741" s="37" t="n"/>
+      <c r="D741" s="38" t="n"/>
+    </row>
+    <row r="742">
+      <c r="B742" s="36" t="n">
+        <v>738</v>
+      </c>
+      <c r="C742" s="39" t="n"/>
+      <c r="D742" s="40" t="n"/>
+    </row>
+    <row r="743">
+      <c r="B743" s="36" t="n">
+        <v>739</v>
+      </c>
+      <c r="C743" s="37" t="n"/>
+      <c r="D743" s="38" t="n"/>
+    </row>
+    <row r="744">
+      <c r="B744" s="36" t="n">
+        <v>740</v>
+      </c>
+      <c r="C744" s="39" t="n"/>
+      <c r="D744" s="40" t="n"/>
+    </row>
+    <row r="745">
+      <c r="B745" s="36" t="n">
+        <v>741</v>
+      </c>
+      <c r="C745" s="37" t="n"/>
+      <c r="D745" s="38" t="n"/>
+    </row>
+    <row r="746">
+      <c r="B746" s="36" t="n">
+        <v>742</v>
+      </c>
+      <c r="C746" s="39" t="n"/>
+      <c r="D746" s="40" t="n"/>
+    </row>
+    <row r="747">
+      <c r="B747" s="36" t="n">
+        <v>743</v>
+      </c>
+      <c r="C747" s="37" t="n"/>
+      <c r="D747" s="38" t="n"/>
+    </row>
+    <row r="748">
+      <c r="B748" s="36" t="n">
+        <v>744</v>
+      </c>
+      <c r="C748" s="39" t="n"/>
+      <c r="D748" s="40" t="n"/>
+    </row>
+    <row r="749">
+      <c r="B749" s="36" t="n">
+        <v>745</v>
+      </c>
+      <c r="C749" s="37" t="n"/>
+      <c r="D749" s="38" t="n"/>
+    </row>
+    <row r="750">
+      <c r="B750" s="36" t="n">
+        <v>746</v>
+      </c>
+      <c r="C750" s="39" t="n"/>
+      <c r="D750" s="40" t="n"/>
+    </row>
+    <row r="751">
+      <c r="B751" s="36" t="n">
+        <v>747</v>
+      </c>
+      <c r="C751" s="37" t="n"/>
+      <c r="D751" s="38" t="n"/>
+    </row>
+    <row r="752">
+      <c r="B752" s="36" t="n">
+        <v>748</v>
+      </c>
+      <c r="C752" s="39" t="n"/>
+      <c r="D752" s="40" t="n"/>
+    </row>
+    <row r="753">
+      <c r="B753" s="36" t="n">
+        <v>749</v>
+      </c>
+      <c r="C753" s="37" t="n"/>
+      <c r="D753" s="38" t="n"/>
+    </row>
+    <row r="754">
+      <c r="B754" s="36" t="n">
+        <v>750</v>
+      </c>
+      <c r="C754" s="39" t="n"/>
+      <c r="D754" s="40" t="n"/>
+    </row>
+    <row r="755">
+      <c r="B755" s="36" t="n">
+        <v>751</v>
+      </c>
+      <c r="C755" s="37" t="n"/>
+      <c r="D755" s="38" t="n"/>
+    </row>
+    <row r="756">
+      <c r="B756" s="36" t="n">
+        <v>752</v>
+      </c>
+      <c r="C756" s="39" t="n"/>
+      <c r="D756" s="40" t="n"/>
+    </row>
+    <row r="757">
+      <c r="B757" s="36" t="n">
+        <v>753</v>
+      </c>
+      <c r="C757" s="37" t="n"/>
+      <c r="D757" s="38" t="n"/>
+    </row>
+    <row r="758">
+      <c r="B758" s="36" t="n">
+        <v>754</v>
+      </c>
+      <c r="C758" s="39" t="n"/>
+      <c r="D758" s="40" t="n"/>
+    </row>
+    <row r="759">
+      <c r="B759" s="36" t="n">
+        <v>755</v>
+      </c>
+      <c r="C759" s="37" t="n"/>
+      <c r="D759" s="38" t="n"/>
+    </row>
+    <row r="760">
+      <c r="B760" s="36" t="n">
+        <v>756</v>
+      </c>
+      <c r="C760" s="39" t="n"/>
+      <c r="D760" s="40" t="n"/>
+    </row>
+    <row r="761">
+      <c r="B761" s="36" t="n">
+        <v>757</v>
+      </c>
+      <c r="C761" s="37" t="n"/>
+      <c r="D761" s="38" t="n"/>
+    </row>
+    <row r="762">
+      <c r="B762" s="36" t="n">
+        <v>758</v>
+      </c>
+      <c r="C762" s="39" t="n"/>
+      <c r="D762" s="40" t="n"/>
+    </row>
+    <row r="763">
+      <c r="B763" s="36" t="n">
+        <v>759</v>
+      </c>
+      <c r="C763" s="37" t="n"/>
+      <c r="D763" s="38" t="n"/>
+    </row>
+    <row r="764">
+      <c r="B764" s="36" t="n">
+        <v>760</v>
+      </c>
+      <c r="C764" s="39" t="n"/>
+      <c r="D764" s="40" t="n"/>
+    </row>
+    <row r="765">
+      <c r="B765" s="36" t="n">
+        <v>761</v>
+      </c>
+      <c r="C765" s="37" t="n"/>
+      <c r="D765" s="38" t="n"/>
+    </row>
+    <row r="766">
+      <c r="B766" s="36" t="n">
+        <v>762</v>
+      </c>
+      <c r="C766" s="39" t="n"/>
+      <c r="D766" s="40" t="n"/>
+    </row>
+    <row r="767">
+      <c r="B767" s="36" t="n">
+        <v>763</v>
+      </c>
+      <c r="C767" s="37" t="n"/>
+      <c r="D767" s="38" t="n"/>
+    </row>
+    <row r="768">
+      <c r="B768" s="36" t="n">
+        <v>764</v>
+      </c>
+      <c r="C768" s="39" t="n"/>
+      <c r="D768" s="40" t="n"/>
+    </row>
+    <row r="769">
+      <c r="B769" s="36" t="n">
+        <v>765</v>
+      </c>
+      <c r="C769" s="37" t="n"/>
+      <c r="D769" s="38" t="n"/>
+    </row>
+    <row r="770">
+      <c r="B770" s="36" t="n">
+        <v>766</v>
+      </c>
+      <c r="C770" s="39" t="n"/>
+      <c r="D770" s="40" t="n"/>
+    </row>
+    <row r="771">
+      <c r="B771" s="36" t="n">
+        <v>767</v>
+      </c>
+      <c r="C771" s="37" t="n"/>
+      <c r="D771" s="38" t="n"/>
+    </row>
+    <row r="772">
+      <c r="B772" s="36" t="n">
+        <v>768</v>
+      </c>
+      <c r="C772" s="39" t="n"/>
+      <c r="D772" s="40" t="n"/>
+    </row>
+    <row r="773">
+      <c r="B773" s="36" t="n">
+        <v>769</v>
+      </c>
+      <c r="C773" s="37" t="n"/>
+      <c r="D773" s="38" t="n"/>
+    </row>
+    <row r="774">
+      <c r="B774" s="36" t="n">
+        <v>770</v>
+      </c>
+      <c r="C774" s="39" t="n"/>
+      <c r="D774" s="40" t="n"/>
+    </row>
+    <row r="775">
+      <c r="B775" s="36" t="n">
+        <v>771</v>
+      </c>
+      <c r="C775" s="37" t="n"/>
+      <c r="D775" s="38" t="n"/>
+    </row>
+    <row r="776">
+      <c r="B776" s="36" t="n">
+        <v>772</v>
+      </c>
+      <c r="C776" s="39" t="n"/>
+      <c r="D776" s="40" t="n"/>
+    </row>
+    <row r="777">
+      <c r="B777" s="36" t="n">
+        <v>773</v>
+      </c>
+      <c r="C777" s="37" t="n"/>
+      <c r="D777" s="38" t="n"/>
+    </row>
+    <row r="778">
+      <c r="B778" s="36" t="n">
+        <v>774</v>
+      </c>
+      <c r="C778" s="39" t="n"/>
+      <c r="D778" s="40" t="n"/>
+    </row>
+    <row r="779">
+      <c r="B779" s="36" t="n">
+        <v>775</v>
+      </c>
+      <c r="C779" s="37" t="n"/>
+      <c r="D779" s="38" t="n"/>
+    </row>
+    <row r="780">
+      <c r="B780" s="36" t="n">
+        <v>776</v>
+      </c>
+      <c r="C780" s="39" t="n"/>
+      <c r="D780" s="40" t="n"/>
+    </row>
+    <row r="781">
+      <c r="B781" s="36" t="n">
+        <v>777</v>
+      </c>
+      <c r="C781" s="37" t="n"/>
+      <c r="D781" s="38" t="n"/>
+    </row>
+    <row r="782">
+      <c r="B782" s="36" t="n">
+        <v>778</v>
+      </c>
+      <c r="C782" s="39" t="n"/>
+      <c r="D782" s="40" t="n"/>
+    </row>
+    <row r="783">
+      <c r="B783" s="36" t="n">
+        <v>779</v>
+      </c>
+      <c r="C783" s="37" t="n"/>
+      <c r="D783" s="38" t="n"/>
+    </row>
+    <row r="784">
+      <c r="B784" s="36" t="n">
+        <v>780</v>
+      </c>
+      <c r="C784" s="39" t="n"/>
+      <c r="D784" s="40" t="n"/>
+    </row>
+    <row r="785">
+      <c r="B785" s="36" t="n">
+        <v>781</v>
+      </c>
+      <c r="C785" s="37" t="n"/>
+      <c r="D785" s="38" t="n"/>
+    </row>
+    <row r="786">
+      <c r="B786" s="36" t="n">
+        <v>782</v>
+      </c>
+      <c r="C786" s="39" t="n"/>
+      <c r="D786" s="40" t="n"/>
+    </row>
+    <row r="787">
+      <c r="B787" s="36" t="n">
+        <v>783</v>
+      </c>
+      <c r="C787" s="37" t="n"/>
+      <c r="D787" s="38" t="n"/>
+    </row>
+    <row r="788">
+      <c r="B788" s="36" t="n">
+        <v>784</v>
+      </c>
+      <c r="C788" s="39" t="n"/>
+      <c r="D788" s="40" t="n"/>
+    </row>
+    <row r="789">
+      <c r="B789" s="36" t="n">
+        <v>785</v>
+      </c>
+      <c r="C789" s="37" t="n"/>
+      <c r="D789" s="38" t="n"/>
+    </row>
+    <row r="790">
+      <c r="B790" s="36" t="n">
+        <v>786</v>
+      </c>
+      <c r="C790" s="39" t="n"/>
+      <c r="D790" s="40" t="n"/>
+    </row>
+    <row r="791">
+      <c r="B791" s="36" t="n">
+        <v>787</v>
+      </c>
+      <c r="C791" s="37" t="n"/>
+      <c r="D791" s="38" t="n"/>
+    </row>
+    <row r="792">
+      <c r="B792" s="36" t="n">
+        <v>788</v>
+      </c>
+      <c r="C792" s="39" t="n"/>
+      <c r="D792" s="40" t="n"/>
+    </row>
+    <row r="793">
+      <c r="B793" s="36" t="n">
+        <v>789</v>
+      </c>
+      <c r="C793" s="37" t="n"/>
+      <c r="D793" s="38" t="n"/>
+    </row>
+    <row r="794">
+      <c r="B794" s="36" t="n">
+        <v>790</v>
+      </c>
+      <c r="C794" s="39" t="n"/>
+      <c r="D794" s="40" t="n"/>
+    </row>
+    <row r="795">
+      <c r="B795" s="36" t="n">
+        <v>791</v>
+      </c>
+      <c r="C795" s="37" t="n"/>
+      <c r="D795" s="38" t="n"/>
+    </row>
+    <row r="796">
+      <c r="B796" s="36" t="n">
+        <v>792</v>
+      </c>
+      <c r="C796" s="39" t="n"/>
+      <c r="D796" s="40" t="n"/>
+    </row>
+    <row r="797">
+      <c r="B797" s="36" t="n">
+        <v>793</v>
+      </c>
+      <c r="C797" s="37" t="n"/>
+      <c r="D797" s="38" t="n"/>
+    </row>
+    <row r="798">
+      <c r="B798" s="36" t="n">
+        <v>794</v>
+      </c>
+      <c r="C798" s="39" t="n"/>
+      <c r="D798" s="40" t="n"/>
+    </row>
+    <row r="799">
+      <c r="B799" s="36" t="n">
+        <v>795</v>
+      </c>
+      <c r="C799" s="37" t="n"/>
+      <c r="D799" s="38" t="n"/>
+    </row>
+    <row r="800">
+      <c r="B800" s="36" t="n">
+        <v>796</v>
+      </c>
+      <c r="C800" s="39" t="n"/>
+      <c r="D800" s="40" t="n"/>
+    </row>
+    <row r="801">
+      <c r="B801" s="36" t="n">
+        <v>797</v>
+      </c>
+      <c r="C801" s="37" t="n"/>
+      <c r="D801" s="38" t="n"/>
+    </row>
+    <row r="802">
+      <c r="B802" s="36" t="n">
+        <v>798</v>
+      </c>
+      <c r="C802" s="39" t="n"/>
+      <c r="D802" s="40" t="n"/>
+    </row>
+    <row r="803">
+      <c r="B803" s="36" t="n">
+        <v>799</v>
+      </c>
+      <c r="C803" s="37" t="n"/>
+      <c r="D803" s="38" t="n"/>
+    </row>
+    <row r="804">
+      <c r="B804" s="36" t="n">
+        <v>800</v>
+      </c>
+      <c r="C804" s="39" t="n"/>
+      <c r="D804" s="40" t="n"/>
+    </row>
+    <row r="805">
+      <c r="B805" s="36" t="n">
+        <v>801</v>
+      </c>
+      <c r="C805" s="37" t="n"/>
+      <c r="D805" s="38" t="n"/>
+    </row>
+    <row r="806">
+      <c r="B806" s="36" t="n">
+        <v>802</v>
+      </c>
+      <c r="C806" s="39" t="n"/>
+      <c r="D806" s="40" t="n"/>
+    </row>
+    <row r="807">
+      <c r="B807" s="36" t="n">
+        <v>803</v>
+      </c>
+      <c r="C807" s="37" t="n"/>
+      <c r="D807" s="38" t="n"/>
+    </row>
+    <row r="808">
+      <c r="B808" s="36" t="n">
+        <v>804</v>
+      </c>
+      <c r="C808" s="39" t="n"/>
+      <c r="D808" s="40" t="n"/>
+    </row>
+    <row r="809">
+      <c r="B809" s="36" t="n">
+        <v>805</v>
+      </c>
+      <c r="C809" s="37" t="n"/>
+      <c r="D809" s="38" t="n"/>
+    </row>
+    <row r="810">
+      <c r="B810" s="36" t="n">
+        <v>806</v>
+      </c>
+      <c r="C810" s="39" t="n"/>
+      <c r="D810" s="40" t="n"/>
+    </row>
+    <row r="811">
+      <c r="B811" s="36" t="n">
+        <v>807</v>
+      </c>
+      <c r="C811" s="37" t="n"/>
+      <c r="D811" s="38" t="n"/>
+    </row>
+    <row r="812">
+      <c r="B812" s="36" t="n">
+        <v>808</v>
+      </c>
+      <c r="C812" s="39" t="n"/>
+      <c r="D812" s="40" t="n"/>
+    </row>
+    <row r="813">
+      <c r="B813" s="36" t="n">
+        <v>809</v>
+      </c>
+      <c r="C813" s="37" t="n"/>
+      <c r="D813" s="38" t="n"/>
+    </row>
+    <row r="814">
+      <c r="B814" s="36" t="n">
+        <v>810</v>
+      </c>
+      <c r="C814" s="39" t="n"/>
+      <c r="D814" s="40" t="n"/>
+    </row>
+    <row r="815">
+      <c r="B815" s="36" t="n">
+        <v>811</v>
+      </c>
+      <c r="C815" s="37" t="n"/>
+      <c r="D815" s="38" t="n"/>
+    </row>
+    <row r="816">
+      <c r="B816" s="36" t="n">
+        <v>812</v>
+      </c>
+      <c r="C816" s="39" t="n"/>
+      <c r="D816" s="40" t="n"/>
+    </row>
+    <row r="817">
+      <c r="B817" s="36" t="n">
+        <v>813</v>
+      </c>
+      <c r="C817" s="37" t="n"/>
+      <c r="D817" s="38" t="n"/>
+    </row>
+    <row r="818">
+      <c r="B818" s="36" t="n">
+        <v>814</v>
+      </c>
+      <c r="C818" s="39" t="n"/>
+      <c r="D818" s="40" t="n"/>
+    </row>
+    <row r="819">
+      <c r="B819" s="36" t="n">
+        <v>815</v>
+      </c>
+      <c r="C819" s="37" t="n"/>
+      <c r="D819" s="38" t="n"/>
+    </row>
+    <row r="820">
+      <c r="B820" s="36" t="n">
+        <v>816</v>
+      </c>
+      <c r="C820" s="39" t="n"/>
+      <c r="D820" s="40" t="n"/>
+    </row>
+    <row r="821">
+      <c r="B821" s="36" t="n">
+        <v>817</v>
+      </c>
+      <c r="C821" s="37" t="n"/>
+      <c r="D821" s="38" t="n"/>
+    </row>
+    <row r="822">
+      <c r="B822" s="36" t="n">
+        <v>818</v>
+      </c>
+      <c r="C822" s="39" t="n"/>
+      <c r="D822" s="40" t="n"/>
+    </row>
+    <row r="823">
+      <c r="B823" s="36" t="n">
+        <v>819</v>
+      </c>
+      <c r="C823" s="37" t="n"/>
+      <c r="D823" s="38" t="n"/>
+    </row>
+    <row r="824">
+      <c r="B824" s="36" t="n">
+        <v>820</v>
+      </c>
+      <c r="C824" s="39" t="n"/>
+      <c r="D824" s="40" t="n"/>
+    </row>
+    <row r="825">
+      <c r="B825" s="36" t="n">
+        <v>821</v>
+      </c>
+      <c r="C825" s="37" t="n"/>
+      <c r="D825" s="38" t="n"/>
+    </row>
+    <row r="826">
+      <c r="B826" s="36" t="n">
+        <v>822</v>
+      </c>
+      <c r="C826" s="39" t="n"/>
+      <c r="D826" s="40" t="n"/>
+    </row>
+    <row r="827">
+      <c r="B827" s="36" t="n">
+        <v>823</v>
+      </c>
+      <c r="C827" s="37" t="n"/>
+      <c r="D827" s="38" t="n"/>
+    </row>
+    <row r="828">
+      <c r="B828" s="36" t="n">
+        <v>824</v>
+      </c>
+      <c r="C828" s="39" t="n"/>
+      <c r="D828" s="40" t="n"/>
+    </row>
+    <row r="829">
+      <c r="B829" s="36" t="n">
+        <v>825</v>
+      </c>
+      <c r="C829" s="37" t="n"/>
+      <c r="D829" s="38" t="n"/>
+    </row>
+    <row r="830">
+      <c r="B830" s="36" t="n">
+        <v>826</v>
+      </c>
+      <c r="C830" s="39" t="n"/>
+      <c r="D830" s="40" t="n"/>
+    </row>
+    <row r="831">
+      <c r="B831" s="36" t="n">
+        <v>827</v>
+      </c>
+      <c r="C831" s="37" t="n"/>
+      <c r="D831" s="38" t="n"/>
+    </row>
+    <row r="832">
+      <c r="B832" s="36" t="n">
+        <v>828</v>
+      </c>
+      <c r="C832" s="39" t="n"/>
+      <c r="D832" s="40" t="n"/>
+    </row>
+    <row r="833">
+      <c r="B833" s="36" t="n">
+        <v>829</v>
+      </c>
+      <c r="C833" s="37" t="n"/>
+      <c r="D833" s="38" t="n"/>
+    </row>
+    <row r="834">
+      <c r="B834" s="36" t="n">
+        <v>830</v>
+      </c>
+      <c r="C834" s="39" t="n"/>
+      <c r="D834" s="40" t="n"/>
+    </row>
+    <row r="835">
+      <c r="B835" s="36" t="n">
+        <v>831</v>
+      </c>
+      <c r="C835" s="37" t="n"/>
+      <c r="D835" s="38" t="n"/>
+    </row>
+    <row r="836">
+      <c r="B836" s="36" t="n">
+        <v>832</v>
+      </c>
+      <c r="C836" s="39" t="n"/>
+      <c r="D836" s="40" t="n"/>
+    </row>
+    <row r="837">
+      <c r="B837" s="36" t="n">
+        <v>833</v>
+      </c>
+      <c r="C837" s="37" t="n"/>
+      <c r="D837" s="38" t="n"/>
+    </row>
+    <row r="838">
+      <c r="B838" s="36" t="n">
+        <v>834</v>
+      </c>
+      <c r="C838" s="39" t="n"/>
+      <c r="D838" s="40" t="n"/>
+    </row>
+    <row r="839">
+      <c r="B839" s="36" t="n">
+        <v>835</v>
+      </c>
+      <c r="C839" s="37" t="n"/>
+      <c r="D839" s="38" t="n"/>
+    </row>
+    <row r="840">
+      <c r="B840" s="36" t="n">
+        <v>836</v>
+      </c>
+      <c r="C840" s="39" t="n"/>
+      <c r="D840" s="40" t="n"/>
+    </row>
+    <row r="841">
+      <c r="B841" s="36" t="n">
+        <v>837</v>
+      </c>
+      <c r="C841" s="37" t="n"/>
+      <c r="D841" s="38" t="n"/>
+    </row>
+    <row r="842">
+      <c r="B842" s="36" t="n">
+        <v>838</v>
+      </c>
+      <c r="C842" s="39" t="n"/>
+      <c r="D842" s="40" t="n"/>
+    </row>
+    <row r="843">
+      <c r="B843" s="36" t="n">
+        <v>839</v>
+      </c>
+      <c r="C843" s="37" t="n"/>
+      <c r="D843" s="38" t="n"/>
+    </row>
+    <row r="844">
+      <c r="B844" s="36" t="n">
+        <v>840</v>
+      </c>
+      <c r="C844" s="39" t="n"/>
+      <c r="D844" s="40" t="n"/>
+    </row>
+    <row r="845">
+      <c r="B845" s="36" t="n">
+        <v>841</v>
+      </c>
+      <c r="C845" s="37" t="n"/>
+      <c r="D845" s="38" t="n"/>
+    </row>
+    <row r="846">
+      <c r="B846" s="36" t="n">
+        <v>842</v>
+      </c>
+      <c r="C846" s="39" t="n"/>
+      <c r="D846" s="40" t="n"/>
+    </row>
+    <row r="847">
+      <c r="B847" s="36" t="n">
+        <v>843</v>
+      </c>
+      <c r="C847" s="37" t="n"/>
+      <c r="D847" s="38" t="n"/>
+    </row>
+    <row r="848">
+      <c r="B848" s="36" t="n">
+        <v>844</v>
+      </c>
+      <c r="C848" s="39" t="n"/>
+      <c r="D848" s="40" t="n"/>
+    </row>
+    <row r="849">
+      <c r="B849" s="36" t="n">
+        <v>845</v>
+      </c>
+      <c r="C849" s="37" t="n"/>
+      <c r="D849" s="38" t="n"/>
+    </row>
+    <row r="850">
+      <c r="B850" s="36" t="n">
+        <v>846</v>
+      </c>
+      <c r="C850" s="39" t="n"/>
+      <c r="D850" s="40" t="n"/>
+    </row>
+    <row r="851">
+      <c r="B851" s="36" t="n">
+        <v>847</v>
+      </c>
+      <c r="C851" s="37" t="n"/>
+      <c r="D851" s="38" t="n"/>
+    </row>
+    <row r="852">
+      <c r="B852" s="36" t="n">
+        <v>848</v>
+      </c>
+      <c r="C852" s="39" t="n"/>
+      <c r="D852" s="40" t="n"/>
+    </row>
+    <row r="853">
+      <c r="B853" s="36" t="n">
+        <v>849</v>
+      </c>
+      <c r="C853" s="37" t="n"/>
+      <c r="D853" s="38" t="n"/>
+    </row>
+    <row r="854">
+      <c r="B854" s="36" t="n">
+        <v>850</v>
+      </c>
+      <c r="C854" s="39" t="n"/>
+      <c r="D854" s="40" t="n"/>
+    </row>
+    <row r="855">
+      <c r="B855" s="36" t="n">
+        <v>851</v>
+      </c>
+      <c r="C855" s="37" t="n"/>
+      <c r="D855" s="38" t="n"/>
+    </row>
+    <row r="856">
+      <c r="B856" s="36" t="n">
+        <v>852</v>
+      </c>
+      <c r="C856" s="39" t="n"/>
+      <c r="D856" s="40" t="n"/>
+    </row>
+    <row r="857">
+      <c r="B857" s="36" t="n">
+        <v>853</v>
+      </c>
+      <c r="C857" s="37" t="n"/>
+      <c r="D857" s="38" t="n"/>
+    </row>
+    <row r="858">
+      <c r="B858" s="36" t="n">
+        <v>854</v>
+      </c>
+      <c r="C858" s="39" t="n"/>
+      <c r="D858" s="40" t="n"/>
+    </row>
+    <row r="859">
+      <c r="B859" s="36" t="n">
+        <v>855</v>
+      </c>
+      <c r="C859" s="37" t="n"/>
+      <c r="D859" s="38" t="n"/>
+    </row>
+    <row r="860">
+      <c r="B860" s="36" t="n">
+        <v>856</v>
+      </c>
+      <c r="C860" s="39" t="n"/>
+      <c r="D860" s="40" t="n"/>
+    </row>
+    <row r="861">
+      <c r="B861" s="36" t="n">
+        <v>857</v>
+      </c>
+      <c r="C861" s="37" t="n"/>
+      <c r="D861" s="38" t="n"/>
+    </row>
+    <row r="862">
+      <c r="B862" s="36" t="n">
+        <v>858</v>
+      </c>
+      <c r="C862" s="39" t="n"/>
+      <c r="D862" s="40" t="n"/>
+    </row>
+    <row r="863">
+      <c r="B863" s="36" t="n">
+        <v>859</v>
+      </c>
+      <c r="C863" s="37" t="n"/>
+      <c r="D863" s="38" t="n"/>
+    </row>
+    <row r="864">
+      <c r="B864" s="36" t="n">
+        <v>860</v>
+      </c>
+      <c r="C864" s="39" t="n"/>
+      <c r="D864" s="40" t="n"/>
+    </row>
+    <row r="865">
+      <c r="B865" s="36" t="n">
+        <v>861</v>
+      </c>
+      <c r="C865" s="37" t="n"/>
+      <c r="D865" s="38" t="n"/>
+    </row>
+    <row r="866">
+      <c r="B866" s="36" t="n">
+        <v>862</v>
+      </c>
+      <c r="C866" s="39" t="n"/>
+      <c r="D866" s="40" t="n"/>
+    </row>
+    <row r="867">
+      <c r="B867" s="36" t="n">
+        <v>863</v>
+      </c>
+      <c r="C867" s="37" t="n"/>
+      <c r="D867" s="38" t="n"/>
+    </row>
+    <row r="868">
+      <c r="B868" s="36" t="n">
+        <v>864</v>
+      </c>
+      <c r="C868" s="39" t="n"/>
+      <c r="D868" s="40" t="n"/>
+    </row>
+    <row r="869">
+      <c r="B869" s="36" t="n">
+        <v>865</v>
+      </c>
+      <c r="C869" s="37" t="n"/>
+      <c r="D869" s="38" t="n"/>
+    </row>
+    <row r="870">
+      <c r="B870" s="36" t="n">
+        <v>866</v>
+      </c>
+      <c r="C870" s="39" t="n"/>
+      <c r="D870" s="40" t="n"/>
+    </row>
+    <row r="871">
+      <c r="B871" s="36" t="n">
+        <v>867</v>
+      </c>
+      <c r="C871" s="37" t="n"/>
+      <c r="D871" s="38" t="n"/>
+    </row>
+    <row r="872">
+      <c r="B872" s="36" t="n">
+        <v>868</v>
+      </c>
+      <c r="C872" s="39" t="n"/>
+      <c r="D872" s="40" t="n"/>
+    </row>
+    <row r="873">
+      <c r="B873" s="36" t="n">
+        <v>869</v>
+      </c>
+      <c r="C873" s="37" t="n"/>
+      <c r="D873" s="38" t="n"/>
+    </row>
+    <row r="874">
+      <c r="B874" s="36" t="n">
+        <v>870</v>
+      </c>
+      <c r="C874" s="39" t="n"/>
+      <c r="D874" s="40" t="n"/>
+    </row>
+    <row r="875">
+      <c r="B875" s="36" t="n">
+        <v>871</v>
+      </c>
+      <c r="C875" s="37" t="n"/>
+      <c r="D875" s="38" t="n"/>
+    </row>
+    <row r="876">
+      <c r="B876" s="36" t="n">
+        <v>872</v>
+      </c>
+      <c r="C876" s="39" t="n"/>
+      <c r="D876" s="40" t="n"/>
+    </row>
+    <row r="877">
+      <c r="B877" s="36" t="n">
+        <v>873</v>
+      </c>
+      <c r="C877" s="37" t="n"/>
+      <c r="D877" s="38" t="n"/>
+    </row>
+    <row r="878">
+      <c r="B878" s="36" t="n">
+        <v>874</v>
+      </c>
+      <c r="C878" s="39" t="n"/>
+      <c r="D878" s="40" t="n"/>
+    </row>
+    <row r="879">
+      <c r="B879" s="36" t="n">
+        <v>875</v>
+      </c>
+      <c r="C879" s="37" t="n"/>
+      <c r="D879" s="38" t="n"/>
+    </row>
+    <row r="880">
+      <c r="B880" s="36" t="n">
+        <v>876</v>
+      </c>
+      <c r="C880" s="39" t="n"/>
+      <c r="D880" s="40" t="n"/>
+    </row>
+    <row r="881">
+      <c r="B881" s="36" t="n">
+        <v>877</v>
+      </c>
+      <c r="C881" s="37" t="n"/>
+      <c r="D881" s="38" t="n"/>
+    </row>
+    <row r="882">
+      <c r="B882" s="36" t="n">
+        <v>878</v>
+      </c>
+      <c r="C882" s="39" t="n"/>
+      <c r="D882" s="40" t="n"/>
+    </row>
+    <row r="883">
+      <c r="B883" s="36" t="n">
+        <v>879</v>
+      </c>
+      <c r="C883" s="37" t="n"/>
+      <c r="D883" s="38" t="n"/>
+    </row>
+    <row r="884">
+      <c r="B884" s="36" t="n">
+        <v>880</v>
+      </c>
+      <c r="C884" s="39" t="n"/>
+      <c r="D884" s="40" t="n"/>
+    </row>
+    <row r="885">
+      <c r="B885" s="36" t="n">
+        <v>881</v>
+      </c>
+      <c r="C885" s="37" t="n"/>
+      <c r="D885" s="38" t="n"/>
+    </row>
+    <row r="886">
+      <c r="B886" s="36" t="n">
+        <v>882</v>
+      </c>
+      <c r="C886" s="39" t="n"/>
+      <c r="D886" s="40" t="n"/>
+    </row>
+    <row r="887">
+      <c r="B887" s="36" t="n">
+        <v>883</v>
+      </c>
+      <c r="C887" s="37" t="n"/>
+      <c r="D887" s="38" t="n"/>
+    </row>
+    <row r="888">
+      <c r="B888" s="36" t="n">
+        <v>884</v>
+      </c>
+      <c r="C888" s="39" t="n"/>
+      <c r="D888" s="40" t="n"/>
+    </row>
+    <row r="889">
+      <c r="B889" s="36" t="n">
+        <v>885</v>
+      </c>
+      <c r="C889" s="37" t="n"/>
+      <c r="D889" s="38" t="n"/>
+    </row>
+    <row r="890">
+      <c r="B890" s="36" t="n">
+        <v>886</v>
+      </c>
+      <c r="C890" s="39" t="n"/>
+      <c r="D890" s="40" t="n"/>
+    </row>
+    <row r="891">
+      <c r="B891" s="36" t="n">
+        <v>887</v>
+      </c>
+      <c r="C891" s="37" t="n"/>
+      <c r="D891" s="38" t="n"/>
+    </row>
+    <row r="892">
+      <c r="B892" s="36" t="n">
+        <v>888</v>
+      </c>
+      <c r="C892" s="39" t="n"/>
+      <c r="D892" s="40" t="n"/>
+    </row>
+    <row r="893">
+      <c r="B893" s="36" t="n">
+        <v>889</v>
+      </c>
+      <c r="C893" s="37" t="n"/>
+      <c r="D893" s="38" t="n"/>
+    </row>
+    <row r="894">
+      <c r="B894" s="36" t="n">
+        <v>890</v>
+      </c>
+      <c r="C894" s="39" t="n"/>
+      <c r="D894" s="40" t="n"/>
+    </row>
+    <row r="895">
+      <c r="B895" s="36" t="n">
+        <v>891</v>
+      </c>
+      <c r="C895" s="37" t="n"/>
+      <c r="D895" s="38" t="n"/>
+    </row>
+    <row r="896">
+      <c r="B896" s="36" t="n">
+        <v>892</v>
+      </c>
+      <c r="C896" s="39" t="n"/>
+      <c r="D896" s="40" t="n"/>
+    </row>
+    <row r="897">
+      <c r="B897" s="36" t="n">
+        <v>893</v>
+      </c>
+      <c r="C897" s="37" t="n"/>
+      <c r="D897" s="38" t="n"/>
+    </row>
+    <row r="898">
+      <c r="B898" s="36" t="n">
+        <v>894</v>
+      </c>
+      <c r="C898" s="39" t="n"/>
+      <c r="D898" s="40" t="n"/>
+    </row>
+    <row r="899">
+      <c r="B899" s="36" t="n">
+        <v>895</v>
+      </c>
+      <c r="C899" s="37" t="n"/>
+      <c r="D899" s="38" t="n"/>
+    </row>
+    <row r="900">
+      <c r="B900" s="36" t="n">
+        <v>896</v>
+      </c>
+      <c r="C900" s="39" t="n"/>
+      <c r="D900" s="40" t="n"/>
+    </row>
+    <row r="901">
+      <c r="B901" s="36" t="n">
+        <v>897</v>
+      </c>
+      <c r="C901" s="37" t="n"/>
+      <c r="D901" s="38" t="n"/>
+    </row>
+    <row r="902">
+      <c r="B902" s="36" t="n">
+        <v>898</v>
+      </c>
+      <c r="C902" s="39" t="n"/>
+      <c r="D902" s="40" t="n"/>
+    </row>
+    <row r="903">
+      <c r="B903" s="36" t="n">
+        <v>899</v>
+      </c>
+      <c r="C903" s="37" t="n"/>
+      <c r="D903" s="38" t="n"/>
+    </row>
+    <row r="904">
+      <c r="B904" s="36" t="n">
+        <v>900</v>
+      </c>
+      <c r="C904" s="39" t="n"/>
+      <c r="D904" s="40" t="n"/>
+    </row>
+    <row r="905">
+      <c r="B905" s="36" t="n">
+        <v>901</v>
+      </c>
+      <c r="C905" s="37" t="n"/>
+      <c r="D905" s="38" t="n"/>
+    </row>
+    <row r="906">
+      <c r="B906" s="36" t="n">
+        <v>902</v>
+      </c>
+      <c r="C906" s="39" t="n"/>
+      <c r="D906" s="40" t="n"/>
+    </row>
+    <row r="907">
+      <c r="B907" s="36" t="n">
+        <v>903</v>
+      </c>
+      <c r="C907" s="37" t="n"/>
+      <c r="D907" s="38" t="n"/>
+    </row>
+    <row r="908">
+      <c r="B908" s="36" t="n">
+        <v>904</v>
+      </c>
+      <c r="C908" s="39" t="n"/>
+      <c r="D908" s="40" t="n"/>
+    </row>
+    <row r="909">
+      <c r="B909" s="36" t="n">
+        <v>905</v>
+      </c>
+      <c r="C909" s="37" t="n"/>
+      <c r="D909" s="38" t="n"/>
+    </row>
+    <row r="910">
+      <c r="B910" s="36" t="n">
+        <v>906</v>
+      </c>
+      <c r="C910" s="39" t="n"/>
+      <c r="D910" s="40" t="n"/>
+    </row>
+    <row r="911">
+      <c r="B911" s="36" t="n">
+        <v>907</v>
+      </c>
+      <c r="C911" s="37" t="n"/>
+      <c r="D911" s="38" t="n"/>
+    </row>
+    <row r="912">
+      <c r="B912" s="36" t="n">
+        <v>908</v>
+      </c>
+      <c r="C912" s="39" t="n"/>
+      <c r="D912" s="40" t="n"/>
+    </row>
+    <row r="913">
+      <c r="B913" s="36" t="n">
+        <v>909</v>
+      </c>
+      <c r="C913" s="37" t="n"/>
+      <c r="D913" s="38" t="n"/>
+    </row>
+    <row r="914">
+      <c r="B914" s="36" t="n">
+        <v>910</v>
+      </c>
+      <c r="C914" s="39" t="n"/>
+      <c r="D914" s="40" t="n"/>
+    </row>
+    <row r="915">
+      <c r="B915" s="36" t="n">
+        <v>911</v>
+      </c>
+      <c r="C915" s="37" t="n"/>
+      <c r="D915" s="38" t="n"/>
+    </row>
+    <row r="916">
+      <c r="B916" s="36" t="n">
+        <v>912</v>
+      </c>
+      <c r="C916" s="39" t="n"/>
+      <c r="D916" s="40" t="n"/>
+    </row>
+    <row r="917">
+      <c r="B917" s="36" t="n">
+        <v>913</v>
+      </c>
+      <c r="C917" s="37" t="n"/>
+      <c r="D917" s="38" t="n"/>
+    </row>
+    <row r="918">
+      <c r="B918" s="36" t="n">
+        <v>914</v>
+      </c>
+      <c r="C918" s="39" t="n"/>
+      <c r="D918" s="40" t="n"/>
+    </row>
+    <row r="919">
+      <c r="B919" s="36" t="n">
+        <v>915</v>
+      </c>
+      <c r="C919" s="37" t="n"/>
+      <c r="D919" s="38" t="n"/>
+    </row>
+    <row r="920">
+      <c r="B920" s="36" t="n">
+        <v>916</v>
+      </c>
+      <c r="C920" s="39" t="n"/>
+      <c r="D920" s="40" t="n"/>
+    </row>
+    <row r="921">
+      <c r="B921" s="36" t="n">
+        <v>917</v>
+      </c>
+      <c r="C921" s="37" t="n"/>
+      <c r="D921" s="38" t="n"/>
+    </row>
+    <row r="922">
+      <c r="B922" s="36" t="n">
+        <v>918</v>
+      </c>
+      <c r="C922" s="39" t="n"/>
+      <c r="D922" s="40" t="n"/>
+    </row>
+    <row r="923">
+      <c r="B923" s="36" t="n">
+        <v>919</v>
+      </c>
+      <c r="C923" s="37" t="n"/>
+      <c r="D923" s="38" t="n"/>
+    </row>
+    <row r="924">
+      <c r="B924" s="36" t="n">
+        <v>920</v>
+      </c>
+      <c r="C924" s="39" t="n"/>
+      <c r="D924" s="40" t="n"/>
+    </row>
+    <row r="925">
+      <c r="B925" s="36" t="n">
+        <v>921</v>
+      </c>
+      <c r="C925" s="37" t="n"/>
+      <c r="D925" s="38" t="n"/>
+    </row>
+    <row r="926">
+      <c r="B926" s="36" t="n">
+        <v>922</v>
+      </c>
+      <c r="C926" s="39" t="n"/>
+      <c r="D926" s="40" t="n"/>
+    </row>
+    <row r="927">
+      <c r="B927" s="36" t="n">
+        <v>923</v>
+      </c>
+      <c r="C927" s="37" t="n"/>
+      <c r="D927" s="38" t="n"/>
+    </row>
+    <row r="928">
+      <c r="B928" s="36" t="n">
+        <v>924</v>
+      </c>
+      <c r="C928" s="39" t="n"/>
+      <c r="D928" s="40" t="n"/>
+    </row>
+    <row r="929">
+      <c r="B929" s="36" t="n">
+        <v>925</v>
+      </c>
+      <c r="C929" s="37" t="n"/>
+      <c r="D929" s="38" t="n"/>
+    </row>
+    <row r="930">
+      <c r="B930" s="36" t="n">
+        <v>926</v>
+      </c>
+      <c r="C930" s="39" t="n"/>
+      <c r="D930" s="40" t="n"/>
+    </row>
+    <row r="931">
+      <c r="B931" s="36" t="n">
+        <v>927</v>
+      </c>
+      <c r="C931" s="37" t="n"/>
+      <c r="D931" s="38" t="n"/>
+    </row>
+    <row r="932">
+      <c r="B932" s="36" t="n">
+        <v>928</v>
+      </c>
+      <c r="C932" s="39" t="n"/>
+      <c r="D932" s="40" t="n"/>
+    </row>
+    <row r="933">
+      <c r="B933" s="36" t="n">
+        <v>929</v>
+      </c>
+      <c r="C933" s="37" t="n"/>
+      <c r="D933" s="38" t="n"/>
+    </row>
+    <row r="934">
+      <c r="B934" s="36" t="n">
+        <v>930</v>
+      </c>
+      <c r="C934" s="39" t="n"/>
+      <c r="D934" s="40" t="n"/>
+    </row>
+    <row r="935">
+      <c r="B935" s="36" t="n">
+        <v>931</v>
+      </c>
+      <c r="C935" s="37" t="n"/>
+      <c r="D935" s="38" t="n"/>
+    </row>
+    <row r="936">
+      <c r="B936" s="36" t="n">
+        <v>932</v>
+      </c>
+      <c r="C936" s="39" t="n"/>
+      <c r="D936" s="40" t="n"/>
+    </row>
+    <row r="937">
+      <c r="B937" s="36" t="n">
+        <v>933</v>
+      </c>
+      <c r="C937" s="37" t="n"/>
+      <c r="D937" s="38" t="n"/>
+    </row>
+    <row r="938">
+      <c r="B938" s="36" t="n">
+        <v>934</v>
+      </c>
+      <c r="C938" s="39" t="n"/>
+      <c r="D938" s="40" t="n"/>
+    </row>
+    <row r="939">
+      <c r="B939" s="36" t="n">
+        <v>935</v>
+      </c>
+      <c r="C939" s="37" t="n"/>
+      <c r="D939" s="38" t="n"/>
+    </row>
+    <row r="940">
+      <c r="B940" s="36" t="n">
+        <v>936</v>
+      </c>
+      <c r="C940" s="39" t="n"/>
+      <c r="D940" s="40" t="n"/>
+    </row>
+    <row r="941">
+      <c r="B941" s="36" t="n">
+        <v>937</v>
+      </c>
+      <c r="C941" s="37" t="n"/>
+      <c r="D941" s="38" t="n"/>
+    </row>
+    <row r="942">
+      <c r="B942" s="36" t="n">
+        <v>938</v>
+      </c>
+      <c r="C942" s="39" t="n"/>
+      <c r="D942" s="40" t="n"/>
+    </row>
+    <row r="943">
+      <c r="B943" s="36" t="n">
+        <v>939</v>
+      </c>
+      <c r="C943" s="37" t="n"/>
+      <c r="D943" s="38" t="n"/>
+    </row>
+    <row r="944">
+      <c r="B944" s="36" t="n">
+        <v>940</v>
+      </c>
+      <c r="C944" s="39" t="n"/>
+      <c r="D944" s="40" t="n"/>
+    </row>
+    <row r="945">
+      <c r="B945" s="36" t="n">
+        <v>941</v>
+      </c>
+      <c r="C945" s="37" t="n"/>
+      <c r="D945" s="38" t="n"/>
+    </row>
+    <row r="946">
+      <c r="B946" s="36" t="n">
+        <v>942</v>
+      </c>
+      <c r="C946" s="39" t="n"/>
+      <c r="D946" s="40" t="n"/>
+    </row>
+    <row r="947">
+      <c r="B947" s="36" t="n">
+        <v>943</v>
+      </c>
+      <c r="C947" s="37" t="n"/>
+      <c r="D947" s="38" t="n"/>
+    </row>
+    <row r="948">
+      <c r="B948" s="36" t="n">
+        <v>944</v>
+      </c>
+      <c r="C948" s="39" t="n"/>
+      <c r="D948" s="40" t="n"/>
+    </row>
+    <row r="949">
+      <c r="B949" s="36" t="n">
+        <v>945</v>
+      </c>
+      <c r="C949" s="37" t="n"/>
+      <c r="D949" s="38" t="n"/>
+    </row>
+    <row r="950">
+      <c r="B950" s="36" t="n">
+        <v>946</v>
+      </c>
+      <c r="C950" s="39" t="n"/>
+      <c r="D950" s="40" t="n"/>
+    </row>
+    <row r="951">
+      <c r="B951" s="36" t="n">
+        <v>947</v>
+      </c>
+      <c r="C951" s="37" t="n"/>
+      <c r="D951" s="38" t="n"/>
+    </row>
+    <row r="952">
+      <c r="B952" s="36" t="n">
+        <v>948</v>
+      </c>
+      <c r="C952" s="39" t="n"/>
+      <c r="D952" s="40" t="n"/>
+    </row>
+    <row r="953">
+      <c r="B953" s="36" t="n">
+        <v>949</v>
+      </c>
+      <c r="C953" s="37" t="n"/>
+      <c r="D953" s="38" t="n"/>
+    </row>
+    <row r="954">
+      <c r="B954" s="36" t="n">
+        <v>950</v>
+      </c>
+      <c r="C954" s="39" t="n"/>
+      <c r="D954" s="40" t="n"/>
+    </row>
+    <row r="955">
+      <c r="B955" s="36" t="n">
+        <v>951</v>
+      </c>
+      <c r="C955" s="37" t="n"/>
+      <c r="D955" s="38" t="n"/>
+    </row>
+    <row r="956">
+      <c r="B956" s="36" t="n">
+        <v>952</v>
+      </c>
+      <c r="C956" s="39" t="n"/>
+      <c r="D956" s="40" t="n"/>
+    </row>
+    <row r="957">
+      <c r="B957" s="36" t="n">
+        <v>953</v>
+      </c>
+      <c r="C957" s="37" t="n"/>
+      <c r="D957" s="38" t="n"/>
+    </row>
+    <row r="958">
+      <c r="B958" s="36" t="n">
+        <v>954</v>
+      </c>
+      <c r="C958" s="39" t="n"/>
+      <c r="D958" s="40" t="n"/>
+    </row>
+    <row r="959">
+      <c r="B959" s="36" t="n">
+        <v>955</v>
+      </c>
+      <c r="C959" s="37" t="n"/>
+      <c r="D959" s="38" t="n"/>
+    </row>
+    <row r="960">
+      <c r="B960" s="36" t="n">
+        <v>956</v>
+      </c>
+      <c r="C960" s="39" t="n"/>
+      <c r="D960" s="40" t="n"/>
+    </row>
+    <row r="961">
+      <c r="B961" s="36" t="n">
+        <v>957</v>
+      </c>
+      <c r="C961" s="37" t="n"/>
+      <c r="D961" s="38" t="n"/>
+    </row>
+    <row r="962">
+      <c r="B962" s="36" t="n">
+        <v>958</v>
+      </c>
+      <c r="C962" s="39" t="n"/>
+      <c r="D962" s="40" t="n"/>
+    </row>
+    <row r="963">
+      <c r="B963" s="36" t="n">
+        <v>959</v>
+      </c>
+      <c r="C963" s="37" t="n"/>
+      <c r="D963" s="38" t="n"/>
+    </row>
+    <row r="964">
+      <c r="B964" s="36" t="n">
+        <v>960</v>
+      </c>
+      <c r="C964" s="39" t="n"/>
+      <c r="D964" s="40" t="n"/>
+    </row>
+    <row r="965">
+      <c r="B965" s="36" t="n">
+        <v>961</v>
+      </c>
+      <c r="C965" s="37" t="n"/>
+      <c r="D965" s="38" t="n"/>
+    </row>
+    <row r="966">
+      <c r="B966" s="36" t="n">
+        <v>962</v>
+      </c>
+      <c r="C966" s="39" t="n"/>
+      <c r="D966" s="40" t="n"/>
+    </row>
+    <row r="967">
+      <c r="B967" s="36" t="n">
+        <v>963</v>
+      </c>
+      <c r="C967" s="37" t="n"/>
+      <c r="D967" s="38" t="n"/>
+    </row>
+    <row r="968">
+      <c r="B968" s="36" t="n">
+        <v>964</v>
+      </c>
+      <c r="C968" s="39" t="n"/>
+      <c r="D968" s="40" t="n"/>
+    </row>
+    <row r="969">
+      <c r="B969" s="36" t="n">
+        <v>965</v>
+      </c>
+      <c r="C969" s="37" t="n"/>
+      <c r="D969" s="38" t="n"/>
+    </row>
+    <row r="970">
+      <c r="B970" s="36" t="n">
+        <v>966</v>
+      </c>
+      <c r="C970" s="39" t="n"/>
+      <c r="D970" s="40" t="n"/>
+    </row>
+    <row r="971">
+      <c r="B971" s="36" t="n">
+        <v>967</v>
+      </c>
+      <c r="C971" s="37" t="n"/>
+      <c r="D971" s="38" t="n"/>
+    </row>
+    <row r="972">
+      <c r="B972" s="36" t="n">
+        <v>968</v>
+      </c>
+      <c r="C972" s="39" t="n"/>
+      <c r="D972" s="40" t="n"/>
+    </row>
+    <row r="973">
+      <c r="B973" s="36" t="n">
+        <v>969</v>
+      </c>
+      <c r="C973" s="37" t="n"/>
+      <c r="D973" s="38" t="n"/>
+    </row>
+    <row r="974">
+      <c r="B974" s="36" t="n">
+        <v>970</v>
+      </c>
+      <c r="C974" s="39" t="n"/>
+      <c r="D974" s="40" t="n"/>
+    </row>
+    <row r="975">
+      <c r="B975" s="36" t="n">
+        <v>971</v>
+      </c>
+      <c r="C975" s="37" t="n"/>
+      <c r="D975" s="38" t="n"/>
+    </row>
+    <row r="976">
+      <c r="B976" s="36" t="n">
+        <v>972</v>
+      </c>
+      <c r="C976" s="39" t="n"/>
+      <c r="D976" s="40" t="n"/>
+    </row>
+    <row r="977">
+      <c r="B977" s="36" t="n">
+        <v>973</v>
+      </c>
+      <c r="C977" s="37" t="n"/>
+      <c r="D977" s="38" t="n"/>
+    </row>
+    <row r="978">
+      <c r="B978" s="36" t="n">
+        <v>974</v>
+      </c>
+      <c r="C978" s="39" t="n"/>
+      <c r="D978" s="40" t="n"/>
+    </row>
+    <row r="979">
+      <c r="B979" s="36" t="n">
+        <v>975</v>
+      </c>
+      <c r="C979" s="37" t="n"/>
+      <c r="D979" s="38" t="n"/>
+    </row>
+    <row r="980">
+      <c r="B980" s="36" t="n">
+        <v>976</v>
+      </c>
+      <c r="C980" s="39" t="n"/>
+      <c r="D980" s="40" t="n"/>
+    </row>
+    <row r="981">
+      <c r="B981" s="36" t="n">
+        <v>977</v>
+      </c>
+      <c r="C981" s="37" t="n"/>
+      <c r="D981" s="38" t="n"/>
+    </row>
+    <row r="982">
+      <c r="B982" s="36" t="n">
+        <v>978</v>
+      </c>
+      <c r="C982" s="39" t="n"/>
+      <c r="D982" s="40" t="n"/>
+    </row>
+    <row r="983">
+      <c r="B983" s="36" t="n">
+        <v>979</v>
+      </c>
+      <c r="C983" s="37" t="n"/>
+      <c r="D983" s="38" t="n"/>
+    </row>
+    <row r="984">
+      <c r="B984" s="36" t="n">
+        <v>980</v>
+      </c>
+      <c r="C984" s="39" t="n"/>
+      <c r="D984" s="40" t="n"/>
+    </row>
+    <row r="985">
+      <c r="B985" s="36" t="n">
+        <v>981</v>
+      </c>
+      <c r="C985" s="37" t="n"/>
+      <c r="D985" s="38" t="n"/>
+    </row>
+    <row r="986">
+      <c r="B986" s="36" t="n">
+        <v>982</v>
+      </c>
+      <c r="C986" s="39" t="n"/>
+      <c r="D986" s="40" t="n"/>
+    </row>
+    <row r="987">
+      <c r="B987" s="36" t="n">
+        <v>983</v>
+      </c>
+      <c r="C987" s="37" t="n"/>
+      <c r="D987" s="38" t="n"/>
+    </row>
+    <row r="988">
+      <c r="B988" s="36" t="n">
+        <v>984</v>
+      </c>
+      <c r="C988" s="39" t="n"/>
+      <c r="D988" s="40" t="n"/>
+    </row>
+    <row r="989">
+      <c r="B989" s="36" t="n">
+        <v>985</v>
+      </c>
+      <c r="C989" s="37" t="n"/>
+      <c r="D989" s="38" t="n"/>
+    </row>
+    <row r="990">
+      <c r="B990" s="36" t="n">
+        <v>986</v>
+      </c>
+      <c r="C990" s="39" t="n"/>
+      <c r="D990" s="40" t="n"/>
+    </row>
+    <row r="991">
+      <c r="B991" s="36" t="n">
+        <v>987</v>
+      </c>
+      <c r="C991" s="37" t="n"/>
+      <c r="D991" s="38" t="n"/>
+    </row>
+    <row r="992">
+      <c r="B992" s="36" t="n">
+        <v>988</v>
+      </c>
+      <c r="C992" s="39" t="n"/>
+      <c r="D992" s="40" t="n"/>
+    </row>
+    <row r="993">
+      <c r="B993" s="36" t="n">
+        <v>989</v>
+      </c>
+      <c r="C993" s="37" t="n"/>
+      <c r="D993" s="38" t="n"/>
+    </row>
+    <row r="994">
+      <c r="B994" s="36" t="n">
+        <v>990</v>
+      </c>
+      <c r="C994" s="39" t="n"/>
+      <c r="D994" s="40" t="n"/>
+    </row>
+    <row r="995">
+      <c r="B995" s="36" t="n">
+        <v>991</v>
+      </c>
+      <c r="C995" s="37" t="n"/>
+      <c r="D995" s="38" t="n"/>
+    </row>
+    <row r="996">
+      <c r="B996" s="36" t="n">
+        <v>992</v>
+      </c>
+      <c r="C996" s="39" t="n"/>
+      <c r="D996" s="40" t="n"/>
+    </row>
+    <row r="997">
+      <c r="B997" s="36" t="n">
+        <v>993</v>
+      </c>
+      <c r="C997" s="37" t="n"/>
+      <c r="D997" s="38" t="n"/>
+    </row>
+    <row r="998">
+      <c r="B998" s="36" t="n">
+        <v>994</v>
+      </c>
+      <c r="C998" s="39" t="n"/>
+      <c r="D998" s="40" t="n"/>
+    </row>
+    <row r="999">
+      <c r="B999" s="36" t="n">
+        <v>995</v>
+      </c>
+      <c r="C999" s="37" t="n"/>
+      <c r="D999" s="38" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="B1000" s="36" t="n">
+        <v>996</v>
+      </c>
+      <c r="C1000" s="39" t="n"/>
+      <c r="D1000" s="40" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="B1001" s="36" t="n">
+        <v>997</v>
+      </c>
+      <c r="C1001" s="37" t="n"/>
+      <c r="D1001" s="38" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="B1002" s="36" t="n">
+        <v>998</v>
+      </c>
+      <c r="C1002" s="39" t="n"/>
+      <c r="D1002" s="40" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="B1003" s="36" t="n">
+        <v>999</v>
+      </c>
+      <c r="C1003" s="37" t="n"/>
+      <c r="D1003" s="38" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="B1004" s="36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1004" s="39" t="n"/>
+      <c r="D1004" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/SPC_Statistical_Calculator.xlsx
+++ b/SPC_Statistical_Calculator.xlsx
@@ -22,16 +22,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="170" formatCode=";;;"/>
+    <numFmt numFmtId="171" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,6 +133,16 @@
       <b val="1"/>
       <color rgb="00047857"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F97316"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -254,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -360,6 +371,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -367,7 +385,7 @@
     <xf numFmtId="1" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -761,12 +779,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$H$5:$H$54</f>
+              <f>'Charts'!$H$5:$H$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$I$5:$I$54</f>
+              <f>'Charts'!$I$5:$I$104</f>
             </numRef>
           </val>
         </ser>
@@ -796,12 +814,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$H$5:$H$54</f>
+              <f>'Charts'!$H$5:$H$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$K$5:$K$54</f>
+              <f>'Charts'!$K$5:$K$104</f>
             </numRef>
           </val>
         </ser>
@@ -831,12 +849,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$H$5:$H$54</f>
+              <f>'Charts'!$H$5:$H$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$L$5:$L$54</f>
+              <f>'Charts'!$L$5:$L$104</f>
             </numRef>
           </val>
         </ser>
@@ -866,12 +884,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$H$5:$H$54</f>
+              <f>'Charts'!$H$5:$H$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$M$5:$M$54</f>
+              <f>'Charts'!$M$5:$M$104</f>
             </numRef>
           </val>
         </ser>
@@ -988,12 +1006,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$H$5:$H$54</f>
+              <f>'Charts'!$H$5:$H$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$J$5:$J$54</f>
+              <f>'Charts'!$J$5:$J$104</f>
             </numRef>
           </val>
         </ser>
@@ -9577,7 +9595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M54"/>
+  <dimension ref="B1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9602,6 +9620,20 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="H2" s="43" t="inlineStr">
+        <is>
+          <t>Show Points:</t>
+        </is>
+      </c>
+      <c r="I2" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" s="45">
+        <f>IF(I2="All",1000,I2)</f>
+        <v/>
+      </c>
+    </row>
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -9613,7 +9645,7 @@
       <c r="E3" s="4" t="n"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>I-MR Control Chart Data (from Data Worksheet)</t>
+          <t>I-MR Control Chart Data (filtered by Show Points)</t>
         </is>
       </c>
       <c r="I3" s="4" t="n"/>
@@ -9675,1322 +9707,1322 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="43" t="n">
+      <c r="B5" s="46" t="n">
         <v>-4</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="47">
         <f>Analysis!G9+B5*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B5^2),0)</f>
         <v/>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C5-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="45">
-        <f>IF(Data!D5="""",NA(),Data!D5)</f>
-        <v/>
-      </c>
-      <c r="J5" s="45">
-        <f>NA()</f>
-        <v/>
-      </c>
-      <c r="K5" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L5" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M5" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I5" s="48">
+        <f>IF(OR(1&gt;$J$2,Data!D5=""),NA(),Data!D5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="48">
+        <f>IF(1&gt;$J$2,NA(),NA())</f>
+        <v/>
+      </c>
+      <c r="K5" s="48">
+        <f>IF(OR(1&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L5" s="48">
+        <f>IF(OR(1&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M5" s="48">
+        <f>IF(OR(1&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="46" t="n">
         <v>-3.75</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="47">
         <f>Analysis!G9+B6*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B6^2),0)</f>
         <v/>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C6-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="45">
-        <f>IF(Data!D6="""",NA(),Data!D6)</f>
-        <v/>
-      </c>
-      <c r="J6" s="45">
-        <f>IF(OR(Data!D6="""",Data!D5=""""),NA(),ABS(Data!D6-Data!D5))</f>
-        <v/>
-      </c>
-      <c r="K6" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L6" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M6" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I6" s="48">
+        <f>IF(OR(2&gt;$J$2,Data!D6=""),NA(),Data!D6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="48">
+        <f>IF(OR(2&gt;$J$2,Data!D6="",Data!D5=""),NA(),ABS(Data!D6-Data!D5))</f>
+        <v/>
+      </c>
+      <c r="K6" s="48">
+        <f>IF(OR(2&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="48">
+        <f>IF(OR(2&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M6" s="48">
+        <f>IF(OR(2&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="46" t="n">
         <v>-3.5</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="47">
         <f>Analysis!G9+B7*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B7^2),0)</f>
         <v/>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C7-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="45">
-        <f>IF(Data!D7="""",NA(),Data!D7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="45">
-        <f>IF(OR(Data!D7="""",Data!D6=""""),NA(),ABS(Data!D7-Data!D6))</f>
-        <v/>
-      </c>
-      <c r="K7" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L7" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M7" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I7" s="48">
+        <f>IF(OR(3&gt;$J$2,Data!D7=""),NA(),Data!D7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="48">
+        <f>IF(OR(3&gt;$J$2,Data!D7="",Data!D6=""),NA(),ABS(Data!D7-Data!D6))</f>
+        <v/>
+      </c>
+      <c r="K7" s="48">
+        <f>IF(OR(3&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L7" s="48">
+        <f>IF(OR(3&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M7" s="48">
+        <f>IF(OR(3&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="43" t="n">
+      <c r="B8" s="46" t="n">
         <v>-3.25</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="47">
         <f>Analysis!G9+B8*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B8^2),0)</f>
         <v/>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C8-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H8" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="45">
-        <f>IF(Data!D8="""",NA(),Data!D8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="45">
-        <f>IF(OR(Data!D8="""",Data!D7=""""),NA(),ABS(Data!D8-Data!D7))</f>
-        <v/>
-      </c>
-      <c r="K8" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L8" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M8" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I8" s="48">
+        <f>IF(OR(4&gt;$J$2,Data!D8=""),NA(),Data!D8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="48">
+        <f>IF(OR(4&gt;$J$2,Data!D8="",Data!D7=""),NA(),ABS(Data!D8-Data!D7))</f>
+        <v/>
+      </c>
+      <c r="K8" s="48">
+        <f>IF(OR(4&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L8" s="48">
+        <f>IF(OR(4&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M8" s="48">
+        <f>IF(OR(4&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="43" t="n">
+      <c r="B9" s="46" t="n">
         <v>-3</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="47">
         <f>Analysis!G9+B9*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B9^2),0)</f>
         <v/>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C9-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H9" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="45">
-        <f>IF(Data!D9="""",NA(),Data!D9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="45">
-        <f>IF(OR(Data!D9="""",Data!D8=""""),NA(),ABS(Data!D9-Data!D8))</f>
-        <v/>
-      </c>
-      <c r="K9" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L9" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M9" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I9" s="48">
+        <f>IF(OR(5&gt;$J$2,Data!D9=""),NA(),Data!D9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="48">
+        <f>IF(OR(5&gt;$J$2,Data!D9="",Data!D8=""),NA(),ABS(Data!D9-Data!D8))</f>
+        <v/>
+      </c>
+      <c r="K9" s="48">
+        <f>IF(OR(5&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L9" s="48">
+        <f>IF(OR(5&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M9" s="48">
+        <f>IF(OR(5&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="43" t="n">
+      <c r="B10" s="46" t="n">
         <v>-2.75</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="47">
         <f>Analysis!G9+B10*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B10^2),0)</f>
         <v/>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C10-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H10" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="45">
-        <f>IF(Data!D10="""",NA(),Data!D10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="45">
-        <f>IF(OR(Data!D10="""",Data!D9=""""),NA(),ABS(Data!D10-Data!D9))</f>
-        <v/>
-      </c>
-      <c r="K10" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L10" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M10" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I10" s="48">
+        <f>IF(OR(6&gt;$J$2,Data!D10=""),NA(),Data!D10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="48">
+        <f>IF(OR(6&gt;$J$2,Data!D10="",Data!D9=""),NA(),ABS(Data!D10-Data!D9))</f>
+        <v/>
+      </c>
+      <c r="K10" s="48">
+        <f>IF(OR(6&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L10" s="48">
+        <f>IF(OR(6&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M10" s="48">
+        <f>IF(OR(6&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="46" t="n">
         <v>-2.5</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="47">
         <f>Analysis!G9+B11*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B11^2),0)</f>
         <v/>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C11-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H11" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="45">
-        <f>IF(Data!D11="""",NA(),Data!D11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="45">
-        <f>IF(OR(Data!D11="""",Data!D10=""""),NA(),ABS(Data!D11-Data!D10))</f>
-        <v/>
-      </c>
-      <c r="K11" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L11" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M11" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I11" s="48">
+        <f>IF(OR(7&gt;$J$2,Data!D11=""),NA(),Data!D11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="48">
+        <f>IF(OR(7&gt;$J$2,Data!D11="",Data!D10=""),NA(),ABS(Data!D11-Data!D10))</f>
+        <v/>
+      </c>
+      <c r="K11" s="48">
+        <f>IF(OR(7&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L11" s="48">
+        <f>IF(OR(7&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M11" s="48">
+        <f>IF(OR(7&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="43" t="n">
+      <c r="B12" s="46" t="n">
         <v>-2.25</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="47">
         <f>Analysis!G9+B12*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B12^2),0)</f>
         <v/>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C12-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H12" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="I12" s="45">
-        <f>IF(Data!D12="""",NA(),Data!D12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="45">
-        <f>IF(OR(Data!D12="""",Data!D11=""""),NA(),ABS(Data!D12-Data!D11))</f>
-        <v/>
-      </c>
-      <c r="K12" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L12" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M12" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I12" s="48">
+        <f>IF(OR(8&gt;$J$2,Data!D12=""),NA(),Data!D12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="48">
+        <f>IF(OR(8&gt;$J$2,Data!D12="",Data!D11=""),NA(),ABS(Data!D12-Data!D11))</f>
+        <v/>
+      </c>
+      <c r="K12" s="48">
+        <f>IF(OR(8&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L12" s="48">
+        <f>IF(OR(8&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M12" s="48">
+        <f>IF(OR(8&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="46" t="n">
         <v>-2</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="47">
         <f>Analysis!G9+B13*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B13^2),0)</f>
         <v/>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C13-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H13" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="I13" s="45">
-        <f>IF(Data!D13="""",NA(),Data!D13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="45">
-        <f>IF(OR(Data!D13="""",Data!D12=""""),NA(),ABS(Data!D13-Data!D12))</f>
-        <v/>
-      </c>
-      <c r="K13" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L13" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M13" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I13" s="48">
+        <f>IF(OR(9&gt;$J$2,Data!D13=""),NA(),Data!D13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="48">
+        <f>IF(OR(9&gt;$J$2,Data!D13="",Data!D12=""),NA(),ABS(Data!D13-Data!D12))</f>
+        <v/>
+      </c>
+      <c r="K13" s="48">
+        <f>IF(OR(9&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L13" s="48">
+        <f>IF(OR(9&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M13" s="48">
+        <f>IF(OR(9&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="43" t="n">
+      <c r="B14" s="46" t="n">
         <v>-1.75</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="47">
         <f>Analysis!G9+B14*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B14^2),0)</f>
         <v/>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C14-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H14" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="I14" s="45">
-        <f>IF(Data!D14="""",NA(),Data!D14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="45">
-        <f>IF(OR(Data!D14="""",Data!D13=""""),NA(),ABS(Data!D14-Data!D13))</f>
-        <v/>
-      </c>
-      <c r="K14" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L14" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M14" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I14" s="48">
+        <f>IF(OR(10&gt;$J$2,Data!D14=""),NA(),Data!D14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="48">
+        <f>IF(OR(10&gt;$J$2,Data!D14="",Data!D13=""),NA(),ABS(Data!D14-Data!D13))</f>
+        <v/>
+      </c>
+      <c r="K14" s="48">
+        <f>IF(OR(10&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L14" s="48">
+        <f>IF(OR(10&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M14" s="48">
+        <f>IF(OR(10&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="43" t="n">
+      <c r="B15" s="46" t="n">
         <v>-1.5</v>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="47">
         <f>Analysis!G9+B15*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B15^2),0)</f>
         <v/>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C15-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H15" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="I15" s="45">
-        <f>IF(Data!D15="""",NA(),Data!D15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="45">
-        <f>IF(OR(Data!D15="""",Data!D14=""""),NA(),ABS(Data!D15-Data!D14))</f>
-        <v/>
-      </c>
-      <c r="K15" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L15" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M15" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I15" s="48">
+        <f>IF(OR(11&gt;$J$2,Data!D15=""),NA(),Data!D15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="48">
+        <f>IF(OR(11&gt;$J$2,Data!D15="",Data!D14=""),NA(),ABS(Data!D15-Data!D14))</f>
+        <v/>
+      </c>
+      <c r="K15" s="48">
+        <f>IF(OR(11&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L15" s="48">
+        <f>IF(OR(11&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M15" s="48">
+        <f>IF(OR(11&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="43" t="n">
+      <c r="B16" s="46" t="n">
         <v>-1.25</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="47">
         <f>Analysis!G9+B16*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B16^2),0)</f>
         <v/>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C16-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H16" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="I16" s="45">
-        <f>IF(Data!D16="""",NA(),Data!D16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="45">
-        <f>IF(OR(Data!D16="""",Data!D15=""""),NA(),ABS(Data!D16-Data!D15))</f>
-        <v/>
-      </c>
-      <c r="K16" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L16" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M16" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I16" s="48">
+        <f>IF(OR(12&gt;$J$2,Data!D16=""),NA(),Data!D16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="48">
+        <f>IF(OR(12&gt;$J$2,Data!D16="",Data!D15=""),NA(),ABS(Data!D16-Data!D15))</f>
+        <v/>
+      </c>
+      <c r="K16" s="48">
+        <f>IF(OR(12&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L16" s="48">
+        <f>IF(OR(12&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M16" s="48">
+        <f>IF(OR(12&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="43" t="n">
+      <c r="B17" s="46" t="n">
         <v>-1</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="47">
         <f>Analysis!G9+B17*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B17^2),0)</f>
         <v/>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C17-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H17" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="I17" s="45">
-        <f>IF(Data!D17="""",NA(),Data!D17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="45">
-        <f>IF(OR(Data!D17="""",Data!D16=""""),NA(),ABS(Data!D17-Data!D16))</f>
-        <v/>
-      </c>
-      <c r="K17" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L17" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M17" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I17" s="48">
+        <f>IF(OR(13&gt;$J$2,Data!D17=""),NA(),Data!D17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="48">
+        <f>IF(OR(13&gt;$J$2,Data!D17="",Data!D16=""),NA(),ABS(Data!D17-Data!D16))</f>
+        <v/>
+      </c>
+      <c r="K17" s="48">
+        <f>IF(OR(13&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L17" s="48">
+        <f>IF(OR(13&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M17" s="48">
+        <f>IF(OR(13&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="43" t="n">
+      <c r="B18" s="46" t="n">
         <v>-0.75</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="47">
         <f>Analysis!G9+B18*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B18^2),0)</f>
         <v/>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C18-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H18" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="I18" s="45">
-        <f>IF(Data!D18="""",NA(),Data!D18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="45">
-        <f>IF(OR(Data!D18="""",Data!D17=""""),NA(),ABS(Data!D18-Data!D17))</f>
-        <v/>
-      </c>
-      <c r="K18" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L18" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M18" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I18" s="48">
+        <f>IF(OR(14&gt;$J$2,Data!D18=""),NA(),Data!D18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="48">
+        <f>IF(OR(14&gt;$J$2,Data!D18="",Data!D17=""),NA(),ABS(Data!D18-Data!D17))</f>
+        <v/>
+      </c>
+      <c r="K18" s="48">
+        <f>IF(OR(14&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L18" s="48">
+        <f>IF(OR(14&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M18" s="48">
+        <f>IF(OR(14&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="43" t="n">
+      <c r="B19" s="46" t="n">
         <v>-0.5</v>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="47">
         <f>Analysis!G9+B19*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B19^2),0)</f>
         <v/>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C19-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H19" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="I19" s="45">
-        <f>IF(Data!D19="""",NA(),Data!D19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="45">
-        <f>IF(OR(Data!D19="""",Data!D18=""""),NA(),ABS(Data!D19-Data!D18))</f>
-        <v/>
-      </c>
-      <c r="K19" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L19" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M19" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I19" s="48">
+        <f>IF(OR(15&gt;$J$2,Data!D19=""),NA(),Data!D19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="48">
+        <f>IF(OR(15&gt;$J$2,Data!D19="",Data!D18=""),NA(),ABS(Data!D19-Data!D18))</f>
+        <v/>
+      </c>
+      <c r="K19" s="48">
+        <f>IF(OR(15&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L19" s="48">
+        <f>IF(OR(15&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M19" s="48">
+        <f>IF(OR(15&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="43" t="n">
+      <c r="B20" s="46" t="n">
         <v>-0.25</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="47">
         <f>Analysis!G9+B20*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B20^2),0)</f>
         <v/>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C20-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H20" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="I20" s="45">
-        <f>IF(Data!D20="""",NA(),Data!D20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="45">
-        <f>IF(OR(Data!D20="""",Data!D19=""""),NA(),ABS(Data!D20-Data!D19))</f>
-        <v/>
-      </c>
-      <c r="K20" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L20" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M20" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I20" s="48">
+        <f>IF(OR(16&gt;$J$2,Data!D20=""),NA(),Data!D20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="48">
+        <f>IF(OR(16&gt;$J$2,Data!D20="",Data!D19=""),NA(),ABS(Data!D20-Data!D19))</f>
+        <v/>
+      </c>
+      <c r="K20" s="48">
+        <f>IF(OR(16&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L20" s="48">
+        <f>IF(OR(16&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M20" s="48">
+        <f>IF(OR(16&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="43" t="n">
+      <c r="B21" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="47">
         <f>Analysis!G9+B21*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B21^2),0)</f>
         <v/>
       </c>
-      <c r="E21" s="44">
+      <c r="E21" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C21-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H21" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="I21" s="45">
-        <f>IF(Data!D21="""",NA(),Data!D21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="45">
-        <f>IF(OR(Data!D21="""",Data!D20=""""),NA(),ABS(Data!D21-Data!D20))</f>
-        <v/>
-      </c>
-      <c r="K21" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L21" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M21" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I21" s="48">
+        <f>IF(OR(17&gt;$J$2,Data!D21=""),NA(),Data!D21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="48">
+        <f>IF(OR(17&gt;$J$2,Data!D21="",Data!D20=""),NA(),ABS(Data!D21-Data!D20))</f>
+        <v/>
+      </c>
+      <c r="K21" s="48">
+        <f>IF(OR(17&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L21" s="48">
+        <f>IF(OR(17&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M21" s="48">
+        <f>IF(OR(17&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="43" t="n">
+      <c r="B22" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="47">
         <f>Analysis!G9+B22*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B22^2),0)</f>
         <v/>
       </c>
-      <c r="E22" s="44">
+      <c r="E22" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C22-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H22" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I22" s="45">
-        <f>IF(Data!D22="""",NA(),Data!D22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="45">
-        <f>IF(OR(Data!D22="""",Data!D21=""""),NA(),ABS(Data!D22-Data!D21))</f>
-        <v/>
-      </c>
-      <c r="K22" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L22" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M22" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I22" s="48">
+        <f>IF(OR(18&gt;$J$2,Data!D22=""),NA(),Data!D22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="48">
+        <f>IF(OR(18&gt;$J$2,Data!D22="",Data!D21=""),NA(),ABS(Data!D22-Data!D21))</f>
+        <v/>
+      </c>
+      <c r="K22" s="48">
+        <f>IF(OR(18&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L22" s="48">
+        <f>IF(OR(18&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M22" s="48">
+        <f>IF(OR(18&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="43" t="n">
+      <c r="B23" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="47">
         <f>Analysis!G9+B23*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B23^2),0)</f>
         <v/>
       </c>
-      <c r="E23" s="44">
+      <c r="E23" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C23-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H23" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="I23" s="45">
-        <f>IF(Data!D23="""",NA(),Data!D23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="45">
-        <f>IF(OR(Data!D23="""",Data!D22=""""),NA(),ABS(Data!D23-Data!D22))</f>
-        <v/>
-      </c>
-      <c r="K23" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L23" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M23" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I23" s="48">
+        <f>IF(OR(19&gt;$J$2,Data!D23=""),NA(),Data!D23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="48">
+        <f>IF(OR(19&gt;$J$2,Data!D23="",Data!D22=""),NA(),ABS(Data!D23-Data!D22))</f>
+        <v/>
+      </c>
+      <c r="K23" s="48">
+        <f>IF(OR(19&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L23" s="48">
+        <f>IF(OR(19&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M23" s="48">
+        <f>IF(OR(19&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="43" t="n">
+      <c r="B24" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="47">
         <f>Analysis!G9+B24*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B24^2),0)</f>
         <v/>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C24-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H24" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="I24" s="45">
-        <f>IF(Data!D24="""",NA(),Data!D24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="45">
-        <f>IF(OR(Data!D24="""",Data!D23=""""),NA(),ABS(Data!D24-Data!D23))</f>
-        <v/>
-      </c>
-      <c r="K24" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L24" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M24" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I24" s="48">
+        <f>IF(OR(20&gt;$J$2,Data!D24=""),NA(),Data!D24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="48">
+        <f>IF(OR(20&gt;$J$2,Data!D24="",Data!D23=""),NA(),ABS(Data!D24-Data!D23))</f>
+        <v/>
+      </c>
+      <c r="K24" s="48">
+        <f>IF(OR(20&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L24" s="48">
+        <f>IF(OR(20&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M24" s="48">
+        <f>IF(OR(20&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="43" t="n">
+      <c r="B25" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="44">
+      <c r="C25" s="47">
         <f>Analysis!G9+B25*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D25" s="44">
+      <c r="D25" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B25^2),0)</f>
         <v/>
       </c>
-      <c r="E25" s="44">
+      <c r="E25" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C25-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H25" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="I25" s="45">
-        <f>IF(Data!D25="""",NA(),Data!D25)</f>
-        <v/>
-      </c>
-      <c r="J25" s="45">
-        <f>IF(OR(Data!D25="""",Data!D24=""""),NA(),ABS(Data!D25-Data!D24))</f>
-        <v/>
-      </c>
-      <c r="K25" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L25" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M25" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I25" s="48">
+        <f>IF(OR(21&gt;$J$2,Data!D25=""),NA(),Data!D25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="48">
+        <f>IF(OR(21&gt;$J$2,Data!D25="",Data!D24=""),NA(),ABS(Data!D25-Data!D24))</f>
+        <v/>
+      </c>
+      <c r="K25" s="48">
+        <f>IF(OR(21&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L25" s="48">
+        <f>IF(OR(21&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M25" s="48">
+        <f>IF(OR(21&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="43" t="n">
+      <c r="B26" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="47">
         <f>Analysis!G9+B26*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D26" s="44">
+      <c r="D26" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B26^2),0)</f>
         <v/>
       </c>
-      <c r="E26" s="44">
+      <c r="E26" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C26-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H26" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="I26" s="45">
-        <f>IF(Data!D26="""",NA(),Data!D26)</f>
-        <v/>
-      </c>
-      <c r="J26" s="45">
-        <f>IF(OR(Data!D26="""",Data!D25=""""),NA(),ABS(Data!D26-Data!D25))</f>
-        <v/>
-      </c>
-      <c r="K26" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L26" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M26" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I26" s="48">
+        <f>IF(OR(22&gt;$J$2,Data!D26=""),NA(),Data!D26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="48">
+        <f>IF(OR(22&gt;$J$2,Data!D26="",Data!D25=""),NA(),ABS(Data!D26-Data!D25))</f>
+        <v/>
+      </c>
+      <c r="K26" s="48">
+        <f>IF(OR(22&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L26" s="48">
+        <f>IF(OR(22&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M26" s="48">
+        <f>IF(OR(22&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="43" t="n">
+      <c r="B27" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="47">
         <f>Analysis!G9+B27*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D27" s="44">
+      <c r="D27" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B27^2),0)</f>
         <v/>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C27-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H27" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="I27" s="45">
-        <f>IF(Data!D27="""",NA(),Data!D27)</f>
-        <v/>
-      </c>
-      <c r="J27" s="45">
-        <f>IF(OR(Data!D27="""",Data!D26=""""),NA(),ABS(Data!D27-Data!D26))</f>
-        <v/>
-      </c>
-      <c r="K27" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L27" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M27" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I27" s="48">
+        <f>IF(OR(23&gt;$J$2,Data!D27=""),NA(),Data!D27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="48">
+        <f>IF(OR(23&gt;$J$2,Data!D27="",Data!D26=""),NA(),ABS(Data!D27-Data!D26))</f>
+        <v/>
+      </c>
+      <c r="K27" s="48">
+        <f>IF(OR(23&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L27" s="48">
+        <f>IF(OR(23&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M27" s="48">
+        <f>IF(OR(23&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="43" t="n">
+      <c r="B28" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="47">
         <f>Analysis!G9+B28*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D28" s="44">
+      <c r="D28" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B28^2),0)</f>
         <v/>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C28-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H28" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="I28" s="45">
-        <f>IF(Data!D28="""",NA(),Data!D28)</f>
-        <v/>
-      </c>
-      <c r="J28" s="45">
-        <f>IF(OR(Data!D28="""",Data!D27=""""),NA(),ABS(Data!D28-Data!D27))</f>
-        <v/>
-      </c>
-      <c r="K28" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L28" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M28" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I28" s="48">
+        <f>IF(OR(24&gt;$J$2,Data!D28=""),NA(),Data!D28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="48">
+        <f>IF(OR(24&gt;$J$2,Data!D28="",Data!D27=""),NA(),ABS(Data!D28-Data!D27))</f>
+        <v/>
+      </c>
+      <c r="K28" s="48">
+        <f>IF(OR(24&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L28" s="48">
+        <f>IF(OR(24&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M28" s="48">
+        <f>IF(OR(24&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="43" t="n">
+      <c r="B29" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="47">
         <f>Analysis!G9+B29*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D29" s="44">
+      <c r="D29" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B29^2),0)</f>
         <v/>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C29-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H29" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="45">
-        <f>IF(Data!D29="""",NA(),Data!D29)</f>
-        <v/>
-      </c>
-      <c r="J29" s="45">
-        <f>IF(OR(Data!D29="""",Data!D28=""""),NA(),ABS(Data!D29-Data!D28))</f>
-        <v/>
-      </c>
-      <c r="K29" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L29" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M29" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I29" s="48">
+        <f>IF(OR(25&gt;$J$2,Data!D29=""),NA(),Data!D29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="48">
+        <f>IF(OR(25&gt;$J$2,Data!D29="",Data!D28=""),NA(),ABS(Data!D29-Data!D28))</f>
+        <v/>
+      </c>
+      <c r="K29" s="48">
+        <f>IF(OR(25&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L29" s="48">
+        <f>IF(OR(25&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M29" s="48">
+        <f>IF(OR(25&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="43" t="n">
+      <c r="B30" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="47">
         <f>Analysis!G9+B30*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B30^2),0)</f>
         <v/>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C30-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H30" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="I30" s="45">
-        <f>IF(Data!D30="""",NA(),Data!D30)</f>
-        <v/>
-      </c>
-      <c r="J30" s="45">
-        <f>IF(OR(Data!D30="""",Data!D29=""""),NA(),ABS(Data!D30-Data!D29))</f>
-        <v/>
-      </c>
-      <c r="K30" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L30" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M30" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I30" s="48">
+        <f>IF(OR(26&gt;$J$2,Data!D30=""),NA(),Data!D30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="48">
+        <f>IF(OR(26&gt;$J$2,Data!D30="",Data!D29=""),NA(),ABS(Data!D30-Data!D29))</f>
+        <v/>
+      </c>
+      <c r="K30" s="48">
+        <f>IF(OR(26&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L30" s="48">
+        <f>IF(OR(26&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M30" s="48">
+        <f>IF(OR(26&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="43" t="n">
+      <c r="B31" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="47">
         <f>Analysis!G9+B31*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D31" s="44">
+      <c r="D31" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B31^2),0)</f>
         <v/>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C31-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H31" s="36" t="n">
         <v>27</v>
       </c>
-      <c r="I31" s="45">
-        <f>IF(Data!D31="""",NA(),Data!D31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="45">
-        <f>IF(OR(Data!D31="""",Data!D30=""""),NA(),ABS(Data!D31-Data!D30))</f>
-        <v/>
-      </c>
-      <c r="K31" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L31" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M31" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I31" s="48">
+        <f>IF(OR(27&gt;$J$2,Data!D31=""),NA(),Data!D31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="48">
+        <f>IF(OR(27&gt;$J$2,Data!D31="",Data!D30=""),NA(),ABS(Data!D31-Data!D30))</f>
+        <v/>
+      </c>
+      <c r="K31" s="48">
+        <f>IF(OR(27&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L31" s="48">
+        <f>IF(OR(27&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M31" s="48">
+        <f>IF(OR(27&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="43" t="n">
+      <c r="B32" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="47">
         <f>Analysis!G9+B32*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B32^2),0)</f>
         <v/>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C32-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H32" s="36" t="n">
         <v>28</v>
       </c>
-      <c r="I32" s="45">
-        <f>IF(Data!D32="""",NA(),Data!D32)</f>
-        <v/>
-      </c>
-      <c r="J32" s="45">
-        <f>IF(OR(Data!D32="""",Data!D31=""""),NA(),ABS(Data!D32-Data!D31))</f>
-        <v/>
-      </c>
-      <c r="K32" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L32" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M32" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I32" s="48">
+        <f>IF(OR(28&gt;$J$2,Data!D32=""),NA(),Data!D32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="48">
+        <f>IF(OR(28&gt;$J$2,Data!D32="",Data!D31=""),NA(),ABS(Data!D32-Data!D31))</f>
+        <v/>
+      </c>
+      <c r="K32" s="48">
+        <f>IF(OR(28&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L32" s="48">
+        <f>IF(OR(28&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M32" s="48">
+        <f>IF(OR(28&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="43" t="n">
+      <c r="B33" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="47">
         <f>Analysis!G9+B33*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D33" s="44">
+      <c r="D33" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B33^2),0)</f>
         <v/>
       </c>
-      <c r="E33" s="44">
+      <c r="E33" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C33-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H33" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="I33" s="45">
-        <f>IF(Data!D33="""",NA(),Data!D33)</f>
-        <v/>
-      </c>
-      <c r="J33" s="45">
-        <f>IF(OR(Data!D33="""",Data!D32=""""),NA(),ABS(Data!D33-Data!D32))</f>
-        <v/>
-      </c>
-      <c r="K33" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L33" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M33" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I33" s="48">
+        <f>IF(OR(29&gt;$J$2,Data!D33=""),NA(),Data!D33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="48">
+        <f>IF(OR(29&gt;$J$2,Data!D33="",Data!D32=""),NA(),ABS(Data!D33-Data!D32))</f>
+        <v/>
+      </c>
+      <c r="K33" s="48">
+        <f>IF(OR(29&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L33" s="48">
+        <f>IF(OR(29&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M33" s="48">
+        <f>IF(OR(29&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="43" t="n">
+      <c r="B34" s="46" t="n">
         <v>3.25</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="47">
         <f>Analysis!G9+B34*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D34" s="44">
+      <c r="D34" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B34^2),0)</f>
         <v/>
       </c>
-      <c r="E34" s="44">
+      <c r="E34" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C34-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H34" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="I34" s="45">
-        <f>IF(Data!D34="""",NA(),Data!D34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="45">
-        <f>IF(OR(Data!D34="""",Data!D33=""""),NA(),ABS(Data!D34-Data!D33))</f>
-        <v/>
-      </c>
-      <c r="K34" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L34" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M34" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I34" s="48">
+        <f>IF(OR(30&gt;$J$2,Data!D34=""),NA(),Data!D34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="48">
+        <f>IF(OR(30&gt;$J$2,Data!D34="",Data!D33=""),NA(),ABS(Data!D34-Data!D33))</f>
+        <v/>
+      </c>
+      <c r="K34" s="48">
+        <f>IF(OR(30&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L34" s="48">
+        <f>IF(OR(30&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M34" s="48">
+        <f>IF(OR(30&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="43" t="n">
+      <c r="B35" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="C35" s="44">
+      <c r="C35" s="47">
         <f>Analysis!G9+B35*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D35" s="44">
+      <c r="D35" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B35^2),0)</f>
         <v/>
       </c>
-      <c r="E35" s="44">
+      <c r="E35" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C35-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H35" s="36" t="n">
         <v>31</v>
       </c>
-      <c r="I35" s="45">
-        <f>IF(Data!D35="""",NA(),Data!D35)</f>
-        <v/>
-      </c>
-      <c r="J35" s="45">
-        <f>IF(OR(Data!D35="""",Data!D34=""""),NA(),ABS(Data!D35-Data!D34))</f>
-        <v/>
-      </c>
-      <c r="K35" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L35" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M35" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I35" s="48">
+        <f>IF(OR(31&gt;$J$2,Data!D35=""),NA(),Data!D35)</f>
+        <v/>
+      </c>
+      <c r="J35" s="48">
+        <f>IF(OR(31&gt;$J$2,Data!D35="",Data!D34=""),NA(),ABS(Data!D35-Data!D34))</f>
+        <v/>
+      </c>
+      <c r="K35" s="48">
+        <f>IF(OR(31&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L35" s="48">
+        <f>IF(OR(31&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M35" s="48">
+        <f>IF(OR(31&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="43" t="n">
+      <c r="B36" s="46" t="n">
         <v>3.75</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="47">
         <f>Analysis!G9+B36*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B36^2),0)</f>
         <v/>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C36-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H36" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="I36" s="45">
-        <f>IF(Data!D36="""",NA(),Data!D36)</f>
-        <v/>
-      </c>
-      <c r="J36" s="45">
-        <f>IF(OR(Data!D36="""",Data!D35=""""),NA(),ABS(Data!D36-Data!D35))</f>
-        <v/>
-      </c>
-      <c r="K36" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L36" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M36" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I36" s="48">
+        <f>IF(OR(32&gt;$J$2,Data!D36=""),NA(),Data!D36)</f>
+        <v/>
+      </c>
+      <c r="J36" s="48">
+        <f>IF(OR(32&gt;$J$2,Data!D36="",Data!D35=""),NA(),ABS(Data!D36-Data!D35))</f>
+        <v/>
+      </c>
+      <c r="K36" s="48">
+        <f>IF(OR(32&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L36" s="48">
+        <f>IF(OR(32&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M36" s="48">
+        <f>IF(OR(32&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="43" t="n">
+      <c r="B37" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="47">
         <f>Analysis!G9+B37*Analysis!G10</f>
         <v/>
       </c>
-      <c r="D37" s="44">
+      <c r="D37" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*B37^2),0)</f>
         <v/>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="47">
         <f>IF(Analysis!G10&gt;0,(1/(Analysis!G10*SQRT(2*PI())))*EXP(-0.5*((C37-Analysis!C6)/Analysis!G10)^2),0)</f>
         <v/>
       </c>
       <c r="H37" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="I37" s="45">
-        <f>IF(Data!D37="""",NA(),Data!D37)</f>
-        <v/>
-      </c>
-      <c r="J37" s="45">
-        <f>IF(OR(Data!D37="""",Data!D36=""""),NA(),ABS(Data!D37-Data!D36))</f>
-        <v/>
-      </c>
-      <c r="K37" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L37" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M37" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I37" s="48">
+        <f>IF(OR(33&gt;$J$2,Data!D37=""),NA(),Data!D37)</f>
+        <v/>
+      </c>
+      <c r="J37" s="48">
+        <f>IF(OR(33&gt;$J$2,Data!D37="",Data!D36=""),NA(),ABS(Data!D37-Data!D36))</f>
+        <v/>
+      </c>
+      <c r="K37" s="48">
+        <f>IF(OR(33&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L37" s="48">
+        <f>IF(OR(33&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M37" s="48">
+        <f>IF(OR(33&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -10998,24 +11030,24 @@
       <c r="H38" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="I38" s="45">
-        <f>IF(Data!D38="""",NA(),Data!D38)</f>
-        <v/>
-      </c>
-      <c r="J38" s="45">
-        <f>IF(OR(Data!D38="""",Data!D37=""""),NA(),ABS(Data!D38-Data!D37))</f>
-        <v/>
-      </c>
-      <c r="K38" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L38" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M38" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I38" s="48">
+        <f>IF(OR(34&gt;$J$2,Data!D38=""),NA(),Data!D38)</f>
+        <v/>
+      </c>
+      <c r="J38" s="48">
+        <f>IF(OR(34&gt;$J$2,Data!D38="",Data!D37=""),NA(),ABS(Data!D38-Data!D37))</f>
+        <v/>
+      </c>
+      <c r="K38" s="48">
+        <f>IF(OR(34&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L38" s="48">
+        <f>IF(OR(34&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M38" s="48">
+        <f>IF(OR(34&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11023,24 +11055,24 @@
       <c r="H39" s="36" t="n">
         <v>35</v>
       </c>
-      <c r="I39" s="45">
-        <f>IF(Data!D39="""",NA(),Data!D39)</f>
-        <v/>
-      </c>
-      <c r="J39" s="45">
-        <f>IF(OR(Data!D39="""",Data!D38=""""),NA(),ABS(Data!D39-Data!D38))</f>
-        <v/>
-      </c>
-      <c r="K39" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L39" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M39" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I39" s="48">
+        <f>IF(OR(35&gt;$J$2,Data!D39=""),NA(),Data!D39)</f>
+        <v/>
+      </c>
+      <c r="J39" s="48">
+        <f>IF(OR(35&gt;$J$2,Data!D39="",Data!D38=""),NA(),ABS(Data!D39-Data!D38))</f>
+        <v/>
+      </c>
+      <c r="K39" s="48">
+        <f>IF(OR(35&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L39" s="48">
+        <f>IF(OR(35&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M39" s="48">
+        <f>IF(OR(35&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11056,24 +11088,24 @@
       <c r="H40" s="36" t="n">
         <v>36</v>
       </c>
-      <c r="I40" s="45">
-        <f>IF(Data!D40="""",NA(),Data!D40)</f>
-        <v/>
-      </c>
-      <c r="J40" s="45">
-        <f>IF(OR(Data!D40="""",Data!D39=""""),NA(),ABS(Data!D40-Data!D39))</f>
-        <v/>
-      </c>
-      <c r="K40" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L40" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M40" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I40" s="48">
+        <f>IF(OR(36&gt;$J$2,Data!D40=""),NA(),Data!D40)</f>
+        <v/>
+      </c>
+      <c r="J40" s="48">
+        <f>IF(OR(36&gt;$J$2,Data!D40="",Data!D39=""),NA(),ABS(Data!D40-Data!D39))</f>
+        <v/>
+      </c>
+      <c r="K40" s="48">
+        <f>IF(OR(36&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L40" s="48">
+        <f>IF(OR(36&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M40" s="48">
+        <f>IF(OR(36&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11101,106 +11133,106 @@
       <c r="H41" s="36" t="n">
         <v>37</v>
       </c>
-      <c r="I41" s="45">
-        <f>IF(Data!D41="""",NA(),Data!D41)</f>
-        <v/>
-      </c>
-      <c r="J41" s="45">
-        <f>IF(OR(Data!D41="""",Data!D40=""""),NA(),ABS(Data!D41-Data!D40))</f>
-        <v/>
-      </c>
-      <c r="K41" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L41" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M41" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I41" s="48">
+        <f>IF(OR(37&gt;$J$2,Data!D41=""),NA(),Data!D41)</f>
+        <v/>
+      </c>
+      <c r="J41" s="48">
+        <f>IF(OR(37&gt;$J$2,Data!D41="",Data!D40=""),NA(),ABS(Data!D41-Data!D40))</f>
+        <v/>
+      </c>
+      <c r="K41" s="48">
+        <f>IF(OR(37&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L41" s="48">
+        <f>IF(OR(37&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M41" s="48">
+        <f>IF(OR(37&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="46" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>Cp</t>
         </is>
       </c>
-      <c r="C42" s="43">
+      <c r="C42" s="46">
         <f>Analysis!G17</f>
         <v/>
       </c>
-      <c r="D42" s="43">
+      <c r="D42" s="46">
         <f>Analysis!C16</f>
         <v/>
       </c>
-      <c r="E42" s="43" t="n">
+      <c r="E42" s="46" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="I42" s="45">
-        <f>IF(Data!D42="""",NA(),Data!D42)</f>
-        <v/>
-      </c>
-      <c r="J42" s="45">
-        <f>IF(OR(Data!D42="""",Data!D41=""""),NA(),ABS(Data!D42-Data!D41))</f>
-        <v/>
-      </c>
-      <c r="K42" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L42" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M42" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I42" s="48">
+        <f>IF(OR(38&gt;$J$2,Data!D42=""),NA(),Data!D42)</f>
+        <v/>
+      </c>
+      <c r="J42" s="48">
+        <f>IF(OR(38&gt;$J$2,Data!D42="",Data!D41=""),NA(),ABS(Data!D42-Data!D41))</f>
+        <v/>
+      </c>
+      <c r="K42" s="48">
+        <f>IF(OR(38&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L42" s="48">
+        <f>IF(OR(38&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M42" s="48">
+        <f>IF(OR(38&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="46" t="inlineStr">
+      <c r="B43" s="49" t="inlineStr">
         <is>
           <t>Cpk</t>
         </is>
       </c>
-      <c r="C43" s="43">
+      <c r="C43" s="46">
         <f>Analysis!G18</f>
         <v/>
       </c>
-      <c r="D43" s="43">
+      <c r="D43" s="46">
         <f>Analysis!C16</f>
         <v/>
       </c>
-      <c r="E43" s="43" t="n">
+      <c r="E43" s="46" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="36" t="n">
         <v>39</v>
       </c>
-      <c r="I43" s="45">
-        <f>IF(Data!D43="""",NA(),Data!D43)</f>
-        <v/>
-      </c>
-      <c r="J43" s="45">
-        <f>IF(OR(Data!D43="""",Data!D42=""""),NA(),ABS(Data!D43-Data!D42))</f>
-        <v/>
-      </c>
-      <c r="K43" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L43" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M43" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I43" s="48">
+        <f>IF(OR(39&gt;$J$2,Data!D43=""),NA(),Data!D43)</f>
+        <v/>
+      </c>
+      <c r="J43" s="48">
+        <f>IF(OR(39&gt;$J$2,Data!D43="",Data!D42=""),NA(),ABS(Data!D43-Data!D42))</f>
+        <v/>
+      </c>
+      <c r="K43" s="48">
+        <f>IF(OR(39&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L43" s="48">
+        <f>IF(OR(39&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M43" s="48">
+        <f>IF(OR(39&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11208,24 +11240,24 @@
       <c r="H44" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="I44" s="45">
-        <f>IF(Data!D44="""",NA(),Data!D44)</f>
-        <v/>
-      </c>
-      <c r="J44" s="45">
-        <f>IF(OR(Data!D44="""",Data!D43=""""),NA(),ABS(Data!D44-Data!D43))</f>
-        <v/>
-      </c>
-      <c r="K44" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L44" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M44" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I44" s="48">
+        <f>IF(OR(40&gt;$J$2,Data!D44=""),NA(),Data!D44)</f>
+        <v/>
+      </c>
+      <c r="J44" s="48">
+        <f>IF(OR(40&gt;$J$2,Data!D44="",Data!D43=""),NA(),ABS(Data!D44-Data!D43))</f>
+        <v/>
+      </c>
+      <c r="K44" s="48">
+        <f>IF(OR(40&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L44" s="48">
+        <f>IF(OR(40&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M44" s="48">
+        <f>IF(OR(40&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11233,24 +11265,24 @@
       <c r="H45" s="36" t="n">
         <v>41</v>
       </c>
-      <c r="I45" s="45">
-        <f>IF(Data!D45="""",NA(),Data!D45)</f>
-        <v/>
-      </c>
-      <c r="J45" s="45">
-        <f>IF(OR(Data!D45="""",Data!D44=""""),NA(),ABS(Data!D45-Data!D44))</f>
-        <v/>
-      </c>
-      <c r="K45" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L45" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M45" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I45" s="48">
+        <f>IF(OR(41&gt;$J$2,Data!D45=""),NA(),Data!D45)</f>
+        <v/>
+      </c>
+      <c r="J45" s="48">
+        <f>IF(OR(41&gt;$J$2,Data!D45="",Data!D44=""),NA(),ABS(Data!D45-Data!D44))</f>
+        <v/>
+      </c>
+      <c r="K45" s="48">
+        <f>IF(OR(41&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L45" s="48">
+        <f>IF(OR(41&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M45" s="48">
+        <f>IF(OR(41&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11266,24 +11298,24 @@
       <c r="H46" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="I46" s="45">
-        <f>IF(Data!D46="""",NA(),Data!D46)</f>
-        <v/>
-      </c>
-      <c r="J46" s="45">
-        <f>IF(OR(Data!D46="""",Data!D45=""""),NA(),ABS(Data!D46-Data!D45))</f>
-        <v/>
-      </c>
-      <c r="K46" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L46" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M46" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I46" s="48">
+        <f>IF(OR(42&gt;$J$2,Data!D46=""),NA(),Data!D46)</f>
+        <v/>
+      </c>
+      <c r="J46" s="48">
+        <f>IF(OR(42&gt;$J$2,Data!D46="",Data!D45=""),NA(),ABS(Data!D46-Data!D45))</f>
+        <v/>
+      </c>
+      <c r="K46" s="48">
+        <f>IF(OR(42&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L46" s="48">
+        <f>IF(OR(42&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M46" s="48">
+        <f>IF(OR(42&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11309,24 +11341,24 @@
       <c r="H47" s="36" t="n">
         <v>43</v>
       </c>
-      <c r="I47" s="45">
-        <f>IF(Data!D47="""",NA(),Data!D47)</f>
-        <v/>
-      </c>
-      <c r="J47" s="45">
-        <f>IF(OR(Data!D47="""",Data!D46=""""),NA(),ABS(Data!D47-Data!D46))</f>
-        <v/>
-      </c>
-      <c r="K47" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L47" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M47" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I47" s="48">
+        <f>IF(OR(43&gt;$J$2,Data!D47=""),NA(),Data!D47)</f>
+        <v/>
+      </c>
+      <c r="J47" s="48">
+        <f>IF(OR(43&gt;$J$2,Data!D47="",Data!D46=""),NA(),ABS(Data!D47-Data!D46))</f>
+        <v/>
+      </c>
+      <c r="K47" s="48">
+        <f>IF(OR(43&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L47" s="48">
+        <f>IF(OR(43&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M47" s="48">
+        <f>IF(OR(43&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11352,24 +11384,24 @@
       <c r="H48" s="36" t="n">
         <v>44</v>
       </c>
-      <c r="I48" s="45">
-        <f>IF(Data!D48="""",NA(),Data!D48)</f>
-        <v/>
-      </c>
-      <c r="J48" s="45">
-        <f>IF(OR(Data!D48="""",Data!D47=""""),NA(),ABS(Data!D48-Data!D47))</f>
-        <v/>
-      </c>
-      <c r="K48" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L48" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M48" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I48" s="48">
+        <f>IF(OR(44&gt;$J$2,Data!D48=""),NA(),Data!D48)</f>
+        <v/>
+      </c>
+      <c r="J48" s="48">
+        <f>IF(OR(44&gt;$J$2,Data!D48="",Data!D47=""),NA(),ABS(Data!D48-Data!D47))</f>
+        <v/>
+      </c>
+      <c r="K48" s="48">
+        <f>IF(OR(44&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L48" s="48">
+        <f>IF(OR(44&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M48" s="48">
+        <f>IF(OR(44&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11388,31 +11420,31 @@
           <t>n (ACTIVE)</t>
         </is>
       </c>
-      <c r="E49" s="47">
+      <c r="E49" s="50">
         <f>Analysis!G11</f>
         <v/>
       </c>
       <c r="H49" s="36" t="n">
         <v>45</v>
       </c>
-      <c r="I49" s="45">
-        <f>IF(Data!D49="""",NA(),Data!D49)</f>
-        <v/>
-      </c>
-      <c r="J49" s="45">
-        <f>IF(OR(Data!D49="""",Data!D48=""""),NA(),ABS(Data!D49-Data!D48))</f>
-        <v/>
-      </c>
-      <c r="K49" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L49" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M49" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I49" s="48">
+        <f>IF(OR(45&gt;$J$2,Data!D49=""),NA(),Data!D49)</f>
+        <v/>
+      </c>
+      <c r="J49" s="48">
+        <f>IF(OR(45&gt;$J$2,Data!D49="",Data!D48=""),NA(),ABS(Data!D49-Data!D48))</f>
+        <v/>
+      </c>
+      <c r="K49" s="48">
+        <f>IF(OR(45&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L49" s="48">
+        <f>IF(OR(45&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M49" s="48">
+        <f>IF(OR(45&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11438,24 +11470,24 @@
       <c r="H50" s="36" t="n">
         <v>46</v>
       </c>
-      <c r="I50" s="45">
-        <f>IF(Data!D50="""",NA(),Data!D50)</f>
-        <v/>
-      </c>
-      <c r="J50" s="45">
-        <f>IF(OR(Data!D50="""",Data!D49=""""),NA(),ABS(Data!D50-Data!D49))</f>
-        <v/>
-      </c>
-      <c r="K50" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L50" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M50" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I50" s="48">
+        <f>IF(OR(46&gt;$J$2,Data!D50=""),NA(),Data!D50)</f>
+        <v/>
+      </c>
+      <c r="J50" s="48">
+        <f>IF(OR(46&gt;$J$2,Data!D50="",Data!D49=""),NA(),ABS(Data!D50-Data!D49))</f>
+        <v/>
+      </c>
+      <c r="K50" s="48">
+        <f>IF(OR(46&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L50" s="48">
+        <f>IF(OR(46&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M50" s="48">
+        <f>IF(OR(46&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11463,24 +11495,24 @@
       <c r="H51" s="36" t="n">
         <v>47</v>
       </c>
-      <c r="I51" s="45">
-        <f>IF(Data!D51="""",NA(),Data!D51)</f>
-        <v/>
-      </c>
-      <c r="J51" s="45">
-        <f>IF(OR(Data!D51="""",Data!D50=""""),NA(),ABS(Data!D51-Data!D50))</f>
-        <v/>
-      </c>
-      <c r="K51" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L51" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M51" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I51" s="48">
+        <f>IF(OR(47&gt;$J$2,Data!D51=""),NA(),Data!D51)</f>
+        <v/>
+      </c>
+      <c r="J51" s="48">
+        <f>IF(OR(47&gt;$J$2,Data!D51="",Data!D50=""),NA(),ABS(Data!D51-Data!D50))</f>
+        <v/>
+      </c>
+      <c r="K51" s="48">
+        <f>IF(OR(47&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L51" s="48">
+        <f>IF(OR(47&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M51" s="48">
+        <f>IF(OR(47&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11488,24 +11520,24 @@
       <c r="H52" s="36" t="n">
         <v>48</v>
       </c>
-      <c r="I52" s="45">
-        <f>IF(Data!D52="""",NA(),Data!D52)</f>
-        <v/>
-      </c>
-      <c r="J52" s="45">
-        <f>IF(OR(Data!D52="""",Data!D51=""""),NA(),ABS(Data!D52-Data!D51))</f>
-        <v/>
-      </c>
-      <c r="K52" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L52" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M52" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I52" s="48">
+        <f>IF(OR(48&gt;$J$2,Data!D52=""),NA(),Data!D52)</f>
+        <v/>
+      </c>
+      <c r="J52" s="48">
+        <f>IF(OR(48&gt;$J$2,Data!D52="",Data!D51=""),NA(),ABS(Data!D52-Data!D51))</f>
+        <v/>
+      </c>
+      <c r="K52" s="48">
+        <f>IF(OR(48&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L52" s="48">
+        <f>IF(OR(48&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M52" s="48">
+        <f>IF(OR(48&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11513,24 +11545,24 @@
       <c r="H53" s="36" t="n">
         <v>49</v>
       </c>
-      <c r="I53" s="45">
-        <f>IF(Data!D53="""",NA(),Data!D53)</f>
-        <v/>
-      </c>
-      <c r="J53" s="45">
-        <f>IF(OR(Data!D53="""",Data!D52=""""),NA(),ABS(Data!D53-Data!D52))</f>
-        <v/>
-      </c>
-      <c r="K53" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L53" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M53" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I53" s="48">
+        <f>IF(OR(49&gt;$J$2,Data!D53=""),NA(),Data!D53)</f>
+        <v/>
+      </c>
+      <c r="J53" s="48">
+        <f>IF(OR(49&gt;$J$2,Data!D53="",Data!D52=""),NA(),ABS(Data!D53-Data!D52))</f>
+        <v/>
+      </c>
+      <c r="K53" s="48">
+        <f>IF(OR(49&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L53" s="48">
+        <f>IF(OR(49&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M53" s="48">
+        <f>IF(OR(49&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11538,24 +11570,1274 @@
       <c r="H54" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="I54" s="45">
-        <f>IF(Data!D54="""",NA(),Data!D54)</f>
-        <v/>
-      </c>
-      <c r="J54" s="45">
-        <f>IF(OR(Data!D54="""",Data!D53=""""),NA(),ABS(Data!D54-Data!D53))</f>
-        <v/>
-      </c>
-      <c r="K54" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6,NA())</f>
-        <v/>
-      </c>
-      <c r="L54" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6+2.66*AVERAGE(J6:J54),NA())</f>
-        <v/>
-      </c>
-      <c r="M54" s="45">
-        <f>IF(Data!G5&gt;=2,Data!G6-2.66*AVERAGE(J6:J54),NA())</f>
+      <c r="I54" s="48">
+        <f>IF(OR(50&gt;$J$2,Data!D54=""),NA(),Data!D54)</f>
+        <v/>
+      </c>
+      <c r="J54" s="48">
+        <f>IF(OR(50&gt;$J$2,Data!D54="",Data!D53=""),NA(),ABS(Data!D54-Data!D53))</f>
+        <v/>
+      </c>
+      <c r="K54" s="48">
+        <f>IF(OR(50&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L54" s="48">
+        <f>IF(OR(50&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M54" s="48">
+        <f>IF(OR(50&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55" s="36" t="n">
+        <v>51</v>
+      </c>
+      <c r="I55" s="48">
+        <f>IF(OR(51&gt;$J$2,Data!D55=""),NA(),Data!D55)</f>
+        <v/>
+      </c>
+      <c r="J55" s="48">
+        <f>IF(OR(51&gt;$J$2,Data!D55="",Data!D54=""),NA(),ABS(Data!D55-Data!D54))</f>
+        <v/>
+      </c>
+      <c r="K55" s="48">
+        <f>IF(OR(51&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L55" s="48">
+        <f>IF(OR(51&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M55" s="48">
+        <f>IF(OR(51&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56" s="36" t="n">
+        <v>52</v>
+      </c>
+      <c r="I56" s="48">
+        <f>IF(OR(52&gt;$J$2,Data!D56=""),NA(),Data!D56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="48">
+        <f>IF(OR(52&gt;$J$2,Data!D56="",Data!D55=""),NA(),ABS(Data!D56-Data!D55))</f>
+        <v/>
+      </c>
+      <c r="K56" s="48">
+        <f>IF(OR(52&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L56" s="48">
+        <f>IF(OR(52&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M56" s="48">
+        <f>IF(OR(52&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="H57" s="36" t="n">
+        <v>53</v>
+      </c>
+      <c r="I57" s="48">
+        <f>IF(OR(53&gt;$J$2,Data!D57=""),NA(),Data!D57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="48">
+        <f>IF(OR(53&gt;$J$2,Data!D57="",Data!D56=""),NA(),ABS(Data!D57-Data!D56))</f>
+        <v/>
+      </c>
+      <c r="K57" s="48">
+        <f>IF(OR(53&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L57" s="48">
+        <f>IF(OR(53&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M57" s="48">
+        <f>IF(OR(53&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="H58" s="36" t="n">
+        <v>54</v>
+      </c>
+      <c r="I58" s="48">
+        <f>IF(OR(54&gt;$J$2,Data!D58=""),NA(),Data!D58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="48">
+        <f>IF(OR(54&gt;$J$2,Data!D58="",Data!D57=""),NA(),ABS(Data!D58-Data!D57))</f>
+        <v/>
+      </c>
+      <c r="K58" s="48">
+        <f>IF(OR(54&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L58" s="48">
+        <f>IF(OR(54&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M58" s="48">
+        <f>IF(OR(54&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="H59" s="36" t="n">
+        <v>55</v>
+      </c>
+      <c r="I59" s="48">
+        <f>IF(OR(55&gt;$J$2,Data!D59=""),NA(),Data!D59)</f>
+        <v/>
+      </c>
+      <c r="J59" s="48">
+        <f>IF(OR(55&gt;$J$2,Data!D59="",Data!D58=""),NA(),ABS(Data!D59-Data!D58))</f>
+        <v/>
+      </c>
+      <c r="K59" s="48">
+        <f>IF(OR(55&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L59" s="48">
+        <f>IF(OR(55&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M59" s="48">
+        <f>IF(OR(55&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="H60" s="36" t="n">
+        <v>56</v>
+      </c>
+      <c r="I60" s="48">
+        <f>IF(OR(56&gt;$J$2,Data!D60=""),NA(),Data!D60)</f>
+        <v/>
+      </c>
+      <c r="J60" s="48">
+        <f>IF(OR(56&gt;$J$2,Data!D60="",Data!D59=""),NA(),ABS(Data!D60-Data!D59))</f>
+        <v/>
+      </c>
+      <c r="K60" s="48">
+        <f>IF(OR(56&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L60" s="48">
+        <f>IF(OR(56&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M60" s="48">
+        <f>IF(OR(56&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61" s="36" t="n">
+        <v>57</v>
+      </c>
+      <c r="I61" s="48">
+        <f>IF(OR(57&gt;$J$2,Data!D61=""),NA(),Data!D61)</f>
+        <v/>
+      </c>
+      <c r="J61" s="48">
+        <f>IF(OR(57&gt;$J$2,Data!D61="",Data!D60=""),NA(),ABS(Data!D61-Data!D60))</f>
+        <v/>
+      </c>
+      <c r="K61" s="48">
+        <f>IF(OR(57&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L61" s="48">
+        <f>IF(OR(57&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M61" s="48">
+        <f>IF(OR(57&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="H62" s="36" t="n">
+        <v>58</v>
+      </c>
+      <c r="I62" s="48">
+        <f>IF(OR(58&gt;$J$2,Data!D62=""),NA(),Data!D62)</f>
+        <v/>
+      </c>
+      <c r="J62" s="48">
+        <f>IF(OR(58&gt;$J$2,Data!D62="",Data!D61=""),NA(),ABS(Data!D62-Data!D61))</f>
+        <v/>
+      </c>
+      <c r="K62" s="48">
+        <f>IF(OR(58&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L62" s="48">
+        <f>IF(OR(58&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M62" s="48">
+        <f>IF(OR(58&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="H63" s="36" t="n">
+        <v>59</v>
+      </c>
+      <c r="I63" s="48">
+        <f>IF(OR(59&gt;$J$2,Data!D63=""),NA(),Data!D63)</f>
+        <v/>
+      </c>
+      <c r="J63" s="48">
+        <f>IF(OR(59&gt;$J$2,Data!D63="",Data!D62=""),NA(),ABS(Data!D63-Data!D62))</f>
+        <v/>
+      </c>
+      <c r="K63" s="48">
+        <f>IF(OR(59&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L63" s="48">
+        <f>IF(OR(59&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M63" s="48">
+        <f>IF(OR(59&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="H64" s="36" t="n">
+        <v>60</v>
+      </c>
+      <c r="I64" s="48">
+        <f>IF(OR(60&gt;$J$2,Data!D64=""),NA(),Data!D64)</f>
+        <v/>
+      </c>
+      <c r="J64" s="48">
+        <f>IF(OR(60&gt;$J$2,Data!D64="",Data!D63=""),NA(),ABS(Data!D64-Data!D63))</f>
+        <v/>
+      </c>
+      <c r="K64" s="48">
+        <f>IF(OR(60&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L64" s="48">
+        <f>IF(OR(60&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M64" s="48">
+        <f>IF(OR(60&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="H65" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="I65" s="48">
+        <f>IF(OR(61&gt;$J$2,Data!D65=""),NA(),Data!D65)</f>
+        <v/>
+      </c>
+      <c r="J65" s="48">
+        <f>IF(OR(61&gt;$J$2,Data!D65="",Data!D64=""),NA(),ABS(Data!D65-Data!D64))</f>
+        <v/>
+      </c>
+      <c r="K65" s="48">
+        <f>IF(OR(61&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L65" s="48">
+        <f>IF(OR(61&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M65" s="48">
+        <f>IF(OR(61&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66" s="36" t="n">
+        <v>62</v>
+      </c>
+      <c r="I66" s="48">
+        <f>IF(OR(62&gt;$J$2,Data!D66=""),NA(),Data!D66)</f>
+        <v/>
+      </c>
+      <c r="J66" s="48">
+        <f>IF(OR(62&gt;$J$2,Data!D66="",Data!D65=""),NA(),ABS(Data!D66-Data!D65))</f>
+        <v/>
+      </c>
+      <c r="K66" s="48">
+        <f>IF(OR(62&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L66" s="48">
+        <f>IF(OR(62&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M66" s="48">
+        <f>IF(OR(62&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="H67" s="36" t="n">
+        <v>63</v>
+      </c>
+      <c r="I67" s="48">
+        <f>IF(OR(63&gt;$J$2,Data!D67=""),NA(),Data!D67)</f>
+        <v/>
+      </c>
+      <c r="J67" s="48">
+        <f>IF(OR(63&gt;$J$2,Data!D67="",Data!D66=""),NA(),ABS(Data!D67-Data!D66))</f>
+        <v/>
+      </c>
+      <c r="K67" s="48">
+        <f>IF(OR(63&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L67" s="48">
+        <f>IF(OR(63&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M67" s="48">
+        <f>IF(OR(63&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="H68" s="36" t="n">
+        <v>64</v>
+      </c>
+      <c r="I68" s="48">
+        <f>IF(OR(64&gt;$J$2,Data!D68=""),NA(),Data!D68)</f>
+        <v/>
+      </c>
+      <c r="J68" s="48">
+        <f>IF(OR(64&gt;$J$2,Data!D68="",Data!D67=""),NA(),ABS(Data!D68-Data!D67))</f>
+        <v/>
+      </c>
+      <c r="K68" s="48">
+        <f>IF(OR(64&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L68" s="48">
+        <f>IF(OR(64&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M68" s="48">
+        <f>IF(OR(64&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69" s="36" t="n">
+        <v>65</v>
+      </c>
+      <c r="I69" s="48">
+        <f>IF(OR(65&gt;$J$2,Data!D69=""),NA(),Data!D69)</f>
+        <v/>
+      </c>
+      <c r="J69" s="48">
+        <f>IF(OR(65&gt;$J$2,Data!D69="",Data!D68=""),NA(),ABS(Data!D69-Data!D68))</f>
+        <v/>
+      </c>
+      <c r="K69" s="48">
+        <f>IF(OR(65&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L69" s="48">
+        <f>IF(OR(65&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M69" s="48">
+        <f>IF(OR(65&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="H70" s="36" t="n">
+        <v>66</v>
+      </c>
+      <c r="I70" s="48">
+        <f>IF(OR(66&gt;$J$2,Data!D70=""),NA(),Data!D70)</f>
+        <v/>
+      </c>
+      <c r="J70" s="48">
+        <f>IF(OR(66&gt;$J$2,Data!D70="",Data!D69=""),NA(),ABS(Data!D70-Data!D69))</f>
+        <v/>
+      </c>
+      <c r="K70" s="48">
+        <f>IF(OR(66&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L70" s="48">
+        <f>IF(OR(66&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M70" s="48">
+        <f>IF(OR(66&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="H71" s="36" t="n">
+        <v>67</v>
+      </c>
+      <c r="I71" s="48">
+        <f>IF(OR(67&gt;$J$2,Data!D71=""),NA(),Data!D71)</f>
+        <v/>
+      </c>
+      <c r="J71" s="48">
+        <f>IF(OR(67&gt;$J$2,Data!D71="",Data!D70=""),NA(),ABS(Data!D71-Data!D70))</f>
+        <v/>
+      </c>
+      <c r="K71" s="48">
+        <f>IF(OR(67&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L71" s="48">
+        <f>IF(OR(67&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M71" s="48">
+        <f>IF(OR(67&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="H72" s="36" t="n">
+        <v>68</v>
+      </c>
+      <c r="I72" s="48">
+        <f>IF(OR(68&gt;$J$2,Data!D72=""),NA(),Data!D72)</f>
+        <v/>
+      </c>
+      <c r="J72" s="48">
+        <f>IF(OR(68&gt;$J$2,Data!D72="",Data!D71=""),NA(),ABS(Data!D72-Data!D71))</f>
+        <v/>
+      </c>
+      <c r="K72" s="48">
+        <f>IF(OR(68&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L72" s="48">
+        <f>IF(OR(68&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M72" s="48">
+        <f>IF(OR(68&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73" s="36" t="n">
+        <v>69</v>
+      </c>
+      <c r="I73" s="48">
+        <f>IF(OR(69&gt;$J$2,Data!D73=""),NA(),Data!D73)</f>
+        <v/>
+      </c>
+      <c r="J73" s="48">
+        <f>IF(OR(69&gt;$J$2,Data!D73="",Data!D72=""),NA(),ABS(Data!D73-Data!D72))</f>
+        <v/>
+      </c>
+      <c r="K73" s="48">
+        <f>IF(OR(69&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L73" s="48">
+        <f>IF(OR(69&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M73" s="48">
+        <f>IF(OR(69&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="H74" s="36" t="n">
+        <v>70</v>
+      </c>
+      <c r="I74" s="48">
+        <f>IF(OR(70&gt;$J$2,Data!D74=""),NA(),Data!D74)</f>
+        <v/>
+      </c>
+      <c r="J74" s="48">
+        <f>IF(OR(70&gt;$J$2,Data!D74="",Data!D73=""),NA(),ABS(Data!D74-Data!D73))</f>
+        <v/>
+      </c>
+      <c r="K74" s="48">
+        <f>IF(OR(70&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L74" s="48">
+        <f>IF(OR(70&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M74" s="48">
+        <f>IF(OR(70&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="H75" s="36" t="n">
+        <v>71</v>
+      </c>
+      <c r="I75" s="48">
+        <f>IF(OR(71&gt;$J$2,Data!D75=""),NA(),Data!D75)</f>
+        <v/>
+      </c>
+      <c r="J75" s="48">
+        <f>IF(OR(71&gt;$J$2,Data!D75="",Data!D74=""),NA(),ABS(Data!D75-Data!D74))</f>
+        <v/>
+      </c>
+      <c r="K75" s="48">
+        <f>IF(OR(71&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L75" s="48">
+        <f>IF(OR(71&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M75" s="48">
+        <f>IF(OR(71&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="H76" s="36" t="n">
+        <v>72</v>
+      </c>
+      <c r="I76" s="48">
+        <f>IF(OR(72&gt;$J$2,Data!D76=""),NA(),Data!D76)</f>
+        <v/>
+      </c>
+      <c r="J76" s="48">
+        <f>IF(OR(72&gt;$J$2,Data!D76="",Data!D75=""),NA(),ABS(Data!D76-Data!D75))</f>
+        <v/>
+      </c>
+      <c r="K76" s="48">
+        <f>IF(OR(72&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L76" s="48">
+        <f>IF(OR(72&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M76" s="48">
+        <f>IF(OR(72&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="H77" s="36" t="n">
+        <v>73</v>
+      </c>
+      <c r="I77" s="48">
+        <f>IF(OR(73&gt;$J$2,Data!D77=""),NA(),Data!D77)</f>
+        <v/>
+      </c>
+      <c r="J77" s="48">
+        <f>IF(OR(73&gt;$J$2,Data!D77="",Data!D76=""),NA(),ABS(Data!D77-Data!D76))</f>
+        <v/>
+      </c>
+      <c r="K77" s="48">
+        <f>IF(OR(73&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L77" s="48">
+        <f>IF(OR(73&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M77" s="48">
+        <f>IF(OR(73&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="H78" s="36" t="n">
+        <v>74</v>
+      </c>
+      <c r="I78" s="48">
+        <f>IF(OR(74&gt;$J$2,Data!D78=""),NA(),Data!D78)</f>
+        <v/>
+      </c>
+      <c r="J78" s="48">
+        <f>IF(OR(74&gt;$J$2,Data!D78="",Data!D77=""),NA(),ABS(Data!D78-Data!D77))</f>
+        <v/>
+      </c>
+      <c r="K78" s="48">
+        <f>IF(OR(74&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L78" s="48">
+        <f>IF(OR(74&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M78" s="48">
+        <f>IF(OR(74&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="H79" s="36" t="n">
+        <v>75</v>
+      </c>
+      <c r="I79" s="48">
+        <f>IF(OR(75&gt;$J$2,Data!D79=""),NA(),Data!D79)</f>
+        <v/>
+      </c>
+      <c r="J79" s="48">
+        <f>IF(OR(75&gt;$J$2,Data!D79="",Data!D78=""),NA(),ABS(Data!D79-Data!D78))</f>
+        <v/>
+      </c>
+      <c r="K79" s="48">
+        <f>IF(OR(75&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L79" s="48">
+        <f>IF(OR(75&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M79" s="48">
+        <f>IF(OR(75&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="H80" s="36" t="n">
+        <v>76</v>
+      </c>
+      <c r="I80" s="48">
+        <f>IF(OR(76&gt;$J$2,Data!D80=""),NA(),Data!D80)</f>
+        <v/>
+      </c>
+      <c r="J80" s="48">
+        <f>IF(OR(76&gt;$J$2,Data!D80="",Data!D79=""),NA(),ABS(Data!D80-Data!D79))</f>
+        <v/>
+      </c>
+      <c r="K80" s="48">
+        <f>IF(OR(76&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L80" s="48">
+        <f>IF(OR(76&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M80" s="48">
+        <f>IF(OR(76&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="H81" s="36" t="n">
+        <v>77</v>
+      </c>
+      <c r="I81" s="48">
+        <f>IF(OR(77&gt;$J$2,Data!D81=""),NA(),Data!D81)</f>
+        <v/>
+      </c>
+      <c r="J81" s="48">
+        <f>IF(OR(77&gt;$J$2,Data!D81="",Data!D80=""),NA(),ABS(Data!D81-Data!D80))</f>
+        <v/>
+      </c>
+      <c r="K81" s="48">
+        <f>IF(OR(77&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L81" s="48">
+        <f>IF(OR(77&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M81" s="48">
+        <f>IF(OR(77&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="H82" s="36" t="n">
+        <v>78</v>
+      </c>
+      <c r="I82" s="48">
+        <f>IF(OR(78&gt;$J$2,Data!D82=""),NA(),Data!D82)</f>
+        <v/>
+      </c>
+      <c r="J82" s="48">
+        <f>IF(OR(78&gt;$J$2,Data!D82="",Data!D81=""),NA(),ABS(Data!D82-Data!D81))</f>
+        <v/>
+      </c>
+      <c r="K82" s="48">
+        <f>IF(OR(78&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L82" s="48">
+        <f>IF(OR(78&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M82" s="48">
+        <f>IF(OR(78&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="H83" s="36" t="n">
+        <v>79</v>
+      </c>
+      <c r="I83" s="48">
+        <f>IF(OR(79&gt;$J$2,Data!D83=""),NA(),Data!D83)</f>
+        <v/>
+      </c>
+      <c r="J83" s="48">
+        <f>IF(OR(79&gt;$J$2,Data!D83="",Data!D82=""),NA(),ABS(Data!D83-Data!D82))</f>
+        <v/>
+      </c>
+      <c r="K83" s="48">
+        <f>IF(OR(79&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L83" s="48">
+        <f>IF(OR(79&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M83" s="48">
+        <f>IF(OR(79&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="H84" s="36" t="n">
+        <v>80</v>
+      </c>
+      <c r="I84" s="48">
+        <f>IF(OR(80&gt;$J$2,Data!D84=""),NA(),Data!D84)</f>
+        <v/>
+      </c>
+      <c r="J84" s="48">
+        <f>IF(OR(80&gt;$J$2,Data!D84="",Data!D83=""),NA(),ABS(Data!D84-Data!D83))</f>
+        <v/>
+      </c>
+      <c r="K84" s="48">
+        <f>IF(OR(80&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L84" s="48">
+        <f>IF(OR(80&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M84" s="48">
+        <f>IF(OR(80&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="H85" s="36" t="n">
+        <v>81</v>
+      </c>
+      <c r="I85" s="48">
+        <f>IF(OR(81&gt;$J$2,Data!D85=""),NA(),Data!D85)</f>
+        <v/>
+      </c>
+      <c r="J85" s="48">
+        <f>IF(OR(81&gt;$J$2,Data!D85="",Data!D84=""),NA(),ABS(Data!D85-Data!D84))</f>
+        <v/>
+      </c>
+      <c r="K85" s="48">
+        <f>IF(OR(81&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L85" s="48">
+        <f>IF(OR(81&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M85" s="48">
+        <f>IF(OR(81&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="H86" s="36" t="n">
+        <v>82</v>
+      </c>
+      <c r="I86" s="48">
+        <f>IF(OR(82&gt;$J$2,Data!D86=""),NA(),Data!D86)</f>
+        <v/>
+      </c>
+      <c r="J86" s="48">
+        <f>IF(OR(82&gt;$J$2,Data!D86="",Data!D85=""),NA(),ABS(Data!D86-Data!D85))</f>
+        <v/>
+      </c>
+      <c r="K86" s="48">
+        <f>IF(OR(82&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L86" s="48">
+        <f>IF(OR(82&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M86" s="48">
+        <f>IF(OR(82&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="H87" s="36" t="n">
+        <v>83</v>
+      </c>
+      <c r="I87" s="48">
+        <f>IF(OR(83&gt;$J$2,Data!D87=""),NA(),Data!D87)</f>
+        <v/>
+      </c>
+      <c r="J87" s="48">
+        <f>IF(OR(83&gt;$J$2,Data!D87="",Data!D86=""),NA(),ABS(Data!D87-Data!D86))</f>
+        <v/>
+      </c>
+      <c r="K87" s="48">
+        <f>IF(OR(83&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L87" s="48">
+        <f>IF(OR(83&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M87" s="48">
+        <f>IF(OR(83&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="H88" s="36" t="n">
+        <v>84</v>
+      </c>
+      <c r="I88" s="48">
+        <f>IF(OR(84&gt;$J$2,Data!D88=""),NA(),Data!D88)</f>
+        <v/>
+      </c>
+      <c r="J88" s="48">
+        <f>IF(OR(84&gt;$J$2,Data!D88="",Data!D87=""),NA(),ABS(Data!D88-Data!D87))</f>
+        <v/>
+      </c>
+      <c r="K88" s="48">
+        <f>IF(OR(84&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L88" s="48">
+        <f>IF(OR(84&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M88" s="48">
+        <f>IF(OR(84&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="H89" s="36" t="n">
+        <v>85</v>
+      </c>
+      <c r="I89" s="48">
+        <f>IF(OR(85&gt;$J$2,Data!D89=""),NA(),Data!D89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="48">
+        <f>IF(OR(85&gt;$J$2,Data!D89="",Data!D88=""),NA(),ABS(Data!D89-Data!D88))</f>
+        <v/>
+      </c>
+      <c r="K89" s="48">
+        <f>IF(OR(85&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L89" s="48">
+        <f>IF(OR(85&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M89" s="48">
+        <f>IF(OR(85&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="H90" s="36" t="n">
+        <v>86</v>
+      </c>
+      <c r="I90" s="48">
+        <f>IF(OR(86&gt;$J$2,Data!D90=""),NA(),Data!D90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="48">
+        <f>IF(OR(86&gt;$J$2,Data!D90="",Data!D89=""),NA(),ABS(Data!D90-Data!D89))</f>
+        <v/>
+      </c>
+      <c r="K90" s="48">
+        <f>IF(OR(86&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L90" s="48">
+        <f>IF(OR(86&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M90" s="48">
+        <f>IF(OR(86&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="H91" s="36" t="n">
+        <v>87</v>
+      </c>
+      <c r="I91" s="48">
+        <f>IF(OR(87&gt;$J$2,Data!D91=""),NA(),Data!D91)</f>
+        <v/>
+      </c>
+      <c r="J91" s="48">
+        <f>IF(OR(87&gt;$J$2,Data!D91="",Data!D90=""),NA(),ABS(Data!D91-Data!D90))</f>
+        <v/>
+      </c>
+      <c r="K91" s="48">
+        <f>IF(OR(87&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L91" s="48">
+        <f>IF(OR(87&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M91" s="48">
+        <f>IF(OR(87&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="H92" s="36" t="n">
+        <v>88</v>
+      </c>
+      <c r="I92" s="48">
+        <f>IF(OR(88&gt;$J$2,Data!D92=""),NA(),Data!D92)</f>
+        <v/>
+      </c>
+      <c r="J92" s="48">
+        <f>IF(OR(88&gt;$J$2,Data!D92="",Data!D91=""),NA(),ABS(Data!D92-Data!D91))</f>
+        <v/>
+      </c>
+      <c r="K92" s="48">
+        <f>IF(OR(88&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L92" s="48">
+        <f>IF(OR(88&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M92" s="48">
+        <f>IF(OR(88&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="H93" s="36" t="n">
+        <v>89</v>
+      </c>
+      <c r="I93" s="48">
+        <f>IF(OR(89&gt;$J$2,Data!D93=""),NA(),Data!D93)</f>
+        <v/>
+      </c>
+      <c r="J93" s="48">
+        <f>IF(OR(89&gt;$J$2,Data!D93="",Data!D92=""),NA(),ABS(Data!D93-Data!D92))</f>
+        <v/>
+      </c>
+      <c r="K93" s="48">
+        <f>IF(OR(89&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L93" s="48">
+        <f>IF(OR(89&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M93" s="48">
+        <f>IF(OR(89&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="H94" s="36" t="n">
+        <v>90</v>
+      </c>
+      <c r="I94" s="48">
+        <f>IF(OR(90&gt;$J$2,Data!D94=""),NA(),Data!D94)</f>
+        <v/>
+      </c>
+      <c r="J94" s="48">
+        <f>IF(OR(90&gt;$J$2,Data!D94="",Data!D93=""),NA(),ABS(Data!D94-Data!D93))</f>
+        <v/>
+      </c>
+      <c r="K94" s="48">
+        <f>IF(OR(90&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L94" s="48">
+        <f>IF(OR(90&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M94" s="48">
+        <f>IF(OR(90&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="H95" s="36" t="n">
+        <v>91</v>
+      </c>
+      <c r="I95" s="48">
+        <f>IF(OR(91&gt;$J$2,Data!D95=""),NA(),Data!D95)</f>
+        <v/>
+      </c>
+      <c r="J95" s="48">
+        <f>IF(OR(91&gt;$J$2,Data!D95="",Data!D94=""),NA(),ABS(Data!D95-Data!D94))</f>
+        <v/>
+      </c>
+      <c r="K95" s="48">
+        <f>IF(OR(91&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L95" s="48">
+        <f>IF(OR(91&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M95" s="48">
+        <f>IF(OR(91&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="H96" s="36" t="n">
+        <v>92</v>
+      </c>
+      <c r="I96" s="48">
+        <f>IF(OR(92&gt;$J$2,Data!D96=""),NA(),Data!D96)</f>
+        <v/>
+      </c>
+      <c r="J96" s="48">
+        <f>IF(OR(92&gt;$J$2,Data!D96="",Data!D95=""),NA(),ABS(Data!D96-Data!D95))</f>
+        <v/>
+      </c>
+      <c r="K96" s="48">
+        <f>IF(OR(92&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L96" s="48">
+        <f>IF(OR(92&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M96" s="48">
+        <f>IF(OR(92&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="H97" s="36" t="n">
+        <v>93</v>
+      </c>
+      <c r="I97" s="48">
+        <f>IF(OR(93&gt;$J$2,Data!D97=""),NA(),Data!D97)</f>
+        <v/>
+      </c>
+      <c r="J97" s="48">
+        <f>IF(OR(93&gt;$J$2,Data!D97="",Data!D96=""),NA(),ABS(Data!D97-Data!D96))</f>
+        <v/>
+      </c>
+      <c r="K97" s="48">
+        <f>IF(OR(93&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L97" s="48">
+        <f>IF(OR(93&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M97" s="48">
+        <f>IF(OR(93&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="H98" s="36" t="n">
+        <v>94</v>
+      </c>
+      <c r="I98" s="48">
+        <f>IF(OR(94&gt;$J$2,Data!D98=""),NA(),Data!D98)</f>
+        <v/>
+      </c>
+      <c r="J98" s="48">
+        <f>IF(OR(94&gt;$J$2,Data!D98="",Data!D97=""),NA(),ABS(Data!D98-Data!D97))</f>
+        <v/>
+      </c>
+      <c r="K98" s="48">
+        <f>IF(OR(94&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L98" s="48">
+        <f>IF(OR(94&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M98" s="48">
+        <f>IF(OR(94&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="H99" s="36" t="n">
+        <v>95</v>
+      </c>
+      <c r="I99" s="48">
+        <f>IF(OR(95&gt;$J$2,Data!D99=""),NA(),Data!D99)</f>
+        <v/>
+      </c>
+      <c r="J99" s="48">
+        <f>IF(OR(95&gt;$J$2,Data!D99="",Data!D98=""),NA(),ABS(Data!D99-Data!D98))</f>
+        <v/>
+      </c>
+      <c r="K99" s="48">
+        <f>IF(OR(95&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L99" s="48">
+        <f>IF(OR(95&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M99" s="48">
+        <f>IF(OR(95&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="H100" s="36" t="n">
+        <v>96</v>
+      </c>
+      <c r="I100" s="48">
+        <f>IF(OR(96&gt;$J$2,Data!D100=""),NA(),Data!D100)</f>
+        <v/>
+      </c>
+      <c r="J100" s="48">
+        <f>IF(OR(96&gt;$J$2,Data!D100="",Data!D99=""),NA(),ABS(Data!D100-Data!D99))</f>
+        <v/>
+      </c>
+      <c r="K100" s="48">
+        <f>IF(OR(96&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L100" s="48">
+        <f>IF(OR(96&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M100" s="48">
+        <f>IF(OR(96&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="H101" s="36" t="n">
+        <v>97</v>
+      </c>
+      <c r="I101" s="48">
+        <f>IF(OR(97&gt;$J$2,Data!D101=""),NA(),Data!D101)</f>
+        <v/>
+      </c>
+      <c r="J101" s="48">
+        <f>IF(OR(97&gt;$J$2,Data!D101="",Data!D100=""),NA(),ABS(Data!D101-Data!D100))</f>
+        <v/>
+      </c>
+      <c r="K101" s="48">
+        <f>IF(OR(97&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L101" s="48">
+        <f>IF(OR(97&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M101" s="48">
+        <f>IF(OR(97&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="H102" s="36" t="n">
+        <v>98</v>
+      </c>
+      <c r="I102" s="48">
+        <f>IF(OR(98&gt;$J$2,Data!D102=""),NA(),Data!D102)</f>
+        <v/>
+      </c>
+      <c r="J102" s="48">
+        <f>IF(OR(98&gt;$J$2,Data!D102="",Data!D101=""),NA(),ABS(Data!D102-Data!D101))</f>
+        <v/>
+      </c>
+      <c r="K102" s="48">
+        <f>IF(OR(98&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L102" s="48">
+        <f>IF(OR(98&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M102" s="48">
+        <f>IF(OR(98&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="H103" s="36" t="n">
+        <v>99</v>
+      </c>
+      <c r="I103" s="48">
+        <f>IF(OR(99&gt;$J$2,Data!D103=""),NA(),Data!D103)</f>
+        <v/>
+      </c>
+      <c r="J103" s="48">
+        <f>IF(OR(99&gt;$J$2,Data!D103="",Data!D102=""),NA(),ABS(Data!D103-Data!D102))</f>
+        <v/>
+      </c>
+      <c r="K103" s="48">
+        <f>IF(OR(99&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L103" s="48">
+        <f>IF(OR(99&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M103" s="48">
+        <f>IF(OR(99&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I104" s="48">
+        <f>IF(OR(100&gt;$J$2,Data!D104=""),NA(),Data!D104)</f>
+        <v/>
+      </c>
+      <c r="J104" s="48">
+        <f>IF(OR(100&gt;$J$2,Data!D104="",Data!D103=""),NA(),ABS(Data!D104-Data!D103))</f>
+        <v/>
+      </c>
+      <c r="K104" s="48">
+        <f>IF(OR(100&gt;$J$2,Data!G5&lt;2),NA(),Data!G6)</f>
+        <v/>
+      </c>
+      <c r="L104" s="48">
+        <f>IF(OR(100&gt;$J$2,Data!G5&lt;2),NA(),Data!G6+2.66*AVERAGE(J6:J104))</f>
+        <v/>
+      </c>
+      <c r="M104" s="48">
+        <f>IF(OR(100&gt;$J$2,Data!G5&lt;2),NA(),Data!G6-2.66*AVERAGE(J6:J104))</f>
         <v/>
       </c>
     </row>
@@ -11567,6 +12849,11 @@
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="H3:M3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="I2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="Filter" prompt="Choose how many data points to show in control charts" type="list">
+      <formula1>"10,25,50,100,All"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -11686,59 +12973,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="48">
+      <c r="B4" s="51">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C4" s="49">
+      <c r="C4" s="52">
         <f>Analysis!C5</f>
         <v/>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="52">
         <f>Analysis!C10</f>
         <v/>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="53">
         <f>Analysis!C6</f>
         <v/>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="53">
         <f>Analysis!C7</f>
         <v/>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="53">
         <f>Analysis!C8</f>
         <v/>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="54">
         <f>Analysis!G9</f>
         <v/>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="54">
         <f>Analysis!G10</f>
         <v/>
       </c>
-      <c r="J4" s="52">
+      <c r="J4" s="55">
         <f>Analysis!G11</f>
         <v/>
       </c>
-      <c r="K4" s="50">
+      <c r="K4" s="53">
         <f>Analysis!G17</f>
         <v/>
       </c>
-      <c r="L4" s="50">
+      <c r="L4" s="53">
         <f>Analysis!G18</f>
         <v/>
       </c>
-      <c r="M4" s="53">
+      <c r="M4" s="56">
         <f>Analysis!J10</f>
         <v/>
       </c>
-      <c r="N4" s="50">
+      <c r="N4" s="53">
         <f>Analysis!G19</f>
         <v/>
       </c>
-      <c r="O4" s="49">
+      <c r="O4" s="52">
         <f>Analysis!B28</f>
         <v/>
       </c>
@@ -12591,325 +13878,325 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="54" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Reference Guide — Formulas, Definitions &amp; How to Use</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="55" t="inlineStr"/>
+      <c r="B3" s="58" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t>How to Use This Workbook</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="55" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>1. Enter specifications (Tₘ, LSL, USL) in the Analysis sheet (blue cells)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>2. Choose Mode: 'Enter Manually' or 'Use Data Worksheet' (dropdown in C10)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>3. If Manual: enter x̄, σ, n directly in the Analysis sheet</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>4. If Worksheet: enter part data in the Data sheet — mean &amp; σ auto-link</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="55" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>5. All results, probability, hypothesis test, and verdict update INSTANTLY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>6. View charts in the Charts sheet (bell curve + capability bars)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>7. To save a run: go to History sheet, copy Row 4, paste as VALUES into Row 5+</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="55" t="inlineStr"/>
+      <c r="B12" s="58" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>Core Capability Formulas</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cp = (USL − LSL) / 6σ  — Potential capability if process is perfectly centered</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cpk = min[(USL − x̄) / 3σ,  (x̄ − LSL) / 3σ]  — Actual capability with centering error</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Required Shift (Δ) = Tₘ − x̄  — How far to adjust the process mean</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="55" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Required Tolerance = Target Index × 6σ  — Minimum tolerance band needed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="55" t="inlineStr"/>
+      <c r="B18" s="58" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Capability Index Interpretation (Automotive Standards)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cpk ≥ 1.67  →  ✅ GOOD — Capable (standard automotive target)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="55" t="inlineStr">
+      <c r="B21" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.33 ≤ Cpk &lt; 1.67  →  ⚠ ACCEPTABLE — Meets minimum but below target</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.00 ≤ Cpk &lt; 1.33  →  ⚠ MARGINAL — High risk, improvement needed</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="55" t="inlineStr">
+      <c r="B23" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cpk &lt; 1.00  →  ❌ NOT CAPABLE — Produces significant defects</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="55" t="inlineStr"/>
+      <c r="B24" s="58" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="56" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>Probability &amp; PPM</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="55" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  P(x &gt; USL) — Probability a part exceeds upper spec limit</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="55" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  P(x &lt; LSL) — Probability a part falls below lower spec limit</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="55" t="inlineStr">
+      <c r="B28" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  PPM = Probability × 1,000,000 — Parts Per Million defective</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="55" t="inlineStr"/>
+      <c r="B29" s="58" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="56" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>Hypothesis Testing</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="55" t="inlineStr">
+      <c r="B31" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  H₀: μ = Tₘ (process is on target)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="55" t="inlineStr">
+      <c r="B32" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Z = (x̄ − Tₘ) / (σ / √n)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="55" t="inlineStr">
+      <c r="B33" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  p-value &lt; α → Reject H₀ → Significant shift detected</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="55" t="inlineStr">
+      <c r="B34" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  p-value ≥ α → Fail to Reject H₀ → No significant shift</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="55" t="inlineStr">
+      <c r="B35" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Two-Sided: tests if mean differs in either direction</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="55" t="inlineStr">
+      <c r="B36" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upper-Sided: tests if mean is significantly above target</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="55" t="inlineStr">
+      <c r="B37" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  Lower-Sided: tests if mean is significantly below target</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="55" t="inlineStr"/>
+      <c r="B38" s="58" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="B39" s="56" t="inlineStr">
+      <c r="B39" s="59" t="inlineStr">
         <is>
           <t>Robustness Assessment</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="55" t="inlineStr">
+      <c r="B40" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  ROBUST: ±4σ spread contained within specification limits</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="55" t="inlineStr">
+      <c r="B41" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARGINAL: ±3σ contained but ±4σ is NOT — low tolerance for future shifts</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="55" t="inlineStr">
+      <c r="B42" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOT ROBUST: ±3σ breaches specification limits</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="55" t="inlineStr"/>
+      <c r="B43" s="58" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="B44" s="56" t="inlineStr">
+      <c r="B44" s="59" t="inlineStr">
         <is>
           <t>Spread Metrics</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="55" t="inlineStr">
+      <c r="B45" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  6σ Spread — Contains ~99.73% of process output (±3σ)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="55" t="inlineStr">
+      <c r="B46" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  8σ Spread — Contains ~99.9937% of process output (±4σ)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="55" t="inlineStr"/>
+      <c r="B47" s="58" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="B48" s="56" t="inlineStr">
+      <c r="B48" s="59" t="inlineStr">
         <is>
           <t>Color Coding</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="55" t="inlineStr">
+      <c r="B49" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  🟢 Green cells = Good / Capable / Within target</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="55" t="inlineStr">
+      <c r="B50" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  🟡 Yellow cells = Warning / Marginal</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="55" t="inlineStr">
+      <c r="B51" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  🔴 Red cells = Bad / Action Required / Not capable</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="55" t="inlineStr">
+      <c r="B52" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  🔵 Blue cells = Input cells (enter your data here)</t>
         </is>

--- a/SPC_Statistical_Calculator.xlsx
+++ b/SPC_Statistical_Calculator.xlsx
@@ -32,7 +32,7 @@
     <numFmt numFmtId="170" formatCode=";;;"/>
     <numFmt numFmtId="171" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -143,6 +143,12 @@
     <font>
       <color rgb="00FFFFFF"/>
       <sz val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -265,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -404,12 +410,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12866,24 +12883,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O54"/>
+  <dimension ref="B1:Q107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12913,60 +12932,70 @@
       </c>
       <c r="D3" s="35" t="inlineStr">
         <is>
+          <t>Characteristic</t>
+        </is>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
+        <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>Tₘ</t>
         </is>
       </c>
-      <c r="F3" s="35" t="inlineStr">
+      <c r="G3" s="35" t="inlineStr">
         <is>
           <t>LSL</t>
         </is>
       </c>
-      <c r="G3" s="35" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>USL</t>
         </is>
       </c>
-      <c r="H3" s="35" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>x̄</t>
         </is>
       </c>
-      <c r="I3" s="35" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>σ</t>
         </is>
       </c>
-      <c r="J3" s="35" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="K3" s="35" t="inlineStr">
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>Cp</t>
         </is>
       </c>
-      <c r="L3" s="35" t="inlineStr">
+      <c r="M3" s="35" t="inlineStr">
         <is>
           <t>Cpk</t>
         </is>
       </c>
-      <c r="M3" s="35" t="inlineStr">
-        <is>
-          <t>PPM Total</t>
-        </is>
-      </c>
       <c r="N3" s="35" t="inlineStr">
         <is>
           <t>Shift (Δ)</t>
         </is>
       </c>
       <c r="O3" s="35" t="inlineStr">
+        <is>
+          <t>PPM &lt; LSL</t>
+        </is>
+      </c>
+      <c r="P3" s="35" t="inlineStr">
+        <is>
+          <t>PPM &gt; USL</t>
+        </is>
+      </c>
+      <c r="Q3" s="35" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
@@ -12982,50 +13011,58 @@
         <v/>
       </c>
       <c r="D4" s="52">
+        <f>Analysis!C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="52">
         <f>Analysis!C10</f>
         <v/>
       </c>
-      <c r="E4" s="53">
+      <c r="F4" s="53">
         <f>Analysis!C6</f>
         <v/>
       </c>
-      <c r="F4" s="53">
+      <c r="G4" s="53">
         <f>Analysis!C7</f>
         <v/>
       </c>
-      <c r="G4" s="53">
+      <c r="H4" s="53">
         <f>Analysis!C8</f>
         <v/>
       </c>
-      <c r="H4" s="54">
+      <c r="I4" s="54">
         <f>Analysis!G9</f>
         <v/>
       </c>
-      <c r="I4" s="54">
+      <c r="J4" s="54">
         <f>Analysis!G10</f>
         <v/>
       </c>
-      <c r="J4" s="55">
+      <c r="K4" s="55">
         <f>Analysis!G11</f>
         <v/>
       </c>
-      <c r="K4" s="53">
+      <c r="L4" s="53">
         <f>Analysis!G17</f>
         <v/>
       </c>
-      <c r="L4" s="53">
+      <c r="M4" s="53">
         <f>Analysis!G18</f>
-        <v/>
-      </c>
-      <c r="M4" s="56">
-        <f>Analysis!J10</f>
         <v/>
       </c>
       <c r="N4" s="53">
         <f>Analysis!G19</f>
         <v/>
       </c>
-      <c r="O4" s="52">
+      <c r="O4" s="56">
+        <f>Analysis!I9</f>
+        <v/>
+      </c>
+      <c r="P4" s="56">
+        <f>Analysis!I10</f>
+        <v/>
+      </c>
+      <c r="Q4" s="52">
         <f>Analysis!B28</f>
         <v/>
       </c>
@@ -13045,6 +13082,8 @@
       <c r="M5" s="39" t="n"/>
       <c r="N5" s="39" t="n"/>
       <c r="O5" s="39" t="n"/>
+      <c r="P5" s="39" t="n"/>
+      <c r="Q5" s="39" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="37" t="n"/>
@@ -13061,6 +13100,8 @@
       <c r="M6" s="37" t="n"/>
       <c r="N6" s="37" t="n"/>
       <c r="O6" s="37" t="n"/>
+      <c r="P6" s="37" t="n"/>
+      <c r="Q6" s="37" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="39" t="n"/>
@@ -13077,6 +13118,8 @@
       <c r="M7" s="39" t="n"/>
       <c r="N7" s="39" t="n"/>
       <c r="O7" s="39" t="n"/>
+      <c r="P7" s="39" t="n"/>
+      <c r="Q7" s="39" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="37" t="n"/>
@@ -13093,6 +13136,8 @@
       <c r="M8" s="37" t="n"/>
       <c r="N8" s="37" t="n"/>
       <c r="O8" s="37" t="n"/>
+      <c r="P8" s="37" t="n"/>
+      <c r="Q8" s="37" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="39" t="n"/>
@@ -13109,6 +13154,8 @@
       <c r="M9" s="39" t="n"/>
       <c r="N9" s="39" t="n"/>
       <c r="O9" s="39" t="n"/>
+      <c r="P9" s="39" t="n"/>
+      <c r="Q9" s="39" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="37" t="n"/>
@@ -13125,6 +13172,8 @@
       <c r="M10" s="37" t="n"/>
       <c r="N10" s="37" t="n"/>
       <c r="O10" s="37" t="n"/>
+      <c r="P10" s="37" t="n"/>
+      <c r="Q10" s="37" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="39" t="n"/>
@@ -13141,6 +13190,8 @@
       <c r="M11" s="39" t="n"/>
       <c r="N11" s="39" t="n"/>
       <c r="O11" s="39" t="n"/>
+      <c r="P11" s="39" t="n"/>
+      <c r="Q11" s="39" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="37" t="n"/>
@@ -13157,6 +13208,8 @@
       <c r="M12" s="37" t="n"/>
       <c r="N12" s="37" t="n"/>
       <c r="O12" s="37" t="n"/>
+      <c r="P12" s="37" t="n"/>
+      <c r="Q12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="39" t="n"/>
@@ -13173,6 +13226,8 @@
       <c r="M13" s="39" t="n"/>
       <c r="N13" s="39" t="n"/>
       <c r="O13" s="39" t="n"/>
+      <c r="P13" s="39" t="n"/>
+      <c r="Q13" s="39" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="37" t="n"/>
@@ -13189,6 +13244,8 @@
       <c r="M14" s="37" t="n"/>
       <c r="N14" s="37" t="n"/>
       <c r="O14" s="37" t="n"/>
+      <c r="P14" s="37" t="n"/>
+      <c r="Q14" s="37" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="39" t="n"/>
@@ -13205,6 +13262,8 @@
       <c r="M15" s="39" t="n"/>
       <c r="N15" s="39" t="n"/>
       <c r="O15" s="39" t="n"/>
+      <c r="P15" s="39" t="n"/>
+      <c r="Q15" s="39" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="37" t="n"/>
@@ -13221,6 +13280,8 @@
       <c r="M16" s="37" t="n"/>
       <c r="N16" s="37" t="n"/>
       <c r="O16" s="37" t="n"/>
+      <c r="P16" s="37" t="n"/>
+      <c r="Q16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="39" t="n"/>
@@ -13237,6 +13298,8 @@
       <c r="M17" s="39" t="n"/>
       <c r="N17" s="39" t="n"/>
       <c r="O17" s="39" t="n"/>
+      <c r="P17" s="39" t="n"/>
+      <c r="Q17" s="39" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="37" t="n"/>
@@ -13253,6 +13316,8 @@
       <c r="M18" s="37" t="n"/>
       <c r="N18" s="37" t="n"/>
       <c r="O18" s="37" t="n"/>
+      <c r="P18" s="37" t="n"/>
+      <c r="Q18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="39" t="n"/>
@@ -13269,6 +13334,8 @@
       <c r="M19" s="39" t="n"/>
       <c r="N19" s="39" t="n"/>
       <c r="O19" s="39" t="n"/>
+      <c r="P19" s="39" t="n"/>
+      <c r="Q19" s="39" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="37" t="n"/>
@@ -13285,6 +13352,8 @@
       <c r="M20" s="37" t="n"/>
       <c r="N20" s="37" t="n"/>
       <c r="O20" s="37" t="n"/>
+      <c r="P20" s="37" t="n"/>
+      <c r="Q20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="39" t="n"/>
@@ -13301,6 +13370,8 @@
       <c r="M21" s="39" t="n"/>
       <c r="N21" s="39" t="n"/>
       <c r="O21" s="39" t="n"/>
+      <c r="P21" s="39" t="n"/>
+      <c r="Q21" s="39" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="37" t="n"/>
@@ -13317,6 +13388,8 @@
       <c r="M22" s="37" t="n"/>
       <c r="N22" s="37" t="n"/>
       <c r="O22" s="37" t="n"/>
+      <c r="P22" s="37" t="n"/>
+      <c r="Q22" s="37" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="39" t="n"/>
@@ -13333,6 +13406,8 @@
       <c r="M23" s="39" t="n"/>
       <c r="N23" s="39" t="n"/>
       <c r="O23" s="39" t="n"/>
+      <c r="P23" s="39" t="n"/>
+      <c r="Q23" s="39" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="37" t="n"/>
@@ -13349,6 +13424,8 @@
       <c r="M24" s="37" t="n"/>
       <c r="N24" s="37" t="n"/>
       <c r="O24" s="37" t="n"/>
+      <c r="P24" s="37" t="n"/>
+      <c r="Q24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="39" t="n"/>
@@ -13365,6 +13442,8 @@
       <c r="M25" s="39" t="n"/>
       <c r="N25" s="39" t="n"/>
       <c r="O25" s="39" t="n"/>
+      <c r="P25" s="39" t="n"/>
+      <c r="Q25" s="39" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="37" t="n"/>
@@ -13381,6 +13460,8 @@
       <c r="M26" s="37" t="n"/>
       <c r="N26" s="37" t="n"/>
       <c r="O26" s="37" t="n"/>
+      <c r="P26" s="37" t="n"/>
+      <c r="Q26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="39" t="n"/>
@@ -13397,6 +13478,8 @@
       <c r="M27" s="39" t="n"/>
       <c r="N27" s="39" t="n"/>
       <c r="O27" s="39" t="n"/>
+      <c r="P27" s="39" t="n"/>
+      <c r="Q27" s="39" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="37" t="n"/>
@@ -13413,6 +13496,8 @@
       <c r="M28" s="37" t="n"/>
       <c r="N28" s="37" t="n"/>
       <c r="O28" s="37" t="n"/>
+      <c r="P28" s="37" t="n"/>
+      <c r="Q28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="39" t="n"/>
@@ -13429,6 +13514,8 @@
       <c r="M29" s="39" t="n"/>
       <c r="N29" s="39" t="n"/>
       <c r="O29" s="39" t="n"/>
+      <c r="P29" s="39" t="n"/>
+      <c r="Q29" s="39" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="37" t="n"/>
@@ -13445,6 +13532,8 @@
       <c r="M30" s="37" t="n"/>
       <c r="N30" s="37" t="n"/>
       <c r="O30" s="37" t="n"/>
+      <c r="P30" s="37" t="n"/>
+      <c r="Q30" s="37" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="39" t="n"/>
@@ -13461,6 +13550,8 @@
       <c r="M31" s="39" t="n"/>
       <c r="N31" s="39" t="n"/>
       <c r="O31" s="39" t="n"/>
+      <c r="P31" s="39" t="n"/>
+      <c r="Q31" s="39" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="37" t="n"/>
@@ -13477,6 +13568,8 @@
       <c r="M32" s="37" t="n"/>
       <c r="N32" s="37" t="n"/>
       <c r="O32" s="37" t="n"/>
+      <c r="P32" s="37" t="n"/>
+      <c r="Q32" s="37" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="39" t="n"/>
@@ -13493,6 +13586,8 @@
       <c r="M33" s="39" t="n"/>
       <c r="N33" s="39" t="n"/>
       <c r="O33" s="39" t="n"/>
+      <c r="P33" s="39" t="n"/>
+      <c r="Q33" s="39" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="37" t="n"/>
@@ -13509,6 +13604,8 @@
       <c r="M34" s="37" t="n"/>
       <c r="N34" s="37" t="n"/>
       <c r="O34" s="37" t="n"/>
+      <c r="P34" s="37" t="n"/>
+      <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="39" t="n"/>
@@ -13525,6 +13622,8 @@
       <c r="M35" s="39" t="n"/>
       <c r="N35" s="39" t="n"/>
       <c r="O35" s="39" t="n"/>
+      <c r="P35" s="39" t="n"/>
+      <c r="Q35" s="39" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="37" t="n"/>
@@ -13541,6 +13640,8 @@
       <c r="M36" s="37" t="n"/>
       <c r="N36" s="37" t="n"/>
       <c r="O36" s="37" t="n"/>
+      <c r="P36" s="37" t="n"/>
+      <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="39" t="n"/>
@@ -13557,6 +13658,8 @@
       <c r="M37" s="39" t="n"/>
       <c r="N37" s="39" t="n"/>
       <c r="O37" s="39" t="n"/>
+      <c r="P37" s="39" t="n"/>
+      <c r="Q37" s="39" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="37" t="n"/>
@@ -13573,6 +13676,8 @@
       <c r="M38" s="37" t="n"/>
       <c r="N38" s="37" t="n"/>
       <c r="O38" s="37" t="n"/>
+      <c r="P38" s="37" t="n"/>
+      <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="39" t="n"/>
@@ -13589,6 +13694,8 @@
       <c r="M39" s="39" t="n"/>
       <c r="N39" s="39" t="n"/>
       <c r="O39" s="39" t="n"/>
+      <c r="P39" s="39" t="n"/>
+      <c r="Q39" s="39" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="37" t="n"/>
@@ -13605,6 +13712,8 @@
       <c r="M40" s="37" t="n"/>
       <c r="N40" s="37" t="n"/>
       <c r="O40" s="37" t="n"/>
+      <c r="P40" s="37" t="n"/>
+      <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="39" t="n"/>
@@ -13621,6 +13730,8 @@
       <c r="M41" s="39" t="n"/>
       <c r="N41" s="39" t="n"/>
       <c r="O41" s="39" t="n"/>
+      <c r="P41" s="39" t="n"/>
+      <c r="Q41" s="39" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="37" t="n"/>
@@ -13637,6 +13748,8 @@
       <c r="M42" s="37" t="n"/>
       <c r="N42" s="37" t="n"/>
       <c r="O42" s="37" t="n"/>
+      <c r="P42" s="37" t="n"/>
+      <c r="Q42" s="37" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="39" t="n"/>
@@ -13653,6 +13766,8 @@
       <c r="M43" s="39" t="n"/>
       <c r="N43" s="39" t="n"/>
       <c r="O43" s="39" t="n"/>
+      <c r="P43" s="39" t="n"/>
+      <c r="Q43" s="39" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="37" t="n"/>
@@ -13669,6 +13784,8 @@
       <c r="M44" s="37" t="n"/>
       <c r="N44" s="37" t="n"/>
       <c r="O44" s="37" t="n"/>
+      <c r="P44" s="37" t="n"/>
+      <c r="Q44" s="37" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="39" t="n"/>
@@ -13685,6 +13802,8 @@
       <c r="M45" s="39" t="n"/>
       <c r="N45" s="39" t="n"/>
       <c r="O45" s="39" t="n"/>
+      <c r="P45" s="39" t="n"/>
+      <c r="Q45" s="39" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="37" t="n"/>
@@ -13701,6 +13820,8 @@
       <c r="M46" s="37" t="n"/>
       <c r="N46" s="37" t="n"/>
       <c r="O46" s="37" t="n"/>
+      <c r="P46" s="37" t="n"/>
+      <c r="Q46" s="37" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="39" t="n"/>
@@ -13717,6 +13838,8 @@
       <c r="M47" s="39" t="n"/>
       <c r="N47" s="39" t="n"/>
       <c r="O47" s="39" t="n"/>
+      <c r="P47" s="39" t="n"/>
+      <c r="Q47" s="39" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="37" t="n"/>
@@ -13733,6 +13856,8 @@
       <c r="M48" s="37" t="n"/>
       <c r="N48" s="37" t="n"/>
       <c r="O48" s="37" t="n"/>
+      <c r="P48" s="37" t="n"/>
+      <c r="Q48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="39" t="n"/>
@@ -13749,6 +13874,8 @@
       <c r="M49" s="39" t="n"/>
       <c r="N49" s="39" t="n"/>
       <c r="O49" s="39" t="n"/>
+      <c r="P49" s="39" t="n"/>
+      <c r="Q49" s="39" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="37" t="n"/>
@@ -13765,6 +13892,8 @@
       <c r="M50" s="37" t="n"/>
       <c r="N50" s="37" t="n"/>
       <c r="O50" s="37" t="n"/>
+      <c r="P50" s="37" t="n"/>
+      <c r="Q50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="39" t="n"/>
@@ -13781,6 +13910,8 @@
       <c r="M51" s="39" t="n"/>
       <c r="N51" s="39" t="n"/>
       <c r="O51" s="39" t="n"/>
+      <c r="P51" s="39" t="n"/>
+      <c r="Q51" s="39" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="37" t="n"/>
@@ -13797,6 +13928,8 @@
       <c r="M52" s="37" t="n"/>
       <c r="N52" s="37" t="n"/>
       <c r="O52" s="37" t="n"/>
+      <c r="P52" s="37" t="n"/>
+      <c r="Q52" s="37" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="39" t="n"/>
@@ -13813,6 +13946,8 @@
       <c r="M53" s="39" t="n"/>
       <c r="N53" s="39" t="n"/>
       <c r="O53" s="39" t="n"/>
+      <c r="P53" s="39" t="n"/>
+      <c r="Q53" s="39" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="37" t="n"/>
@@ -13829,13 +13964,923 @@
       <c r="M54" s="37" t="n"/>
       <c r="N54" s="37" t="n"/>
       <c r="O54" s="37" t="n"/>
+      <c r="P54" s="37" t="n"/>
+      <c r="Q54" s="37" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="39" t="n"/>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="39" t="n"/>
+      <c r="F55" s="39" t="n"/>
+      <c r="G55" s="39" t="n"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="n"/>
+      <c r="J55" s="39" t="n"/>
+      <c r="K55" s="39" t="n"/>
+      <c r="L55" s="39" t="n"/>
+      <c r="M55" s="39" t="n"/>
+      <c r="N55" s="39" t="n"/>
+      <c r="O55" s="39" t="n"/>
+      <c r="P55" s="39" t="n"/>
+      <c r="Q55" s="39" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="37" t="n"/>
+      <c r="C56" s="37" t="n"/>
+      <c r="D56" s="37" t="n"/>
+      <c r="E56" s="37" t="n"/>
+      <c r="F56" s="37" t="n"/>
+      <c r="G56" s="37" t="n"/>
+      <c r="H56" s="37" t="n"/>
+      <c r="I56" s="37" t="n"/>
+      <c r="J56" s="37" t="n"/>
+      <c r="K56" s="37" t="n"/>
+      <c r="L56" s="37" t="n"/>
+      <c r="M56" s="37" t="n"/>
+      <c r="N56" s="37" t="n"/>
+      <c r="O56" s="37" t="n"/>
+      <c r="P56" s="37" t="n"/>
+      <c r="Q56" s="37" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="39" t="n"/>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="39" t="n"/>
+      <c r="E57" s="39" t="n"/>
+      <c r="F57" s="39" t="n"/>
+      <c r="G57" s="39" t="n"/>
+      <c r="H57" s="39" t="n"/>
+      <c r="I57" s="39" t="n"/>
+      <c r="J57" s="39" t="n"/>
+      <c r="K57" s="39" t="n"/>
+      <c r="L57" s="39" t="n"/>
+      <c r="M57" s="39" t="n"/>
+      <c r="N57" s="39" t="n"/>
+      <c r="O57" s="39" t="n"/>
+      <c r="P57" s="39" t="n"/>
+      <c r="Q57" s="39" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="37" t="n"/>
+      <c r="C58" s="37" t="n"/>
+      <c r="D58" s="37" t="n"/>
+      <c r="E58" s="37" t="n"/>
+      <c r="F58" s="37" t="n"/>
+      <c r="G58" s="37" t="n"/>
+      <c r="H58" s="37" t="n"/>
+      <c r="I58" s="37" t="n"/>
+      <c r="J58" s="37" t="n"/>
+      <c r="K58" s="37" t="n"/>
+      <c r="L58" s="37" t="n"/>
+      <c r="M58" s="37" t="n"/>
+      <c r="N58" s="37" t="n"/>
+      <c r="O58" s="37" t="n"/>
+      <c r="P58" s="37" t="n"/>
+      <c r="Q58" s="37" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="39" t="n"/>
+      <c r="C59" s="39" t="n"/>
+      <c r="D59" s="39" t="n"/>
+      <c r="E59" s="39" t="n"/>
+      <c r="F59" s="39" t="n"/>
+      <c r="G59" s="39" t="n"/>
+      <c r="H59" s="39" t="n"/>
+      <c r="I59" s="39" t="n"/>
+      <c r="J59" s="39" t="n"/>
+      <c r="K59" s="39" t="n"/>
+      <c r="L59" s="39" t="n"/>
+      <c r="M59" s="39" t="n"/>
+      <c r="N59" s="39" t="n"/>
+      <c r="O59" s="39" t="n"/>
+      <c r="P59" s="39" t="n"/>
+      <c r="Q59" s="39" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="37" t="n"/>
+      <c r="C60" s="37" t="n"/>
+      <c r="D60" s="37" t="n"/>
+      <c r="E60" s="37" t="n"/>
+      <c r="F60" s="37" t="n"/>
+      <c r="G60" s="37" t="n"/>
+      <c r="H60" s="37" t="n"/>
+      <c r="I60" s="37" t="n"/>
+      <c r="J60" s="37" t="n"/>
+      <c r="K60" s="37" t="n"/>
+      <c r="L60" s="37" t="n"/>
+      <c r="M60" s="37" t="n"/>
+      <c r="N60" s="37" t="n"/>
+      <c r="O60" s="37" t="n"/>
+      <c r="P60" s="37" t="n"/>
+      <c r="Q60" s="37" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="39" t="n"/>
+      <c r="C61" s="39" t="n"/>
+      <c r="D61" s="39" t="n"/>
+      <c r="E61" s="39" t="n"/>
+      <c r="F61" s="39" t="n"/>
+      <c r="G61" s="39" t="n"/>
+      <c r="H61" s="39" t="n"/>
+      <c r="I61" s="39" t="n"/>
+      <c r="J61" s="39" t="n"/>
+      <c r="K61" s="39" t="n"/>
+      <c r="L61" s="39" t="n"/>
+      <c r="M61" s="39" t="n"/>
+      <c r="N61" s="39" t="n"/>
+      <c r="O61" s="39" t="n"/>
+      <c r="P61" s="39" t="n"/>
+      <c r="Q61" s="39" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="37" t="n"/>
+      <c r="C62" s="37" t="n"/>
+      <c r="D62" s="37" t="n"/>
+      <c r="E62" s="37" t="n"/>
+      <c r="F62" s="37" t="n"/>
+      <c r="G62" s="37" t="n"/>
+      <c r="H62" s="37" t="n"/>
+      <c r="I62" s="37" t="n"/>
+      <c r="J62" s="37" t="n"/>
+      <c r="K62" s="37" t="n"/>
+      <c r="L62" s="37" t="n"/>
+      <c r="M62" s="37" t="n"/>
+      <c r="N62" s="37" t="n"/>
+      <c r="O62" s="37" t="n"/>
+      <c r="P62" s="37" t="n"/>
+      <c r="Q62" s="37" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="39" t="n"/>
+      <c r="C63" s="39" t="n"/>
+      <c r="D63" s="39" t="n"/>
+      <c r="E63" s="39" t="n"/>
+      <c r="F63" s="39" t="n"/>
+      <c r="G63" s="39" t="n"/>
+      <c r="H63" s="39" t="n"/>
+      <c r="I63" s="39" t="n"/>
+      <c r="J63" s="39" t="n"/>
+      <c r="K63" s="39" t="n"/>
+      <c r="L63" s="39" t="n"/>
+      <c r="M63" s="39" t="n"/>
+      <c r="N63" s="39" t="n"/>
+      <c r="O63" s="39" t="n"/>
+      <c r="P63" s="39" t="n"/>
+      <c r="Q63" s="39" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="37" t="n"/>
+      <c r="C64" s="37" t="n"/>
+      <c r="D64" s="37" t="n"/>
+      <c r="E64" s="37" t="n"/>
+      <c r="F64" s="37" t="n"/>
+      <c r="G64" s="37" t="n"/>
+      <c r="H64" s="37" t="n"/>
+      <c r="I64" s="37" t="n"/>
+      <c r="J64" s="37" t="n"/>
+      <c r="K64" s="37" t="n"/>
+      <c r="L64" s="37" t="n"/>
+      <c r="M64" s="37" t="n"/>
+      <c r="N64" s="37" t="n"/>
+      <c r="O64" s="37" t="n"/>
+      <c r="P64" s="37" t="n"/>
+      <c r="Q64" s="37" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="39" t="n"/>
+      <c r="C65" s="39" t="n"/>
+      <c r="D65" s="39" t="n"/>
+      <c r="E65" s="39" t="n"/>
+      <c r="F65" s="39" t="n"/>
+      <c r="G65" s="39" t="n"/>
+      <c r="H65" s="39" t="n"/>
+      <c r="I65" s="39" t="n"/>
+      <c r="J65" s="39" t="n"/>
+      <c r="K65" s="39" t="n"/>
+      <c r="L65" s="39" t="n"/>
+      <c r="M65" s="39" t="n"/>
+      <c r="N65" s="39" t="n"/>
+      <c r="O65" s="39" t="n"/>
+      <c r="P65" s="39" t="n"/>
+      <c r="Q65" s="39" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="37" t="n"/>
+      <c r="C66" s="37" t="n"/>
+      <c r="D66" s="37" t="n"/>
+      <c r="E66" s="37" t="n"/>
+      <c r="F66" s="37" t="n"/>
+      <c r="G66" s="37" t="n"/>
+      <c r="H66" s="37" t="n"/>
+      <c r="I66" s="37" t="n"/>
+      <c r="J66" s="37" t="n"/>
+      <c r="K66" s="37" t="n"/>
+      <c r="L66" s="37" t="n"/>
+      <c r="M66" s="37" t="n"/>
+      <c r="N66" s="37" t="n"/>
+      <c r="O66" s="37" t="n"/>
+      <c r="P66" s="37" t="n"/>
+      <c r="Q66" s="37" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="39" t="n"/>
+      <c r="C67" s="39" t="n"/>
+      <c r="D67" s="39" t="n"/>
+      <c r="E67" s="39" t="n"/>
+      <c r="F67" s="39" t="n"/>
+      <c r="G67" s="39" t="n"/>
+      <c r="H67" s="39" t="n"/>
+      <c r="I67" s="39" t="n"/>
+      <c r="J67" s="39" t="n"/>
+      <c r="K67" s="39" t="n"/>
+      <c r="L67" s="39" t="n"/>
+      <c r="M67" s="39" t="n"/>
+      <c r="N67" s="39" t="n"/>
+      <c r="O67" s="39" t="n"/>
+      <c r="P67" s="39" t="n"/>
+      <c r="Q67" s="39" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="37" t="n"/>
+      <c r="C68" s="37" t="n"/>
+      <c r="D68" s="37" t="n"/>
+      <c r="E68" s="37" t="n"/>
+      <c r="F68" s="37" t="n"/>
+      <c r="G68" s="37" t="n"/>
+      <c r="H68" s="37" t="n"/>
+      <c r="I68" s="37" t="n"/>
+      <c r="J68" s="37" t="n"/>
+      <c r="K68" s="37" t="n"/>
+      <c r="L68" s="37" t="n"/>
+      <c r="M68" s="37" t="n"/>
+      <c r="N68" s="37" t="n"/>
+      <c r="O68" s="37" t="n"/>
+      <c r="P68" s="37" t="n"/>
+      <c r="Q68" s="37" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="39" t="n"/>
+      <c r="C69" s="39" t="n"/>
+      <c r="D69" s="39" t="n"/>
+      <c r="E69" s="39" t="n"/>
+      <c r="F69" s="39" t="n"/>
+      <c r="G69" s="39" t="n"/>
+      <c r="H69" s="39" t="n"/>
+      <c r="I69" s="39" t="n"/>
+      <c r="J69" s="39" t="n"/>
+      <c r="K69" s="39" t="n"/>
+      <c r="L69" s="39" t="n"/>
+      <c r="M69" s="39" t="n"/>
+      <c r="N69" s="39" t="n"/>
+      <c r="O69" s="39" t="n"/>
+      <c r="P69" s="39" t="n"/>
+      <c r="Q69" s="39" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="37" t="n"/>
+      <c r="C70" s="37" t="n"/>
+      <c r="D70" s="37" t="n"/>
+      <c r="E70" s="37" t="n"/>
+      <c r="F70" s="37" t="n"/>
+      <c r="G70" s="37" t="n"/>
+      <c r="H70" s="37" t="n"/>
+      <c r="I70" s="37" t="n"/>
+      <c r="J70" s="37" t="n"/>
+      <c r="K70" s="37" t="n"/>
+      <c r="L70" s="37" t="n"/>
+      <c r="M70" s="37" t="n"/>
+      <c r="N70" s="37" t="n"/>
+      <c r="O70" s="37" t="n"/>
+      <c r="P70" s="37" t="n"/>
+      <c r="Q70" s="37" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="39" t="n"/>
+      <c r="C71" s="39" t="n"/>
+      <c r="D71" s="39" t="n"/>
+      <c r="E71" s="39" t="n"/>
+      <c r="F71" s="39" t="n"/>
+      <c r="G71" s="39" t="n"/>
+      <c r="H71" s="39" t="n"/>
+      <c r="I71" s="39" t="n"/>
+      <c r="J71" s="39" t="n"/>
+      <c r="K71" s="39" t="n"/>
+      <c r="L71" s="39" t="n"/>
+      <c r="M71" s="39" t="n"/>
+      <c r="N71" s="39" t="n"/>
+      <c r="O71" s="39" t="n"/>
+      <c r="P71" s="39" t="n"/>
+      <c r="Q71" s="39" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="37" t="n"/>
+      <c r="C72" s="37" t="n"/>
+      <c r="D72" s="37" t="n"/>
+      <c r="E72" s="37" t="n"/>
+      <c r="F72" s="37" t="n"/>
+      <c r="G72" s="37" t="n"/>
+      <c r="H72" s="37" t="n"/>
+      <c r="I72" s="37" t="n"/>
+      <c r="J72" s="37" t="n"/>
+      <c r="K72" s="37" t="n"/>
+      <c r="L72" s="37" t="n"/>
+      <c r="M72" s="37" t="n"/>
+      <c r="N72" s="37" t="n"/>
+      <c r="O72" s="37" t="n"/>
+      <c r="P72" s="37" t="n"/>
+      <c r="Q72" s="37" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="39" t="n"/>
+      <c r="C73" s="39" t="n"/>
+      <c r="D73" s="39" t="n"/>
+      <c r="E73" s="39" t="n"/>
+      <c r="F73" s="39" t="n"/>
+      <c r="G73" s="39" t="n"/>
+      <c r="H73" s="39" t="n"/>
+      <c r="I73" s="39" t="n"/>
+      <c r="J73" s="39" t="n"/>
+      <c r="K73" s="39" t="n"/>
+      <c r="L73" s="39" t="n"/>
+      <c r="M73" s="39" t="n"/>
+      <c r="N73" s="39" t="n"/>
+      <c r="O73" s="39" t="n"/>
+      <c r="P73" s="39" t="n"/>
+      <c r="Q73" s="39" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="37" t="n"/>
+      <c r="C74" s="37" t="n"/>
+      <c r="D74" s="37" t="n"/>
+      <c r="E74" s="37" t="n"/>
+      <c r="F74" s="37" t="n"/>
+      <c r="G74" s="37" t="n"/>
+      <c r="H74" s="37" t="n"/>
+      <c r="I74" s="37" t="n"/>
+      <c r="J74" s="37" t="n"/>
+      <c r="K74" s="37" t="n"/>
+      <c r="L74" s="37" t="n"/>
+      <c r="M74" s="37" t="n"/>
+      <c r="N74" s="37" t="n"/>
+      <c r="O74" s="37" t="n"/>
+      <c r="P74" s="37" t="n"/>
+      <c r="Q74" s="37" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="39" t="n"/>
+      <c r="C75" s="39" t="n"/>
+      <c r="D75" s="39" t="n"/>
+      <c r="E75" s="39" t="n"/>
+      <c r="F75" s="39" t="n"/>
+      <c r="G75" s="39" t="n"/>
+      <c r="H75" s="39" t="n"/>
+      <c r="I75" s="39" t="n"/>
+      <c r="J75" s="39" t="n"/>
+      <c r="K75" s="39" t="n"/>
+      <c r="L75" s="39" t="n"/>
+      <c r="M75" s="39" t="n"/>
+      <c r="N75" s="39" t="n"/>
+      <c r="O75" s="39" t="n"/>
+      <c r="P75" s="39" t="n"/>
+      <c r="Q75" s="39" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="37" t="n"/>
+      <c r="C76" s="37" t="n"/>
+      <c r="D76" s="37" t="n"/>
+      <c r="E76" s="37" t="n"/>
+      <c r="F76" s="37" t="n"/>
+      <c r="G76" s="37" t="n"/>
+      <c r="H76" s="37" t="n"/>
+      <c r="I76" s="37" t="n"/>
+      <c r="J76" s="37" t="n"/>
+      <c r="K76" s="37" t="n"/>
+      <c r="L76" s="37" t="n"/>
+      <c r="M76" s="37" t="n"/>
+      <c r="N76" s="37" t="n"/>
+      <c r="O76" s="37" t="n"/>
+      <c r="P76" s="37" t="n"/>
+      <c r="Q76" s="37" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="39" t="n"/>
+      <c r="C77" s="39" t="n"/>
+      <c r="D77" s="39" t="n"/>
+      <c r="E77" s="39" t="n"/>
+      <c r="F77" s="39" t="n"/>
+      <c r="G77" s="39" t="n"/>
+      <c r="H77" s="39" t="n"/>
+      <c r="I77" s="39" t="n"/>
+      <c r="J77" s="39" t="n"/>
+      <c r="K77" s="39" t="n"/>
+      <c r="L77" s="39" t="n"/>
+      <c r="M77" s="39" t="n"/>
+      <c r="N77" s="39" t="n"/>
+      <c r="O77" s="39" t="n"/>
+      <c r="P77" s="39" t="n"/>
+      <c r="Q77" s="39" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="37" t="n"/>
+      <c r="C78" s="37" t="n"/>
+      <c r="D78" s="37" t="n"/>
+      <c r="E78" s="37" t="n"/>
+      <c r="F78" s="37" t="n"/>
+      <c r="G78" s="37" t="n"/>
+      <c r="H78" s="37" t="n"/>
+      <c r="I78" s="37" t="n"/>
+      <c r="J78" s="37" t="n"/>
+      <c r="K78" s="37" t="n"/>
+      <c r="L78" s="37" t="n"/>
+      <c r="M78" s="37" t="n"/>
+      <c r="N78" s="37" t="n"/>
+      <c r="O78" s="37" t="n"/>
+      <c r="P78" s="37" t="n"/>
+      <c r="Q78" s="37" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="39" t="n"/>
+      <c r="C79" s="39" t="n"/>
+      <c r="D79" s="39" t="n"/>
+      <c r="E79" s="39" t="n"/>
+      <c r="F79" s="39" t="n"/>
+      <c r="G79" s="39" t="n"/>
+      <c r="H79" s="39" t="n"/>
+      <c r="I79" s="39" t="n"/>
+      <c r="J79" s="39" t="n"/>
+      <c r="K79" s="39" t="n"/>
+      <c r="L79" s="39" t="n"/>
+      <c r="M79" s="39" t="n"/>
+      <c r="N79" s="39" t="n"/>
+      <c r="O79" s="39" t="n"/>
+      <c r="P79" s="39" t="n"/>
+      <c r="Q79" s="39" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="37" t="n"/>
+      <c r="C80" s="37" t="n"/>
+      <c r="D80" s="37" t="n"/>
+      <c r="E80" s="37" t="n"/>
+      <c r="F80" s="37" t="n"/>
+      <c r="G80" s="37" t="n"/>
+      <c r="H80" s="37" t="n"/>
+      <c r="I80" s="37" t="n"/>
+      <c r="J80" s="37" t="n"/>
+      <c r="K80" s="37" t="n"/>
+      <c r="L80" s="37" t="n"/>
+      <c r="M80" s="37" t="n"/>
+      <c r="N80" s="37" t="n"/>
+      <c r="O80" s="37" t="n"/>
+      <c r="P80" s="37" t="n"/>
+      <c r="Q80" s="37" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="39" t="n"/>
+      <c r="C81" s="39" t="n"/>
+      <c r="D81" s="39" t="n"/>
+      <c r="E81" s="39" t="n"/>
+      <c r="F81" s="39" t="n"/>
+      <c r="G81" s="39" t="n"/>
+      <c r="H81" s="39" t="n"/>
+      <c r="I81" s="39" t="n"/>
+      <c r="J81" s="39" t="n"/>
+      <c r="K81" s="39" t="n"/>
+      <c r="L81" s="39" t="n"/>
+      <c r="M81" s="39" t="n"/>
+      <c r="N81" s="39" t="n"/>
+      <c r="O81" s="39" t="n"/>
+      <c r="P81" s="39" t="n"/>
+      <c r="Q81" s="39" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="37" t="n"/>
+      <c r="C82" s="37" t="n"/>
+      <c r="D82" s="37" t="n"/>
+      <c r="E82" s="37" t="n"/>
+      <c r="F82" s="37" t="n"/>
+      <c r="G82" s="37" t="n"/>
+      <c r="H82" s="37" t="n"/>
+      <c r="I82" s="37" t="n"/>
+      <c r="J82" s="37" t="n"/>
+      <c r="K82" s="37" t="n"/>
+      <c r="L82" s="37" t="n"/>
+      <c r="M82" s="37" t="n"/>
+      <c r="N82" s="37" t="n"/>
+      <c r="O82" s="37" t="n"/>
+      <c r="P82" s="37" t="n"/>
+      <c r="Q82" s="37" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="39" t="n"/>
+      <c r="C83" s="39" t="n"/>
+      <c r="D83" s="39" t="n"/>
+      <c r="E83" s="39" t="n"/>
+      <c r="F83" s="39" t="n"/>
+      <c r="G83" s="39" t="n"/>
+      <c r="H83" s="39" t="n"/>
+      <c r="I83" s="39" t="n"/>
+      <c r="J83" s="39" t="n"/>
+      <c r="K83" s="39" t="n"/>
+      <c r="L83" s="39" t="n"/>
+      <c r="M83" s="39" t="n"/>
+      <c r="N83" s="39" t="n"/>
+      <c r="O83" s="39" t="n"/>
+      <c r="P83" s="39" t="n"/>
+      <c r="Q83" s="39" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="37" t="n"/>
+      <c r="C84" s="37" t="n"/>
+      <c r="D84" s="37" t="n"/>
+      <c r="E84" s="37" t="n"/>
+      <c r="F84" s="37" t="n"/>
+      <c r="G84" s="37" t="n"/>
+      <c r="H84" s="37" t="n"/>
+      <c r="I84" s="37" t="n"/>
+      <c r="J84" s="37" t="n"/>
+      <c r="K84" s="37" t="n"/>
+      <c r="L84" s="37" t="n"/>
+      <c r="M84" s="37" t="n"/>
+      <c r="N84" s="37" t="n"/>
+      <c r="O84" s="37" t="n"/>
+      <c r="P84" s="37" t="n"/>
+      <c r="Q84" s="37" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="39" t="n"/>
+      <c r="C85" s="39" t="n"/>
+      <c r="D85" s="39" t="n"/>
+      <c r="E85" s="39" t="n"/>
+      <c r="F85" s="39" t="n"/>
+      <c r="G85" s="39" t="n"/>
+      <c r="H85" s="39" t="n"/>
+      <c r="I85" s="39" t="n"/>
+      <c r="J85" s="39" t="n"/>
+      <c r="K85" s="39" t="n"/>
+      <c r="L85" s="39" t="n"/>
+      <c r="M85" s="39" t="n"/>
+      <c r="N85" s="39" t="n"/>
+      <c r="O85" s="39" t="n"/>
+      <c r="P85" s="39" t="n"/>
+      <c r="Q85" s="39" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="37" t="n"/>
+      <c r="C86" s="37" t="n"/>
+      <c r="D86" s="37" t="n"/>
+      <c r="E86" s="37" t="n"/>
+      <c r="F86" s="37" t="n"/>
+      <c r="G86" s="37" t="n"/>
+      <c r="H86" s="37" t="n"/>
+      <c r="I86" s="37" t="n"/>
+      <c r="J86" s="37" t="n"/>
+      <c r="K86" s="37" t="n"/>
+      <c r="L86" s="37" t="n"/>
+      <c r="M86" s="37" t="n"/>
+      <c r="N86" s="37" t="n"/>
+      <c r="O86" s="37" t="n"/>
+      <c r="P86" s="37" t="n"/>
+      <c r="Q86" s="37" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="39" t="n"/>
+      <c r="C87" s="39" t="n"/>
+      <c r="D87" s="39" t="n"/>
+      <c r="E87" s="39" t="n"/>
+      <c r="F87" s="39" t="n"/>
+      <c r="G87" s="39" t="n"/>
+      <c r="H87" s="39" t="n"/>
+      <c r="I87" s="39" t="n"/>
+      <c r="J87" s="39" t="n"/>
+      <c r="K87" s="39" t="n"/>
+      <c r="L87" s="39" t="n"/>
+      <c r="M87" s="39" t="n"/>
+      <c r="N87" s="39" t="n"/>
+      <c r="O87" s="39" t="n"/>
+      <c r="P87" s="39" t="n"/>
+      <c r="Q87" s="39" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="37" t="n"/>
+      <c r="C88" s="37" t="n"/>
+      <c r="D88" s="37" t="n"/>
+      <c r="E88" s="37" t="n"/>
+      <c r="F88" s="37" t="n"/>
+      <c r="G88" s="37" t="n"/>
+      <c r="H88" s="37" t="n"/>
+      <c r="I88" s="37" t="n"/>
+      <c r="J88" s="37" t="n"/>
+      <c r="K88" s="37" t="n"/>
+      <c r="L88" s="37" t="n"/>
+      <c r="M88" s="37" t="n"/>
+      <c r="N88" s="37" t="n"/>
+      <c r="O88" s="37" t="n"/>
+      <c r="P88" s="37" t="n"/>
+      <c r="Q88" s="37" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="39" t="n"/>
+      <c r="C89" s="39" t="n"/>
+      <c r="D89" s="39" t="n"/>
+      <c r="E89" s="39" t="n"/>
+      <c r="F89" s="39" t="n"/>
+      <c r="G89" s="39" t="n"/>
+      <c r="H89" s="39" t="n"/>
+      <c r="I89" s="39" t="n"/>
+      <c r="J89" s="39" t="n"/>
+      <c r="K89" s="39" t="n"/>
+      <c r="L89" s="39" t="n"/>
+      <c r="M89" s="39" t="n"/>
+      <c r="N89" s="39" t="n"/>
+      <c r="O89" s="39" t="n"/>
+      <c r="P89" s="39" t="n"/>
+      <c r="Q89" s="39" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="37" t="n"/>
+      <c r="C90" s="37" t="n"/>
+      <c r="D90" s="37" t="n"/>
+      <c r="E90" s="37" t="n"/>
+      <c r="F90" s="37" t="n"/>
+      <c r="G90" s="37" t="n"/>
+      <c r="H90" s="37" t="n"/>
+      <c r="I90" s="37" t="n"/>
+      <c r="J90" s="37" t="n"/>
+      <c r="K90" s="37" t="n"/>
+      <c r="L90" s="37" t="n"/>
+      <c r="M90" s="37" t="n"/>
+      <c r="N90" s="37" t="n"/>
+      <c r="O90" s="37" t="n"/>
+      <c r="P90" s="37" t="n"/>
+      <c r="Q90" s="37" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="39" t="n"/>
+      <c r="C91" s="39" t="n"/>
+      <c r="D91" s="39" t="n"/>
+      <c r="E91" s="39" t="n"/>
+      <c r="F91" s="39" t="n"/>
+      <c r="G91" s="39" t="n"/>
+      <c r="H91" s="39" t="n"/>
+      <c r="I91" s="39" t="n"/>
+      <c r="J91" s="39" t="n"/>
+      <c r="K91" s="39" t="n"/>
+      <c r="L91" s="39" t="n"/>
+      <c r="M91" s="39" t="n"/>
+      <c r="N91" s="39" t="n"/>
+      <c r="O91" s="39" t="n"/>
+      <c r="P91" s="39" t="n"/>
+      <c r="Q91" s="39" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="37" t="n"/>
+      <c r="C92" s="37" t="n"/>
+      <c r="D92" s="37" t="n"/>
+      <c r="E92" s="37" t="n"/>
+      <c r="F92" s="37" t="n"/>
+      <c r="G92" s="37" t="n"/>
+      <c r="H92" s="37" t="n"/>
+      <c r="I92" s="37" t="n"/>
+      <c r="J92" s="37" t="n"/>
+      <c r="K92" s="37" t="n"/>
+      <c r="L92" s="37" t="n"/>
+      <c r="M92" s="37" t="n"/>
+      <c r="N92" s="37" t="n"/>
+      <c r="O92" s="37" t="n"/>
+      <c r="P92" s="37" t="n"/>
+      <c r="Q92" s="37" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="39" t="n"/>
+      <c r="C93" s="39" t="n"/>
+      <c r="D93" s="39" t="n"/>
+      <c r="E93" s="39" t="n"/>
+      <c r="F93" s="39" t="n"/>
+      <c r="G93" s="39" t="n"/>
+      <c r="H93" s="39" t="n"/>
+      <c r="I93" s="39" t="n"/>
+      <c r="J93" s="39" t="n"/>
+      <c r="K93" s="39" t="n"/>
+      <c r="L93" s="39" t="n"/>
+      <c r="M93" s="39" t="n"/>
+      <c r="N93" s="39" t="n"/>
+      <c r="O93" s="39" t="n"/>
+      <c r="P93" s="39" t="n"/>
+      <c r="Q93" s="39" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="37" t="n"/>
+      <c r="C94" s="37" t="n"/>
+      <c r="D94" s="37" t="n"/>
+      <c r="E94" s="37" t="n"/>
+      <c r="F94" s="37" t="n"/>
+      <c r="G94" s="37" t="n"/>
+      <c r="H94" s="37" t="n"/>
+      <c r="I94" s="37" t="n"/>
+      <c r="J94" s="37" t="n"/>
+      <c r="K94" s="37" t="n"/>
+      <c r="L94" s="37" t="n"/>
+      <c r="M94" s="37" t="n"/>
+      <c r="N94" s="37" t="n"/>
+      <c r="O94" s="37" t="n"/>
+      <c r="P94" s="37" t="n"/>
+      <c r="Q94" s="37" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="39" t="n"/>
+      <c r="C95" s="39" t="n"/>
+      <c r="D95" s="39" t="n"/>
+      <c r="E95" s="39" t="n"/>
+      <c r="F95" s="39" t="n"/>
+      <c r="G95" s="39" t="n"/>
+      <c r="H95" s="39" t="n"/>
+      <c r="I95" s="39" t="n"/>
+      <c r="J95" s="39" t="n"/>
+      <c r="K95" s="39" t="n"/>
+      <c r="L95" s="39" t="n"/>
+      <c r="M95" s="39" t="n"/>
+      <c r="N95" s="39" t="n"/>
+      <c r="O95" s="39" t="n"/>
+      <c r="P95" s="39" t="n"/>
+      <c r="Q95" s="39" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="37" t="n"/>
+      <c r="C96" s="37" t="n"/>
+      <c r="D96" s="37" t="n"/>
+      <c r="E96" s="37" t="n"/>
+      <c r="F96" s="37" t="n"/>
+      <c r="G96" s="37" t="n"/>
+      <c r="H96" s="37" t="n"/>
+      <c r="I96" s="37" t="n"/>
+      <c r="J96" s="37" t="n"/>
+      <c r="K96" s="37" t="n"/>
+      <c r="L96" s="37" t="n"/>
+      <c r="M96" s="37" t="n"/>
+      <c r="N96" s="37" t="n"/>
+      <c r="O96" s="37" t="n"/>
+      <c r="P96" s="37" t="n"/>
+      <c r="Q96" s="37" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="39" t="n"/>
+      <c r="C97" s="39" t="n"/>
+      <c r="D97" s="39" t="n"/>
+      <c r="E97" s="39" t="n"/>
+      <c r="F97" s="39" t="n"/>
+      <c r="G97" s="39" t="n"/>
+      <c r="H97" s="39" t="n"/>
+      <c r="I97" s="39" t="n"/>
+      <c r="J97" s="39" t="n"/>
+      <c r="K97" s="39" t="n"/>
+      <c r="L97" s="39" t="n"/>
+      <c r="M97" s="39" t="n"/>
+      <c r="N97" s="39" t="n"/>
+      <c r="O97" s="39" t="n"/>
+      <c r="P97" s="39" t="n"/>
+      <c r="Q97" s="39" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="37" t="n"/>
+      <c r="C98" s="37" t="n"/>
+      <c r="D98" s="37" t="n"/>
+      <c r="E98" s="37" t="n"/>
+      <c r="F98" s="37" t="n"/>
+      <c r="G98" s="37" t="n"/>
+      <c r="H98" s="37" t="n"/>
+      <c r="I98" s="37" t="n"/>
+      <c r="J98" s="37" t="n"/>
+      <c r="K98" s="37" t="n"/>
+      <c r="L98" s="37" t="n"/>
+      <c r="M98" s="37" t="n"/>
+      <c r="N98" s="37" t="n"/>
+      <c r="O98" s="37" t="n"/>
+      <c r="P98" s="37" t="n"/>
+      <c r="Q98" s="37" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="39" t="n"/>
+      <c r="C99" s="39" t="n"/>
+      <c r="D99" s="39" t="n"/>
+      <c r="E99" s="39" t="n"/>
+      <c r="F99" s="39" t="n"/>
+      <c r="G99" s="39" t="n"/>
+      <c r="H99" s="39" t="n"/>
+      <c r="I99" s="39" t="n"/>
+      <c r="J99" s="39" t="n"/>
+      <c r="K99" s="39" t="n"/>
+      <c r="L99" s="39" t="n"/>
+      <c r="M99" s="39" t="n"/>
+      <c r="N99" s="39" t="n"/>
+      <c r="O99" s="39" t="n"/>
+      <c r="P99" s="39" t="n"/>
+      <c r="Q99" s="39" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="37" t="n"/>
+      <c r="C100" s="37" t="n"/>
+      <c r="D100" s="37" t="n"/>
+      <c r="E100" s="37" t="n"/>
+      <c r="F100" s="37" t="n"/>
+      <c r="G100" s="37" t="n"/>
+      <c r="H100" s="37" t="n"/>
+      <c r="I100" s="37" t="n"/>
+      <c r="J100" s="37" t="n"/>
+      <c r="K100" s="37" t="n"/>
+      <c r="L100" s="37" t="n"/>
+      <c r="M100" s="37" t="n"/>
+      <c r="N100" s="37" t="n"/>
+      <c r="O100" s="37" t="n"/>
+      <c r="P100" s="37" t="n"/>
+      <c r="Q100" s="37" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="39" t="n"/>
+      <c r="C101" s="39" t="n"/>
+      <c r="D101" s="39" t="n"/>
+      <c r="E101" s="39" t="n"/>
+      <c r="F101" s="39" t="n"/>
+      <c r="G101" s="39" t="n"/>
+      <c r="H101" s="39" t="n"/>
+      <c r="I101" s="39" t="n"/>
+      <c r="J101" s="39" t="n"/>
+      <c r="K101" s="39" t="n"/>
+      <c r="L101" s="39" t="n"/>
+      <c r="M101" s="39" t="n"/>
+      <c r="N101" s="39" t="n"/>
+      <c r="O101" s="39" t="n"/>
+      <c r="P101" s="39" t="n"/>
+      <c r="Q101" s="39" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="37" t="n"/>
+      <c r="C102" s="37" t="n"/>
+      <c r="D102" s="37" t="n"/>
+      <c r="E102" s="37" t="n"/>
+      <c r="F102" s="37" t="n"/>
+      <c r="G102" s="37" t="n"/>
+      <c r="H102" s="37" t="n"/>
+      <c r="I102" s="37" t="n"/>
+      <c r="J102" s="37" t="n"/>
+      <c r="K102" s="37" t="n"/>
+      <c r="L102" s="37" t="n"/>
+      <c r="M102" s="37" t="n"/>
+      <c r="N102" s="37" t="n"/>
+      <c r="O102" s="37" t="n"/>
+      <c r="P102" s="37" t="n"/>
+      <c r="Q102" s="37" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="39" t="n"/>
+      <c r="C103" s="39" t="n"/>
+      <c r="D103" s="39" t="n"/>
+      <c r="E103" s="39" t="n"/>
+      <c r="F103" s="39" t="n"/>
+      <c r="G103" s="39" t="n"/>
+      <c r="H103" s="39" t="n"/>
+      <c r="I103" s="39" t="n"/>
+      <c r="J103" s="39" t="n"/>
+      <c r="K103" s="39" t="n"/>
+      <c r="L103" s="39" t="n"/>
+      <c r="M103" s="39" t="n"/>
+      <c r="N103" s="39" t="n"/>
+      <c r="O103" s="39" t="n"/>
+      <c r="P103" s="39" t="n"/>
+      <c r="Q103" s="39" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="37" t="n"/>
+      <c r="C104" s="37" t="n"/>
+      <c r="D104" s="37" t="n"/>
+      <c r="E104" s="37" t="n"/>
+      <c r="F104" s="37" t="n"/>
+      <c r="G104" s="37" t="n"/>
+      <c r="H104" s="37" t="n"/>
+      <c r="I104" s="37" t="n"/>
+      <c r="J104" s="37" t="n"/>
+      <c r="K104" s="37" t="n"/>
+      <c r="L104" s="37" t="n"/>
+      <c r="M104" s="37" t="n"/>
+      <c r="N104" s="37" t="n"/>
+      <c r="O104" s="37" t="n"/>
+      <c r="P104" s="37" t="n"/>
+      <c r="Q104" s="37" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>💡 Tip: Select Row 4 → Copy → Select target row → Paste Special → Values Only. This freezes the current analysis as a permanent record.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B2:O2"/>
+  <mergeCells count="3">
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B107:Q107"/>
+    <mergeCell ref="B1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="L4:L55">
+  <conditionalFormatting sqref="L4:L105">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.67</formula>
     </cfRule>
@@ -13847,7 +14892,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K55">
+  <conditionalFormatting sqref="M4:M105">
     <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.67</formula>
     </cfRule>
@@ -13870,11 +14915,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B52"/>
+  <dimension ref="B1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13885,324 +14933,998 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="58" t="inlineStr"/>
+      <c r="B3" s="58" t="inlineStr">
+        <is>
+          <t>📏 Cpk / Capability Thresholds</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="59" t="inlineStr">
         <is>
-          <t>How to Use This Workbook</t>
+          <t>Cpk Range</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D4" s="59" t="inlineStr">
+        <is>
+          <t>PPM (approx.)</t>
+        </is>
+      </c>
+      <c r="E4" s="59" t="inlineStr">
+        <is>
+          <t>Action</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="58" t="inlineStr">
-        <is>
-          <t>1. Enter specifications (Tₘ, LSL, USL) in the Analysis sheet (blue cells)</t>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>&lt; 1.00</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>❌ Not Capable</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>&gt; 2,700</t>
+        </is>
+      </c>
+      <c r="E5" s="61" t="inlineStr">
+        <is>
+          <t>Process redesign or tighter controls needed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="58" t="inlineStr">
-        <is>
-          <t>2. Choose Mode: 'Enter Manually' or 'Use Data Worksheet' (dropdown in C10)</t>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>1.00 – 1.33</t>
+        </is>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>⚠️ Marginal</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>63 – 2,700</t>
+        </is>
+      </c>
+      <c r="E6" s="61" t="inlineStr">
+        <is>
+          <t>Improvement required, monitor closely</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="58" t="inlineStr">
-        <is>
-          <t>3. If Manual: enter x̄, σ, n directly in the Analysis sheet</t>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>1.33 – 1.67</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>✅ Capable</t>
+        </is>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>0.6 – 63</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="inlineStr">
+        <is>
+          <t>Meets most industry standards</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="58" t="inlineStr">
-        <is>
-          <t>4. If Worksheet: enter part data in the Data sheet — mean &amp; σ auto-link</t>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>1.67 – 2.00</t>
+        </is>
+      </c>
+      <c r="C8" s="61" t="inlineStr">
+        <is>
+          <t>✅ Highly Capable</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>&lt; 0.6</t>
+        </is>
+      </c>
+      <c r="E8" s="61" t="inlineStr">
+        <is>
+          <t>Meets automotive/safety-critical</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="58" t="inlineStr">
-        <is>
-          <t>5. All results, probability, hypothesis test, and verdict update INSTANTLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="58" t="inlineStr">
-        <is>
-          <t>6. View charts in the Charts sheet (bell curve + capability bars)</t>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>≥ 2.00</t>
+        </is>
+      </c>
+      <c r="C9" s="61" t="inlineStr">
+        <is>
+          <t>🏆 Six Sigma</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>&lt; 0.002</t>
+        </is>
+      </c>
+      <c r="E9" s="61" t="inlineStr">
+        <is>
+          <t>World-class capability</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="58" t="inlineStr">
         <is>
-          <t>7. To save a run: go to History sheet, copy Row 4, paste as VALUES into Row 5+</t>
+          <t>📊 Sigma Level &amp; PPM Table</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="58" t="inlineStr"/>
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>Sigma Level</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="inlineStr">
+        <is>
+          <t>Yield (%)</t>
+        </is>
+      </c>
+      <c r="D12" s="59" t="inlineStr">
+        <is>
+          <t>DPMO (PPM)</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="inlineStr">
+        <is>
+          <t>Cpk</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="59" t="inlineStr">
-        <is>
-          <t>Core Capability Formulas</t>
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>1σ</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="inlineStr">
+        <is>
+          <t>30.85%</t>
+        </is>
+      </c>
+      <c r="D13" s="61" t="inlineStr">
+        <is>
+          <t>691,462</t>
+        </is>
+      </c>
+      <c r="E13" s="61" t="inlineStr">
+        <is>
+          <t>0.33</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cp = (USL − LSL) / 6σ  — Potential capability if process is perfectly centered</t>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>2σ</t>
+        </is>
+      </c>
+      <c r="C14" s="61" t="inlineStr">
+        <is>
+          <t>69.15%</t>
+        </is>
+      </c>
+      <c r="D14" s="61" t="inlineStr">
+        <is>
+          <t>308,538</t>
+        </is>
+      </c>
+      <c r="E14" s="61" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cpk = min[(USL − x̄) / 3σ,  (x̄ − LSL) / 3σ]  — Actual capability with centering error</t>
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t>3σ</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>93.32%</t>
+        </is>
+      </c>
+      <c r="D15" s="61" t="inlineStr">
+        <is>
+          <t>66,807</t>
+        </is>
+      </c>
+      <c r="E15" s="61" t="inlineStr">
+        <is>
+          <t>1.00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Required Shift (Δ) = Tₘ − x̄  — How far to adjust the process mean</t>
+      <c r="B16" s="60" t="inlineStr">
+        <is>
+          <t>4σ</t>
+        </is>
+      </c>
+      <c r="C16" s="61" t="inlineStr">
+        <is>
+          <t>99.3790%</t>
+        </is>
+      </c>
+      <c r="D16" s="61" t="inlineStr">
+        <is>
+          <t>6,210</t>
+        </is>
+      </c>
+      <c r="E16" s="61" t="inlineStr">
+        <is>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Required Tolerance = Target Index × 6σ  — Minimum tolerance band needed</t>
+      <c r="B17" s="60" t="inlineStr">
+        <is>
+          <t>5σ</t>
+        </is>
+      </c>
+      <c r="C17" s="61" t="inlineStr">
+        <is>
+          <t>99.97670%</t>
+        </is>
+      </c>
+      <c r="D17" s="61" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="E17" s="61" t="inlineStr">
+        <is>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="58" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="59" t="inlineStr">
-        <is>
-          <t>Capability Index Interpretation (Automotive Standards)</t>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t>6σ</t>
+        </is>
+      </c>
+      <c r="C18" s="61" t="inlineStr">
+        <is>
+          <t>99.99966%</t>
+        </is>
+      </c>
+      <c r="D18" s="61" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="E18" s="61" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cpk ≥ 1.67  →  ✅ GOOD — Capable (standard automotive target)</t>
+          <t>🔬 Core SPC Formulas</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.33 ≤ Cpk &lt; 1.67  →  ⚠ ACCEPTABLE — Meets minimum but below target</t>
-        </is>
-      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C21" s="59" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="D21" s="59" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="E21" s="59" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.00 ≤ Cpk &lt; 1.33  →  ⚠ MARGINAL — High risk, improvement needed</t>
-        </is>
-      </c>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>Cp</t>
+        </is>
+      </c>
+      <c r="C22" s="61" t="inlineStr">
+        <is>
+          <t>(USL − LSL) / 6σ</t>
+        </is>
+      </c>
+      <c r="D22" s="61" t="inlineStr">
+        <is>
+          <t>Potential capability (centered)</t>
+        </is>
+      </c>
+      <c r="E22" s="61" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cpk &lt; 1.00  →  ❌ NOT CAPABLE — Produces significant defects</t>
-        </is>
-      </c>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>Cpk</t>
+        </is>
+      </c>
+      <c r="C23" s="61" t="inlineStr">
+        <is>
+          <t>min[(USL − x̄)/3σ, (x̄ − LSL)/3σ]</t>
+        </is>
+      </c>
+      <c r="D23" s="61" t="inlineStr">
+        <is>
+          <t>Actual capability (with shift)</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="58" t="inlineStr"/>
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>Pp</t>
+        </is>
+      </c>
+      <c r="C24" s="61" t="inlineStr">
+        <is>
+          <t>(USL − LSL) / 6σ_overall</t>
+        </is>
+      </c>
+      <c r="D24" s="61" t="inlineStr">
+        <is>
+          <t>Long-term potential performance</t>
+        </is>
+      </c>
+      <c r="E24" s="61" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="59" t="inlineStr">
-        <is>
-          <t>Probability &amp; PPM</t>
-        </is>
-      </c>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>Ppk</t>
+        </is>
+      </c>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>min[(USL − x̄)/3σ_overall, (x̄ − LSL)/3σ_overall]</t>
+        </is>
+      </c>
+      <c r="D25" s="61" t="inlineStr">
+        <is>
+          <t>Long-term actual performance</t>
+        </is>
+      </c>
+      <c r="E25" s="61" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  P(x &gt; USL) — Probability a part exceeds upper spec limit</t>
-        </is>
-      </c>
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>Shift (Δ)</t>
+        </is>
+      </c>
+      <c r="C26" s="61" t="inlineStr">
+        <is>
+          <t>Tₘ − x̄</t>
+        </is>
+      </c>
+      <c r="D26" s="61" t="inlineStr">
+        <is>
+          <t>Required mean adjustment</t>
+        </is>
+      </c>
+      <c r="E26" s="61" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="B27" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  P(x &lt; LSL) — Probability a part falls below lower spec limit</t>
-        </is>
-      </c>
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>Z-score</t>
+        </is>
+      </c>
+      <c r="C27" s="61" t="inlineStr">
+        <is>
+          <t>(x̄ − Tₘ) / (σ / √n)</t>
+        </is>
+      </c>
+      <c r="D27" s="61" t="inlineStr">
+        <is>
+          <t>Hypothesis test statistic</t>
+        </is>
+      </c>
+      <c r="E27" s="61" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PPM = Probability × 1,000,000 — Parts Per Million defective</t>
-        </is>
-      </c>
+      <c r="B28" s="60" t="inlineStr">
+        <is>
+          <t>UCL</t>
+        </is>
+      </c>
+      <c r="C28" s="61" t="inlineStr">
+        <is>
+          <t>x̄ + 3σ</t>
+        </is>
+      </c>
+      <c r="D28" s="61" t="inlineStr">
+        <is>
+          <t>Upper control limit</t>
+        </is>
+      </c>
+      <c r="E28" s="61" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="B29" s="58" t="inlineStr"/>
+      <c r="B29" s="60" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="C29" s="61" t="inlineStr">
+        <is>
+          <t>x̄ − 3σ</t>
+        </is>
+      </c>
+      <c r="D29" s="61" t="inlineStr">
+        <is>
+          <t>Lower control limit</t>
+        </is>
+      </c>
+      <c r="E29" s="61" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="59" t="inlineStr">
-        <is>
-          <t>Hypothesis Testing</t>
-        </is>
-      </c>
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>MR̄</t>
+        </is>
+      </c>
+      <c r="C30" s="61" t="inlineStr">
+        <is>
+          <t>Σ|Xᵢ − Xᵢ₋₁| / (n−1)</t>
+        </is>
+      </c>
+      <c r="D30" s="61" t="inlineStr">
+        <is>
+          <t>Average moving range</t>
+        </is>
+      </c>
+      <c r="E30" s="61" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  H₀: μ = Tₘ (process is on target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Z = (x̄ − Tₘ) / (σ / √n)</t>
-        </is>
-      </c>
+      <c r="B31" s="60" t="inlineStr">
+        <is>
+          <t>MR UCL</t>
+        </is>
+      </c>
+      <c r="C31" s="61" t="inlineStr">
+        <is>
+          <t>3.267 × MR̄</t>
+        </is>
+      </c>
+      <c r="D31" s="61" t="inlineStr">
+        <is>
+          <t>MR chart upper control limit</t>
+        </is>
+      </c>
+      <c r="E31" s="61" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="B33" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  p-value &lt; α → Reject H₀ → Significant shift detected</t>
+          <t>🎯 Control Chart Zones (I-MR)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  p-value ≥ α → Fail to Reject H₀ → No significant shift</t>
+      <c r="B34" s="59" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="C34" s="59" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="D34" s="59" t="inlineStr">
+        <is>
+          <t>Expected %</t>
+        </is>
+      </c>
+      <c r="E34" s="59" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Two-Sided: tests if mean differs in either direction</t>
+      <c r="B35" s="60" t="inlineStr">
+        <is>
+          <t>Zone C</t>
+        </is>
+      </c>
+      <c r="C35" s="61" t="inlineStr">
+        <is>
+          <t>x̄ ± 1σ</t>
+        </is>
+      </c>
+      <c r="D35" s="61" t="inlineStr">
+        <is>
+          <t>68.27%</t>
+        </is>
+      </c>
+      <c r="E35" s="61" t="inlineStr">
+        <is>
+          <t>Normal — process in control</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Upper-Sided: tests if mean is significantly above target</t>
+      <c r="B36" s="60" t="inlineStr">
+        <is>
+          <t>Zone B</t>
+        </is>
+      </c>
+      <c r="C36" s="61" t="inlineStr">
+        <is>
+          <t>x̄ ± 1σ to ± 2σ</t>
+        </is>
+      </c>
+      <c r="D36" s="61" t="inlineStr">
+        <is>
+          <t>27.18%</t>
+        </is>
+      </c>
+      <c r="E36" s="61" t="inlineStr">
+        <is>
+          <t>Caution — monitor</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Lower-Sided: tests if mean is significantly below target</t>
+      <c r="B37" s="60" t="inlineStr">
+        <is>
+          <t>Zone A</t>
+        </is>
+      </c>
+      <c r="C37" s="61" t="inlineStr">
+        <is>
+          <t>x̄ ± 2σ to ± 3σ</t>
+        </is>
+      </c>
+      <c r="D37" s="61" t="inlineStr">
+        <is>
+          <t>4.28%</t>
+        </is>
+      </c>
+      <c r="E37" s="61" t="inlineStr">
+        <is>
+          <t>Warning — investigate</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="58" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="59" t="inlineStr">
-        <is>
-          <t>Robustness Assessment</t>
+      <c r="B38" s="60" t="inlineStr">
+        <is>
+          <t>Outside</t>
+        </is>
+      </c>
+      <c r="C38" s="61" t="inlineStr">
+        <is>
+          <t>Beyond ± 3σ</t>
+        </is>
+      </c>
+      <c r="D38" s="61" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="E38" s="61" t="inlineStr">
+        <is>
+          <t>Out of Control — action required</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROBUST: ±4σ spread contained within specification limits</t>
+          <t>⚠️ Western Electric Rules</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  MARGINAL: ±3σ contained but ±4σ is NOT — low tolerance for future shifts</t>
-        </is>
-      </c>
+      <c r="B41" s="59" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C41" s="59" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D41" s="59" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="E41" s="59" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="B42" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NOT ROBUST: ±3σ breaches specification limits</t>
-        </is>
-      </c>
+      <c r="B42" s="60" t="inlineStr">
+        <is>
+          <t>Rule 1</t>
+        </is>
+      </c>
+      <c r="C42" s="61" t="inlineStr">
+        <is>
+          <t>Any single point beyond ±3σ</t>
+        </is>
+      </c>
+      <c r="D42" s="61" t="inlineStr">
+        <is>
+          <t>Out of Control</t>
+        </is>
+      </c>
+      <c r="E42" s="61" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="B43" s="58" t="inlineStr"/>
+      <c r="B43" s="60" t="inlineStr">
+        <is>
+          <t>Rule 2</t>
+        </is>
+      </c>
+      <c r="C43" s="61" t="inlineStr">
+        <is>
+          <t>2 of 3 consecutive points beyond ±2σ (same side)</t>
+        </is>
+      </c>
+      <c r="D43" s="61" t="inlineStr">
+        <is>
+          <t>Process shift warning</t>
+        </is>
+      </c>
+      <c r="E43" s="61" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="B44" s="59" t="inlineStr">
-        <is>
-          <t>Spread Metrics</t>
-        </is>
-      </c>
+      <c r="B44" s="60" t="inlineStr">
+        <is>
+          <t>Rule 3</t>
+        </is>
+      </c>
+      <c r="C44" s="61" t="inlineStr">
+        <is>
+          <t>4 of 5 consecutive points beyond ±1σ (same side)</t>
+        </is>
+      </c>
+      <c r="D44" s="61" t="inlineStr">
+        <is>
+          <t>Developing trend</t>
+        </is>
+      </c>
+      <c r="E44" s="61" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="B45" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6σ Spread — Contains ~99.73% of process output (±3σ)</t>
-        </is>
-      </c>
+      <c r="B45" s="60" t="inlineStr">
+        <is>
+          <t>Rule 4</t>
+        </is>
+      </c>
+      <c r="C45" s="61" t="inlineStr">
+        <is>
+          <t>8+ consecutive points on same side of CL</t>
+        </is>
+      </c>
+      <c r="D45" s="61" t="inlineStr">
+        <is>
+          <t>Mean has shifted</t>
+        </is>
+      </c>
+      <c r="E45" s="61" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="B46" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8σ Spread — Contains ~99.9937% of process output (±4σ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="58" t="inlineStr"/>
+      <c r="B46" s="60" t="inlineStr">
+        <is>
+          <t>Rule 5</t>
+        </is>
+      </c>
+      <c r="C46" s="61" t="inlineStr">
+        <is>
+          <t>6 consecutive points trending up or down</t>
+        </is>
+      </c>
+      <c r="D46" s="61" t="inlineStr">
+        <is>
+          <t>Drift (tool wear, temp)</t>
+        </is>
+      </c>
+      <c r="E46" s="61" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="B48" s="59" t="inlineStr">
-        <is>
-          <t>Color Coding</t>
+      <c r="B48" s="58" t="inlineStr">
+        <is>
+          <t>🏭 Industry Standard Requirements</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟢 Green cells = Good / Capable / Within target</t>
-        </is>
-      </c>
+      <c r="B49" s="59" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C49" s="59" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="D49" s="59" t="inlineStr">
+        <is>
+          <t>Cpk Requirement</t>
+        </is>
+      </c>
+      <c r="E49" s="59" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="B50" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🟡 Yellow cells = Warning / Marginal</t>
-        </is>
-      </c>
+      <c r="B50" s="60" t="inlineStr">
+        <is>
+          <t>IATF 16949</t>
+        </is>
+      </c>
+      <c r="C50" s="61" t="inlineStr">
+        <is>
+          <t>Automotive production</t>
+        </is>
+      </c>
+      <c r="D50" s="61" t="inlineStr">
+        <is>
+          <t>≥ 1.33 (ongoing), ≥ 1.67 (new)</t>
+        </is>
+      </c>
+      <c r="E50" s="61" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="B51" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🔴 Red cells = Bad / Action Required / Not capable</t>
-        </is>
-      </c>
+      <c r="B51" s="60" t="inlineStr">
+        <is>
+          <t>VDA 6.1</t>
+        </is>
+      </c>
+      <c r="C51" s="61" t="inlineStr">
+        <is>
+          <t>German automotive</t>
+        </is>
+      </c>
+      <c r="D51" s="61" t="inlineStr">
+        <is>
+          <t>≥ 1.33 (Cmk), ≥ 1.67 (critical)</t>
+        </is>
+      </c>
+      <c r="E51" s="61" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="B52" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  🔵 Blue cells = Input cells (enter your data here)</t>
+      <c r="B52" s="60" t="inlineStr">
+        <is>
+          <t>AS9100</t>
+        </is>
+      </c>
+      <c r="C52" s="61" t="inlineStr">
+        <is>
+          <t>Aerospace</t>
+        </is>
+      </c>
+      <c r="D52" s="61" t="inlineStr">
+        <is>
+          <t>≥ 1.33 (typical), ≥ 1.5 (critical)</t>
+        </is>
+      </c>
+      <c r="E52" s="61" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="60" t="inlineStr">
+        <is>
+          <t>ISO 13485</t>
+        </is>
+      </c>
+      <c r="C53" s="61" t="inlineStr">
+        <is>
+          <t>Medical devices</t>
+        </is>
+      </c>
+      <c r="D53" s="61" t="inlineStr">
+        <is>
+          <t>≥ 1.33 (critical features)</t>
+        </is>
+      </c>
+      <c r="E53" s="61" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="60" t="inlineStr">
+        <is>
+          <t>Six Sigma</t>
+        </is>
+      </c>
+      <c r="C54" s="61" t="inlineStr">
+        <is>
+          <t>General manufacturing</t>
+        </is>
+      </c>
+      <c r="D54" s="61" t="inlineStr">
+        <is>
+          <t>≥ 2.0 (6σ target)</t>
+        </is>
+      </c>
+      <c r="E54" s="61" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="60" t="inlineStr">
+        <is>
+          <t>ISO 22514</t>
+        </is>
+      </c>
+      <c r="C55" s="61" t="inlineStr">
+        <is>
+          <t>Capability study std</t>
+        </is>
+      </c>
+      <c r="D55" s="61" t="inlineStr">
+        <is>
+          <t>Defines Cm/Cmk/Pp/Ppk procedures</t>
+        </is>
+      </c>
+      <c r="E55" s="61" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="58" t="inlineStr">
+        <is>
+          <t>📖 How to Use This Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="62" t="inlineStr">
+        <is>
+          <t>1. Enter specifications (Tₘ, LSL, USL) in the Analysis sheet (blue cells)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="62" t="inlineStr">
+        <is>
+          <t>2. Choose Mode: 'Enter Manually' or 'Use Data Worksheet' (dropdown in C10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="62" t="inlineStr">
+        <is>
+          <t>3. If Manual: enter x̄, σ, n directly in the Analysis sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="62" t="inlineStr">
+        <is>
+          <t>4. If Worksheet: enter part data in the Data sheet — mean &amp; σ auto-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="62" t="inlineStr">
+        <is>
+          <t>5. All results, probability, hypothesis test, and verdict update INSTANTLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="62" t="inlineStr">
+        <is>
+          <t>6. View charts in the Charts sheet (I-MR control chart, bell curve, capability bars)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="62" t="inlineStr">
+        <is>
+          <t>7. To save a run: go to History sheet, copy Row 4, paste as VALUES into Row 5+</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="58" t="inlineStr">
+        <is>
+          <t>🎨 Color Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="63" t="inlineStr">
+        <is>
+          <t>🟢 Green cells</t>
+        </is>
+      </c>
+      <c r="C67" s="64" t="inlineStr">
+        <is>
+          <t>Good / Capable / Within target</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>🟡 Yellow cells</t>
+        </is>
+      </c>
+      <c r="C68" s="64" t="inlineStr">
+        <is>
+          <t>Warning / Marginal</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>🔴 Red cells</t>
+        </is>
+      </c>
+      <c r="C69" s="64" t="inlineStr">
+        <is>
+          <t>Bad / Action Required / Not capable</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>🔵 Blue cells</t>
+        </is>
+      </c>
+      <c r="C70" s="64" t="inlineStr">
+        <is>
+          <t>Input cells (enter your data here)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B66:E66"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>